--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2946,7 +2946,7 @@
         <v>921</v>
       </c>
       <c r="F5" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -3154,7 +3154,7 @@
         <v>921</v>
       </c>
       <c r="F13" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -3362,7 +3362,7 @@
         <v>920</v>
       </c>
       <c r="F21" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3414,7 +3414,7 @@
         <v>921</v>
       </c>
       <c r="F23" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G23" t="n">
         <v>1.0</v>
@@ -4220,7 +4220,7 @@
         <v>921</v>
       </c>
       <c r="F54" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -4298,7 +4298,7 @@
         <v>921</v>
       </c>
       <c r="F57" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -4350,7 +4350,7 @@
         <v>921</v>
       </c>
       <c r="F59" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -4766,7 +4766,7 @@
         <v>920</v>
       </c>
       <c r="F75" t="n">
-        <v>313.0</v>
+        <v>316.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -5234,10 +5234,10 @@
         <v>921</v>
       </c>
       <c r="F93" t="n">
-        <v>122.0</v>
+        <v>124.0</v>
       </c>
       <c r="G93" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -5416,7 +5416,7 @@
         <v>921</v>
       </c>
       <c r="F100" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5936,7 +5936,7 @@
         <v>920</v>
       </c>
       <c r="F120" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G120" t="n">
         <v>0.0</v>
@@ -5962,7 +5962,7 @@
         <v>920</v>
       </c>
       <c r="F121" t="n">
-        <v>263.0</v>
+        <v>264.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>
@@ -6014,7 +6014,7 @@
         <v>921</v>
       </c>
       <c r="F123" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>
@@ -6144,7 +6144,7 @@
         <v>920</v>
       </c>
       <c r="F128" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -6456,7 +6456,7 @@
         <v>921</v>
       </c>
       <c r="F140" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G140" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>921</v>
       </c>
       <c r="F154" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G154" t="n">
         <v>0.0</v>
@@ -6846,7 +6846,7 @@
         <v>921</v>
       </c>
       <c r="F155" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -6924,7 +6924,7 @@
         <v>921</v>
       </c>
       <c r="F158" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G158" t="n">
         <v>0.0</v>
@@ -7080,7 +7080,7 @@
         <v>921</v>
       </c>
       <c r="F164" t="n">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="G164" t="n">
         <v>0.0</v>
@@ -7288,7 +7288,7 @@
         <v>921</v>
       </c>
       <c r="F172" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G172" t="n">
         <v>7.0</v>
@@ -7366,7 +7366,7 @@
         <v>921</v>
       </c>
       <c r="F175" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G175" t="n">
         <v>0.0</v>
@@ -7418,7 +7418,7 @@
         <v>921</v>
       </c>
       <c r="F177" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7522,7 +7522,7 @@
         <v>921</v>
       </c>
       <c r="F181" t="n">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7938,7 +7938,7 @@
         <v>921</v>
       </c>
       <c r="F197" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G197" t="n">
         <v>0.0</v>
@@ -8172,7 +8172,7 @@
         <v>920</v>
       </c>
       <c r="F206" t="n">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="G206" t="n">
         <v>0.0</v>
@@ -8484,7 +8484,7 @@
         <v>921</v>
       </c>
       <c r="F218" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G218" t="n">
         <v>0.0</v>
@@ -8900,7 +8900,7 @@
         <v>920</v>
       </c>
       <c r="F234" t="n">
-        <v>489.0</v>
+        <v>496.0</v>
       </c>
       <c r="G234" t="n">
         <v>1.0</v>
@@ -9082,7 +9082,7 @@
         <v>921</v>
       </c>
       <c r="F241" t="n">
-        <v>600.0</v>
+        <v>601.0</v>
       </c>
       <c r="G241" t="n">
         <v>0.0</v>
@@ -9108,7 +9108,7 @@
         <v>920</v>
       </c>
       <c r="F242" t="n">
-        <v>374.0</v>
+        <v>376.0</v>
       </c>
       <c r="G242" t="n">
         <v>0.0</v>
@@ -9186,7 +9186,7 @@
         <v>920</v>
       </c>
       <c r="F245" t="n">
-        <v>68.0</v>
+        <v>74.0</v>
       </c>
       <c r="G245" t="n">
         <v>0.0</v>
@@ -9264,7 +9264,7 @@
         <v>920</v>
       </c>
       <c r="F248" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G248" t="n">
         <v>0.0</v>
@@ -9342,7 +9342,7 @@
         <v>920</v>
       </c>
       <c r="F251" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G251" t="n">
         <v>0.0</v>
@@ -9368,7 +9368,7 @@
         <v>920</v>
       </c>
       <c r="F252" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G252" t="n">
         <v>0.0</v>
@@ -9498,7 +9498,7 @@
         <v>920</v>
       </c>
       <c r="F257" t="n">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="G257" t="n">
         <v>0.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>965.0</v>
+        <v>967.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -10226,7 +10226,7 @@
         <v>920</v>
       </c>
       <c r="F285" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G285" t="n">
         <v>0.0</v>
@@ -10590,7 +10590,7 @@
         <v>921</v>
       </c>
       <c r="F299" t="n">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
       <c r="G299" t="n">
         <v>1.0</v>
@@ -10720,7 +10720,7 @@
         <v>921</v>
       </c>
       <c r="F304" t="n">
-        <v>125.0</v>
+        <v>133.0</v>
       </c>
       <c r="G304" t="n">
         <v>1.0</v>
@@ -10772,7 +10772,7 @@
         <v>921</v>
       </c>
       <c r="F306" t="n">
-        <v>128.0</v>
+        <v>132.0</v>
       </c>
       <c r="G306" t="n">
         <v>0.0</v>
@@ -11292,7 +11292,7 @@
         <v>920</v>
       </c>
       <c r="F326" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G326" t="n">
         <v>0.0</v>
@@ -11734,7 +11734,7 @@
         <v>920</v>
       </c>
       <c r="F343" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="G343" t="n">
         <v>1.0</v>
@@ -11786,7 +11786,7 @@
         <v>920</v>
       </c>
       <c r="F345" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="G345" t="n">
         <v>0.0</v>
@@ -12046,7 +12046,7 @@
         <v>920</v>
       </c>
       <c r="F355" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G355" t="n">
         <v>0.0</v>
@@ -12280,7 +12280,7 @@
         <v>921</v>
       </c>
       <c r="F364" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G364" t="n">
         <v>1.0</v>
@@ -12592,7 +12592,7 @@
         <v>921</v>
       </c>
       <c r="F376" t="n">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -12618,7 +12618,7 @@
         <v>921</v>
       </c>
       <c r="F377" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12774,7 +12774,7 @@
         <v>921</v>
       </c>
       <c r="F383" t="n">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
       <c r="G383" t="n">
         <v>6.0</v>
@@ -12904,7 +12904,7 @@
         <v>920</v>
       </c>
       <c r="F388" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -13450,7 +13450,7 @@
         <v>921</v>
       </c>
       <c r="F409" t="n">
-        <v>923.0</v>
+        <v>932.0</v>
       </c>
       <c r="G409" t="n">
         <v>5.0</v>
@@ -14126,7 +14126,7 @@
         <v>921</v>
       </c>
       <c r="F435" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G435" t="n">
         <v>0.0</v>
@@ -14334,7 +14334,7 @@
         <v>921</v>
       </c>
       <c r="F443" t="n">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
       <c r="G443" t="n">
         <v>0.0</v>
@@ -14438,7 +14438,7 @@
         <v>920</v>
       </c>
       <c r="F447" t="n">
-        <v>186.0</v>
+        <v>190.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14490,7 +14490,7 @@
         <v>921</v>
       </c>
       <c r="F449" t="n">
-        <v>466.0</v>
+        <v>468.0</v>
       </c>
       <c r="G449" t="n">
         <v>0.0</v>
@@ -15296,7 +15296,7 @@
         <v>920</v>
       </c>
       <c r="F480" t="n">
-        <v>500.0</v>
+        <v>501.0</v>
       </c>
       <c r="G480" t="n">
         <v>1.0</v>
@@ -15712,7 +15712,7 @@
         <v>921</v>
       </c>
       <c r="F496" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15764,7 +15764,7 @@
         <v>921</v>
       </c>
       <c r="F498" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G498" t="n">
         <v>0.0</v>
@@ -15868,7 +15868,7 @@
         <v>920</v>
       </c>
       <c r="F502" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15894,7 +15894,7 @@
         <v>920</v>
       </c>
       <c r="F503" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G503" t="n">
         <v>0.0</v>
@@ -16232,7 +16232,7 @@
         <v>921</v>
       </c>
       <c r="F516" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G516" t="n">
         <v>0.0</v>
@@ -16310,7 +16310,7 @@
         <v>920</v>
       </c>
       <c r="F519" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G519" t="n">
         <v>0.0</v>
@@ -16622,7 +16622,7 @@
         <v>920</v>
       </c>
       <c r="F531" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
       <c r="G531" t="n">
         <v>0.0</v>
@@ -16804,7 +16804,7 @@
         <v>920</v>
       </c>
       <c r="F538" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="G538" t="n">
         <v>0.0</v>
@@ -17038,7 +17038,7 @@
         <v>920</v>
       </c>
       <c r="F547" t="n">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -17272,7 +17272,7 @@
         <v>920</v>
       </c>
       <c r="F556" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G556" t="n">
         <v>0.0</v>
@@ -17402,7 +17402,7 @@
         <v>921</v>
       </c>
       <c r="F561" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G561" t="n">
         <v>0.0</v>
@@ -17506,7 +17506,7 @@
         <v>921</v>
       </c>
       <c r="F565" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -17922,7 +17922,7 @@
         <v>921</v>
       </c>
       <c r="F581" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G581" t="n">
         <v>0.0</v>
@@ -18052,7 +18052,7 @@
         <v>920</v>
       </c>
       <c r="F586" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G586" t="n">
         <v>0.0</v>
@@ -18286,7 +18286,7 @@
         <v>921</v>
       </c>
       <c r="F595" t="n">
-        <v>466.0</v>
+        <v>469.0</v>
       </c>
       <c r="G595" t="n">
         <v>3.0</v>
@@ -18364,7 +18364,7 @@
         <v>921</v>
       </c>
       <c r="F598" t="n">
-        <v>98.0</v>
+        <v>101.0</v>
       </c>
       <c r="G598" t="n">
         <v>1.0</v>
@@ -18390,7 +18390,7 @@
         <v>921</v>
       </c>
       <c r="F599" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
@@ -19118,7 +19118,7 @@
         <v>920</v>
       </c>
       <c r="F627" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G627" t="n">
         <v>0.0</v>
@@ -19248,7 +19248,7 @@
         <v>921</v>
       </c>
       <c r="F632" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="G632" t="n">
         <v>0.0</v>
@@ -19846,7 +19846,7 @@
         <v>920</v>
       </c>
       <c r="F655" t="n">
-        <v>117.0</v>
+        <v>124.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19950,7 +19950,7 @@
         <v>920</v>
       </c>
       <c r="F659" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -20288,7 +20288,7 @@
         <v>921</v>
       </c>
       <c r="F672" t="n">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -20314,7 +20314,7 @@
         <v>920</v>
       </c>
       <c r="F673" t="n">
-        <v>387.0</v>
+        <v>389.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -20418,7 +20418,7 @@
         <v>921</v>
       </c>
       <c r="F677" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G677" t="n">
         <v>0.0</v>
@@ -20470,7 +20470,7 @@
         <v>921</v>
       </c>
       <c r="F679" t="n">
-        <v>182.0</v>
+        <v>184.0</v>
       </c>
       <c r="G679" t="n">
         <v>2.0</v>
@@ -20548,7 +20548,7 @@
         <v>921</v>
       </c>
       <c r="F682" t="n">
-        <v>2241.0</v>
+        <v>2258.0</v>
       </c>
       <c r="G682" t="n">
         <v>44.0</v>
@@ -20574,7 +20574,7 @@
         <v>921</v>
       </c>
       <c r="F683" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
       <c r="G683" t="n">
         <v>1.0</v>
@@ -21250,7 +21250,7 @@
         <v>921</v>
       </c>
       <c r="F709" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
       <c r="G709" t="n">
         <v>0.0</v>
@@ -21588,7 +21588,7 @@
         <v>921</v>
       </c>
       <c r="F722" t="n">
-        <v>300.0</v>
+        <v>301.0</v>
       </c>
       <c r="G722" t="n">
         <v>1.0</v>
@@ -21666,7 +21666,7 @@
         <v>921</v>
       </c>
       <c r="F725" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21744,7 +21744,7 @@
         <v>921</v>
       </c>
       <c r="F728" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="G728" t="n">
         <v>1.0</v>
@@ -21900,7 +21900,7 @@
         <v>921</v>
       </c>
       <c r="F734" t="n">
-        <v>395.0</v>
+        <v>396.0</v>
       </c>
       <c r="G734" t="n">
         <v>0.0</v>
@@ -22082,7 +22082,7 @@
         <v>921</v>
       </c>
       <c r="F741" t="n">
-        <v>333.0</v>
+        <v>335.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22238,7 +22238,7 @@
         <v>920</v>
       </c>
       <c r="F747" t="n">
-        <v>486.0</v>
+        <v>487.0</v>
       </c>
       <c r="G747" t="n">
         <v>1.0</v>
@@ -22576,7 +22576,7 @@
         <v>920</v>
       </c>
       <c r="F760" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22628,7 +22628,7 @@
         <v>921</v>
       </c>
       <c r="F762" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G762" t="n">
         <v>0.0</v>
@@ -22680,7 +22680,7 @@
         <v>921</v>
       </c>
       <c r="F764" t="n">
-        <v>240.0</v>
+        <v>242.0</v>
       </c>
       <c r="G764" t="n">
         <v>0.0</v>
@@ -22940,7 +22940,7 @@
         <v>920</v>
       </c>
       <c r="F774" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G774" t="n">
         <v>0.0</v>
@@ -23668,7 +23668,7 @@
         <v>921</v>
       </c>
       <c r="F802" t="n">
-        <v>260.0</v>
+        <v>263.0</v>
       </c>
       <c r="G802" t="n">
         <v>0.0</v>
@@ -23720,7 +23720,7 @@
         <v>921</v>
       </c>
       <c r="F804" t="n">
-        <v>103.0</v>
+        <v>106.0</v>
       </c>
       <c r="G804" t="n">
         <v>0.0</v>
@@ -24032,7 +24032,7 @@
         <v>921</v>
       </c>
       <c r="F816" t="n">
-        <v>307.0</v>
+        <v>311.0</v>
       </c>
       <c r="G816" t="n">
         <v>0.0</v>
@@ -24162,7 +24162,7 @@
         <v>920</v>
       </c>
       <c r="F821" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G821" t="n">
         <v>0.0</v>
@@ -24214,7 +24214,7 @@
         <v>921</v>
       </c>
       <c r="F823" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G823" t="n">
         <v>0.0</v>
@@ -24448,7 +24448,7 @@
         <v>920</v>
       </c>
       <c r="F832" t="n">
-        <v>306.0</v>
+        <v>309.0</v>
       </c>
       <c r="G832" t="n">
         <v>0.0</v>
@@ -25072,7 +25072,7 @@
         <v>921</v>
       </c>
       <c r="F856" t="n">
-        <v>140.0</v>
+        <v>146.0</v>
       </c>
       <c r="G856" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>553.0</v>
+        <v>556.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -4038,7 +4038,7 @@
         <v>921</v>
       </c>
       <c r="F47" t="n">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -4194,7 +4194,7 @@
         <v>920</v>
       </c>
       <c r="F53" t="n">
-        <v>271.0</v>
+        <v>273.0</v>
       </c>
       <c r="G53" t="n">
         <v>1.0</v>
@@ -5240,7 +5240,7 @@
         <v>3.0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="94">
@@ -5520,7 +5520,7 @@
         <v>921</v>
       </c>
       <c r="F104" t="n">
-        <v>173.0</v>
+        <v>177.0</v>
       </c>
       <c r="G104" t="n">
         <v>15.0</v>
@@ -6404,7 +6404,7 @@
         <v>921</v>
       </c>
       <c r="F138" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -6820,7 +6820,7 @@
         <v>921</v>
       </c>
       <c r="F154" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G154" t="n">
         <v>0.0</v>
@@ -8796,7 +8796,7 @@
         <v>921</v>
       </c>
       <c r="F230" t="n">
-        <v>102.0</v>
+        <v>104.0</v>
       </c>
       <c r="G230" t="n">
         <v>1.0</v>
@@ -9628,7 +9628,7 @@
         <v>920</v>
       </c>
       <c r="F262" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G262" t="n">
         <v>0.0</v>
@@ -10122,7 +10122,7 @@
         <v>921</v>
       </c>
       <c r="F281" t="n">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -10154,7 +10154,7 @@
         <v>0.0</v>
       </c>
       <c r="H282" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="283">
@@ -11318,7 +11318,7 @@
         <v>921</v>
       </c>
       <c r="F327" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G327" t="n">
         <v>0.0</v>
@@ -11344,7 +11344,7 @@
         <v>921</v>
       </c>
       <c r="F328" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="G328" t="n">
         <v>1.0</v>
@@ -18286,7 +18286,7 @@
         <v>921</v>
       </c>
       <c r="F595" t="n">
-        <v>469.0</v>
+        <v>470.0</v>
       </c>
       <c r="G595" t="n">
         <v>3.0</v>
@@ -19742,7 +19742,7 @@
         <v>921</v>
       </c>
       <c r="F651" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -22134,7 +22134,7 @@
         <v>920</v>
       </c>
       <c r="F743" t="n">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="G743" t="n">
         <v>0.0</v>
@@ -23486,7 +23486,7 @@
         <v>920</v>
       </c>
       <c r="F795" t="n">
-        <v>334.0</v>
+        <v>336.0</v>
       </c>
       <c r="G795" t="n">
         <v>0.0</v>
@@ -24032,7 +24032,7 @@
         <v>921</v>
       </c>
       <c r="F816" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="G816" t="n">
         <v>0.0</v>
@@ -24896,7 +24896,7 @@
         <v>3.0</v>
       </c>
       <c r="H849" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="850">
@@ -26086,7 +26086,7 @@
         <v>921</v>
       </c>
       <c r="F895" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G895" t="n">
         <v>5.0</v>
@@ -26476,7 +26476,7 @@
         <v>920</v>
       </c>
       <c r="F910" t="n">
-        <v>19.0</v>
+        <v>25.0</v>
       </c>
       <c r="G910" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2868,7 +2868,7 @@
         <v>920</v>
       </c>
       <c r="F2" t="n">
-        <v>488.0</v>
+        <v>494.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -2894,7 +2894,7 @@
         <v>921</v>
       </c>
       <c r="F3" t="n">
-        <v>76.0</v>
+        <v>79.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -2946,7 +2946,7 @@
         <v>921</v>
       </c>
       <c r="F5" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -2998,7 +2998,7 @@
         <v>921</v>
       </c>
       <c r="F7" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="16">
@@ -3258,7 +3258,7 @@
         <v>921</v>
       </c>
       <c r="F17" t="n">
-        <v>380.0</v>
+        <v>384.0</v>
       </c>
       <c r="G17" t="n">
         <v>3.0</v>
@@ -3284,10 +3284,10 @@
         <v>921</v>
       </c>
       <c r="F18" t="n">
-        <v>222.0</v>
+        <v>226.0</v>
       </c>
       <c r="G18" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="H18" t="n">
         <v>2.0</v>
@@ -3310,7 +3310,7 @@
         <v>920</v>
       </c>
       <c r="F19" t="n">
-        <v>335.0</v>
+        <v>340.0</v>
       </c>
       <c r="G19" t="n">
         <v>1.0</v>
@@ -3336,7 +3336,7 @@
         <v>921</v>
       </c>
       <c r="F20" t="n">
-        <v>233.0</v>
+        <v>236.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -3440,7 +3440,7 @@
         <v>921</v>
       </c>
       <c r="F24" t="n">
-        <v>60.0</v>
+        <v>71.0</v>
       </c>
       <c r="G24" t="n">
         <v>2.0</v>
@@ -3518,7 +3518,7 @@
         <v>920</v>
       </c>
       <c r="F27" t="n">
-        <v>314.0</v>
+        <v>317.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -3758,7 +3758,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="37">
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>556.0</v>
+        <v>564.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -3856,7 +3856,7 @@
         <v>921</v>
       </c>
       <c r="F40" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3986,7 +3986,7 @@
         <v>920</v>
       </c>
       <c r="F45" t="n">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         <v>920</v>
       </c>
       <c r="F46" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="G46" t="n">
         <v>1.0</v>
@@ -4038,7 +4038,7 @@
         <v>921</v>
       </c>
       <c r="F47" t="n">
-        <v>425.0</v>
+        <v>427.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -4090,7 +4090,7 @@
         <v>921</v>
       </c>
       <c r="F49" t="n">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -4148,7 +4148,7 @@
         <v>0.0</v>
       </c>
       <c r="H51" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="52">
@@ -4194,7 +4194,7 @@
         <v>920</v>
       </c>
       <c r="F53" t="n">
-        <v>273.0</v>
+        <v>277.0</v>
       </c>
       <c r="G53" t="n">
         <v>1.0</v>
@@ -4324,7 +4324,7 @@
         <v>920</v>
       </c>
       <c r="F58" t="n">
-        <v>244.0</v>
+        <v>247.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -4402,7 +4402,7 @@
         <v>921</v>
       </c>
       <c r="F61" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -4454,7 +4454,7 @@
         <v>921</v>
       </c>
       <c r="F63" t="n">
-        <v>273.0</v>
+        <v>275.0</v>
       </c>
       <c r="G63" t="n">
         <v>1.0</v>
@@ -4714,7 +4714,7 @@
         <v>921</v>
       </c>
       <c r="F73" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4740,7 +4740,7 @@
         <v>921</v>
       </c>
       <c r="F74" t="n">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -4766,7 +4766,7 @@
         <v>920</v>
       </c>
       <c r="F75" t="n">
-        <v>316.0</v>
+        <v>319.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -4792,7 +4792,7 @@
         <v>921</v>
       </c>
       <c r="F76" t="n">
-        <v>71.0</v>
+        <v>78.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -4896,7 +4896,7 @@
         <v>920</v>
       </c>
       <c r="F80" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -5000,7 +5000,7 @@
         <v>921</v>
       </c>
       <c r="F84" t="n">
-        <v>156.0</v>
+        <v>161.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -5026,13 +5026,13 @@
         <v>921</v>
       </c>
       <c r="F85" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>41.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="86">
@@ -5208,7 +5208,7 @@
         <v>920</v>
       </c>
       <c r="F92" t="n">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -5234,10 +5234,10 @@
         <v>921</v>
       </c>
       <c r="F93" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G93" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H93" t="n">
         <v>1.0</v>
@@ -5416,7 +5416,7 @@
         <v>921</v>
       </c>
       <c r="F100" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5442,7 +5442,7 @@
         <v>921</v>
       </c>
       <c r="F101" t="n">
-        <v>321.0</v>
+        <v>324.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5910,7 +5910,7 @@
         <v>921</v>
       </c>
       <c r="F119" t="n">
-        <v>462.0</v>
+        <v>464.0</v>
       </c>
       <c r="G119" t="n">
         <v>0.0</v>
@@ -5962,7 +5962,7 @@
         <v>920</v>
       </c>
       <c r="F121" t="n">
-        <v>264.0</v>
+        <v>266.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>
@@ -5988,7 +5988,7 @@
         <v>920</v>
       </c>
       <c r="F122" t="n">
-        <v>93.0</v>
+        <v>107.0</v>
       </c>
       <c r="G122" t="n">
         <v>0.0</v>
@@ -6092,7 +6092,7 @@
         <v>921</v>
       </c>
       <c r="F126" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G126" t="n">
         <v>0.0</v>
@@ -6248,7 +6248,7 @@
         <v>920</v>
       </c>
       <c r="F132" t="n">
-        <v>344.0</v>
+        <v>347.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -6352,7 +6352,7 @@
         <v>920</v>
       </c>
       <c r="F136" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -6404,7 +6404,7 @@
         <v>921</v>
       </c>
       <c r="F138" t="n">
-        <v>434.0</v>
+        <v>440.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -6456,7 +6456,7 @@
         <v>921</v>
       </c>
       <c r="F140" t="n">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="G140" t="n">
         <v>1.0</v>
@@ -6716,7 +6716,7 @@
         <v>921</v>
       </c>
       <c r="F150" t="n">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -6748,7 +6748,7 @@
         <v>0.0</v>
       </c>
       <c r="H151" t="n">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="152">
@@ -6768,7 +6768,7 @@
         <v>921</v>
       </c>
       <c r="F152" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -6846,7 +6846,7 @@
         <v>921</v>
       </c>
       <c r="F155" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -6950,7 +6950,7 @@
         <v>921</v>
       </c>
       <c r="F159" t="n">
-        <v>404.0</v>
+        <v>407.0</v>
       </c>
       <c r="G159" t="n">
         <v>1.0</v>
@@ -6976,7 +6976,7 @@
         <v>921</v>
       </c>
       <c r="F160" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -7028,7 +7028,7 @@
         <v>921</v>
       </c>
       <c r="F162" t="n">
-        <v>406.0</v>
+        <v>412.0</v>
       </c>
       <c r="G162" t="n">
         <v>1.0</v>
@@ -7054,7 +7054,7 @@
         <v>920</v>
       </c>
       <c r="F163" t="n">
-        <v>291.0</v>
+        <v>294.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -7080,7 +7080,7 @@
         <v>921</v>
       </c>
       <c r="F164" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G164" t="n">
         <v>0.0</v>
@@ -7132,7 +7132,7 @@
         <v>920</v>
       </c>
       <c r="F166" t="n">
-        <v>236.0</v>
+        <v>241.0</v>
       </c>
       <c r="G166" t="n">
         <v>1.0</v>
@@ -7158,7 +7158,7 @@
         <v>920</v>
       </c>
       <c r="F167" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -7340,7 +7340,7 @@
         <v>920</v>
       </c>
       <c r="F174" t="n">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="G174" t="n">
         <v>0.0</v>
@@ -7392,7 +7392,7 @@
         <v>921</v>
       </c>
       <c r="F176" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -7418,7 +7418,7 @@
         <v>921</v>
       </c>
       <c r="F177" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7496,7 +7496,7 @@
         <v>921</v>
       </c>
       <c r="F180" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -7548,7 +7548,7 @@
         <v>921</v>
       </c>
       <c r="F182" t="n">
-        <v>122.0</v>
+        <v>127.0</v>
       </c>
       <c r="G182" t="n">
         <v>1.0</v>
@@ -7626,13 +7626,13 @@
         <v>921</v>
       </c>
       <c r="F185" t="n">
-        <v>584.0</v>
+        <v>593.0</v>
       </c>
       <c r="G185" t="n">
         <v>1.0</v>
       </c>
       <c r="H185" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="186">
@@ -7834,7 +7834,7 @@
         <v>921</v>
       </c>
       <c r="F193" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7860,7 +7860,7 @@
         <v>920</v>
       </c>
       <c r="F194" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="G194" t="n">
         <v>0.0</v>
@@ -7912,7 +7912,7 @@
         <v>920</v>
       </c>
       <c r="F196" t="n">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="G196" t="n">
         <v>0.0</v>
@@ -7938,7 +7938,7 @@
         <v>921</v>
       </c>
       <c r="F197" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G197" t="n">
         <v>0.0</v>
@@ -7964,7 +7964,7 @@
         <v>921</v>
       </c>
       <c r="F198" t="n">
-        <v>185.0</v>
+        <v>189.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -8146,7 +8146,7 @@
         <v>921</v>
       </c>
       <c r="F205" t="n">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -8172,7 +8172,7 @@
         <v>920</v>
       </c>
       <c r="F206" t="n">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="G206" t="n">
         <v>0.0</v>
@@ -8198,7 +8198,7 @@
         <v>921</v>
       </c>
       <c r="F207" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G207" t="n">
         <v>1.0</v>
@@ -8250,7 +8250,7 @@
         <v>921</v>
       </c>
       <c r="F209" t="n">
-        <v>197.0</v>
+        <v>199.0</v>
       </c>
       <c r="G209" t="n">
         <v>0.0</v>
@@ -8302,7 +8302,7 @@
         <v>920</v>
       </c>
       <c r="F211" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="G211" t="n">
         <v>0.0</v>
@@ -8328,7 +8328,7 @@
         <v>921</v>
       </c>
       <c r="F212" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -8354,7 +8354,7 @@
         <v>921</v>
       </c>
       <c r="F213" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G213" t="n">
         <v>0.0</v>
@@ -8380,7 +8380,7 @@
         <v>921</v>
       </c>
       <c r="F214" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G214" t="n">
         <v>0.0</v>
@@ -8458,7 +8458,7 @@
         <v>921</v>
       </c>
       <c r="F217" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G217" t="n">
         <v>0.0</v>
@@ -8510,7 +8510,7 @@
         <v>921</v>
       </c>
       <c r="F219" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="G219" t="n">
         <v>0.0</v>
@@ -8588,7 +8588,7 @@
         <v>921</v>
       </c>
       <c r="F222" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G222" t="n">
         <v>6.0</v>
@@ -8614,7 +8614,7 @@
         <v>920</v>
       </c>
       <c r="F223" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G223" t="n">
         <v>0.0</v>
@@ -8666,13 +8666,13 @@
         <v>921</v>
       </c>
       <c r="F225" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G225" t="n">
         <v>0.0</v>
       </c>
       <c r="H225" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="226">
@@ -8718,7 +8718,7 @@
         <v>921</v>
       </c>
       <c r="F227" t="n">
-        <v>250.0</v>
+        <v>252.0</v>
       </c>
       <c r="G227" t="n">
         <v>0.0</v>
@@ -8744,7 +8744,7 @@
         <v>920</v>
       </c>
       <c r="F228" t="n">
-        <v>451.0</v>
+        <v>454.0</v>
       </c>
       <c r="G228" t="n">
         <v>0.0</v>
@@ -8822,7 +8822,7 @@
         <v>921</v>
       </c>
       <c r="F231" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G231" t="n">
         <v>0.0</v>
@@ -8900,7 +8900,7 @@
         <v>920</v>
       </c>
       <c r="F234" t="n">
-        <v>496.0</v>
+        <v>514.0</v>
       </c>
       <c r="G234" t="n">
         <v>1.0</v>
@@ -9082,7 +9082,7 @@
         <v>921</v>
       </c>
       <c r="F241" t="n">
-        <v>601.0</v>
+        <v>604.0</v>
       </c>
       <c r="G241" t="n">
         <v>0.0</v>
@@ -9108,7 +9108,7 @@
         <v>920</v>
       </c>
       <c r="F242" t="n">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
       <c r="G242" t="n">
         <v>0.0</v>
@@ -9186,7 +9186,7 @@
         <v>920</v>
       </c>
       <c r="F245" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G245" t="n">
         <v>0.0</v>
@@ -9264,7 +9264,7 @@
         <v>920</v>
       </c>
       <c r="F248" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G248" t="n">
         <v>0.0</v>
@@ -9316,7 +9316,7 @@
         <v>921</v>
       </c>
       <c r="F250" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="G250" t="n">
         <v>2.0</v>
@@ -9368,7 +9368,7 @@
         <v>920</v>
       </c>
       <c r="F252" t="n">
-        <v>63.0</v>
+        <v>71.0</v>
       </c>
       <c r="G252" t="n">
         <v>0.0</v>
@@ -9472,7 +9472,7 @@
         <v>921</v>
       </c>
       <c r="F256" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G256" t="n">
         <v>0.0</v>
@@ -9550,7 +9550,7 @@
         <v>920</v>
       </c>
       <c r="F259" t="n">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="G259" t="n">
         <v>0.0</v>
@@ -9576,7 +9576,7 @@
         <v>921</v>
       </c>
       <c r="F260" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G260" t="n">
         <v>0.0</v>
@@ -9602,7 +9602,7 @@
         <v>920</v>
       </c>
       <c r="F261" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G261" t="n">
         <v>0.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>967.0</v>
+        <v>971.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -9758,7 +9758,7 @@
         <v>920</v>
       </c>
       <c r="F267" t="n">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9940,7 +9940,7 @@
         <v>921</v>
       </c>
       <c r="F274" t="n">
-        <v>274.0</v>
+        <v>277.0</v>
       </c>
       <c r="G274" t="n">
         <v>0.0</v>
@@ -9966,7 +9966,7 @@
         <v>921</v>
       </c>
       <c r="F275" t="n">
-        <v>369.0</v>
+        <v>370.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -10122,7 +10122,7 @@
         <v>921</v>
       </c>
       <c r="F281" t="n">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -10226,7 +10226,7 @@
         <v>920</v>
       </c>
       <c r="F285" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="G285" t="n">
         <v>0.0</v>
@@ -10434,7 +10434,7 @@
         <v>921</v>
       </c>
       <c r="F293" t="n">
-        <v>96.0</v>
+        <v>104.0</v>
       </c>
       <c r="G293" t="n">
         <v>0.0</v>
@@ -10668,7 +10668,7 @@
         <v>921</v>
       </c>
       <c r="F302" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G302" t="n">
         <v>1.0</v>
@@ -10856,7 +10856,7 @@
         <v>0.0</v>
       </c>
       <c r="H309" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="310">
@@ -10876,7 +10876,7 @@
         <v>921</v>
       </c>
       <c r="F310" t="n">
-        <v>381.0</v>
+        <v>388.0</v>
       </c>
       <c r="G310" t="n">
         <v>1.0</v>
@@ -10954,7 +10954,7 @@
         <v>920</v>
       </c>
       <c r="F313" t="n">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="G313" t="n">
         <v>0.0</v>
@@ -11110,7 +11110,7 @@
         <v>920</v>
       </c>
       <c r="F319" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G319" t="n">
         <v>0.0</v>
@@ -11272,7 +11272,7 @@
         <v>0.0</v>
       </c>
       <c r="H325" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="326">
@@ -11318,7 +11318,7 @@
         <v>921</v>
       </c>
       <c r="F327" t="n">
-        <v>117.0</v>
+        <v>120.0</v>
       </c>
       <c r="G327" t="n">
         <v>0.0</v>
@@ -11474,7 +11474,7 @@
         <v>921</v>
       </c>
       <c r="F333" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G333" t="n">
         <v>0.0</v>
@@ -11734,7 +11734,7 @@
         <v>920</v>
       </c>
       <c r="F343" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G343" t="n">
         <v>1.0</v>
@@ -11786,7 +11786,7 @@
         <v>920</v>
       </c>
       <c r="F345" t="n">
-        <v>165.0</v>
+        <v>167.0</v>
       </c>
       <c r="G345" t="n">
         <v>0.0</v>
@@ -11968,7 +11968,7 @@
         <v>921</v>
       </c>
       <c r="F352" t="n">
-        <v>218.0</v>
+        <v>220.0</v>
       </c>
       <c r="G352" t="n">
         <v>0.0</v>
@@ -12046,7 +12046,7 @@
         <v>920</v>
       </c>
       <c r="F355" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
       <c r="G355" t="n">
         <v>0.0</v>
@@ -12124,7 +12124,7 @@
         <v>921</v>
       </c>
       <c r="F358" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G358" t="n">
         <v>0.0</v>
@@ -12228,13 +12228,13 @@
         <v>921</v>
       </c>
       <c r="F362" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="G362" t="n">
         <v>0.0</v>
       </c>
       <c r="H362" t="n">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="363">
@@ -12410,7 +12410,7 @@
         <v>921</v>
       </c>
       <c r="F369" t="n">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="G369" t="n">
         <v>0.0</v>
@@ -12468,7 +12468,7 @@
         <v>0.0</v>
       </c>
       <c r="H371" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="372">
@@ -12566,7 +12566,7 @@
         <v>921</v>
       </c>
       <c r="F375" t="n">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12592,7 +12592,7 @@
         <v>921</v>
       </c>
       <c r="F376" t="n">
-        <v>66.0</v>
+        <v>72.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -12618,7 +12618,7 @@
         <v>921</v>
       </c>
       <c r="F377" t="n">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12644,7 +12644,7 @@
         <v>921</v>
       </c>
       <c r="F378" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G378" t="n">
         <v>0.0</v>
@@ -12670,7 +12670,7 @@
         <v>921</v>
       </c>
       <c r="F379" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G379" t="n">
         <v>2.0</v>
@@ -12748,13 +12748,13 @@
         <v>921</v>
       </c>
       <c r="F382" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G382" t="n">
         <v>1.0</v>
       </c>
       <c r="H382" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="383">
@@ -12904,7 +12904,7 @@
         <v>920</v>
       </c>
       <c r="F388" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -13034,7 +13034,7 @@
         <v>921</v>
       </c>
       <c r="F393" t="n">
-        <v>204.0</v>
+        <v>206.0</v>
       </c>
       <c r="G393" t="n">
         <v>1.0</v>
@@ -13060,7 +13060,7 @@
         <v>921</v>
       </c>
       <c r="F394" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -13144,7 +13144,7 @@
         <v>0.0</v>
       </c>
       <c r="H397" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="398">
@@ -13164,7 +13164,7 @@
         <v>921</v>
       </c>
       <c r="F398" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G398" t="n">
         <v>0.0</v>
@@ -13268,7 +13268,7 @@
         <v>920</v>
       </c>
       <c r="F402" t="n">
-        <v>369.0</v>
+        <v>371.0</v>
       </c>
       <c r="G402" t="n">
         <v>0.0</v>
@@ -13294,7 +13294,7 @@
         <v>920</v>
       </c>
       <c r="F403" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="G403" t="n">
         <v>0.0</v>
@@ -13372,7 +13372,7 @@
         <v>921</v>
       </c>
       <c r="F406" t="n">
-        <v>95.0</v>
+        <v>106.0</v>
       </c>
       <c r="G406" t="n">
         <v>2.0</v>
@@ -13398,7 +13398,7 @@
         <v>920</v>
       </c>
       <c r="F407" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -13430,7 +13430,7 @@
         <v>4.0</v>
       </c>
       <c r="H408" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="409">
@@ -13450,7 +13450,7 @@
         <v>921</v>
       </c>
       <c r="F409" t="n">
-        <v>932.0</v>
+        <v>933.0</v>
       </c>
       <c r="G409" t="n">
         <v>5.0</v>
@@ -13528,7 +13528,7 @@
         <v>921</v>
       </c>
       <c r="F412" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G412" t="n">
         <v>0.0</v>
@@ -13554,7 +13554,7 @@
         <v>921</v>
       </c>
       <c r="F413" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G413" t="n">
         <v>4.0</v>
@@ -13580,7 +13580,7 @@
         <v>921</v>
       </c>
       <c r="F414" t="n">
-        <v>410.0</v>
+        <v>418.0</v>
       </c>
       <c r="G414" t="n">
         <v>4.0</v>
@@ -13612,7 +13612,7 @@
         <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="416">
@@ -13632,13 +13632,13 @@
         <v>921</v>
       </c>
       <c r="F416" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="G416" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H416" t="n">
         <v>17.0</v>
-      </c>
-      <c r="G416" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H416" t="n">
-        <v>13.0</v>
       </c>
     </row>
     <row r="417">
@@ -13710,7 +13710,7 @@
         <v>921</v>
       </c>
       <c r="F419" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G419" t="n">
         <v>0.0</v>
@@ -13840,7 +13840,7 @@
         <v>920</v>
       </c>
       <c r="F424" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -13944,7 +13944,7 @@
         <v>921</v>
       </c>
       <c r="F428" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G428" t="n">
         <v>1.0</v>
@@ -14126,7 +14126,7 @@
         <v>921</v>
       </c>
       <c r="F435" t="n">
-        <v>257.0</v>
+        <v>260.0</v>
       </c>
       <c r="G435" t="n">
         <v>0.0</v>
@@ -14230,7 +14230,7 @@
         <v>920</v>
       </c>
       <c r="F439" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G439" t="n">
         <v>0.0</v>
@@ -14360,13 +14360,13 @@
         <v>921</v>
       </c>
       <c r="F444" t="n">
-        <v>350.0</v>
+        <v>356.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
       </c>
       <c r="H444" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="445">
@@ -14392,7 +14392,7 @@
         <v>0.0</v>
       </c>
       <c r="H445" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="446">
@@ -14490,7 +14490,7 @@
         <v>921</v>
       </c>
       <c r="F449" t="n">
-        <v>468.0</v>
+        <v>470.0</v>
       </c>
       <c r="G449" t="n">
         <v>0.0</v>
@@ -14672,7 +14672,7 @@
         <v>921</v>
       </c>
       <c r="F456" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="G456" t="n">
         <v>2.0</v>
@@ -15244,7 +15244,7 @@
         <v>920</v>
       </c>
       <c r="F478" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G478" t="n">
         <v>0.0</v>
@@ -15296,7 +15296,7 @@
         <v>920</v>
       </c>
       <c r="F480" t="n">
-        <v>501.0</v>
+        <v>502.0</v>
       </c>
       <c r="G480" t="n">
         <v>1.0</v>
@@ -15426,7 +15426,7 @@
         <v>921</v>
       </c>
       <c r="F485" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
@@ -15452,7 +15452,7 @@
         <v>921</v>
       </c>
       <c r="F486" t="n">
-        <v>91.0</v>
+        <v>96.0</v>
       </c>
       <c r="G486" t="n">
         <v>0.0</v>
@@ -15608,7 +15608,7 @@
         <v>921</v>
       </c>
       <c r="F492" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G492" t="n">
         <v>0.0</v>
@@ -15712,7 +15712,7 @@
         <v>921</v>
       </c>
       <c r="F496" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15764,7 +15764,7 @@
         <v>921</v>
       </c>
       <c r="F498" t="n">
-        <v>99.0</v>
+        <v>104.0</v>
       </c>
       <c r="G498" t="n">
         <v>0.0</v>
@@ -15790,7 +15790,7 @@
         <v>920</v>
       </c>
       <c r="F499" t="n">
-        <v>146.0</v>
+        <v>152.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -15842,7 +15842,7 @@
         <v>921</v>
       </c>
       <c r="F501" t="n">
-        <v>121.0</v>
+        <v>128.0</v>
       </c>
       <c r="G501" t="n">
         <v>0.0</v>
@@ -15972,7 +15972,7 @@
         <v>921</v>
       </c>
       <c r="F506" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="G506" t="n">
         <v>0.0</v>
@@ -16050,7 +16050,7 @@
         <v>920</v>
       </c>
       <c r="F509" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G509" t="n">
         <v>0.0</v>
@@ -16232,7 +16232,7 @@
         <v>921</v>
       </c>
       <c r="F516" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G516" t="n">
         <v>0.0</v>
@@ -16388,7 +16388,7 @@
         <v>921</v>
       </c>
       <c r="F522" t="n">
-        <v>213.0</v>
+        <v>215.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -16622,7 +16622,7 @@
         <v>920</v>
       </c>
       <c r="F531" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="G531" t="n">
         <v>0.0</v>
@@ -16778,7 +16778,7 @@
         <v>921</v>
       </c>
       <c r="F537" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16804,7 +16804,7 @@
         <v>920</v>
       </c>
       <c r="F538" t="n">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="G538" t="n">
         <v>0.0</v>
@@ -16830,7 +16830,7 @@
         <v>920</v>
       </c>
       <c r="F539" t="n">
-        <v>325.0</v>
+        <v>327.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16934,7 +16934,7 @@
         <v>921</v>
       </c>
       <c r="F543" t="n">
-        <v>423.0</v>
+        <v>424.0</v>
       </c>
       <c r="G543" t="n">
         <v>1.0</v>
@@ -16960,7 +16960,7 @@
         <v>920</v>
       </c>
       <c r="F544" t="n">
-        <v>33.0</v>
+        <v>38.0</v>
       </c>
       <c r="G544" t="n">
         <v>0.0</v>
@@ -17038,7 +17038,7 @@
         <v>920</v>
       </c>
       <c r="F547" t="n">
-        <v>331.0</v>
+        <v>333.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -17194,7 +17194,7 @@
         <v>920</v>
       </c>
       <c r="F553" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -17324,7 +17324,7 @@
         <v>920</v>
       </c>
       <c r="F558" t="n">
-        <v>61.0</v>
+        <v>64.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
@@ -17350,7 +17350,7 @@
         <v>921</v>
       </c>
       <c r="F559" t="n">
-        <v>257.0</v>
+        <v>262.0</v>
       </c>
       <c r="G559" t="n">
         <v>6.0</v>
@@ -17376,7 +17376,7 @@
         <v>920</v>
       </c>
       <c r="F560" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G560" t="n">
         <v>0.0</v>
@@ -17506,7 +17506,7 @@
         <v>921</v>
       </c>
       <c r="F565" t="n">
-        <v>169.0</v>
+        <v>174.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -17746,7 +17746,7 @@
         <v>0.0</v>
       </c>
       <c r="H574" t="n">
-        <v>20.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="575">
@@ -17766,7 +17766,7 @@
         <v>921</v>
       </c>
       <c r="F575" t="n">
-        <v>262.0</v>
+        <v>266.0</v>
       </c>
       <c r="G575" t="n">
         <v>0.0</v>
@@ -18052,7 +18052,7 @@
         <v>920</v>
       </c>
       <c r="F586" t="n">
-        <v>94.0</v>
+        <v>98.0</v>
       </c>
       <c r="G586" t="n">
         <v>0.0</v>
@@ -18208,7 +18208,7 @@
         <v>920</v>
       </c>
       <c r="F592" t="n">
-        <v>76.0</v>
+        <v>79.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -18286,7 +18286,7 @@
         <v>921</v>
       </c>
       <c r="F595" t="n">
-        <v>470.0</v>
+        <v>484.0</v>
       </c>
       <c r="G595" t="n">
         <v>3.0</v>
@@ -18364,7 +18364,7 @@
         <v>921</v>
       </c>
       <c r="F598" t="n">
-        <v>101.0</v>
+        <v>111.0</v>
       </c>
       <c r="G598" t="n">
         <v>1.0</v>
@@ -18572,7 +18572,7 @@
         <v>920</v>
       </c>
       <c r="F606" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G606" t="n">
         <v>0.0</v>
@@ -18676,7 +18676,7 @@
         <v>921</v>
       </c>
       <c r="F610" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
@@ -18702,7 +18702,7 @@
         <v>921</v>
       </c>
       <c r="F611" t="n">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
       <c r="G611" t="n">
         <v>0.0</v>
@@ -18936,7 +18936,7 @@
         <v>921</v>
       </c>
       <c r="F620" t="n">
-        <v>513.0</v>
+        <v>517.0</v>
       </c>
       <c r="G620" t="n">
         <v>2.0</v>
@@ -19222,7 +19222,7 @@
         <v>921</v>
       </c>
       <c r="F631" t="n">
-        <v>127.0</v>
+        <v>129.0</v>
       </c>
       <c r="G631" t="n">
         <v>1.0</v>
@@ -19378,7 +19378,7 @@
         <v>921</v>
       </c>
       <c r="F637" t="n">
-        <v>59.0</v>
+        <v>64.0</v>
       </c>
       <c r="G637" t="n">
         <v>0.0</v>
@@ -19456,7 +19456,7 @@
         <v>921</v>
       </c>
       <c r="F640" t="n">
-        <v>131.0</v>
+        <v>136.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -19586,7 +19586,7 @@
         <v>920</v>
       </c>
       <c r="F645" t="n">
-        <v>207.0</v>
+        <v>210.0</v>
       </c>
       <c r="G645" t="n">
         <v>1.0</v>
@@ -19638,7 +19638,7 @@
         <v>921</v>
       </c>
       <c r="F647" t="n">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19872,7 +19872,7 @@
         <v>921</v>
       </c>
       <c r="F656" t="n">
-        <v>377.0</v>
+        <v>378.0</v>
       </c>
       <c r="G656" t="n">
         <v>2.0</v>
@@ -19976,7 +19976,7 @@
         <v>921</v>
       </c>
       <c r="F660" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G660" t="n">
         <v>0.0</v>
@@ -20106,7 +20106,7 @@
         <v>921</v>
       </c>
       <c r="F665" t="n">
-        <v>483.0</v>
+        <v>489.0</v>
       </c>
       <c r="G665" t="n">
         <v>1.0</v>
@@ -20158,7 +20158,7 @@
         <v>921</v>
       </c>
       <c r="F667" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -20184,7 +20184,7 @@
         <v>921</v>
       </c>
       <c r="F668" t="n">
-        <v>39.0</v>
+        <v>43.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -20288,7 +20288,7 @@
         <v>921</v>
       </c>
       <c r="F672" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -20314,7 +20314,7 @@
         <v>920</v>
       </c>
       <c r="F673" t="n">
-        <v>389.0</v>
+        <v>391.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -20502,7 +20502,7 @@
         <v>0.0</v>
       </c>
       <c r="H680" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="681">
@@ -20522,7 +20522,7 @@
         <v>921</v>
       </c>
       <c r="F681" t="n">
-        <v>326.0</v>
+        <v>330.0</v>
       </c>
       <c r="G681" t="n">
         <v>0.0</v>
@@ -20548,7 +20548,7 @@
         <v>921</v>
       </c>
       <c r="F682" t="n">
-        <v>2258.0</v>
+        <v>2263.0</v>
       </c>
       <c r="G682" t="n">
         <v>44.0</v>
@@ -20600,7 +20600,7 @@
         <v>921</v>
       </c>
       <c r="F684" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20860,7 +20860,7 @@
         <v>921</v>
       </c>
       <c r="F694" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G694" t="n">
         <v>1.0</v>
@@ -21042,7 +21042,7 @@
         <v>921</v>
       </c>
       <c r="F701" t="n">
-        <v>391.0</v>
+        <v>392.0</v>
       </c>
       <c r="G701" t="n">
         <v>9.0</v>
@@ -21302,7 +21302,7 @@
         <v>921</v>
       </c>
       <c r="F711" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21516,7 +21516,7 @@
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="720">
@@ -21588,7 +21588,7 @@
         <v>921</v>
       </c>
       <c r="F722" t="n">
-        <v>301.0</v>
+        <v>304.0</v>
       </c>
       <c r="G722" t="n">
         <v>1.0</v>
@@ -21640,13 +21640,13 @@
         <v>921</v>
       </c>
       <c r="F724" t="n">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
       </c>
       <c r="H724" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="725">
@@ -21666,7 +21666,7 @@
         <v>921</v>
       </c>
       <c r="F725" t="n">
-        <v>235.0</v>
+        <v>237.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21900,7 +21900,7 @@
         <v>921</v>
       </c>
       <c r="F734" t="n">
-        <v>396.0</v>
+        <v>397.0</v>
       </c>
       <c r="G734" t="n">
         <v>0.0</v>
@@ -22134,7 +22134,7 @@
         <v>920</v>
       </c>
       <c r="F743" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G743" t="n">
         <v>0.0</v>
@@ -22238,7 +22238,7 @@
         <v>920</v>
       </c>
       <c r="F747" t="n">
-        <v>487.0</v>
+        <v>497.0</v>
       </c>
       <c r="G747" t="n">
         <v>1.0</v>
@@ -22576,7 +22576,7 @@
         <v>920</v>
       </c>
       <c r="F760" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22680,7 +22680,7 @@
         <v>921</v>
       </c>
       <c r="F764" t="n">
-        <v>242.0</v>
+        <v>245.0</v>
       </c>
       <c r="G764" t="n">
         <v>0.0</v>
@@ -22758,7 +22758,7 @@
         <v>921</v>
       </c>
       <c r="F767" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G767" t="n">
         <v>1.0</v>
@@ -22862,7 +22862,7 @@
         <v>921</v>
       </c>
       <c r="F771" t="n">
-        <v>266.0</v>
+        <v>273.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>
@@ -23174,7 +23174,7 @@
         <v>921</v>
       </c>
       <c r="F783" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G783" t="n">
         <v>0.0</v>
@@ -23304,7 +23304,7 @@
         <v>920</v>
       </c>
       <c r="F788" t="n">
-        <v>238.0</v>
+        <v>241.0</v>
       </c>
       <c r="G788" t="n">
         <v>0.0</v>
@@ -23486,7 +23486,7 @@
         <v>920</v>
       </c>
       <c r="F795" t="n">
-        <v>336.0</v>
+        <v>338.0</v>
       </c>
       <c r="G795" t="n">
         <v>0.0</v>
@@ -23564,7 +23564,7 @@
         <v>921</v>
       </c>
       <c r="F798" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
       <c r="G798" t="n">
         <v>3.0</v>
@@ -23668,7 +23668,7 @@
         <v>921</v>
       </c>
       <c r="F802" t="n">
-        <v>263.0</v>
+        <v>265.0</v>
       </c>
       <c r="G802" t="n">
         <v>0.0</v>
@@ -23720,7 +23720,7 @@
         <v>921</v>
       </c>
       <c r="F804" t="n">
-        <v>106.0</v>
+        <v>111.0</v>
       </c>
       <c r="G804" t="n">
         <v>0.0</v>
@@ -24006,7 +24006,7 @@
         <v>920</v>
       </c>
       <c r="F815" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G815" t="n">
         <v>0.0</v>
@@ -24032,7 +24032,7 @@
         <v>921</v>
       </c>
       <c r="F816" t="n">
-        <v>312.0</v>
+        <v>317.0</v>
       </c>
       <c r="G816" t="n">
         <v>0.0</v>
@@ -24162,7 +24162,7 @@
         <v>920</v>
       </c>
       <c r="F821" t="n">
-        <v>153.0</v>
+        <v>155.0</v>
       </c>
       <c r="G821" t="n">
         <v>0.0</v>
@@ -24448,7 +24448,7 @@
         <v>920</v>
       </c>
       <c r="F832" t="n">
-        <v>309.0</v>
+        <v>311.0</v>
       </c>
       <c r="G832" t="n">
         <v>0.0</v>
@@ -24656,7 +24656,7 @@
         <v>920</v>
       </c>
       <c r="F840" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="G840" t="n">
         <v>0.0</v>
@@ -24890,10 +24890,10 @@
         <v>921</v>
       </c>
       <c r="F849" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G849" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H849" t="n">
         <v>75.0</v>
@@ -25098,7 +25098,7 @@
         <v>921</v>
       </c>
       <c r="F857" t="n">
-        <v>155.0</v>
+        <v>158.0</v>
       </c>
       <c r="G857" t="n">
         <v>0.0</v>
@@ -25150,7 +25150,7 @@
         <v>921</v>
       </c>
       <c r="F859" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G859" t="n">
         <v>0.0</v>
@@ -25436,7 +25436,7 @@
         <v>920</v>
       </c>
       <c r="F870" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G870" t="n">
         <v>0.0</v>
@@ -25566,7 +25566,7 @@
         <v>920</v>
       </c>
       <c r="F875" t="n">
-        <v>130.0</v>
+        <v>133.0</v>
       </c>
       <c r="G875" t="n">
         <v>0.0</v>
@@ -25592,7 +25592,7 @@
         <v>921</v>
       </c>
       <c r="F876" t="n">
-        <v>347.0</v>
+        <v>349.0</v>
       </c>
       <c r="G876" t="n">
         <v>0.0</v>
@@ -25800,7 +25800,7 @@
         <v>921</v>
       </c>
       <c r="F884" t="n">
-        <v>162.0</v>
+        <v>165.0</v>
       </c>
       <c r="G884" t="n">
         <v>0.0</v>
@@ -25878,7 +25878,7 @@
         <v>921</v>
       </c>
       <c r="F887" t="n">
-        <v>93.0</v>
+        <v>96.0</v>
       </c>
       <c r="G887" t="n">
         <v>0.0</v>
@@ -25982,7 +25982,7 @@
         <v>921</v>
       </c>
       <c r="F891" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="G891" t="n">
         <v>1.0</v>
@@ -26066,7 +26066,7 @@
         <v>0.0</v>
       </c>
       <c r="H894" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="895">
@@ -26089,7 +26089,7 @@
         <v>108.0</v>
       </c>
       <c r="G895" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H895" t="n">
         <v>0.0</v>
@@ -26138,7 +26138,7 @@
         <v>920</v>
       </c>
       <c r="F897" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G897" t="n">
         <v>0.0</v>
@@ -26268,7 +26268,7 @@
         <v>920</v>
       </c>
       <c r="F902" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G902" t="n">
         <v>0.0</v>
@@ -26294,7 +26294,7 @@
         <v>920</v>
       </c>
       <c r="F903" t="n">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
       <c r="G903" t="n">
         <v>0.0</v>
@@ -26320,7 +26320,7 @@
         <v>920</v>
       </c>
       <c r="F904" t="n">
-        <v>79.0</v>
+        <v>83.0</v>
       </c>
       <c r="G904" t="n">
         <v>0.0</v>
@@ -26346,7 +26346,7 @@
         <v>920</v>
       </c>
       <c r="F905" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
       <c r="G905" t="n">
         <v>0.0</v>
@@ -26398,7 +26398,7 @@
         <v>920</v>
       </c>
       <c r="F907" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G907" t="n">
         <v>0.0</v>
@@ -26424,7 +26424,7 @@
         <v>920</v>
       </c>
       <c r="F908" t="n">
-        <v>74.0</v>
+        <v>77.0</v>
       </c>
       <c r="G908" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3232,7 +3232,7 @@
         <v>921</v>
       </c>
       <c r="F16" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -4324,7 +4324,7 @@
         <v>920</v>
       </c>
       <c r="F58" t="n">
-        <v>247.0</v>
+        <v>250.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -5156,7 +5156,7 @@
         <v>921</v>
       </c>
       <c r="F90" t="n">
-        <v>200.0</v>
+        <v>202.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -5754,7 +5754,7 @@
         <v>921</v>
       </c>
       <c r="F113" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -5936,7 +5936,7 @@
         <v>920</v>
       </c>
       <c r="F120" t="n">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
       <c r="G120" t="n">
         <v>0.0</v>
@@ -6534,7 +6534,7 @@
         <v>921</v>
       </c>
       <c r="F143" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -7034,7 +7034,7 @@
         <v>1.0</v>
       </c>
       <c r="H162" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="163">
@@ -7288,7 +7288,7 @@
         <v>921</v>
       </c>
       <c r="F172" t="n">
-        <v>220.0</v>
+        <v>222.0</v>
       </c>
       <c r="G172" t="n">
         <v>7.0</v>
@@ -7522,7 +7522,7 @@
         <v>921</v>
       </c>
       <c r="F181" t="n">
-        <v>105.0</v>
+        <v>109.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7548,7 +7548,7 @@
         <v>921</v>
       </c>
       <c r="F182" t="n">
-        <v>127.0</v>
+        <v>129.0</v>
       </c>
       <c r="G182" t="n">
         <v>1.0</v>
@@ -8198,7 +8198,7 @@
         <v>921</v>
       </c>
       <c r="F207" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="G207" t="n">
         <v>1.0</v>
@@ -8692,7 +8692,7 @@
         <v>920</v>
       </c>
       <c r="F226" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G226" t="n">
         <v>1.0</v>
@@ -8770,7 +8770,7 @@
         <v>920</v>
       </c>
       <c r="F229" t="n">
-        <v>95.0</v>
+        <v>97.0</v>
       </c>
       <c r="G229" t="n">
         <v>0.0</v>
@@ -9628,7 +9628,7 @@
         <v>920</v>
       </c>
       <c r="F262" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G262" t="n">
         <v>0.0</v>
@@ -12332,7 +12332,7 @@
         <v>921</v>
       </c>
       <c r="F366" t="n">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
       <c r="G366" t="n">
         <v>0.0</v>
@@ -12774,7 +12774,7 @@
         <v>921</v>
       </c>
       <c r="F383" t="n">
-        <v>523.0</v>
+        <v>524.0</v>
       </c>
       <c r="G383" t="n">
         <v>6.0</v>
@@ -15790,7 +15790,7 @@
         <v>920</v>
       </c>
       <c r="F499" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -17324,7 +17324,7 @@
         <v>920</v>
       </c>
       <c r="F558" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
@@ -18364,7 +18364,7 @@
         <v>921</v>
       </c>
       <c r="F598" t="n">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
       <c r="G598" t="n">
         <v>1.0</v>
@@ -19274,7 +19274,7 @@
         <v>921</v>
       </c>
       <c r="F633" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -20548,7 +20548,7 @@
         <v>921</v>
       </c>
       <c r="F682" t="n">
-        <v>2263.0</v>
+        <v>2264.0</v>
       </c>
       <c r="G682" t="n">
         <v>44.0</v>
@@ -21250,7 +21250,7 @@
         <v>921</v>
       </c>
       <c r="F709" t="n">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
       <c r="G709" t="n">
         <v>0.0</v>
@@ -22316,7 +22316,7 @@
         <v>921</v>
       </c>
       <c r="F750" t="n">
-        <v>253.0</v>
+        <v>254.0</v>
       </c>
       <c r="G750" t="n">
         <v>1.0</v>
@@ -22446,7 +22446,7 @@
         <v>921</v>
       </c>
       <c r="F755" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G755" t="n">
         <v>1.0</v>
@@ -22914,7 +22914,7 @@
         <v>920</v>
       </c>
       <c r="F773" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="G773" t="n">
         <v>0.0</v>
@@ -23388,7 +23388,7 @@
         <v>11.0</v>
       </c>
       <c r="H791" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="792">
@@ -23434,7 +23434,7 @@
         <v>920</v>
       </c>
       <c r="F793" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G793" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2894,7 +2894,7 @@
         <v>921</v>
       </c>
       <c r="F3" t="n">
-        <v>79.0</v>
+        <v>83.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -2998,7 +2998,7 @@
         <v>921</v>
       </c>
       <c r="F7" t="n">
-        <v>118.0</v>
+        <v>120.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -4324,7 +4324,7 @@
         <v>920</v>
       </c>
       <c r="F58" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -7418,7 +7418,7 @@
         <v>921</v>
       </c>
       <c r="F177" t="n">
-        <v>168.0</v>
+        <v>170.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7860,7 +7860,7 @@
         <v>920</v>
       </c>
       <c r="F194" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G194" t="n">
         <v>0.0</v>
@@ -9550,7 +9550,7 @@
         <v>920</v>
       </c>
       <c r="F259" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G259" t="n">
         <v>0.0</v>
@@ -10070,7 +10070,7 @@
         <v>921</v>
       </c>
       <c r="F279" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G279" t="n">
         <v>3.0</v>
@@ -11578,7 +11578,7 @@
         <v>921</v>
       </c>
       <c r="F337" t="n">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="G337" t="n">
         <v>0.0</v>
@@ -12618,7 +12618,7 @@
         <v>921</v>
       </c>
       <c r="F377" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -13144,7 +13144,7 @@
         <v>0.0</v>
       </c>
       <c r="H397" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="398">
@@ -13528,7 +13528,7 @@
         <v>921</v>
       </c>
       <c r="F412" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G412" t="n">
         <v>0.0</v>
@@ -13554,7 +13554,7 @@
         <v>921</v>
       </c>
       <c r="F413" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G413" t="n">
         <v>4.0</v>
@@ -15712,7 +15712,7 @@
         <v>921</v>
       </c>
       <c r="F496" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -17116,7 +17116,7 @@
         <v>921</v>
       </c>
       <c r="F550" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G550" t="n">
         <v>0.0</v>
@@ -18364,7 +18364,7 @@
         <v>921</v>
       </c>
       <c r="F598" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="G598" t="n">
         <v>1.0</v>
@@ -19404,7 +19404,7 @@
         <v>921</v>
       </c>
       <c r="F638" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -21646,7 +21646,7 @@
         <v>0.0</v>
       </c>
       <c r="H724" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="725">
@@ -21692,7 +21692,7 @@
         <v>921</v>
       </c>
       <c r="F726" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -22212,7 +22212,7 @@
         <v>921</v>
       </c>
       <c r="F746" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G746" t="n">
         <v>0.0</v>
@@ -22368,7 +22368,7 @@
         <v>921</v>
       </c>
       <c r="F752" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G752" t="n">
         <v>0.0</v>
@@ -22628,7 +22628,7 @@
         <v>921</v>
       </c>
       <c r="F762" t="n">
-        <v>109.0</v>
+        <v>111.0</v>
       </c>
       <c r="G762" t="n">
         <v>0.0</v>
@@ -23330,7 +23330,7 @@
         <v>921</v>
       </c>
       <c r="F789" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G789" t="n">
         <v>0.0</v>
@@ -23720,7 +23720,7 @@
         <v>921</v>
       </c>
       <c r="F804" t="n">
-        <v>111.0</v>
+        <v>115.0</v>
       </c>
       <c r="G804" t="n">
         <v>0.0</v>
@@ -24032,7 +24032,7 @@
         <v>921</v>
       </c>
       <c r="F816" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="G816" t="n">
         <v>0.0</v>
@@ -25098,7 +25098,7 @@
         <v>921</v>
       </c>
       <c r="F857" t="n">
-        <v>158.0</v>
+        <v>164.0</v>
       </c>
       <c r="G857" t="n">
         <v>0.0</v>
@@ -25800,7 +25800,7 @@
         <v>921</v>
       </c>
       <c r="F884" t="n">
-        <v>165.0</v>
+        <v>173.0</v>
       </c>
       <c r="G884" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2868,7 +2868,7 @@
         <v>920</v>
       </c>
       <c r="F2" t="n">
-        <v>494.0</v>
+        <v>501.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -3258,7 +3258,7 @@
         <v>921</v>
       </c>
       <c r="F17" t="n">
-        <v>384.0</v>
+        <v>386.0</v>
       </c>
       <c r="G17" t="n">
         <v>3.0</v>
@@ -3310,7 +3310,7 @@
         <v>920</v>
       </c>
       <c r="F19" t="n">
-        <v>340.0</v>
+        <v>341.0</v>
       </c>
       <c r="G19" t="n">
         <v>1.0</v>
@@ -3518,7 +3518,7 @@
         <v>920</v>
       </c>
       <c r="F27" t="n">
-        <v>317.0</v>
+        <v>321.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>564.0</v>
+        <v>568.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -5520,7 +5520,7 @@
         <v>921</v>
       </c>
       <c r="F104" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="G104" t="n">
         <v>15.0</v>
@@ -6248,7 +6248,7 @@
         <v>920</v>
       </c>
       <c r="F132" t="n">
-        <v>347.0</v>
+        <v>352.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -7054,7 +7054,7 @@
         <v>920</v>
       </c>
       <c r="F163" t="n">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -8458,7 +8458,7 @@
         <v>921</v>
       </c>
       <c r="F217" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G217" t="n">
         <v>0.0</v>
@@ -8510,7 +8510,7 @@
         <v>921</v>
       </c>
       <c r="F219" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="G219" t="n">
         <v>0.0</v>
@@ -10876,7 +10876,7 @@
         <v>921</v>
       </c>
       <c r="F310" t="n">
-        <v>388.0</v>
+        <v>389.0</v>
       </c>
       <c r="G310" t="n">
         <v>1.0</v>
@@ -14360,7 +14360,7 @@
         <v>921</v>
       </c>
       <c r="F444" t="n">
-        <v>356.0</v>
+        <v>357.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
@@ -17356,7 +17356,7 @@
         <v>6.0</v>
       </c>
       <c r="H559" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="560">
@@ -18832,7 +18832,7 @@
         <v>921</v>
       </c>
       <c r="F616" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -23486,7 +23486,7 @@
         <v>920</v>
       </c>
       <c r="F795" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="G795" t="n">
         <v>0.0</v>
@@ -26190,7 +26190,7 @@
         <v>921</v>
       </c>
       <c r="F899" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="G899" t="n">
         <v>2.0</v>
@@ -26294,7 +26294,7 @@
         <v>920</v>
       </c>
       <c r="F903" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G903" t="n">
         <v>0.0</v>
@@ -26346,7 +26346,7 @@
         <v>920</v>
       </c>
       <c r="F905" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G905" t="n">
         <v>0.0</v>
@@ -26398,7 +26398,7 @@
         <v>920</v>
       </c>
       <c r="F907" t="n">
-        <v>81.0</v>
+        <v>85.0</v>
       </c>
       <c r="G907" t="n">
         <v>0.0</v>
@@ -26424,7 +26424,7 @@
         <v>920</v>
       </c>
       <c r="F908" t="n">
-        <v>77.0</v>
+        <v>80.0</v>
       </c>
       <c r="G908" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3258,7 +3258,7 @@
         <v>921</v>
       </c>
       <c r="F17" t="n">
-        <v>386.0</v>
+        <v>390.0</v>
       </c>
       <c r="G17" t="n">
         <v>3.0</v>
@@ -4148,7 +4148,7 @@
         <v>0.0</v>
       </c>
       <c r="H51" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="52">
@@ -4740,7 +4740,7 @@
         <v>921</v>
       </c>
       <c r="F74" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -5338,7 +5338,7 @@
         <v>920</v>
       </c>
       <c r="F97" t="n">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -5442,7 +5442,7 @@
         <v>921</v>
       </c>
       <c r="F101" t="n">
-        <v>324.0</v>
+        <v>327.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -6248,7 +6248,7 @@
         <v>920</v>
       </c>
       <c r="F132" t="n">
-        <v>352.0</v>
+        <v>356.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -6820,7 +6820,7 @@
         <v>921</v>
       </c>
       <c r="F154" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G154" t="n">
         <v>0.0</v>
@@ -6950,7 +6950,7 @@
         <v>921</v>
       </c>
       <c r="F159" t="n">
-        <v>407.0</v>
+        <v>408.0</v>
       </c>
       <c r="G159" t="n">
         <v>1.0</v>
@@ -7080,7 +7080,7 @@
         <v>921</v>
       </c>
       <c r="F164" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G164" t="n">
         <v>0.0</v>
@@ -7834,7 +7834,7 @@
         <v>921</v>
       </c>
       <c r="F193" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -8692,7 +8692,7 @@
         <v>920</v>
       </c>
       <c r="F226" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G226" t="n">
         <v>1.0</v>
@@ -8718,7 +8718,7 @@
         <v>921</v>
       </c>
       <c r="F227" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G227" t="n">
         <v>0.0</v>
@@ -8900,7 +8900,7 @@
         <v>920</v>
       </c>
       <c r="F234" t="n">
-        <v>514.0</v>
+        <v>519.0</v>
       </c>
       <c r="G234" t="n">
         <v>1.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>971.0</v>
+        <v>973.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -10856,7 +10856,7 @@
         <v>0.0</v>
       </c>
       <c r="H309" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="310">
@@ -12384,7 +12384,7 @@
         <v>921</v>
       </c>
       <c r="F368" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -12774,7 +12774,7 @@
         <v>921</v>
       </c>
       <c r="F383" t="n">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="G383" t="n">
         <v>6.0</v>
@@ -13268,7 +13268,7 @@
         <v>920</v>
       </c>
       <c r="F402" t="n">
-        <v>371.0</v>
+        <v>373.0</v>
       </c>
       <c r="G402" t="n">
         <v>0.0</v>
@@ -14360,7 +14360,7 @@
         <v>921</v>
       </c>
       <c r="F444" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
@@ -15790,7 +15790,7 @@
         <v>920</v>
       </c>
       <c r="F499" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -18416,7 +18416,7 @@
         <v>921</v>
       </c>
       <c r="F600" t="n">
-        <v>748.0</v>
+        <v>749.0</v>
       </c>
       <c r="G600" t="n">
         <v>2.0</v>
@@ -18832,7 +18832,7 @@
         <v>921</v>
       </c>
       <c r="F616" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -19742,7 +19742,7 @@
         <v>921</v>
       </c>
       <c r="F651" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -20106,7 +20106,7 @@
         <v>921</v>
       </c>
       <c r="F665" t="n">
-        <v>489.0</v>
+        <v>490.0</v>
       </c>
       <c r="G665" t="n">
         <v>1.0</v>
@@ -21250,7 +21250,7 @@
         <v>921</v>
       </c>
       <c r="F709" t="n">
-        <v>190.0</v>
+        <v>192.0</v>
       </c>
       <c r="G709" t="n">
         <v>0.0</v>
@@ -22082,7 +22082,7 @@
         <v>921</v>
       </c>
       <c r="F741" t="n">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22862,7 +22862,7 @@
         <v>921</v>
       </c>
       <c r="F771" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>
@@ -23616,7 +23616,7 @@
         <v>921</v>
       </c>
       <c r="F800" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="G800" t="n">
         <v>0.0</v>
@@ -24032,7 +24032,7 @@
         <v>921</v>
       </c>
       <c r="F816" t="n">
-        <v>318.0</v>
+        <v>321.0</v>
       </c>
       <c r="G816" t="n">
         <v>0.0</v>
@@ -25228,7 +25228,7 @@
         <v>921</v>
       </c>
       <c r="F862" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="G862" t="n">
         <v>0.0</v>
@@ -25566,7 +25566,7 @@
         <v>920</v>
       </c>
       <c r="F875" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G875" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4792,7 +4792,7 @@
         <v>921</v>
       </c>
       <c r="F76" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -5442,7 +5442,7 @@
         <v>921</v>
       </c>
       <c r="F101" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -7158,7 +7158,7 @@
         <v>920</v>
       </c>
       <c r="F167" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -7860,7 +7860,7 @@
         <v>920</v>
       </c>
       <c r="F194" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G194" t="n">
         <v>0.0</v>
@@ -9628,7 +9628,7 @@
         <v>920</v>
       </c>
       <c r="F262" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G262" t="n">
         <v>0.0</v>
@@ -10434,7 +10434,7 @@
         <v>921</v>
       </c>
       <c r="F293" t="n">
-        <v>104.0</v>
+        <v>108.0</v>
       </c>
       <c r="G293" t="n">
         <v>0.0</v>
@@ -16778,13 +16778,13 @@
         <v>921</v>
       </c>
       <c r="F537" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
       </c>
       <c r="H537" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="538">
@@ -17194,7 +17194,7 @@
         <v>920</v>
       </c>
       <c r="F553" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -18286,7 +18286,7 @@
         <v>921</v>
       </c>
       <c r="F595" t="n">
-        <v>484.0</v>
+        <v>489.0</v>
       </c>
       <c r="G595" t="n">
         <v>3.0</v>
@@ -22056,7 +22056,7 @@
         <v>921</v>
       </c>
       <c r="F740" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G740" t="n">
         <v>1.0</v>
@@ -22810,7 +22810,7 @@
         <v>921</v>
       </c>
       <c r="F769" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G769" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2868,7 +2868,7 @@
         <v>920</v>
       </c>
       <c r="F2" t="n">
-        <v>501.0</v>
+        <v>503.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -3212,7 +3212,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="16">
@@ -3258,7 +3258,7 @@
         <v>921</v>
       </c>
       <c r="F17" t="n">
-        <v>390.0</v>
+        <v>392.0</v>
       </c>
       <c r="G17" t="n">
         <v>3.0</v>
@@ -3310,7 +3310,7 @@
         <v>920</v>
       </c>
       <c r="F19" t="n">
-        <v>341.0</v>
+        <v>345.0</v>
       </c>
       <c r="G19" t="n">
         <v>1.0</v>
@@ -3336,7 +3336,7 @@
         <v>921</v>
       </c>
       <c r="F20" t="n">
-        <v>236.0</v>
+        <v>243.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>568.0</v>
+        <v>574.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -4090,7 +4090,7 @@
         <v>921</v>
       </c>
       <c r="F49" t="n">
-        <v>140.0</v>
+        <v>143.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -4148,7 +4148,7 @@
         <v>0.0</v>
       </c>
       <c r="H51" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="52">
@@ -4168,7 +4168,7 @@
         <v>921</v>
       </c>
       <c r="F52" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -4324,7 +4324,7 @@
         <v>920</v>
       </c>
       <c r="F58" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -4402,7 +4402,7 @@
         <v>921</v>
       </c>
       <c r="F61" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -5032,7 +5032,7 @@
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="86">
@@ -6404,13 +6404,13 @@
         <v>921</v>
       </c>
       <c r="F138" t="n">
-        <v>440.0</v>
+        <v>443.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="139">
@@ -6716,7 +6716,7 @@
         <v>921</v>
       </c>
       <c r="F150" t="n">
-        <v>231.0</v>
+        <v>232.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -7028,7 +7028,7 @@
         <v>921</v>
       </c>
       <c r="F162" t="n">
-        <v>412.0</v>
+        <v>413.0</v>
       </c>
       <c r="G162" t="n">
         <v>1.0</v>
@@ -7054,7 +7054,7 @@
         <v>920</v>
       </c>
       <c r="F163" t="n">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -7626,7 +7626,7 @@
         <v>921</v>
       </c>
       <c r="F185" t="n">
-        <v>593.0</v>
+        <v>596.0</v>
       </c>
       <c r="G185" t="n">
         <v>1.0</v>
@@ -7860,7 +7860,7 @@
         <v>920</v>
       </c>
       <c r="F194" t="n">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
       <c r="G194" t="n">
         <v>0.0</v>
@@ -7964,7 +7964,7 @@
         <v>921</v>
       </c>
       <c r="F198" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -8146,7 +8146,7 @@
         <v>921</v>
       </c>
       <c r="F205" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -8588,7 +8588,7 @@
         <v>921</v>
       </c>
       <c r="F222" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="G222" t="n">
         <v>6.0</v>
@@ -8718,7 +8718,7 @@
         <v>921</v>
       </c>
       <c r="F227" t="n">
-        <v>253.0</v>
+        <v>254.0</v>
       </c>
       <c r="G227" t="n">
         <v>0.0</v>
@@ -10928,7 +10928,7 @@
         <v>920</v>
       </c>
       <c r="F312" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G312" t="n">
         <v>0.0</v>
@@ -12228,13 +12228,13 @@
         <v>921</v>
       </c>
       <c r="F362" t="n">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
       <c r="G362" t="n">
         <v>0.0</v>
       </c>
       <c r="H362" t="n">
-        <v>27.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="363">
@@ -12774,7 +12774,7 @@
         <v>921</v>
       </c>
       <c r="F383" t="n">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
       <c r="G383" t="n">
         <v>6.0</v>
@@ -13450,7 +13450,7 @@
         <v>921</v>
       </c>
       <c r="F409" t="n">
-        <v>933.0</v>
+        <v>934.0</v>
       </c>
       <c r="G409" t="n">
         <v>5.0</v>
@@ -13580,7 +13580,7 @@
         <v>921</v>
       </c>
       <c r="F414" t="n">
-        <v>418.0</v>
+        <v>423.0</v>
       </c>
       <c r="G414" t="n">
         <v>4.0</v>
@@ -13612,7 +13612,7 @@
         <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="416">
@@ -14360,7 +14360,7 @@
         <v>921</v>
       </c>
       <c r="F444" t="n">
-        <v>358.0</v>
+        <v>361.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
@@ -15010,7 +15010,7 @@
         <v>921</v>
       </c>
       <c r="F469" t="n">
-        <v>107.0</v>
+        <v>113.0</v>
       </c>
       <c r="G469" t="n">
         <v>0.0</v>
@@ -15426,7 +15426,7 @@
         <v>921</v>
       </c>
       <c r="F485" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
@@ -15790,7 +15790,7 @@
         <v>920</v>
       </c>
       <c r="F499" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -15972,7 +15972,7 @@
         <v>921</v>
       </c>
       <c r="F506" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G506" t="n">
         <v>0.0</v>
@@ -17194,7 +17194,7 @@
         <v>920</v>
       </c>
       <c r="F553" t="n">
-        <v>258.0</v>
+        <v>260.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -17688,7 +17688,7 @@
         <v>921</v>
       </c>
       <c r="F572" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17766,7 +17766,7 @@
         <v>921</v>
       </c>
       <c r="F575" t="n">
-        <v>266.0</v>
+        <v>267.0</v>
       </c>
       <c r="G575" t="n">
         <v>0.0</v>
@@ -18286,7 +18286,7 @@
         <v>921</v>
       </c>
       <c r="F595" t="n">
-        <v>489.0</v>
+        <v>493.0</v>
       </c>
       <c r="G595" t="n">
         <v>3.0</v>
@@ -19586,7 +19586,7 @@
         <v>920</v>
       </c>
       <c r="F645" t="n">
-        <v>210.0</v>
+        <v>213.0</v>
       </c>
       <c r="G645" t="n">
         <v>1.0</v>
@@ -20106,7 +20106,7 @@
         <v>921</v>
       </c>
       <c r="F665" t="n">
-        <v>490.0</v>
+        <v>492.0</v>
       </c>
       <c r="G665" t="n">
         <v>1.0</v>
@@ -20548,7 +20548,7 @@
         <v>921</v>
       </c>
       <c r="F682" t="n">
-        <v>2264.0</v>
+        <v>2266.0</v>
       </c>
       <c r="G682" t="n">
         <v>44.0</v>
@@ -21510,13 +21510,13 @@
         <v>921</v>
       </c>
       <c r="F719" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="720">
@@ -21640,7 +21640,7 @@
         <v>921</v>
       </c>
       <c r="F724" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
@@ -23486,7 +23486,7 @@
         <v>920</v>
       </c>
       <c r="F795" t="n">
-        <v>339.0</v>
+        <v>341.0</v>
       </c>
       <c r="G795" t="n">
         <v>0.0</v>
@@ -23538,7 +23538,7 @@
         <v>921</v>
       </c>
       <c r="F797" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G797" t="n">
         <v>0.0</v>
@@ -24500,7 +24500,7 @@
         <v>921</v>
       </c>
       <c r="F834" t="n">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="G834" t="n">
         <v>0.0</v>
@@ -25644,7 +25644,7 @@
         <v>921</v>
       </c>
       <c r="F878" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G878" t="n">
         <v>7.0</v>
@@ -26138,7 +26138,7 @@
         <v>920</v>
       </c>
       <c r="F897" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G897" t="n">
         <v>0.0</v>
@@ -26190,13 +26190,13 @@
         <v>921</v>
       </c>
       <c r="F899" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G899" t="n">
         <v>2.0</v>
       </c>
       <c r="H899" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="900">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2998,7 +2998,7 @@
         <v>921</v>
       </c>
       <c r="F7" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -3154,7 +3154,7 @@
         <v>921</v>
       </c>
       <c r="F13" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -4792,7 +4792,7 @@
         <v>921</v>
       </c>
       <c r="F76" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -4818,7 +4818,7 @@
         <v>921</v>
       </c>
       <c r="F77" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -6430,7 +6430,7 @@
         <v>921</v>
       </c>
       <c r="F139" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>
@@ -7470,7 +7470,7 @@
         <v>921</v>
       </c>
       <c r="F179" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7834,7 +7834,7 @@
         <v>921</v>
       </c>
       <c r="F193" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -8770,7 +8770,7 @@
         <v>920</v>
       </c>
       <c r="F229" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G229" t="n">
         <v>0.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>973.0</v>
+        <v>974.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -12234,7 +12234,7 @@
         <v>0.0</v>
       </c>
       <c r="H362" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="363">
@@ -12592,7 +12592,7 @@
         <v>921</v>
       </c>
       <c r="F376" t="n">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -13144,7 +13144,7 @@
         <v>0.0</v>
       </c>
       <c r="H397" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="398">
@@ -14672,7 +14672,7 @@
         <v>921</v>
       </c>
       <c r="F456" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
       <c r="G456" t="n">
         <v>2.0</v>
@@ -16960,7 +16960,7 @@
         <v>920</v>
       </c>
       <c r="F544" t="n">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
       <c r="G544" t="n">
         <v>0.0</v>
@@ -20522,7 +20522,7 @@
         <v>921</v>
       </c>
       <c r="F681" t="n">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="G681" t="n">
         <v>0.0</v>
@@ -21328,7 +21328,7 @@
         <v>920</v>
       </c>
       <c r="F712" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G712" t="n">
         <v>0.0</v>
@@ -21516,7 +21516,7 @@
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="720">
@@ -21646,7 +21646,7 @@
         <v>0.0</v>
       </c>
       <c r="H724" t="n">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="725">
@@ -21848,7 +21848,7 @@
         <v>921</v>
       </c>
       <c r="F732" t="n">
-        <v>165.0</v>
+        <v>168.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21903,7 +21903,7 @@
         <v>397.0</v>
       </c>
       <c r="G734" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H734" t="n">
         <v>0.0</v>
@@ -22082,7 +22082,7 @@
         <v>921</v>
       </c>
       <c r="F741" t="n">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -25182,7 +25182,7 @@
         <v>0.0</v>
       </c>
       <c r="H860" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="861">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2868,7 +2868,7 @@
         <v>920</v>
       </c>
       <c r="F2" t="n">
-        <v>503.0</v>
+        <v>506.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -2894,7 +2894,7 @@
         <v>921</v>
       </c>
       <c r="F3" t="n">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="16">
@@ -3258,7 +3258,7 @@
         <v>921</v>
       </c>
       <c r="F17" t="n">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="G17" t="n">
         <v>3.0</v>
@@ -3310,7 +3310,7 @@
         <v>920</v>
       </c>
       <c r="F19" t="n">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
       <c r="G19" t="n">
         <v>1.0</v>
@@ -3362,7 +3362,7 @@
         <v>920</v>
       </c>
       <c r="F21" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>574.0</v>
+        <v>575.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -4038,7 +4038,7 @@
         <v>921</v>
       </c>
       <c r="F47" t="n">
-        <v>427.0</v>
+        <v>428.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -4714,7 +4714,7 @@
         <v>921</v>
       </c>
       <c r="F73" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4740,7 +4740,7 @@
         <v>921</v>
       </c>
       <c r="F74" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -4766,7 +4766,7 @@
         <v>920</v>
       </c>
       <c r="F75" t="n">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -5078,7 +5078,7 @@
         <v>921</v>
       </c>
       <c r="F87" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -5338,7 +5338,7 @@
         <v>920</v>
       </c>
       <c r="F97" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -5442,7 +5442,7 @@
         <v>921</v>
       </c>
       <c r="F101" t="n">
-        <v>328.0</v>
+        <v>330.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5962,7 +5962,7 @@
         <v>920</v>
       </c>
       <c r="F121" t="n">
-        <v>266.0</v>
+        <v>269.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>
@@ -6014,7 +6014,7 @@
         <v>921</v>
       </c>
       <c r="F123" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>
@@ -7028,7 +7028,7 @@
         <v>921</v>
       </c>
       <c r="F162" t="n">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="G162" t="n">
         <v>1.0</v>
@@ -7626,7 +7626,7 @@
         <v>921</v>
       </c>
       <c r="F185" t="n">
-        <v>596.0</v>
+        <v>597.0</v>
       </c>
       <c r="G185" t="n">
         <v>1.0</v>
@@ -7808,7 +7808,7 @@
         <v>921</v>
       </c>
       <c r="F192" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G192" t="n">
         <v>0.0</v>
@@ -7912,7 +7912,7 @@
         <v>920</v>
       </c>
       <c r="F196" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
       <c r="G196" t="n">
         <v>0.0</v>
@@ -8172,7 +8172,7 @@
         <v>920</v>
       </c>
       <c r="F206" t="n">
-        <v>271.0</v>
+        <v>277.0</v>
       </c>
       <c r="G206" t="n">
         <v>0.0</v>
@@ -8328,7 +8328,7 @@
         <v>921</v>
       </c>
       <c r="F212" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -8432,7 +8432,7 @@
         <v>921</v>
       </c>
       <c r="F216" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G216" t="n">
         <v>0.0</v>
@@ -8510,7 +8510,7 @@
         <v>921</v>
       </c>
       <c r="F219" t="n">
-        <v>290.0</v>
+        <v>291.0</v>
       </c>
       <c r="G219" t="n">
         <v>0.0</v>
@@ -9056,7 +9056,7 @@
         <v>921</v>
       </c>
       <c r="F240" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G240" t="n">
         <v>0.0</v>
@@ -9082,7 +9082,7 @@
         <v>921</v>
       </c>
       <c r="F241" t="n">
-        <v>604.0</v>
+        <v>607.0</v>
       </c>
       <c r="G241" t="n">
         <v>0.0</v>
@@ -9108,7 +9108,7 @@
         <v>920</v>
       </c>
       <c r="F242" t="n">
-        <v>377.0</v>
+        <v>382.0</v>
       </c>
       <c r="G242" t="n">
         <v>0.0</v>
@@ -9264,7 +9264,7 @@
         <v>920</v>
       </c>
       <c r="F248" t="n">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
       <c r="G248" t="n">
         <v>0.0</v>
@@ -9602,7 +9602,7 @@
         <v>920</v>
       </c>
       <c r="F261" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G261" t="n">
         <v>0.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>974.0</v>
+        <v>975.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -9940,7 +9940,7 @@
         <v>921</v>
       </c>
       <c r="F274" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
       <c r="G274" t="n">
         <v>0.0</v>
@@ -9966,7 +9966,7 @@
         <v>921</v>
       </c>
       <c r="F275" t="n">
-        <v>370.0</v>
+        <v>371.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -10070,7 +10070,7 @@
         <v>921</v>
       </c>
       <c r="F279" t="n">
-        <v>123.0</v>
+        <v>133.0</v>
       </c>
       <c r="G279" t="n">
         <v>3.0</v>
@@ -10538,7 +10538,7 @@
         <v>921</v>
       </c>
       <c r="F297" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
       <c r="G297" t="n">
         <v>0.0</v>
@@ -10590,7 +10590,7 @@
         <v>921</v>
       </c>
       <c r="F299" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G299" t="n">
         <v>1.0</v>
@@ -11110,7 +11110,7 @@
         <v>920</v>
       </c>
       <c r="F319" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="G319" t="n">
         <v>0.0</v>
@@ -11636,7 +11636,7 @@
         <v>16.0</v>
       </c>
       <c r="H339" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="340">
@@ -11734,7 +11734,7 @@
         <v>920</v>
       </c>
       <c r="F343" t="n">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="G343" t="n">
         <v>1.0</v>
@@ -11786,7 +11786,7 @@
         <v>920</v>
       </c>
       <c r="F345" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G345" t="n">
         <v>0.0</v>
@@ -12046,7 +12046,7 @@
         <v>920</v>
       </c>
       <c r="F355" t="n">
-        <v>191.0</v>
+        <v>194.0</v>
       </c>
       <c r="G355" t="n">
         <v>0.0</v>
@@ -12202,7 +12202,7 @@
         <v>921</v>
       </c>
       <c r="F361" t="n">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -12280,7 +12280,7 @@
         <v>921</v>
       </c>
       <c r="F364" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G364" t="n">
         <v>1.0</v>
@@ -12566,7 +12566,7 @@
         <v>921</v>
       </c>
       <c r="F375" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12618,7 +12618,7 @@
         <v>921</v>
       </c>
       <c r="F377" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12751,7 +12751,7 @@
         <v>39.0</v>
       </c>
       <c r="G382" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H382" t="n">
         <v>13.0</v>
@@ -12904,7 +12904,7 @@
         <v>920</v>
       </c>
       <c r="F388" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -12982,7 +12982,7 @@
         <v>921</v>
       </c>
       <c r="F391" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G391" t="n">
         <v>0.0</v>
@@ -13268,7 +13268,7 @@
         <v>920</v>
       </c>
       <c r="F402" t="n">
-        <v>373.0</v>
+        <v>375.0</v>
       </c>
       <c r="G402" t="n">
         <v>0.0</v>
@@ -13372,7 +13372,7 @@
         <v>921</v>
       </c>
       <c r="F406" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="G406" t="n">
         <v>2.0</v>
@@ -13398,7 +13398,7 @@
         <v>920</v>
       </c>
       <c r="F407" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -13580,7 +13580,7 @@
         <v>921</v>
       </c>
       <c r="F414" t="n">
-        <v>423.0</v>
+        <v>426.0</v>
       </c>
       <c r="G414" t="n">
         <v>4.0</v>
@@ -14126,7 +14126,7 @@
         <v>921</v>
       </c>
       <c r="F435" t="n">
-        <v>260.0</v>
+        <v>262.0</v>
       </c>
       <c r="G435" t="n">
         <v>0.0</v>
@@ -14230,7 +14230,7 @@
         <v>920</v>
       </c>
       <c r="F439" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G439" t="n">
         <v>0.0</v>
@@ -14334,7 +14334,7 @@
         <v>921</v>
       </c>
       <c r="F443" t="n">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="G443" t="n">
         <v>0.0</v>
@@ -14490,7 +14490,7 @@
         <v>921</v>
       </c>
       <c r="F449" t="n">
-        <v>470.0</v>
+        <v>476.0</v>
       </c>
       <c r="G449" t="n">
         <v>0.0</v>
@@ -15426,7 +15426,7 @@
         <v>921</v>
       </c>
       <c r="F485" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
@@ -15712,7 +15712,7 @@
         <v>921</v>
       </c>
       <c r="F496" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -16232,7 +16232,7 @@
         <v>921</v>
       </c>
       <c r="F516" t="n">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
       <c r="G516" t="n">
         <v>0.0</v>
@@ -16310,7 +16310,7 @@
         <v>920</v>
       </c>
       <c r="F519" t="n">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
       <c r="G519" t="n">
         <v>0.0</v>
@@ -16388,7 +16388,7 @@
         <v>921</v>
       </c>
       <c r="F522" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -16596,7 +16596,7 @@
         <v>921</v>
       </c>
       <c r="F530" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G530" t="n">
         <v>0.0</v>
@@ -16622,7 +16622,7 @@
         <v>920</v>
       </c>
       <c r="F531" t="n">
-        <v>193.0</v>
+        <v>196.0</v>
       </c>
       <c r="G531" t="n">
         <v>0.0</v>
@@ -16804,7 +16804,7 @@
         <v>920</v>
       </c>
       <c r="F538" t="n">
-        <v>323.0</v>
+        <v>325.0</v>
       </c>
       <c r="G538" t="n">
         <v>0.0</v>
@@ -16830,7 +16830,7 @@
         <v>920</v>
       </c>
       <c r="F539" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -17038,7 +17038,7 @@
         <v>920</v>
       </c>
       <c r="F547" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -17116,7 +17116,7 @@
         <v>921</v>
       </c>
       <c r="F550" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G550" t="n">
         <v>0.0</v>
@@ -17792,7 +17792,7 @@
         <v>921</v>
       </c>
       <c r="F576" t="n">
-        <v>132.0</v>
+        <v>137.0</v>
       </c>
       <c r="G576" t="n">
         <v>1.0</v>
@@ -18286,7 +18286,7 @@
         <v>921</v>
       </c>
       <c r="F595" t="n">
-        <v>493.0</v>
+        <v>494.0</v>
       </c>
       <c r="G595" t="n">
         <v>3.0</v>
@@ -18390,7 +18390,7 @@
         <v>921</v>
       </c>
       <c r="F599" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
@@ -19118,7 +19118,7 @@
         <v>920</v>
       </c>
       <c r="F627" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G627" t="n">
         <v>0.0</v>
@@ -19222,7 +19222,7 @@
         <v>921</v>
       </c>
       <c r="F631" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G631" t="n">
         <v>1.0</v>
@@ -19430,7 +19430,7 @@
         <v>921</v>
       </c>
       <c r="F639" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G639" t="n">
         <v>0.0</v>
@@ -19742,7 +19742,7 @@
         <v>921</v>
       </c>
       <c r="F651" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -20158,7 +20158,7 @@
         <v>921</v>
       </c>
       <c r="F667" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -20314,7 +20314,7 @@
         <v>920</v>
       </c>
       <c r="F673" t="n">
-        <v>391.0</v>
+        <v>394.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -20502,7 +20502,7 @@
         <v>0.0</v>
       </c>
       <c r="H680" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="681">
@@ -21068,7 +21068,7 @@
         <v>921</v>
       </c>
       <c r="F702" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G702" t="n">
         <v>0.0</v>
@@ -21666,7 +21666,7 @@
         <v>921</v>
       </c>
       <c r="F725" t="n">
-        <v>237.0</v>
+        <v>239.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21900,7 +21900,7 @@
         <v>921</v>
       </c>
       <c r="F734" t="n">
-        <v>397.0</v>
+        <v>399.0</v>
       </c>
       <c r="G734" t="n">
         <v>1.0</v>
@@ -22082,7 +22082,7 @@
         <v>921</v>
       </c>
       <c r="F741" t="n">
-        <v>337.0</v>
+        <v>339.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22238,7 +22238,7 @@
         <v>920</v>
       </c>
       <c r="F747" t="n">
-        <v>497.0</v>
+        <v>513.0</v>
       </c>
       <c r="G747" t="n">
         <v>1.0</v>
@@ -22576,7 +22576,7 @@
         <v>920</v>
       </c>
       <c r="F760" t="n">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22680,7 +22680,7 @@
         <v>921</v>
       </c>
       <c r="F764" t="n">
-        <v>245.0</v>
+        <v>247.0</v>
       </c>
       <c r="G764" t="n">
         <v>0.0</v>
@@ -23174,7 +23174,7 @@
         <v>921</v>
       </c>
       <c r="F783" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G783" t="n">
         <v>0.0</v>
@@ -23304,7 +23304,7 @@
         <v>920</v>
       </c>
       <c r="F788" t="n">
-        <v>241.0</v>
+        <v>244.0</v>
       </c>
       <c r="G788" t="n">
         <v>0.0</v>
@@ -23486,7 +23486,7 @@
         <v>920</v>
       </c>
       <c r="F795" t="n">
-        <v>341.0</v>
+        <v>343.0</v>
       </c>
       <c r="G795" t="n">
         <v>0.0</v>
@@ -23668,7 +23668,7 @@
         <v>921</v>
       </c>
       <c r="F802" t="n">
-        <v>265.0</v>
+        <v>269.0</v>
       </c>
       <c r="G802" t="n">
         <v>0.0</v>
@@ -23720,7 +23720,7 @@
         <v>921</v>
       </c>
       <c r="F804" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G804" t="n">
         <v>0.0</v>
@@ -24006,7 +24006,7 @@
         <v>920</v>
       </c>
       <c r="F815" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G815" t="n">
         <v>0.0</v>
@@ -24032,7 +24032,7 @@
         <v>921</v>
       </c>
       <c r="F816" t="n">
-        <v>321.0</v>
+        <v>329.0</v>
       </c>
       <c r="G816" t="n">
         <v>0.0</v>
@@ -24162,7 +24162,7 @@
         <v>920</v>
       </c>
       <c r="F821" t="n">
-        <v>155.0</v>
+        <v>157.0</v>
       </c>
       <c r="G821" t="n">
         <v>0.0</v>
@@ -24214,7 +24214,7 @@
         <v>921</v>
       </c>
       <c r="F823" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G823" t="n">
         <v>0.0</v>
@@ -24448,7 +24448,7 @@
         <v>920</v>
       </c>
       <c r="F832" t="n">
-        <v>311.0</v>
+        <v>314.0</v>
       </c>
       <c r="G832" t="n">
         <v>0.0</v>
@@ -24656,7 +24656,7 @@
         <v>920</v>
       </c>
       <c r="F840" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G840" t="n">
         <v>0.0</v>
@@ -24896,7 +24896,7 @@
         <v>2.0</v>
       </c>
       <c r="H849" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="850">
@@ -25098,7 +25098,7 @@
         <v>921</v>
       </c>
       <c r="F857" t="n">
-        <v>164.0</v>
+        <v>169.0</v>
       </c>
       <c r="G857" t="n">
         <v>0.0</v>
@@ -25592,7 +25592,7 @@
         <v>921</v>
       </c>
       <c r="F876" t="n">
-        <v>349.0</v>
+        <v>351.0</v>
       </c>
       <c r="G876" t="n">
         <v>0.0</v>
@@ -25800,7 +25800,7 @@
         <v>921</v>
       </c>
       <c r="F884" t="n">
-        <v>173.0</v>
+        <v>178.0</v>
       </c>
       <c r="G884" t="n">
         <v>0.0</v>
@@ -26193,7 +26193,7 @@
         <v>52.0</v>
       </c>
       <c r="G899" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H899" t="n">
         <v>2.0</v>
@@ -26398,7 +26398,7 @@
         <v>920</v>
       </c>
       <c r="F907" t="n">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
       <c r="G907" t="n">
         <v>0.0</v>
@@ -26424,7 +26424,7 @@
         <v>920</v>
       </c>
       <c r="F908" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
       <c r="G908" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3264,7 +3264,7 @@
         <v>3.0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
@@ -3284,7 +3284,7 @@
         <v>921</v>
       </c>
       <c r="F18" t="n">
-        <v>226.0</v>
+        <v>230.0</v>
       </c>
       <c r="G18" t="n">
         <v>9.0</v>
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>575.0</v>
+        <v>580.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -4038,7 +4038,7 @@
         <v>921</v>
       </c>
       <c r="F47" t="n">
-        <v>428.0</v>
+        <v>433.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -4194,7 +4194,7 @@
         <v>920</v>
       </c>
       <c r="F53" t="n">
-        <v>277.0</v>
+        <v>288.0</v>
       </c>
       <c r="G53" t="n">
         <v>1.0</v>
@@ -4454,7 +4454,7 @@
         <v>921</v>
       </c>
       <c r="F63" t="n">
-        <v>275.0</v>
+        <v>278.0</v>
       </c>
       <c r="G63" t="n">
         <v>1.0</v>
@@ -5000,13 +5000,13 @@
         <v>921</v>
       </c>
       <c r="F84" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
       </c>
       <c r="H84" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="85">
@@ -7990,7 +7990,7 @@
         <v>920</v>
       </c>
       <c r="F199" t="n">
-        <v>110.0</v>
+        <v>115.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -10122,7 +10122,7 @@
         <v>921</v>
       </c>
       <c r="F281" t="n">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -11318,7 +11318,7 @@
         <v>921</v>
       </c>
       <c r="F327" t="n">
-        <v>120.0</v>
+        <v>125.0</v>
       </c>
       <c r="G327" t="n">
         <v>0.0</v>
@@ -11344,7 +11344,7 @@
         <v>921</v>
       </c>
       <c r="F328" t="n">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="G328" t="n">
         <v>1.0</v>
@@ -11760,7 +11760,7 @@
         <v>921</v>
       </c>
       <c r="F344" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G344" t="n">
         <v>0.0</v>
@@ -12748,7 +12748,7 @@
         <v>921</v>
       </c>
       <c r="F382" t="n">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
       <c r="G382" t="n">
         <v>2.0</v>
@@ -13580,7 +13580,7 @@
         <v>921</v>
       </c>
       <c r="F414" t="n">
-        <v>426.0</v>
+        <v>431.0</v>
       </c>
       <c r="G414" t="n">
         <v>4.0</v>
@@ -15426,7 +15426,7 @@
         <v>921</v>
       </c>
       <c r="F485" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
@@ -17350,7 +17350,7 @@
         <v>921</v>
       </c>
       <c r="F559" t="n">
-        <v>262.0</v>
+        <v>266.0</v>
       </c>
       <c r="G559" t="n">
         <v>6.0</v>
@@ -18832,7 +18832,7 @@
         <v>921</v>
       </c>
       <c r="F616" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -20106,7 +20106,7 @@
         <v>921</v>
       </c>
       <c r="F665" t="n">
-        <v>492.0</v>
+        <v>495.0</v>
       </c>
       <c r="G665" t="n">
         <v>1.0</v>
@@ -25878,7 +25878,7 @@
         <v>921</v>
       </c>
       <c r="F887" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="G887" t="n">
         <v>0.0</v>
@@ -26034,7 +26034,7 @@
         <v>920</v>
       </c>
       <c r="F893" t="n">
-        <v>81.0</v>
+        <v>85.0</v>
       </c>
       <c r="G893" t="n">
         <v>0.0</v>
@@ -26320,7 +26320,7 @@
         <v>920</v>
       </c>
       <c r="F904" t="n">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="G904" t="n">
         <v>0.0</v>
@@ -26476,7 +26476,7 @@
         <v>920</v>
       </c>
       <c r="F910" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G910" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3570,7 +3570,7 @@
         <v>920</v>
       </c>
       <c r="F29" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -5442,7 +5442,7 @@
         <v>921</v>
       </c>
       <c r="F101" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -8900,7 +8900,7 @@
         <v>920</v>
       </c>
       <c r="F234" t="n">
-        <v>519.0</v>
+        <v>521.0</v>
       </c>
       <c r="G234" t="n">
         <v>1.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>975.0</v>
+        <v>976.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -16960,7 +16960,7 @@
         <v>920</v>
       </c>
       <c r="F544" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G544" t="n">
         <v>0.0</v>
@@ -18572,7 +18572,7 @@
         <v>920</v>
       </c>
       <c r="F606" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G606" t="n">
         <v>0.0</v>
@@ -20158,7 +20158,7 @@
         <v>921</v>
       </c>
       <c r="F667" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -22810,7 +22810,7 @@
         <v>921</v>
       </c>
       <c r="F769" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G769" t="n">
         <v>0.0</v>
@@ -24032,7 +24032,7 @@
         <v>921</v>
       </c>
       <c r="F816" t="n">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="G816" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3362,7 +3362,7 @@
         <v>920</v>
       </c>
       <c r="F21" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -4532,7 +4532,7 @@
         <v>921</v>
       </c>
       <c r="F66" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -4714,7 +4714,7 @@
         <v>921</v>
       </c>
       <c r="F73" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4766,7 +4766,7 @@
         <v>920</v>
       </c>
       <c r="F75" t="n">
-        <v>320.0</v>
+        <v>322.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -5416,7 +5416,7 @@
         <v>921</v>
       </c>
       <c r="F100" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -7912,7 +7912,7 @@
         <v>920</v>
       </c>
       <c r="F196" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="G196" t="n">
         <v>0.0</v>
@@ -8328,7 +8328,7 @@
         <v>921</v>
       </c>
       <c r="F212" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -8432,7 +8432,7 @@
         <v>921</v>
       </c>
       <c r="F216" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G216" t="n">
         <v>0.0</v>
@@ -8724,7 +8724,7 @@
         <v>0.0</v>
       </c>
       <c r="H227" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="228">
@@ -9082,7 +9082,7 @@
         <v>921</v>
       </c>
       <c r="F241" t="n">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="G241" t="n">
         <v>0.0</v>
@@ -9108,7 +9108,7 @@
         <v>920</v>
       </c>
       <c r="F242" t="n">
-        <v>382.0</v>
+        <v>383.0</v>
       </c>
       <c r="G242" t="n">
         <v>0.0</v>
@@ -9264,7 +9264,7 @@
         <v>920</v>
       </c>
       <c r="F248" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G248" t="n">
         <v>0.0</v>
@@ -9602,7 +9602,7 @@
         <v>920</v>
       </c>
       <c r="F261" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G261" t="n">
         <v>0.0</v>
@@ -9966,7 +9966,7 @@
         <v>921</v>
       </c>
       <c r="F275" t="n">
-        <v>371.0</v>
+        <v>372.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -10070,7 +10070,7 @@
         <v>921</v>
       </c>
       <c r="F279" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G279" t="n">
         <v>3.0</v>
@@ -10434,7 +10434,7 @@
         <v>921</v>
       </c>
       <c r="F293" t="n">
-        <v>108.0</v>
+        <v>112.0</v>
       </c>
       <c r="G293" t="n">
         <v>0.0</v>
@@ -10538,7 +10538,7 @@
         <v>921</v>
       </c>
       <c r="F297" t="n">
-        <v>238.0</v>
+        <v>240.0</v>
       </c>
       <c r="G297" t="n">
         <v>0.0</v>
@@ -10772,7 +10772,7 @@
         <v>921</v>
       </c>
       <c r="F306" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G306" t="n">
         <v>0.0</v>
@@ -11630,7 +11630,7 @@
         <v>921</v>
       </c>
       <c r="F339" t="n">
-        <v>913.0</v>
+        <v>914.0</v>
       </c>
       <c r="G339" t="n">
         <v>16.0</v>
@@ -11786,7 +11786,7 @@
         <v>920</v>
       </c>
       <c r="F345" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G345" t="n">
         <v>0.0</v>
@@ -12046,7 +12046,7 @@
         <v>920</v>
       </c>
       <c r="F355" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G355" t="n">
         <v>0.0</v>
@@ -12982,7 +12982,7 @@
         <v>921</v>
       </c>
       <c r="F391" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G391" t="n">
         <v>0.0</v>
@@ -13014,7 +13014,7 @@
         <v>0.0</v>
       </c>
       <c r="H392" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="393">
@@ -13398,7 +13398,7 @@
         <v>920</v>
       </c>
       <c r="F407" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -13450,7 +13450,7 @@
         <v>921</v>
       </c>
       <c r="F409" t="n">
-        <v>934.0</v>
+        <v>935.0</v>
       </c>
       <c r="G409" t="n">
         <v>5.0</v>
@@ -13788,7 +13788,7 @@
         <v>921</v>
       </c>
       <c r="F422" t="n">
-        <v>516.0</v>
+        <v>517.0</v>
       </c>
       <c r="G422" t="n">
         <v>2.0</v>
@@ -14438,7 +14438,7 @@
         <v>920</v>
       </c>
       <c r="F447" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14776,7 +14776,7 @@
         <v>921</v>
       </c>
       <c r="F460" t="n">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="G460" t="n">
         <v>0.0</v>
@@ -15172,7 +15172,7 @@
         <v>0.0</v>
       </c>
       <c r="H475" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="476">
@@ -15244,7 +15244,7 @@
         <v>920</v>
       </c>
       <c r="F478" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G478" t="n">
         <v>0.0</v>
@@ -16310,7 +16310,7 @@
         <v>920</v>
       </c>
       <c r="F519" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G519" t="n">
         <v>0.0</v>
@@ -16830,7 +16830,7 @@
         <v>920</v>
       </c>
       <c r="F539" t="n">
-        <v>328.0</v>
+        <v>332.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -17194,7 +17194,7 @@
         <v>920</v>
       </c>
       <c r="F553" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -17356,7 +17356,7 @@
         <v>6.0</v>
       </c>
       <c r="H559" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="560">
@@ -17792,7 +17792,7 @@
         <v>921</v>
       </c>
       <c r="F576" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
       <c r="G576" t="n">
         <v>1.0</v>
@@ -18416,7 +18416,7 @@
         <v>921</v>
       </c>
       <c r="F600" t="n">
-        <v>749.0</v>
+        <v>750.0</v>
       </c>
       <c r="G600" t="n">
         <v>2.0</v>
@@ -19878,7 +19878,7 @@
         <v>2.0</v>
       </c>
       <c r="H656" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="657">
@@ -20314,7 +20314,7 @@
         <v>920</v>
       </c>
       <c r="F673" t="n">
-        <v>394.0</v>
+        <v>395.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -20548,7 +20548,7 @@
         <v>921</v>
       </c>
       <c r="F682" t="n">
-        <v>2266.0</v>
+        <v>2269.0</v>
       </c>
       <c r="G682" t="n">
         <v>44.0</v>
@@ -22134,7 +22134,7 @@
         <v>920</v>
       </c>
       <c r="F743" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G743" t="n">
         <v>0.0</v>
@@ -22238,7 +22238,7 @@
         <v>920</v>
       </c>
       <c r="F747" t="n">
-        <v>513.0</v>
+        <v>514.0</v>
       </c>
       <c r="G747" t="n">
         <v>1.0</v>
@@ -22680,7 +22680,7 @@
         <v>921</v>
       </c>
       <c r="F764" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="G764" t="n">
         <v>0.0</v>
@@ -23304,7 +23304,7 @@
         <v>920</v>
       </c>
       <c r="F788" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G788" t="n">
         <v>0.0</v>
@@ -24162,7 +24162,7 @@
         <v>920</v>
       </c>
       <c r="F821" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="G821" t="n">
         <v>0.0</v>
@@ -24448,7 +24448,7 @@
         <v>920</v>
       </c>
       <c r="F832" t="n">
-        <v>314.0</v>
+        <v>315.0</v>
       </c>
       <c r="G832" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2868,7 +2868,7 @@
         <v>920</v>
       </c>
       <c r="F2" t="n">
-        <v>506.0</v>
+        <v>510.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -3258,7 +3258,7 @@
         <v>921</v>
       </c>
       <c r="F17" t="n">
-        <v>396.0</v>
+        <v>399.0</v>
       </c>
       <c r="G17" t="n">
         <v>3.0</v>
@@ -3284,7 +3284,7 @@
         <v>921</v>
       </c>
       <c r="F18" t="n">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="G18" t="n">
         <v>9.0</v>
@@ -3310,7 +3310,7 @@
         <v>920</v>
       </c>
       <c r="F19" t="n">
-        <v>346.0</v>
+        <v>348.0</v>
       </c>
       <c r="G19" t="n">
         <v>1.0</v>
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>580.0</v>
+        <v>579.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -4090,7 +4090,7 @@
         <v>921</v>
       </c>
       <c r="F49" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -4402,7 +4402,7 @@
         <v>921</v>
       </c>
       <c r="F61" t="n">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -4740,7 +4740,7 @@
         <v>921</v>
       </c>
       <c r="F74" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -6248,7 +6248,7 @@
         <v>920</v>
       </c>
       <c r="F132" t="n">
-        <v>356.0</v>
+        <v>358.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -6404,7 +6404,7 @@
         <v>921</v>
       </c>
       <c r="F138" t="n">
-        <v>443.0</v>
+        <v>446.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -7028,7 +7028,7 @@
         <v>921</v>
       </c>
       <c r="F162" t="n">
-        <v>414.0</v>
+        <v>415.0</v>
       </c>
       <c r="G162" t="n">
         <v>1.0</v>
@@ -7470,13 +7470,13 @@
         <v>921</v>
       </c>
       <c r="F179" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
       </c>
       <c r="H179" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="180">
@@ -7626,7 +7626,7 @@
         <v>921</v>
       </c>
       <c r="F185" t="n">
-        <v>597.0</v>
+        <v>599.0</v>
       </c>
       <c r="G185" t="n">
         <v>1.0</v>
@@ -7964,7 +7964,7 @@
         <v>921</v>
       </c>
       <c r="F198" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -8380,7 +8380,7 @@
         <v>921</v>
       </c>
       <c r="F214" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G214" t="n">
         <v>0.0</v>
@@ -8458,7 +8458,7 @@
         <v>921</v>
       </c>
       <c r="F217" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G217" t="n">
         <v>0.0</v>
@@ -8672,7 +8672,7 @@
         <v>0.0</v>
       </c>
       <c r="H225" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="226">
@@ -8718,7 +8718,7 @@
         <v>921</v>
       </c>
       <c r="F227" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="G227" t="n">
         <v>0.0</v>
@@ -8770,7 +8770,7 @@
         <v>920</v>
       </c>
       <c r="F229" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
       <c r="G229" t="n">
         <v>0.0</v>
@@ -8900,7 +8900,7 @@
         <v>920</v>
       </c>
       <c r="F234" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="G234" t="n">
         <v>1.0</v>
@@ -10746,7 +10746,7 @@
         <v>920</v>
       </c>
       <c r="F305" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G305" t="n">
         <v>0.0</v>
@@ -11763,7 +11763,7 @@
         <v>78.0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H344" t="n">
         <v>0.0</v>
@@ -12878,7 +12878,7 @@
         <v>921</v>
       </c>
       <c r="F387" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="G387" t="n">
         <v>1.0</v>
@@ -13580,7 +13580,7 @@
         <v>921</v>
       </c>
       <c r="F414" t="n">
-        <v>431.0</v>
+        <v>436.0</v>
       </c>
       <c r="G414" t="n">
         <v>4.0</v>
@@ -13638,7 +13638,7 @@
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="417">
@@ -14126,7 +14126,7 @@
         <v>921</v>
       </c>
       <c r="F435" t="n">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="G435" t="n">
         <v>0.0</v>
@@ -14360,7 +14360,7 @@
         <v>921</v>
       </c>
       <c r="F444" t="n">
-        <v>361.0</v>
+        <v>365.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
@@ -15010,7 +15010,7 @@
         <v>921</v>
       </c>
       <c r="F469" t="n">
-        <v>113.0</v>
+        <v>120.0</v>
       </c>
       <c r="G469" t="n">
         <v>0.0</v>
@@ -15426,7 +15426,7 @@
         <v>921</v>
       </c>
       <c r="F485" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
@@ -16362,7 +16362,7 @@
         <v>920</v>
       </c>
       <c r="F521" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G521" t="n">
         <v>0.0</v>
@@ -16388,7 +16388,7 @@
         <v>921</v>
       </c>
       <c r="F522" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -17350,13 +17350,13 @@
         <v>921</v>
       </c>
       <c r="F559" t="n">
-        <v>266.0</v>
+        <v>272.0</v>
       </c>
       <c r="G559" t="n">
         <v>6.0</v>
       </c>
       <c r="H559" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="560">
@@ -18286,7 +18286,7 @@
         <v>921</v>
       </c>
       <c r="F595" t="n">
-        <v>494.0</v>
+        <v>495.0</v>
       </c>
       <c r="G595" t="n">
         <v>3.0</v>
@@ -18832,7 +18832,7 @@
         <v>921</v>
       </c>
       <c r="F616" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -19586,7 +19586,7 @@
         <v>920</v>
       </c>
       <c r="F645" t="n">
-        <v>213.0</v>
+        <v>216.0</v>
       </c>
       <c r="G645" t="n">
         <v>1.0</v>
@@ -19690,7 +19690,7 @@
         <v>920</v>
       </c>
       <c r="F649" t="n">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
       <c r="G649" t="n">
         <v>0.0</v>
@@ -20106,7 +20106,7 @@
         <v>921</v>
       </c>
       <c r="F665" t="n">
-        <v>495.0</v>
+        <v>498.0</v>
       </c>
       <c r="G665" t="n">
         <v>1.0</v>
@@ -20502,7 +20502,7 @@
         <v>0.0</v>
       </c>
       <c r="H680" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="681">
@@ -21302,7 +21302,7 @@
         <v>921</v>
       </c>
       <c r="F711" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21510,13 +21510,13 @@
         <v>921</v>
       </c>
       <c r="F719" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>42.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="720">
@@ -21646,7 +21646,7 @@
         <v>0.0</v>
       </c>
       <c r="H724" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="725">
@@ -22862,7 +22862,7 @@
         <v>921</v>
       </c>
       <c r="F771" t="n">
-        <v>274.0</v>
+        <v>276.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>
@@ -23411,7 +23411,7 @@
         <v>244.0</v>
       </c>
       <c r="G792" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H792" t="n">
         <v>3.0</v>
@@ -25182,7 +25182,7 @@
         <v>0.0</v>
       </c>
       <c r="H860" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="861">
@@ -25884,7 +25884,7 @@
         <v>0.0</v>
       </c>
       <c r="H887" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="888">
@@ -26193,7 +26193,7 @@
         <v>52.0</v>
       </c>
       <c r="G899" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H899" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4148,7 +4148,7 @@
         <v>0.0</v>
       </c>
       <c r="H51" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="52">
@@ -4324,7 +4324,7 @@
         <v>920</v>
       </c>
       <c r="F58" t="n">
-        <v>252.0</v>
+        <v>255.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -4428,7 +4428,7 @@
         <v>920</v>
       </c>
       <c r="F62" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -5032,7 +5032,7 @@
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="86">
@@ -5390,7 +5390,7 @@
         <v>921</v>
       </c>
       <c r="F99" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>
@@ -5442,7 +5442,7 @@
         <v>921</v>
       </c>
       <c r="F101" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5936,7 +5936,7 @@
         <v>920</v>
       </c>
       <c r="F120" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G120" t="n">
         <v>0.0</v>
@@ -6846,7 +6846,7 @@
         <v>921</v>
       </c>
       <c r="F155" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -7548,7 +7548,7 @@
         <v>921</v>
       </c>
       <c r="F182" t="n">
-        <v>129.0</v>
+        <v>132.0</v>
       </c>
       <c r="G182" t="n">
         <v>1.0</v>
@@ -8672,7 +8672,7 @@
         <v>0.0</v>
       </c>
       <c r="H225" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="226">
@@ -8900,7 +8900,7 @@
         <v>920</v>
       </c>
       <c r="F234" t="n">
-        <v>522.0</v>
+        <v>539.0</v>
       </c>
       <c r="G234" t="n">
         <v>1.0</v>
@@ -9368,7 +9368,7 @@
         <v>920</v>
       </c>
       <c r="F252" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G252" t="n">
         <v>0.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>976.0</v>
+        <v>981.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -11006,7 +11006,7 @@
         <v>920</v>
       </c>
       <c r="F315" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="G315" t="n">
         <v>0.0</v>
@@ -12234,7 +12234,7 @@
         <v>0.0</v>
       </c>
       <c r="H362" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="363">
@@ -13144,7 +13144,7 @@
         <v>0.0</v>
       </c>
       <c r="H397" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="398">
@@ -13372,7 +13372,7 @@
         <v>921</v>
       </c>
       <c r="F406" t="n">
-        <v>108.0</v>
+        <v>113.0</v>
       </c>
       <c r="G406" t="n">
         <v>2.0</v>
@@ -15166,7 +15166,7 @@
         <v>921</v>
       </c>
       <c r="F475" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="G475" t="n">
         <v>0.0</v>
@@ -15712,7 +15712,7 @@
         <v>921</v>
       </c>
       <c r="F496" t="n">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15790,7 +15790,7 @@
         <v>920</v>
       </c>
       <c r="F499" t="n">
-        <v>157.0</v>
+        <v>163.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -16726,7 +16726,7 @@
         <v>921</v>
       </c>
       <c r="F535" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G535" t="n">
         <v>7.0</v>
@@ -16778,7 +16778,7 @@
         <v>921</v>
       </c>
       <c r="F537" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -17194,7 +17194,7 @@
         <v>920</v>
       </c>
       <c r="F553" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -17324,7 +17324,7 @@
         <v>920</v>
       </c>
       <c r="F558" t="n">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
@@ -18364,7 +18364,7 @@
         <v>921</v>
       </c>
       <c r="F598" t="n">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="G598" t="n">
         <v>1.0</v>
@@ -19248,7 +19248,7 @@
         <v>921</v>
       </c>
       <c r="F632" t="n">
-        <v>216.0</v>
+        <v>218.0</v>
       </c>
       <c r="G632" t="n">
         <v>0.0</v>
@@ -19742,7 +19742,7 @@
         <v>921</v>
       </c>
       <c r="F651" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -20548,13 +20548,13 @@
         <v>921</v>
       </c>
       <c r="F682" t="n">
-        <v>2269.0</v>
+        <v>2272.0</v>
       </c>
       <c r="G682" t="n">
         <v>44.0</v>
       </c>
       <c r="H682" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
     </row>
     <row r="683">
@@ -21380,7 +21380,7 @@
         <v>921</v>
       </c>
       <c r="F714" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G714" t="n">
         <v>0.0</v>
@@ -21458,7 +21458,7 @@
         <v>921</v>
       </c>
       <c r="F717" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G717" t="n">
         <v>0.0</v>
@@ -22056,7 +22056,7 @@
         <v>921</v>
       </c>
       <c r="F740" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G740" t="n">
         <v>1.0</v>
@@ -22082,7 +22082,7 @@
         <v>921</v>
       </c>
       <c r="F741" t="n">
-        <v>339.0</v>
+        <v>341.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -23356,7 +23356,7 @@
         <v>921</v>
       </c>
       <c r="F790" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G790" t="n">
         <v>0.0</v>
@@ -24942,7 +24942,7 @@
         <v>921</v>
       </c>
       <c r="F851" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G851" t="n">
         <v>0.0</v>
@@ -25182,7 +25182,7 @@
         <v>0.0</v>
       </c>
       <c r="H860" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="861">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2946,7 +2946,7 @@
         <v>921</v>
       </c>
       <c r="F5" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -2998,7 +2998,7 @@
         <v>921</v>
       </c>
       <c r="F7" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -3258,7 +3258,7 @@
         <v>921</v>
       </c>
       <c r="F17" t="n">
-        <v>399.0</v>
+        <v>401.0</v>
       </c>
       <c r="G17" t="n">
         <v>3.0</v>
@@ -3492,7 +3492,7 @@
         <v>920</v>
       </c>
       <c r="F26" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -3830,7 +3830,7 @@
         <v>920</v>
       </c>
       <c r="F39" t="n">
-        <v>579.0</v>
+        <v>586.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -4012,7 +4012,7 @@
         <v>920</v>
       </c>
       <c r="F46" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="G46" t="n">
         <v>1.0</v>
@@ -4038,7 +4038,7 @@
         <v>921</v>
       </c>
       <c r="F47" t="n">
-        <v>433.0</v>
+        <v>439.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -4194,7 +4194,7 @@
         <v>920</v>
       </c>
       <c r="F53" t="n">
-        <v>288.0</v>
+        <v>291.0</v>
       </c>
       <c r="G53" t="n">
         <v>1.0</v>
@@ -4454,7 +4454,7 @@
         <v>921</v>
       </c>
       <c r="F63" t="n">
-        <v>278.0</v>
+        <v>283.0</v>
       </c>
       <c r="G63" t="n">
         <v>1.0</v>
@@ -5000,7 +5000,7 @@
         <v>921</v>
       </c>
       <c r="F84" t="n">
-        <v>162.0</v>
+        <v>167.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -6248,7 +6248,7 @@
         <v>920</v>
       </c>
       <c r="F132" t="n">
-        <v>358.0</v>
+        <v>360.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -6950,7 +6950,7 @@
         <v>921</v>
       </c>
       <c r="F159" t="n">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
       <c r="G159" t="n">
         <v>1.0</v>
@@ -7054,7 +7054,7 @@
         <v>920</v>
       </c>
       <c r="F163" t="n">
-        <v>296.0</v>
+        <v>298.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -7418,7 +7418,7 @@
         <v>921</v>
       </c>
       <c r="F177" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7626,7 +7626,7 @@
         <v>921</v>
       </c>
       <c r="F185" t="n">
-        <v>599.0</v>
+        <v>600.0</v>
       </c>
       <c r="G185" t="n">
         <v>1.0</v>
@@ -7990,7 +7990,7 @@
         <v>920</v>
       </c>
       <c r="F199" t="n">
-        <v>115.0</v>
+        <v>127.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -8458,7 +8458,7 @@
         <v>921</v>
       </c>
       <c r="F217" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G217" t="n">
         <v>0.0</v>
@@ -8510,7 +8510,7 @@
         <v>921</v>
       </c>
       <c r="F219" t="n">
-        <v>291.0</v>
+        <v>293.0</v>
       </c>
       <c r="G219" t="n">
         <v>0.0</v>
@@ -8718,7 +8718,7 @@
         <v>921</v>
       </c>
       <c r="F227" t="n">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
       <c r="G227" t="n">
         <v>0.0</v>
@@ -9654,7 +9654,7 @@
         <v>921</v>
       </c>
       <c r="F263" t="n">
-        <v>981.0</v>
+        <v>982.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -10434,7 +10434,7 @@
         <v>921</v>
       </c>
       <c r="F293" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
       <c r="G293" t="n">
         <v>0.0</v>
@@ -11318,7 +11318,7 @@
         <v>921</v>
       </c>
       <c r="F327" t="n">
-        <v>125.0</v>
+        <v>128.0</v>
       </c>
       <c r="G327" t="n">
         <v>0.0</v>
@@ -11630,7 +11630,7 @@
         <v>921</v>
       </c>
       <c r="F339" t="n">
-        <v>914.0</v>
+        <v>921.0</v>
       </c>
       <c r="G339" t="n">
         <v>16.0</v>
@@ -12098,7 +12098,7 @@
         <v>921</v>
       </c>
       <c r="F357" t="n">
-        <v>223.0</v>
+        <v>225.0</v>
       </c>
       <c r="G357" t="n">
         <v>0.0</v>
@@ -13138,7 +13138,7 @@
         <v>921</v>
       </c>
       <c r="F397" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G397" t="n">
         <v>0.0</v>
@@ -13580,7 +13580,7 @@
         <v>921</v>
       </c>
       <c r="F414" t="n">
-        <v>436.0</v>
+        <v>443.0</v>
       </c>
       <c r="G414" t="n">
         <v>4.0</v>
@@ -13892,7 +13892,7 @@
         <v>921</v>
       </c>
       <c r="F426" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G426" t="n">
         <v>0.0</v>
@@ -15296,7 +15296,7 @@
         <v>920</v>
       </c>
       <c r="F480" t="n">
-        <v>502.0</v>
+        <v>503.0</v>
       </c>
       <c r="G480" t="n">
         <v>1.0</v>
@@ -15426,7 +15426,7 @@
         <v>921</v>
       </c>
       <c r="F485" t="n">
-        <v>79.0</v>
+        <v>86.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
@@ -16388,7 +16388,7 @@
         <v>921</v>
       </c>
       <c r="F522" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -17194,7 +17194,7 @@
         <v>920</v>
       </c>
       <c r="F553" t="n">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -17350,7 +17350,7 @@
         <v>921</v>
       </c>
       <c r="F559" t="n">
-        <v>272.0</v>
+        <v>274.0</v>
       </c>
       <c r="G559" t="n">
         <v>6.0</v>
@@ -18416,7 +18416,7 @@
         <v>921</v>
       </c>
       <c r="F600" t="n">
-        <v>750.0</v>
+        <v>751.0</v>
       </c>
       <c r="G600" t="n">
         <v>2.0</v>
@@ -18832,7 +18832,7 @@
         <v>921</v>
       </c>
       <c r="F616" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -19014,7 +19014,7 @@
         <v>921</v>
       </c>
       <c r="F623" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="G623" t="n">
         <v>7.0</v>
@@ -19326,7 +19326,7 @@
         <v>921</v>
       </c>
       <c r="F635" t="n">
-        <v>92.0</v>
+        <v>96.0</v>
       </c>
       <c r="G635" t="n">
         <v>0.0</v>
@@ -19586,7 +19586,7 @@
         <v>920</v>
       </c>
       <c r="F645" t="n">
-        <v>216.0</v>
+        <v>219.0</v>
       </c>
       <c r="G645" t="n">
         <v>1.0</v>
@@ -20106,7 +20106,7 @@
         <v>921</v>
       </c>
       <c r="F665" t="n">
-        <v>498.0</v>
+        <v>502.0</v>
       </c>
       <c r="G665" t="n">
         <v>1.0</v>
@@ -21042,7 +21042,7 @@
         <v>921</v>
       </c>
       <c r="F701" t="n">
-        <v>392.0</v>
+        <v>393.0</v>
       </c>
       <c r="G701" t="n">
         <v>9.0</v>
@@ -21614,7 +21614,7 @@
         <v>921</v>
       </c>
       <c r="F723" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -22082,7 +22082,7 @@
         <v>921</v>
       </c>
       <c r="F741" t="n">
-        <v>341.0</v>
+        <v>342.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22862,7 +22862,7 @@
         <v>921</v>
       </c>
       <c r="F771" t="n">
-        <v>276.0</v>
+        <v>278.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>
@@ -23486,7 +23486,7 @@
         <v>920</v>
       </c>
       <c r="F795" t="n">
-        <v>343.0</v>
+        <v>344.0</v>
       </c>
       <c r="G795" t="n">
         <v>0.0</v>
@@ -25072,7 +25072,7 @@
         <v>921</v>
       </c>
       <c r="F856" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G856" t="n">
         <v>0.0</v>
@@ -25878,7 +25878,7 @@
         <v>921</v>
       </c>
       <c r="F887" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G887" t="n">
         <v>0.0</v>
@@ -25982,7 +25982,7 @@
         <v>921</v>
       </c>
       <c r="F891" t="n">
-        <v>211.0</v>
+        <v>213.0</v>
       </c>
       <c r="G891" t="n">
         <v>1.0</v>
@@ -26086,7 +26086,7 @@
         <v>921</v>
       </c>
       <c r="F895" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G895" t="n">
         <v>6.0</v>
@@ -26112,7 +26112,7 @@
         <v>920</v>
       </c>
       <c r="F896" t="n">
-        <v>96.0</v>
+        <v>100.0</v>
       </c>
       <c r="G896" t="n">
         <v>0.0</v>
@@ -26138,7 +26138,7 @@
         <v>920</v>
       </c>
       <c r="F897" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G897" t="n">
         <v>0.0</v>
@@ -26476,7 +26476,7 @@
         <v>920</v>
       </c>
       <c r="F910" t="n">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
       <c r="G910" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -26242,7 +26242,7 @@
         <v>921</v>
       </c>
       <c r="F901" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G901" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2907,7 +2907,7 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>439.0</v>
+        <v>440.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3765,7 +3765,7 @@
         <v>674</v>
       </c>
       <c r="F65" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -5611,7 +5611,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>600.0</v>
+        <v>601.0</v>
       </c>
       <c r="G136" t="n">
         <v>1.0</v>
@@ -5897,7 +5897,7 @@
         <v>673</v>
       </c>
       <c r="F147" t="n">
-        <v>193.0</v>
+        <v>195.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -6755,7 +6755,7 @@
         <v>674</v>
       </c>
       <c r="F180" t="n">
-        <v>608.0</v>
+        <v>610.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -7067,7 +7067,7 @@
         <v>674</v>
       </c>
       <c r="F192" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G192" t="n">
         <v>0.0</v>
@@ -9303,7 +9303,7 @@
         <v>673</v>
       </c>
       <c r="F278" t="n">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
       <c r="G278" t="n">
         <v>6.0</v>
@@ -9381,7 +9381,7 @@
         <v>673</v>
       </c>
       <c r="F281" t="n">
-        <v>233.0</v>
+        <v>235.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -9641,7 +9641,7 @@
         <v>674</v>
       </c>
       <c r="F291" t="n">
-        <v>376.0</v>
+        <v>378.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -9901,7 +9901,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>446.0</v>
+        <v>449.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10655,7 +10655,7 @@
         <v>674</v>
       </c>
       <c r="F330" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G330" t="n">
         <v>0.0</v>
@@ -11097,7 +11097,7 @@
         <v>673</v>
       </c>
       <c r="F347" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="G347" t="n">
         <v>2.0</v>
@@ -11747,7 +11747,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -13203,7 +13203,7 @@
         <v>673</v>
       </c>
       <c r="F428" t="n">
-        <v>177.0</v>
+        <v>181.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -14425,7 +14425,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>504.0</v>
+        <v>510.0</v>
       </c>
       <c r="G475" t="n">
         <v>1.0</v>
@@ -15127,7 +15127,7 @@
         <v>674</v>
       </c>
       <c r="F502" t="n">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15465,7 +15465,7 @@
         <v>674</v>
       </c>
       <c r="F515" t="n">
-        <v>304.0</v>
+        <v>305.0</v>
       </c>
       <c r="G515" t="n">
         <v>1.0</v>
@@ -15543,7 +15543,7 @@
         <v>674</v>
       </c>
       <c r="F518" t="n">
-        <v>239.0</v>
+        <v>241.0</v>
       </c>
       <c r="G518" t="n">
         <v>0.0</v>
@@ -16011,7 +16011,7 @@
         <v>674</v>
       </c>
       <c r="F536" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G536" t="n">
         <v>0.0</v>
@@ -16037,7 +16037,7 @@
         <v>674</v>
       </c>
       <c r="F537" t="n">
-        <v>514.0</v>
+        <v>516.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16271,7 +16271,7 @@
         <v>674</v>
       </c>
       <c r="F546" t="n">
-        <v>248.0</v>
+        <v>250.0</v>
       </c>
       <c r="G546" t="n">
         <v>0.0</v>
@@ -17441,7 +17441,7 @@
         <v>674</v>
       </c>
       <c r="F591" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -17675,7 +17675,7 @@
         <v>674</v>
       </c>
       <c r="F600" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -17805,7 +17805,7 @@
         <v>674</v>
       </c>
       <c r="F605" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
       <c r="G605" t="n">
         <v>0.0</v>
@@ -18949,10 +18949,10 @@
         <v>673</v>
       </c>
       <c r="F649" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G649" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H649" t="n">
         <v>2.0</v>
@@ -19417,7 +19417,7 @@
         <v>674</v>
       </c>
       <c r="F667" t="n">
-        <v>319.0</v>
+        <v>322.0</v>
       </c>
       <c r="G667" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3343" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="675">
   <si>
     <t>Regione</t>
   </si>
@@ -2231,7 +2231,7 @@
         <v>673</v>
       </c>
       <c r="F6" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -2517,7 +2517,7 @@
         <v>673</v>
       </c>
       <c r="F17" t="n">
-        <v>243.0</v>
+        <v>246.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -4441,7 +4441,7 @@
         <v>673</v>
       </c>
       <c r="F91" t="n">
-        <v>119.0</v>
+        <v>126.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -4811,7 +4811,7 @@
         <v>0.0</v>
       </c>
       <c r="H105" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="106">
@@ -5455,7 +5455,7 @@
         <v>673</v>
       </c>
       <c r="F130" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -5819,7 +5819,7 @@
         <v>674</v>
       </c>
       <c r="F144" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -6417,13 +6417,13 @@
         <v>673</v>
       </c>
       <c r="F167" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
       </c>
       <c r="H167" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="168">
@@ -6521,7 +6521,7 @@
         <v>674</v>
       </c>
       <c r="F171" t="n">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -6625,7 +6625,7 @@
         <v>674</v>
       </c>
       <c r="F175" t="n">
-        <v>539.0</v>
+        <v>544.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -7899,7 +7899,7 @@
         <v>673</v>
       </c>
       <c r="F224" t="n">
-        <v>389.0</v>
+        <v>393.0</v>
       </c>
       <c r="G224" t="n">
         <v>1.0</v>
@@ -8633,7 +8633,7 @@
         <v>0.0</v>
       </c>
       <c r="H252" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="253">
@@ -8653,7 +8653,7 @@
         <v>673</v>
       </c>
       <c r="F253" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G253" t="n">
         <v>0.0</v>
@@ -8867,7 +8867,7 @@
         <v>0.0</v>
       </c>
       <c r="H261" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="262">
@@ -9017,7 +9017,7 @@
         <v>673</v>
       </c>
       <c r="F267" t="n">
-        <v>103.0</v>
+        <v>106.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9095,7 +9095,7 @@
         <v>674</v>
       </c>
       <c r="F270" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G270" t="n">
         <v>0.0</v>
@@ -9667,7 +9667,7 @@
         <v>674</v>
       </c>
       <c r="F292" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -9959,7 +9959,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="304">
@@ -10213,7 +10213,7 @@
         <v>673</v>
       </c>
       <c r="F313" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G313" t="n">
         <v>1.0</v>
@@ -10915,7 +10915,7 @@
         <v>673</v>
       </c>
       <c r="F340" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G340" t="n">
         <v>0.0</v>
@@ -11877,7 +11877,7 @@
         <v>673</v>
       </c>
       <c r="F377" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12059,7 +12059,7 @@
         <v>673</v>
       </c>
       <c r="F384" t="n">
-        <v>424.0</v>
+        <v>426.0</v>
       </c>
       <c r="G384" t="n">
         <v>1.0</v>
@@ -12553,7 +12553,7 @@
         <v>673</v>
       </c>
       <c r="F403" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G403" t="n">
         <v>0.0</v>
@@ -12605,7 +12605,7 @@
         <v>673</v>
       </c>
       <c r="F405" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="G405" t="n">
         <v>0.0</v>
@@ -13177,7 +13177,7 @@
         <v>673</v>
       </c>
       <c r="F427" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="G427" t="n">
         <v>1.0</v>
@@ -14035,7 +14035,7 @@
         <v>673</v>
       </c>
       <c r="F460" t="n">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
       <c r="G460" t="n">
         <v>0.0</v>
@@ -14061,7 +14061,7 @@
         <v>673</v>
       </c>
       <c r="F461" t="n">
-        <v>529.0</v>
+        <v>530.0</v>
       </c>
       <c r="G461" t="n">
         <v>0.0</v>
@@ -14717,7 +14717,7 @@
         <v>0.0</v>
       </c>
       <c r="H486" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="487">
@@ -15517,13 +15517,13 @@
         <v>673</v>
       </c>
       <c r="F517" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
       </c>
       <c r="H517" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="518">
@@ -15725,7 +15725,7 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
       <c r="G525" t="n">
         <v>1.0</v>
@@ -16089,24 +16089,24 @@
         <v>673</v>
       </c>
       <c r="F539" t="n">
-        <v>254.0</v>
+        <v>0.0</v>
       </c>
       <c r="G539" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H539" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B540" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C540" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D540" t="s">
         <v>672</v>
@@ -16115,24 +16115,24 @@
         <v>673</v>
       </c>
       <c r="F540" t="n">
-        <v>1.0</v>
+        <v>254.0</v>
       </c>
       <c r="G540" t="n">
         <v>1.0</v>
       </c>
       <c r="H540" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B541" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C541" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D541" t="s">
         <v>672</v>
@@ -16141,24 +16141,24 @@
         <v>673</v>
       </c>
       <c r="F541" t="n">
-        <v>54.0</v>
+        <v>1.0</v>
       </c>
       <c r="G541" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H541" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B542" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C542" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D542" t="s">
         <v>672</v>
@@ -16167,24 +16167,24 @@
         <v>673</v>
       </c>
       <c r="F542" t="n">
-        <v>42.0</v>
+        <v>54.0</v>
       </c>
       <c r="G542" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H542" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B543" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C543" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D543" t="s">
         <v>672</v>
@@ -16193,39 +16193,39 @@
         <v>673</v>
       </c>
       <c r="F543" t="n">
-        <v>26.0</v>
+        <v>42.0</v>
       </c>
       <c r="G543" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H543" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B544" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C544" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D544" t="s">
         <v>672</v>
       </c>
       <c r="E544" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F544" t="n">
-        <v>111.0</v>
+        <v>26.0</v>
       </c>
       <c r="G544" t="n">
         <v>0.0</v>
       </c>
       <c r="H544" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -16236,7 +16236,7 @@
         <v>21</v>
       </c>
       <c r="C545" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D545" t="s">
         <v>672</v>
@@ -16245,7 +16245,7 @@
         <v>674</v>
       </c>
       <c r="F545" t="n">
-        <v>6.0</v>
+        <v>111.0</v>
       </c>
       <c r="G545" t="n">
         <v>0.0</v>
@@ -16262,7 +16262,7 @@
         <v>21</v>
       </c>
       <c r="C546" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D546" t="s">
         <v>672</v>
@@ -16271,7 +16271,7 @@
         <v>674</v>
       </c>
       <c r="F546" t="n">
-        <v>250.0</v>
+        <v>6.0</v>
       </c>
       <c r="G546" t="n">
         <v>0.0</v>
@@ -16282,13 +16282,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B547" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C547" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D547" t="s">
         <v>672</v>
@@ -16297,7 +16297,7 @@
         <v>674</v>
       </c>
       <c r="F547" t="n">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16308,13 +16308,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B548" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C548" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D548" t="s">
         <v>672</v>
@@ -16323,7 +16323,7 @@
         <v>674</v>
       </c>
       <c r="F548" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G548" t="n">
         <v>0.0</v>
@@ -16334,25 +16334,25 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B549" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C549" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D549" t="s">
         <v>672</v>
       </c>
       <c r="E549" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F549" t="n">
-        <v>59.0</v>
+        <v>17.0</v>
       </c>
       <c r="G549" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H549" t="n">
         <v>0.0</v>
@@ -16360,25 +16360,25 @@
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B550" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C550" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D550" t="s">
         <v>672</v>
       </c>
       <c r="E550" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F550" t="n">
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="G550" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H550" t="n">
         <v>0.0</v>
@@ -16389,10 +16389,10 @@
         <v>9</v>
       </c>
       <c r="B551" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C551" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D551" t="s">
         <v>672</v>
@@ -16401,7 +16401,7 @@
         <v>674</v>
       </c>
       <c r="F551" t="n">
-        <v>53.0</v>
+        <v>60.0</v>
       </c>
       <c r="G551" t="n">
         <v>0.0</v>
@@ -16412,13 +16412,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B552" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C552" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D552" t="s">
         <v>672</v>
@@ -16427,7 +16427,7 @@
         <v>674</v>
       </c>
       <c r="F552" t="n">
-        <v>278.0</v>
+        <v>53.0</v>
       </c>
       <c r="G552" t="n">
         <v>0.0</v>
@@ -16438,22 +16438,22 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B553" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C553" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D553" t="s">
         <v>672</v>
       </c>
       <c r="E553" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F553" t="n">
-        <v>10.0</v>
+        <v>278.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16467,19 +16467,19 @@
         <v>9</v>
       </c>
       <c r="B554" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C554" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D554" t="s">
         <v>672</v>
       </c>
       <c r="E554" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F554" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G554" t="n">
         <v>0.0</v>
@@ -16490,13 +16490,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B555" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C555" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D555" t="s">
         <v>672</v>
@@ -16505,7 +16505,7 @@
         <v>674</v>
       </c>
       <c r="F555" t="n">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="G555" t="n">
         <v>0.0</v>
@@ -16519,19 +16519,19 @@
         <v>11</v>
       </c>
       <c r="B556" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C556" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D556" t="s">
         <v>672</v>
       </c>
       <c r="E556" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F556" t="n">
-        <v>85.0</v>
+        <v>70.0</v>
       </c>
       <c r="G556" t="n">
         <v>0.0</v>
@@ -16542,13 +16542,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B557" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C557" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D557" t="s">
         <v>672</v>
@@ -16557,39 +16557,39 @@
         <v>673</v>
       </c>
       <c r="F557" t="n">
-        <v>49.0</v>
+        <v>85.0</v>
       </c>
       <c r="G557" t="n">
         <v>0.0</v>
       </c>
       <c r="H557" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B558" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C558" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D558" t="s">
         <v>672</v>
       </c>
       <c r="E558" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F558" t="n">
-        <v>15.0</v>
+        <v>49.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
       </c>
       <c r="H558" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="559">
@@ -16600,22 +16600,22 @@
         <v>21</v>
       </c>
       <c r="C559" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D559" t="s">
         <v>672</v>
       </c>
       <c r="E559" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F559" t="n">
-        <v>77.0</v>
+        <v>15.0</v>
       </c>
       <c r="G559" t="n">
         <v>0.0</v>
       </c>
       <c r="H559" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="560">
@@ -16626,42 +16626,42 @@
         <v>21</v>
       </c>
       <c r="C560" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D560" t="s">
         <v>672</v>
       </c>
       <c r="E560" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F560" t="n">
-        <v>0.0</v>
+        <v>77.0</v>
       </c>
       <c r="G560" t="n">
         <v>0.0</v>
       </c>
       <c r="H560" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B561" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C561" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D561" t="s">
         <v>672</v>
       </c>
       <c r="E561" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F561" t="n">
-        <v>274.0</v>
+        <v>0.0</v>
       </c>
       <c r="G561" t="n">
         <v>0.0</v>
@@ -16672,22 +16672,22 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B562" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C562" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D562" t="s">
         <v>672</v>
       </c>
       <c r="E562" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F562" t="n">
-        <v>87.0</v>
+        <v>275.0</v>
       </c>
       <c r="G562" t="n">
         <v>0.0</v>
@@ -16701,19 +16701,19 @@
         <v>11</v>
       </c>
       <c r="B563" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C563" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D563" t="s">
         <v>672</v>
       </c>
       <c r="E563" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F563" t="n">
-        <v>30.0</v>
+        <v>87.0</v>
       </c>
       <c r="G563" t="n">
         <v>0.0</v>
@@ -16724,13 +16724,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B564" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C564" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D564" t="s">
         <v>672</v>
@@ -16739,7 +16739,7 @@
         <v>673</v>
       </c>
       <c r="F564" t="n">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
       <c r="G564" t="n">
         <v>0.0</v>
@@ -16750,13 +16750,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B565" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C565" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D565" t="s">
         <v>672</v>
@@ -16765,24 +16765,24 @@
         <v>673</v>
       </c>
       <c r="F565" t="n">
-        <v>177.0</v>
+        <v>24.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
       </c>
       <c r="H565" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B566" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C566" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D566" t="s">
         <v>672</v>
@@ -16791,24 +16791,24 @@
         <v>673</v>
       </c>
       <c r="F566" t="n">
+        <v>177.0</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H566" t="n">
         <v>9.0</v>
-      </c>
-      <c r="G566" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H566" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B567" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C567" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D567" t="s">
         <v>672</v>
@@ -16817,24 +16817,24 @@
         <v>673</v>
       </c>
       <c r="F567" t="n">
-        <v>345.0</v>
+        <v>9.0</v>
       </c>
       <c r="G567" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H567" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B568" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C568" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D568" t="s">
         <v>672</v>
@@ -16843,39 +16843,39 @@
         <v>673</v>
       </c>
       <c r="F568" t="n">
-        <v>248.0</v>
+        <v>345.0</v>
       </c>
       <c r="G568" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="H568" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B569" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C569" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D569" t="s">
         <v>672</v>
       </c>
       <c r="E569" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F569" t="n">
-        <v>14.0</v>
+        <v>248.0</v>
       </c>
       <c r="G569" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H569" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="570">
@@ -16883,71 +16883,71 @@
         <v>9</v>
       </c>
       <c r="B570" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C570" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D570" t="s">
         <v>672</v>
       </c>
       <c r="E570" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F570" t="n">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="G570" t="n">
         <v>0.0</v>
       </c>
       <c r="H570" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B571" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C571" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D571" t="s">
         <v>672</v>
       </c>
       <c r="E571" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F571" t="n">
-        <v>344.0</v>
+        <v>19.0</v>
       </c>
       <c r="G571" t="n">
         <v>0.0</v>
       </c>
       <c r="H571" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B572" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C572" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D572" t="s">
         <v>672</v>
       </c>
       <c r="E572" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F572" t="n">
-        <v>10.0</v>
+        <v>344.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -16958,13 +16958,13 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B573" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C573" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D573" t="s">
         <v>672</v>
@@ -16973,24 +16973,24 @@
         <v>673</v>
       </c>
       <c r="F573" t="n">
-        <v>31.0</v>
+        <v>10.0</v>
       </c>
       <c r="G573" t="n">
         <v>0.0</v>
       </c>
       <c r="H573" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B574" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C574" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D574" t="s">
         <v>672</v>
@@ -16999,76 +16999,76 @@
         <v>673</v>
       </c>
       <c r="F574" t="n">
-        <v>210.0</v>
+        <v>31.0</v>
       </c>
       <c r="G574" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H574" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B575" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C575" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D575" t="s">
         <v>672</v>
       </c>
       <c r="E575" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F575" t="n">
-        <v>6.0</v>
+        <v>210.0</v>
       </c>
       <c r="G575" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H575" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B576" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C576" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D576" t="s">
         <v>672</v>
       </c>
       <c r="E576" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F576" t="n">
-        <v>213.0</v>
+        <v>6.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
       </c>
       <c r="H576" t="n">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B577" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C577" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D577" t="s">
         <v>672</v>
@@ -17077,24 +17077,24 @@
         <v>673</v>
       </c>
       <c r="F577" t="n">
-        <v>60.0</v>
+        <v>213.0</v>
       </c>
       <c r="G577" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H577" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B578" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C578" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D578" t="s">
         <v>672</v>
@@ -17103,13 +17103,13 @@
         <v>673</v>
       </c>
       <c r="F578" t="n">
-        <v>16.0</v>
+        <v>60.0</v>
       </c>
       <c r="G578" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H578" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="579">
@@ -17120,7 +17120,7 @@
         <v>15</v>
       </c>
       <c r="C579" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D579" t="s">
         <v>672</v>
@@ -17129,13 +17129,13 @@
         <v>673</v>
       </c>
       <c r="F579" t="n">
-        <v>93.0</v>
+        <v>16.0</v>
       </c>
       <c r="G579" t="n">
         <v>0.0</v>
       </c>
       <c r="H579" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="580">
@@ -17146,7 +17146,7 @@
         <v>15</v>
       </c>
       <c r="C580" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D580" t="s">
         <v>672</v>
@@ -17155,59 +17155,59 @@
         <v>673</v>
       </c>
       <c r="F580" t="n">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="G580" t="n">
         <v>0.0</v>
       </c>
       <c r="H580" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B581" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C581" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D581" t="s">
         <v>672</v>
       </c>
       <c r="E581" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F581" t="n">
-        <v>35.0</v>
+        <v>90.0</v>
       </c>
       <c r="G581" t="n">
         <v>0.0</v>
       </c>
       <c r="H581" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B582" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C582" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D582" t="s">
         <v>672</v>
       </c>
       <c r="E582" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F582" t="n">
-        <v>121.0</v>
+        <v>35.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -17218,13 +17218,13 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B583" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C583" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D583" t="s">
         <v>672</v>
@@ -17233,39 +17233,39 @@
         <v>673</v>
       </c>
       <c r="F583" t="n">
-        <v>23.0</v>
+        <v>121.0</v>
       </c>
       <c r="G583" t="n">
         <v>0.0</v>
       </c>
       <c r="H583" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B584" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C584" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D584" t="s">
         <v>672</v>
       </c>
       <c r="E584" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F584" t="n">
-        <v>332.0</v>
+        <v>23.0</v>
       </c>
       <c r="G584" t="n">
         <v>0.0</v>
       </c>
       <c r="H584" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="585">
@@ -17276,85 +17276,85 @@
         <v>15</v>
       </c>
       <c r="C585" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D585" t="s">
         <v>672</v>
       </c>
       <c r="E585" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F585" t="n">
-        <v>24.0</v>
+        <v>332.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
       </c>
       <c r="H585" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B586" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C586" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D586" t="s">
         <v>672</v>
       </c>
       <c r="E586" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F586" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="G586" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H586" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G586" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H586" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B587" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C587" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D587" t="s">
         <v>672</v>
       </c>
       <c r="E587" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F587" t="n">
-        <v>212.0</v>
+        <v>1.0</v>
       </c>
       <c r="G587" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H587" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B588" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C588" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D588" t="s">
         <v>672</v>
@@ -17363,13 +17363,13 @@
         <v>673</v>
       </c>
       <c r="F588" t="n">
-        <v>12.0</v>
+        <v>212.0</v>
       </c>
       <c r="G588" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H588" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="589">
@@ -17377,19 +17377,19 @@
         <v>9</v>
       </c>
       <c r="B589" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C589" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D589" t="s">
         <v>672</v>
       </c>
       <c r="E589" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F589" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -17400,22 +17400,22 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B590" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C590" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D590" t="s">
         <v>672</v>
       </c>
       <c r="E590" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F590" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G590" t="n">
         <v>0.0</v>
@@ -17432,48 +17432,48 @@
         <v>21</v>
       </c>
       <c r="C591" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D591" t="s">
         <v>672</v>
       </c>
       <c r="E591" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F591" t="n">
-        <v>66.0</v>
+        <v>4.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
       </c>
       <c r="H591" t="n">
-        <v>1851.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B592" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C592" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D592" t="s">
         <v>672</v>
       </c>
       <c r="E592" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F592" t="n">
-        <v>41.0</v>
+        <v>66.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
       </c>
       <c r="H592" t="n">
-        <v>0.0</v>
+        <v>1851.0</v>
       </c>
     </row>
     <row r="593">
@@ -17481,10 +17481,10 @@
         <v>8</v>
       </c>
       <c r="B593" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C593" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D593" t="s">
         <v>672</v>
@@ -17493,24 +17493,24 @@
         <v>673</v>
       </c>
       <c r="F593" t="n">
-        <v>18.0</v>
+        <v>41.0</v>
       </c>
       <c r="G593" t="n">
         <v>0.0</v>
       </c>
       <c r="H593" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B594" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C594" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D594" t="s">
         <v>672</v>
@@ -17519,24 +17519,24 @@
         <v>673</v>
       </c>
       <c r="F594" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
       </c>
       <c r="H594" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B595" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C595" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D595" t="s">
         <v>672</v>
@@ -17545,13 +17545,13 @@
         <v>673</v>
       </c>
       <c r="F595" t="n">
-        <v>67.0</v>
+        <v>10.0</v>
       </c>
       <c r="G595" t="n">
         <v>0.0</v>
       </c>
       <c r="H595" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="596">
@@ -17559,10 +17559,10 @@
         <v>9</v>
       </c>
       <c r="B596" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C596" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D596" t="s">
         <v>672</v>
@@ -17571,13 +17571,13 @@
         <v>673</v>
       </c>
       <c r="F596" t="n">
-        <v>230.0</v>
+        <v>67.0</v>
       </c>
       <c r="G596" t="n">
         <v>0.0</v>
       </c>
       <c r="H596" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="597">
@@ -17585,10 +17585,10 @@
         <v>9</v>
       </c>
       <c r="B597" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C597" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D597" t="s">
         <v>672</v>
@@ -17597,7 +17597,7 @@
         <v>673</v>
       </c>
       <c r="F597" t="n">
-        <v>15.0</v>
+        <v>231.0</v>
       </c>
       <c r="G597" t="n">
         <v>0.0</v>
@@ -17614,7 +17614,7 @@
         <v>18</v>
       </c>
       <c r="C598" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D598" t="s">
         <v>672</v>
@@ -17623,7 +17623,7 @@
         <v>673</v>
       </c>
       <c r="F598" t="n">
-        <v>78.0</v>
+        <v>15.0</v>
       </c>
       <c r="G598" t="n">
         <v>0.0</v>
@@ -17637,10 +17637,10 @@
         <v>9</v>
       </c>
       <c r="B599" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C599" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D599" t="s">
         <v>672</v>
@@ -17649,62 +17649,62 @@
         <v>673</v>
       </c>
       <c r="F599" t="n">
-        <v>66.0</v>
+        <v>78.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
       </c>
       <c r="H599" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B600" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C600" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D600" t="s">
         <v>672</v>
       </c>
       <c r="E600" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F600" t="n">
-        <v>21.0</v>
+        <v>66.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
       </c>
       <c r="H600" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B601" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C601" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D601" t="s">
         <v>672</v>
       </c>
       <c r="E601" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F601" t="n">
-        <v>93.0</v>
+        <v>21.0</v>
       </c>
       <c r="G601" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H601" t="n">
         <v>0.0</v>
@@ -17718,7 +17718,7 @@
         <v>19</v>
       </c>
       <c r="C602" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D602" t="s">
         <v>672</v>
@@ -17727,102 +17727,102 @@
         <v>673</v>
       </c>
       <c r="F602" t="n">
-        <v>142.0</v>
+        <v>93.0</v>
       </c>
       <c r="G602" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H602" t="n">
-        <v>77.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B603" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C603" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D603" t="s">
         <v>672</v>
       </c>
       <c r="E603" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F603" t="n">
-        <v>35.0</v>
+        <v>142.0</v>
       </c>
       <c r="G603" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H603" t="n">
-        <v>1.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B604" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C604" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D604" t="s">
         <v>672</v>
       </c>
       <c r="E604" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F604" t="n">
-        <v>147.0</v>
+        <v>35.0</v>
       </c>
       <c r="G604" t="n">
         <v>0.0</v>
       </c>
       <c r="H604" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B605" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C605" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D605" t="s">
         <v>672</v>
       </c>
       <c r="E605" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F605" t="n">
-        <v>171.0</v>
+        <v>150.0</v>
       </c>
       <c r="G605" t="n">
         <v>0.0</v>
       </c>
       <c r="H605" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B606" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C606" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D606" t="s">
         <v>672</v>
@@ -17831,33 +17831,33 @@
         <v>674</v>
       </c>
       <c r="F606" t="n">
-        <v>18.0</v>
+        <v>171.0</v>
       </c>
       <c r="G606" t="n">
         <v>0.0</v>
       </c>
       <c r="H606" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B607" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C607" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D607" t="s">
         <v>672</v>
       </c>
       <c r="E607" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F607" t="n">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="G607" t="n">
         <v>0.0</v>
@@ -17874,7 +17874,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D608" t="s">
         <v>672</v>
@@ -17883,39 +17883,39 @@
         <v>673</v>
       </c>
       <c r="F608" t="n">
-        <v>54.0</v>
+        <v>5.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
       </c>
       <c r="H608" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B609" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C609" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D609" t="s">
         <v>672</v>
       </c>
       <c r="E609" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F609" t="n">
-        <v>79.0</v>
+        <v>54.0</v>
       </c>
       <c r="G609" t="n">
         <v>0.0</v>
       </c>
       <c r="H609" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="610">
@@ -17926,33 +17926,33 @@
         <v>15</v>
       </c>
       <c r="C610" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D610" t="s">
         <v>672</v>
       </c>
       <c r="E610" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F610" t="n">
-        <v>176.0</v>
+        <v>79.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
       </c>
       <c r="H610" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B611" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C611" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D611" t="s">
         <v>672</v>
@@ -17961,24 +17961,24 @@
         <v>673</v>
       </c>
       <c r="F611" t="n">
-        <v>6.0</v>
+        <v>176.0</v>
       </c>
       <c r="G611" t="n">
         <v>0.0</v>
       </c>
       <c r="H611" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B612" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C612" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D612" t="s">
         <v>672</v>
@@ -17987,24 +17987,24 @@
         <v>673</v>
       </c>
       <c r="F612" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G612" t="n">
         <v>0.0</v>
       </c>
       <c r="H612" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B613" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C613" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D613" t="s">
         <v>672</v>
@@ -18013,7 +18013,7 @@
         <v>673</v>
       </c>
       <c r="F613" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="G613" t="n">
         <v>0.0</v>
@@ -18024,13 +18024,13 @@
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B614" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C614" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D614" t="s">
         <v>672</v>
@@ -18039,7 +18039,7 @@
         <v>673</v>
       </c>
       <c r="F614" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="G614" t="n">
         <v>0.0</v>
@@ -18056,16 +18056,16 @@
         <v>21</v>
       </c>
       <c r="C615" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D615" t="s">
         <v>672</v>
       </c>
       <c r="E615" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F615" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -18082,137 +18082,137 @@
         <v>21</v>
       </c>
       <c r="C616" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D616" t="s">
         <v>672</v>
       </c>
       <c r="E616" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F616" t="n">
-        <v>132.0</v>
+        <v>3.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
       </c>
       <c r="H616" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B617" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C617" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D617" t="s">
         <v>672</v>
       </c>
       <c r="E617" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F617" t="n">
-        <v>17.0</v>
+        <v>132.0</v>
       </c>
       <c r="G617" t="n">
         <v>0.0</v>
       </c>
       <c r="H617" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B618" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C618" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D618" t="s">
         <v>672</v>
       </c>
       <c r="E618" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F618" t="n">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G618" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H618" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B619" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C619" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D619" t="s">
         <v>672</v>
       </c>
       <c r="E619" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F619" t="n">
-        <v>41.0</v>
+        <v>19.0</v>
       </c>
       <c r="G619" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H619" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B620" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C620" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D620" t="s">
         <v>672</v>
       </c>
       <c r="E620" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F620" t="n">
-        <v>24.0</v>
+        <v>41.0</v>
       </c>
       <c r="G620" t="n">
         <v>0.0</v>
       </c>
       <c r="H620" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B621" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C621" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D621" t="s">
         <v>672</v>
@@ -18221,24 +18221,24 @@
         <v>673</v>
       </c>
       <c r="F621" t="n">
-        <v>94.0</v>
+        <v>24.0</v>
       </c>
       <c r="G621" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H621" t="n">
-        <v>44.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B622" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C622" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D622" t="s">
         <v>672</v>
@@ -18247,24 +18247,24 @@
         <v>673</v>
       </c>
       <c r="F622" t="n">
-        <v>4.0</v>
+        <v>94.0</v>
       </c>
       <c r="G622" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H622" t="n">
-        <v>0.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B623" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C623" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D623" t="s">
         <v>672</v>
@@ -18273,7 +18273,7 @@
         <v>673</v>
       </c>
       <c r="F623" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G623" t="n">
         <v>0.0</v>
@@ -18284,22 +18284,22 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B624" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C624" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D624" t="s">
         <v>672</v>
       </c>
       <c r="E624" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F624" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G624" t="n">
         <v>0.0</v>
@@ -18310,19 +18310,19 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B625" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C625" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D625" t="s">
         <v>672</v>
       </c>
       <c r="E625" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F625" t="n">
         <v>0.0</v>
@@ -18331,7 +18331,7 @@
         <v>0.0</v>
       </c>
       <c r="H625" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="626">
@@ -18351,24 +18351,24 @@
         <v>673</v>
       </c>
       <c r="F626" t="n">
-        <v>55.0</v>
+        <v>0.0</v>
       </c>
       <c r="G626" t="n">
         <v>0.0</v>
       </c>
       <c r="H626" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B627" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C627" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D627" t="s">
         <v>672</v>
@@ -18377,24 +18377,24 @@
         <v>673</v>
       </c>
       <c r="F627" t="n">
-        <v>99.0</v>
+        <v>55.0</v>
       </c>
       <c r="G627" t="n">
         <v>0.0</v>
       </c>
       <c r="H627" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B628" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C628" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D628" t="s">
         <v>672</v>
@@ -18403,13 +18403,13 @@
         <v>673</v>
       </c>
       <c r="F628" t="n">
-        <v>0.0</v>
+        <v>99.0</v>
       </c>
       <c r="G628" t="n">
         <v>0.0</v>
       </c>
       <c r="H628" t="n">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="629">
@@ -18429,24 +18429,24 @@
         <v>673</v>
       </c>
       <c r="F629" t="n">
-        <v>169.0</v>
+        <v>0.0</v>
       </c>
       <c r="G629" t="n">
         <v>0.0</v>
       </c>
       <c r="H629" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B630" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C630" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D630" t="s">
         <v>672</v>
@@ -18455,13 +18455,13 @@
         <v>673</v>
       </c>
       <c r="F630" t="n">
-        <v>0.0</v>
+        <v>169.0</v>
       </c>
       <c r="G630" t="n">
         <v>0.0</v>
       </c>
       <c r="H630" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="631">
@@ -18481,13 +18481,13 @@
         <v>673</v>
       </c>
       <c r="F631" t="n">
-        <v>213.0</v>
+        <v>0.0</v>
       </c>
       <c r="G631" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H631" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="632">
@@ -18498,7 +18498,7 @@
         <v>25</v>
       </c>
       <c r="C632" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D632" t="s">
         <v>672</v>
@@ -18507,10 +18507,10 @@
         <v>673</v>
       </c>
       <c r="F632" t="n">
-        <v>55.0</v>
+        <v>213.0</v>
       </c>
       <c r="G632" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H632" t="n">
         <v>0.0</v>
@@ -18524,7 +18524,7 @@
         <v>25</v>
       </c>
       <c r="C633" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D633" t="s">
         <v>672</v>
@@ -18533,7 +18533,7 @@
         <v>673</v>
       </c>
       <c r="F633" t="n">
-        <v>85.0</v>
+        <v>55.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -18550,7 +18550,7 @@
         <v>25</v>
       </c>
       <c r="C634" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D634" t="s">
         <v>672</v>
@@ -18559,13 +18559,13 @@
         <v>673</v>
       </c>
       <c r="F634" t="n">
-        <v>0.0</v>
+        <v>85.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="635">
@@ -18585,13 +18585,13 @@
         <v>673</v>
       </c>
       <c r="F635" t="n">
-        <v>109.0</v>
+        <v>0.0</v>
       </c>
       <c r="G635" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H635" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="636">
@@ -18602,19 +18602,19 @@
         <v>25</v>
       </c>
       <c r="C636" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D636" t="s">
         <v>672</v>
       </c>
       <c r="E636" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F636" t="n">
-        <v>60.0</v>
+        <v>109.0</v>
       </c>
       <c r="G636" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H636" t="n">
         <v>0.0</v>
@@ -18628,7 +18628,7 @@
         <v>25</v>
       </c>
       <c r="C637" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D637" t="s">
         <v>672</v>
@@ -18637,7 +18637,7 @@
         <v>674</v>
       </c>
       <c r="F637" t="n">
-        <v>104.0</v>
+        <v>60.0</v>
       </c>
       <c r="G637" t="n">
         <v>0.0</v>
@@ -18654,16 +18654,16 @@
         <v>25</v>
       </c>
       <c r="C638" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D638" t="s">
         <v>672</v>
       </c>
       <c r="E638" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F638" t="n">
-        <v>100.0</v>
+        <v>104.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -18680,7 +18680,7 @@
         <v>25</v>
       </c>
       <c r="C639" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D639" t="s">
         <v>672</v>
@@ -18689,7 +18689,7 @@
         <v>673</v>
       </c>
       <c r="F639" t="n">
-        <v>42.0</v>
+        <v>100.0</v>
       </c>
       <c r="G639" t="n">
         <v>0.0</v>
@@ -18706,16 +18706,16 @@
         <v>25</v>
       </c>
       <c r="C640" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D640" t="s">
         <v>672</v>
       </c>
       <c r="E640" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F640" t="n">
-        <v>85.0</v>
+        <v>42.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -18732,7 +18732,7 @@
         <v>25</v>
       </c>
       <c r="C641" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D641" t="s">
         <v>672</v>
@@ -18741,7 +18741,7 @@
         <v>674</v>
       </c>
       <c r="F641" t="n">
-        <v>103.0</v>
+        <v>85.0</v>
       </c>
       <c r="G641" t="n">
         <v>0.0</v>
@@ -18758,7 +18758,7 @@
         <v>25</v>
       </c>
       <c r="C642" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D642" t="s">
         <v>672</v>
@@ -18767,7 +18767,7 @@
         <v>674</v>
       </c>
       <c r="F642" t="n">
-        <v>41.0</v>
+        <v>103.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -18784,7 +18784,7 @@
         <v>25</v>
       </c>
       <c r="C643" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D643" t="s">
         <v>672</v>
@@ -18793,7 +18793,7 @@
         <v>674</v>
       </c>
       <c r="F643" t="n">
-        <v>102.0</v>
+        <v>41.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -18810,7 +18810,7 @@
         <v>25</v>
       </c>
       <c r="C644" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D644" t="s">
         <v>672</v>
@@ -18819,7 +18819,7 @@
         <v>674</v>
       </c>
       <c r="F644" t="n">
-        <v>42.0</v>
+        <v>102.0</v>
       </c>
       <c r="G644" t="n">
         <v>0.0</v>
@@ -18836,7 +18836,7 @@
         <v>25</v>
       </c>
       <c r="C645" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D645" t="s">
         <v>672</v>
@@ -18845,7 +18845,7 @@
         <v>674</v>
       </c>
       <c r="F645" t="n">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="G645" t="n">
         <v>0.0</v>
@@ -18862,7 +18862,7 @@
         <v>25</v>
       </c>
       <c r="C646" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D646" t="s">
         <v>672</v>
@@ -18888,7 +18888,7 @@
         <v>25</v>
       </c>
       <c r="C647" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D647" t="s">
         <v>672</v>
@@ -18897,7 +18897,7 @@
         <v>674</v>
       </c>
       <c r="F647" t="n">
-        <v>66.0</v>
+        <v>43.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -18911,19 +18911,19 @@
         <v>8</v>
       </c>
       <c r="B648" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C648" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D648" t="s">
         <v>672</v>
       </c>
       <c r="E648" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F648" t="n">
-        <v>12.0</v>
+        <v>66.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -18940,7 +18940,7 @@
         <v>26</v>
       </c>
       <c r="C649" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D649" t="s">
         <v>672</v>
@@ -18949,13 +18949,13 @@
         <v>673</v>
       </c>
       <c r="F649" t="n">
-        <v>54.0</v>
+        <v>12.0</v>
       </c>
       <c r="G649" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H649" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="650">
@@ -18966,7 +18966,7 @@
         <v>26</v>
       </c>
       <c r="C650" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D650" t="s">
         <v>672</v>
@@ -18975,24 +18975,24 @@
         <v>673</v>
       </c>
       <c r="F650" t="n">
-        <v>4.0</v>
+        <v>54.0</v>
       </c>
       <c r="G650" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H650" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B651" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C651" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D651" t="s">
         <v>672</v>
@@ -19001,7 +19001,7 @@
         <v>673</v>
       </c>
       <c r="F651" t="n">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -19012,22 +19012,22 @@
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B652" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C652" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D652" t="s">
         <v>672</v>
       </c>
       <c r="E652" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F652" t="n">
-        <v>50.0</v>
+        <v>19.0</v>
       </c>
       <c r="G652" t="n">
         <v>0.0</v>
@@ -19044,7 +19044,7 @@
         <v>26</v>
       </c>
       <c r="C653" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D653" t="s">
         <v>672</v>
@@ -19053,7 +19053,7 @@
         <v>674</v>
       </c>
       <c r="F653" t="n">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="G653" t="n">
         <v>0.0</v>
@@ -19070,7 +19070,7 @@
         <v>26</v>
       </c>
       <c r="C654" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D654" t="s">
         <v>672</v>
@@ -19079,7 +19079,7 @@
         <v>674</v>
       </c>
       <c r="F654" t="n">
-        <v>82.0</v>
+        <v>40.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19096,7 +19096,7 @@
         <v>26</v>
       </c>
       <c r="C655" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D655" t="s">
         <v>672</v>
@@ -19105,7 +19105,7 @@
         <v>674</v>
       </c>
       <c r="F655" t="n">
-        <v>99.0</v>
+        <v>82.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19122,7 +19122,7 @@
         <v>26</v>
       </c>
       <c r="C656" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D656" t="s">
         <v>672</v>
@@ -19131,7 +19131,7 @@
         <v>674</v>
       </c>
       <c r="F656" t="n">
-        <v>41.0</v>
+        <v>99.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19148,16 +19148,16 @@
         <v>26</v>
       </c>
       <c r="C657" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D657" t="s">
         <v>672</v>
       </c>
       <c r="E657" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F657" t="n">
-        <v>86.0</v>
+        <v>41.0</v>
       </c>
       <c r="G657" t="n">
         <v>0.0</v>
@@ -19174,16 +19174,16 @@
         <v>26</v>
       </c>
       <c r="C658" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D658" t="s">
         <v>672</v>
       </c>
       <c r="E658" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F658" t="n">
-        <v>34.0</v>
+        <v>86.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -19200,16 +19200,16 @@
         <v>26</v>
       </c>
       <c r="C659" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D659" t="s">
         <v>672</v>
       </c>
       <c r="E659" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F659" t="n">
-        <v>12.0</v>
+        <v>34.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -19226,7 +19226,7 @@
         <v>26</v>
       </c>
       <c r="C660" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D660" t="s">
         <v>672</v>
@@ -19235,7 +19235,7 @@
         <v>673</v>
       </c>
       <c r="F660" t="n">
-        <v>87.0</v>
+        <v>12.0</v>
       </c>
       <c r="G660" t="n">
         <v>0.0</v>
@@ -19252,16 +19252,16 @@
         <v>26</v>
       </c>
       <c r="C661" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D661" t="s">
         <v>672</v>
       </c>
       <c r="E661" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F661" t="n">
-        <v>47.0</v>
+        <v>87.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19278,16 +19278,16 @@
         <v>26</v>
       </c>
       <c r="C662" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D662" t="s">
         <v>672</v>
       </c>
       <c r="E662" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F662" t="n">
-        <v>82.0</v>
+        <v>47.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19298,25 +19298,25 @@
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B663" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C663" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D663" t="s">
         <v>672</v>
       </c>
       <c r="E663" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F663" t="n">
-        <v>144.0</v>
+        <v>82.0</v>
       </c>
       <c r="G663" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H663" t="n">
         <v>0.0</v>
@@ -19324,13 +19324,13 @@
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B664" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C664" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D664" t="s">
         <v>672</v>
@@ -19339,10 +19339,10 @@
         <v>674</v>
       </c>
       <c r="F664" t="n">
-        <v>31.0</v>
+        <v>144.0</v>
       </c>
       <c r="G664" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H664" t="n">
         <v>0.0</v>
@@ -19353,22 +19353,22 @@
         <v>8</v>
       </c>
       <c r="B665" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C665" t="s">
-        <v>14</v>
+        <v>670</v>
       </c>
       <c r="D665" t="s">
         <v>672</v>
       </c>
       <c r="E665" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F665" t="n">
-        <v>269.0</v>
+        <v>31.0</v>
       </c>
       <c r="G665" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H665" t="n">
         <v>0.0</v>
@@ -19382,19 +19382,19 @@
         <v>14</v>
       </c>
       <c r="C666" t="s">
-        <v>671</v>
+        <v>14</v>
       </c>
       <c r="D666" t="s">
         <v>672</v>
       </c>
       <c r="E666" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F666" t="n">
-        <v>123.0</v>
+        <v>269.0</v>
       </c>
       <c r="G666" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H666" t="n">
         <v>0.0</v>
@@ -19408,7 +19408,7 @@
         <v>14</v>
       </c>
       <c r="C667" t="s">
-        <v>14</v>
+        <v>671</v>
       </c>
       <c r="D667" t="s">
         <v>672</v>
@@ -19417,10 +19417,10 @@
         <v>674</v>
       </c>
       <c r="F667" t="n">
-        <v>322.0</v>
+        <v>123.0</v>
       </c>
       <c r="G667" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H667" t="n">
         <v>0.0</v>
@@ -19434,21 +19434,47 @@
         <v>14</v>
       </c>
       <c r="C668" t="s">
+        <v>14</v>
+      </c>
+      <c r="D668" t="s">
+        <v>672</v>
+      </c>
+      <c r="E668" t="s">
+        <v>674</v>
+      </c>
+      <c r="F668" t="n">
+        <v>322.0</v>
+      </c>
+      <c r="G668" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H668" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="s">
+        <v>8</v>
+      </c>
+      <c r="B669" t="s">
+        <v>14</v>
+      </c>
+      <c r="C669" t="s">
         <v>671</v>
       </c>
-      <c r="D668" t="s">
-        <v>672</v>
-      </c>
-      <c r="E668" t="s">
-        <v>673</v>
-      </c>
-      <c r="F668" t="n">
+      <c r="D669" t="s">
+        <v>672</v>
+      </c>
+      <c r="E669" t="s">
+        <v>673</v>
+      </c>
+      <c r="F669" t="n">
         <v>175.0</v>
       </c>
-      <c r="G668" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H668" t="n">
+      <c r="G669" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H669" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2127,7 +2127,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>510.0</v>
+        <v>514.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -2439,7 +2439,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>401.0</v>
+        <v>403.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -2491,7 +2491,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>348.0</v>
+        <v>350.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2933,7 +2933,7 @@
         <v>673</v>
       </c>
       <c r="F33" t="n">
-        <v>144.0</v>
+        <v>150.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3765,7 +3765,7 @@
         <v>674</v>
       </c>
       <c r="F65" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -4649,7 +4649,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>448.0</v>
+        <v>450.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -5117,7 +5117,7 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>415.0</v>
+        <v>416.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5611,7 +5611,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>601.0</v>
+        <v>606.0</v>
       </c>
       <c r="G136" t="n">
         <v>1.0</v>
@@ -6261,7 +6261,7 @@
         <v>674</v>
       </c>
       <c r="F161" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6313,7 +6313,7 @@
         <v>674</v>
       </c>
       <c r="F163" t="n">
-        <v>293.0</v>
+        <v>294.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6469,7 +6469,7 @@
         <v>673</v>
       </c>
       <c r="F169" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -7093,7 +7093,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>982.0</v>
+        <v>983.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -7145,7 +7145,7 @@
         <v>674</v>
       </c>
       <c r="F195" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G195" t="n">
         <v>0.0</v>
@@ -7249,7 +7249,7 @@
         <v>674</v>
       </c>
       <c r="F199" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -8529,7 +8529,7 @@
         <v>16.0</v>
       </c>
       <c r="H248" t="n">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="249">
@@ -9069,7 +9069,7 @@
         <v>673</v>
       </c>
       <c r="F269" t="n">
-        <v>491.0</v>
+        <v>492.0</v>
       </c>
       <c r="G269" t="n">
         <v>0.0</v>
@@ -9488,7 +9488,7 @@
         <v>206.0</v>
       </c>
       <c r="G285" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H285" t="n">
         <v>0.0</v>
@@ -9641,7 +9641,7 @@
         <v>674</v>
       </c>
       <c r="F291" t="n">
-        <v>378.0</v>
+        <v>380.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -9745,7 +9745,7 @@
         <v>673</v>
       </c>
       <c r="F295" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G295" t="n">
         <v>2.0</v>
@@ -9901,7 +9901,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>449.0</v>
+        <v>451.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10135,7 +10135,7 @@
         <v>673</v>
       </c>
       <c r="F310" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G310" t="n">
         <v>1.0</v>
@@ -10447,7 +10447,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>365.0</v>
+        <v>371.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11981,7 +11981,7 @@
         <v>673</v>
       </c>
       <c r="F381" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G381" t="n">
         <v>1.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>495.0</v>
+        <v>498.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13547,7 +13547,7 @@
         <v>0.0</v>
       </c>
       <c r="H441" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="442">
@@ -13775,7 +13775,7 @@
         <v>673</v>
       </c>
       <c r="F450" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G450" t="n">
         <v>0.0</v>
@@ -14425,7 +14425,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>510.0</v>
+        <v>511.0</v>
       </c>
       <c r="G475" t="n">
         <v>1.0</v>
@@ -15751,7 +15751,7 @@
         <v>673</v>
       </c>
       <c r="F526" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="G526" t="n">
         <v>0.0</v>
@@ -16375,7 +16375,7 @@
         <v>673</v>
       </c>
       <c r="F550" t="n">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
       <c r="G550" t="n">
         <v>1.0</v>
@@ -16453,7 +16453,7 @@
         <v>674</v>
       </c>
       <c r="F553" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16947,7 +16947,7 @@
         <v>674</v>
       </c>
       <c r="F572" t="n">
-        <v>344.0</v>
+        <v>347.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17285,7 +17285,7 @@
         <v>674</v>
       </c>
       <c r="F585" t="n">
-        <v>332.0</v>
+        <v>334.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17675,7 +17675,7 @@
         <v>673</v>
       </c>
       <c r="F600" t="n">
-        <v>66.0</v>
+        <v>73.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -17805,7 +17805,7 @@
         <v>673</v>
       </c>
       <c r="F605" t="n">
-        <v>150.0</v>
+        <v>153.0</v>
       </c>
       <c r="G605" t="n">
         <v>0.0</v>
@@ -18715,7 +18715,7 @@
         <v>673</v>
       </c>
       <c r="F640" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -19391,7 +19391,7 @@
         <v>673</v>
       </c>
       <c r="F666" t="n">
-        <v>269.0</v>
+        <v>271.0</v>
       </c>
       <c r="G666" t="n">
         <v>2.0</v>
@@ -19443,7 +19443,7 @@
         <v>674</v>
       </c>
       <c r="F668" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2569,7 +2569,7 @@
         <v>673</v>
       </c>
       <c r="F19" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G19" t="n">
         <v>1.0</v>
@@ -3141,7 +3141,7 @@
         <v>673</v>
       </c>
       <c r="F41" t="n">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -5975,7 +5975,7 @@
         <v>674</v>
       </c>
       <c r="F150" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -9303,7 +9303,7 @@
         <v>673</v>
       </c>
       <c r="F278" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G278" t="n">
         <v>6.0</v>
@@ -11019,7 +11019,7 @@
         <v>673</v>
       </c>
       <c r="F344" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="G344" t="n">
         <v>0.0</v>
@@ -12527,7 +12527,7 @@
         <v>673</v>
       </c>
       <c r="F402" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G402" t="n">
         <v>0.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>498.0</v>
+        <v>501.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -14763,13 +14763,13 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2272.0</v>
+        <v>2275.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
       </c>
       <c r="H488" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
     </row>
     <row r="489">
@@ -16849,7 +16849,7 @@
         <v>11.0</v>
       </c>
       <c r="H568" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="569">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3427,7 +3427,7 @@
         <v>673</v>
       </c>
       <c r="F52" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -12351,7 +12351,7 @@
         <v>6.0</v>
       </c>
       <c r="H395" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="396">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4363,7 +4363,7 @@
         <v>673</v>
       </c>
       <c r="F88" t="n">
-        <v>125.0</v>
+        <v>130.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -4701,7 +4701,7 @@
         <v>673</v>
       </c>
       <c r="F101" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -4753,7 +4753,7 @@
         <v>673</v>
       </c>
       <c r="F103" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -5403,7 +5403,7 @@
         <v>674</v>
       </c>
       <c r="F128" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -6209,7 +6209,7 @@
         <v>673</v>
       </c>
       <c r="F159" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G159" t="n">
         <v>0.0</v>
@@ -7093,7 +7093,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>983.0</v>
+        <v>984.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -7509,7 +7509,7 @@
         <v>674</v>
       </c>
       <c r="F209" t="n">
-        <v>204.0</v>
+        <v>205.0</v>
       </c>
       <c r="G209" t="n">
         <v>0.0</v>
@@ -7691,7 +7691,7 @@
         <v>673</v>
       </c>
       <c r="F216" t="n">
-        <v>257.0</v>
+        <v>259.0</v>
       </c>
       <c r="G216" t="n">
         <v>1.0</v>
@@ -7795,7 +7795,7 @@
         <v>674</v>
       </c>
       <c r="F220" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G220" t="n">
         <v>0.0</v>
@@ -8185,7 +8185,7 @@
         <v>673</v>
       </c>
       <c r="F235" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G235" t="n">
         <v>0.0</v>
@@ -9823,7 +9823,7 @@
         <v>673</v>
       </c>
       <c r="F298" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G298" t="n">
         <v>0.0</v>
@@ -9875,7 +9875,7 @@
         <v>674</v>
       </c>
       <c r="F300" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G300" t="n">
         <v>0.0</v>
@@ -11045,7 +11045,7 @@
         <v>674</v>
       </c>
       <c r="F345" t="n">
-        <v>503.0</v>
+        <v>504.0</v>
       </c>
       <c r="G345" t="n">
         <v>1.0</v>
@@ -11461,7 +11461,7 @@
         <v>674</v>
       </c>
       <c r="F361" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>501.0</v>
+        <v>510.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13203,7 +13203,7 @@
         <v>673</v>
       </c>
       <c r="F428" t="n">
-        <v>181.0</v>
+        <v>183.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -14009,7 +14009,7 @@
         <v>673</v>
       </c>
       <c r="F459" t="n">
-        <v>59.0</v>
+        <v>63.0</v>
       </c>
       <c r="G459" t="n">
         <v>0.0</v>
@@ -14477,7 +14477,7 @@
         <v>674</v>
       </c>
       <c r="F477" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>674</v>
       </c>
       <c r="F480" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G480" t="n">
         <v>0.0</v>
@@ -15725,7 +15725,7 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>400.0</v>
+        <v>401.0</v>
       </c>
       <c r="G525" t="n">
         <v>1.0</v>
@@ -16037,7 +16037,7 @@
         <v>674</v>
       </c>
       <c r="F537" t="n">
-        <v>516.0</v>
+        <v>520.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -17103,7 +17103,7 @@
         <v>673</v>
       </c>
       <c r="F578" t="n">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
       <c r="G578" t="n">
         <v>1.0</v>
@@ -17285,7 +17285,7 @@
         <v>674</v>
       </c>
       <c r="F585" t="n">
-        <v>334.0</v>
+        <v>336.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>403.0</v>
+        <v>406.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -2491,7 +2491,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>674</v>
       </c>
       <c r="F21" t="n">
-        <v>323.0</v>
+        <v>326.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2907,7 +2907,7 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>440.0</v>
+        <v>444.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3173,7 +3173,7 @@
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="43">
@@ -3401,7 +3401,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3765,7 +3765,7 @@
         <v>674</v>
       </c>
       <c r="F65" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3895,7 +3895,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>673</v>
       </c>
       <c r="F76" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="G76" t="n">
         <v>15.0</v>
@@ -4545,7 +4545,7 @@
         <v>674</v>
       </c>
       <c r="F95" t="n">
-        <v>363.0</v>
+        <v>366.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4649,7 +4649,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>450.0</v>
+        <v>453.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -4909,13 +4909,13 @@
         <v>673</v>
       </c>
       <c r="F109" t="n">
-        <v>232.0</v>
+        <v>234.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
       </c>
       <c r="H109" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="110">
@@ -5117,7 +5117,7 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>416.0</v>
+        <v>417.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5533,7 +5533,7 @@
         <v>673</v>
       </c>
       <c r="F133" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G133" t="n">
         <v>1.0</v>
@@ -5663,7 +5663,7 @@
         <v>673</v>
       </c>
       <c r="F138" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -5923,7 +5923,7 @@
         <v>674</v>
       </c>
       <c r="F148" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6261,7 +6261,7 @@
         <v>674</v>
       </c>
       <c r="F161" t="n">
-        <v>173.0</v>
+        <v>175.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6495,7 +6495,7 @@
         <v>674</v>
       </c>
       <c r="F170" t="n">
-        <v>457.0</v>
+        <v>460.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -7561,7 +7561,7 @@
         <v>673</v>
       </c>
       <c r="F211" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G211" t="n">
         <v>0.0</v>
@@ -8237,7 +8237,7 @@
         <v>673</v>
       </c>
       <c r="F237" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -8867,7 +8867,7 @@
         <v>0.0</v>
       </c>
       <c r="H261" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="262">
@@ -9049,7 +9049,7 @@
         <v>0.0</v>
       </c>
       <c r="H268" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="269">
@@ -9797,7 +9797,7 @@
         <v>673</v>
       </c>
       <c r="F297" t="n">
-        <v>935.0</v>
+        <v>938.0</v>
       </c>
       <c r="G297" t="n">
         <v>5.0</v>
@@ -9901,7 +9901,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>451.0</v>
+        <v>454.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -9959,7 +9959,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="304">
@@ -10447,7 +10447,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>371.0</v>
+        <v>372.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11077,7 +11077,7 @@
         <v>1.0</v>
       </c>
       <c r="H346" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="347">
@@ -11097,10 +11097,10 @@
         <v>673</v>
       </c>
       <c r="F347" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G347" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H347" t="n">
         <v>0.0</v>
@@ -11747,7 +11747,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -12085,7 +12085,7 @@
         <v>674</v>
       </c>
       <c r="F385" t="n">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12345,7 +12345,7 @@
         <v>673</v>
       </c>
       <c r="F395" t="n">
-        <v>276.0</v>
+        <v>281.0</v>
       </c>
       <c r="G395" t="n">
         <v>6.0</v>
@@ -12585,7 +12585,7 @@
         <v>0.0</v>
       </c>
       <c r="H404" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="405">
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>510.0</v>
+        <v>514.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -14113,7 +14113,7 @@
         <v>674</v>
       </c>
       <c r="F463" t="n">
-        <v>219.0</v>
+        <v>221.0</v>
       </c>
       <c r="G463" t="n">
         <v>1.0</v>
@@ -14425,7 +14425,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>511.0</v>
+        <v>518.0</v>
       </c>
       <c r="G475" t="n">
         <v>1.0</v>
@@ -15361,7 +15361,7 @@
         <v>674</v>
       </c>
       <c r="F511" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -16453,7 +16453,7 @@
         <v>674</v>
       </c>
       <c r="F553" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16869,7 +16869,7 @@
         <v>673</v>
       </c>
       <c r="F569" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G569" t="n">
         <v>1.0</v>
@@ -16947,7 +16947,7 @@
         <v>674</v>
       </c>
       <c r="F572" t="n">
-        <v>347.0</v>
+        <v>349.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17207,7 +17207,7 @@
         <v>674</v>
       </c>
       <c r="F582" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>674</v>
       </c>
       <c r="F620" t="n">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="G620" t="n">
         <v>0.0</v>
@@ -18435,7 +18435,7 @@
         <v>0.0</v>
       </c>
       <c r="H629" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="630">
@@ -18507,7 +18507,7 @@
         <v>673</v>
       </c>
       <c r="F632" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="G632" t="n">
         <v>1.0</v>
@@ -18663,7 +18663,7 @@
         <v>674</v>
       </c>
       <c r="F638" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -18689,7 +18689,7 @@
         <v>673</v>
       </c>
       <c r="F639" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G639" t="n">
         <v>0.0</v>
@@ -18715,7 +18715,7 @@
         <v>673</v>
       </c>
       <c r="F640" t="n">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -18741,7 +18741,7 @@
         <v>674</v>
       </c>
       <c r="F641" t="n">
-        <v>85.0</v>
+        <v>92.0</v>
       </c>
       <c r="G641" t="n">
         <v>0.0</v>
@@ -18767,7 +18767,7 @@
         <v>674</v>
       </c>
       <c r="F642" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>674</v>
       </c>
       <c r="F643" t="n">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -18897,7 +18897,7 @@
         <v>674</v>
       </c>
       <c r="F647" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -18978,7 +18978,7 @@
         <v>54.0</v>
       </c>
       <c r="G650" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H650" t="n">
         <v>2.0</v>
@@ -19131,7 +19131,7 @@
         <v>674</v>
       </c>
       <c r="F656" t="n">
-        <v>99.0</v>
+        <v>101.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19157,7 +19157,7 @@
         <v>674</v>
       </c>
       <c r="F657" t="n">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="G657" t="n">
         <v>0.0</v>
@@ -19209,7 +19209,7 @@
         <v>674</v>
       </c>
       <c r="F659" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -19365,7 +19365,7 @@
         <v>674</v>
       </c>
       <c r="F665" t="n">
-        <v>31.0</v>
+        <v>44.0</v>
       </c>
       <c r="G665" t="n">
         <v>0.0</v>
@@ -19469,7 +19469,7 @@
         <v>673</v>
       </c>
       <c r="F669" t="n">
-        <v>175.0</v>
+        <v>177.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2127,7 +2127,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>514.0</v>
+        <v>520.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -2179,7 +2179,7 @@
         <v>673</v>
       </c>
       <c r="F4" t="n">
-        <v>87.0</v>
+        <v>90.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -2439,7 +2439,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>406.0</v>
+        <v>415.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -2465,7 +2465,7 @@
         <v>673</v>
       </c>
       <c r="F15" t="n">
-        <v>232.0</v>
+        <v>234.0</v>
       </c>
       <c r="G15" t="n">
         <v>9.0</v>
@@ -2491,7 +2491,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>351.0</v>
+        <v>354.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2517,7 +2517,7 @@
         <v>673</v>
       </c>
       <c r="F17" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>674</v>
       </c>
       <c r="F21" t="n">
-        <v>326.0</v>
+        <v>327.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2855,7 +2855,7 @@
         <v>674</v>
       </c>
       <c r="F30" t="n">
-        <v>37.0</v>
+        <v>44.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -2907,13 +2907,13 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>444.0</v>
+        <v>450.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="33">
@@ -2933,7 +2933,7 @@
         <v>673</v>
       </c>
       <c r="F33" t="n">
-        <v>150.0</v>
+        <v>157.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -3167,13 +3167,13 @@
         <v>673</v>
       </c>
       <c r="F42" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="43">
@@ -3193,7 +3193,7 @@
         <v>673</v>
       </c>
       <c r="F43" t="n">
-        <v>179.0</v>
+        <v>182.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -3375,7 +3375,7 @@
         <v>674</v>
       </c>
       <c r="F50" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3557,7 +3557,7 @@
         <v>673</v>
       </c>
       <c r="F57" t="n">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -3589,7 +3589,7 @@
         <v>0.0</v>
       </c>
       <c r="H58" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="59">
@@ -3687,7 +3687,7 @@
         <v>673</v>
       </c>
       <c r="F62" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -3739,7 +3739,7 @@
         <v>674</v>
       </c>
       <c r="F64" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -3765,7 +3765,7 @@
         <v>674</v>
       </c>
       <c r="F65" t="n">
-        <v>147.0</v>
+        <v>151.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3791,13 +3791,13 @@
         <v>673</v>
       </c>
       <c r="F66" t="n">
-        <v>125.0</v>
+        <v>127.0</v>
       </c>
       <c r="G66" t="n">
         <v>6.0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -3869,7 +3869,7 @@
         <v>673</v>
       </c>
       <c r="F69" t="n">
-        <v>33.0</v>
+        <v>38.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -3895,7 +3895,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -3973,7 +3973,7 @@
         <v>674</v>
       </c>
       <c r="F73" t="n">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -3999,7 +3999,7 @@
         <v>673</v>
       </c>
       <c r="F74" t="n">
-        <v>337.0</v>
+        <v>340.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>673</v>
       </c>
       <c r="F76" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="G76" t="n">
         <v>15.0</v>
@@ -4311,7 +4311,7 @@
         <v>673</v>
       </c>
       <c r="F86" t="n">
-        <v>464.0</v>
+        <v>465.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -4363,7 +4363,7 @@
         <v>673</v>
       </c>
       <c r="F88" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -4545,7 +4545,7 @@
         <v>674</v>
       </c>
       <c r="F95" t="n">
-        <v>366.0</v>
+        <v>369.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4600,7 +4600,7 @@
         <v>138.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -4649,13 +4649,13 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>453.0</v>
+        <v>460.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
       </c>
       <c r="H99" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="100">
@@ -4779,7 +4779,7 @@
         <v>674</v>
       </c>
       <c r="F104" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -4909,13 +4909,13 @@
         <v>673</v>
       </c>
       <c r="F109" t="n">
-        <v>234.0</v>
+        <v>236.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
       </c>
       <c r="H109" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="110">
@@ -5117,13 +5117,13 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>417.0</v>
+        <v>419.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
       </c>
       <c r="H117" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="118">
@@ -5195,7 +5195,7 @@
         <v>674</v>
       </c>
       <c r="F120" t="n">
-        <v>241.0</v>
+        <v>244.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -5325,7 +5325,7 @@
         <v>674</v>
       </c>
       <c r="F125" t="n">
-        <v>282.0</v>
+        <v>283.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
@@ -5481,7 +5481,7 @@
         <v>673</v>
       </c>
       <c r="F131" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
@@ -5533,7 +5533,7 @@
         <v>673</v>
       </c>
       <c r="F133" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G133" t="n">
         <v>1.0</v>
@@ -5611,7 +5611,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>606.0</v>
+        <v>610.0</v>
       </c>
       <c r="G136" t="n">
         <v>1.0</v>
@@ -5689,7 +5689,7 @@
         <v>673</v>
       </c>
       <c r="F139" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>
@@ -6261,7 +6261,7 @@
         <v>674</v>
       </c>
       <c r="F161" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6313,7 +6313,7 @@
         <v>674</v>
       </c>
       <c r="F163" t="n">
-        <v>294.0</v>
+        <v>297.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6423,7 +6423,7 @@
         <v>0.0</v>
       </c>
       <c r="H167" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="168">
@@ -6469,7 +6469,7 @@
         <v>673</v>
       </c>
       <c r="F169" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6495,7 +6495,7 @@
         <v>674</v>
       </c>
       <c r="F170" t="n">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6599,7 +6599,7 @@
         <v>673</v>
       </c>
       <c r="F174" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G174" t="n">
         <v>1.0</v>
@@ -6625,7 +6625,7 @@
         <v>674</v>
       </c>
       <c r="F175" t="n">
-        <v>544.0</v>
+        <v>545.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -6755,7 +6755,7 @@
         <v>674</v>
       </c>
       <c r="F180" t="n">
-        <v>610.0</v>
+        <v>618.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -6885,7 +6885,7 @@
         <v>673</v>
       </c>
       <c r="F185" t="n">
-        <v>306.0</v>
+        <v>310.0</v>
       </c>
       <c r="G185" t="n">
         <v>2.0</v>
@@ -6937,7 +6937,7 @@
         <v>673</v>
       </c>
       <c r="F187" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7093,7 +7093,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>984.0</v>
+        <v>985.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -7249,7 +7249,7 @@
         <v>674</v>
       </c>
       <c r="F199" t="n">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>673</v>
       </c>
       <c r="F212" t="n">
-        <v>114.0</v>
+        <v>119.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -7639,7 +7639,7 @@
         <v>673</v>
       </c>
       <c r="F214" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="G214" t="n">
         <v>0.0</v>
@@ -7899,7 +7899,7 @@
         <v>673</v>
       </c>
       <c r="F224" t="n">
-        <v>393.0</v>
+        <v>394.0</v>
       </c>
       <c r="G224" t="n">
         <v>1.0</v>
@@ -8237,7 +8237,7 @@
         <v>673</v>
       </c>
       <c r="F237" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -8263,7 +8263,7 @@
         <v>673</v>
       </c>
       <c r="F238" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
       <c r="G238" t="n">
         <v>0.0</v>
@@ -8289,7 +8289,7 @@
         <v>673</v>
       </c>
       <c r="F239" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G239" t="n">
         <v>1.0</v>
@@ -8529,7 +8529,7 @@
         <v>16.0</v>
       </c>
       <c r="H248" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="249">
@@ -8757,7 +8757,7 @@
         <v>673</v>
       </c>
       <c r="F257" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G257" t="n">
         <v>0.0</v>
@@ -8835,7 +8835,7 @@
         <v>673</v>
       </c>
       <c r="F260" t="n">
-        <v>608.0</v>
+        <v>610.0</v>
       </c>
       <c r="G260" t="n">
         <v>0.0</v>
@@ -8867,7 +8867,7 @@
         <v>0.0</v>
       </c>
       <c r="H261" t="n">
-        <v>41.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="262">
@@ -9017,7 +9017,7 @@
         <v>673</v>
       </c>
       <c r="F267" t="n">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9173,7 +9173,7 @@
         <v>674</v>
       </c>
       <c r="F273" t="n">
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
       <c r="G273" t="n">
         <v>0.0</v>
@@ -9303,7 +9303,7 @@
         <v>673</v>
       </c>
       <c r="F278" t="n">
-        <v>528.0</v>
+        <v>532.0</v>
       </c>
       <c r="G278" t="n">
         <v>6.0</v>
@@ -9355,10 +9355,10 @@
         <v>673</v>
       </c>
       <c r="F280" t="n">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="G280" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H280" t="n">
         <v>13.0</v>
@@ -9543,7 +9543,7 @@
         <v>0.0</v>
       </c>
       <c r="H287" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="288">
@@ -9641,7 +9641,7 @@
         <v>674</v>
       </c>
       <c r="F291" t="n">
-        <v>380.0</v>
+        <v>384.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -9797,7 +9797,7 @@
         <v>673</v>
       </c>
       <c r="F297" t="n">
-        <v>938.0</v>
+        <v>939.0</v>
       </c>
       <c r="G297" t="n">
         <v>5.0</v>
@@ -9823,7 +9823,7 @@
         <v>673</v>
       </c>
       <c r="F298" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G298" t="n">
         <v>0.0</v>
@@ -9901,7 +9901,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>454.0</v>
+        <v>460.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -9933,7 +9933,7 @@
         <v>0.0</v>
       </c>
       <c r="H302" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="303">
@@ -9953,13 +9953,13 @@
         <v>673</v>
       </c>
       <c r="F303" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G303" t="n">
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="304">
@@ -10057,13 +10057,13 @@
         <v>673</v>
       </c>
       <c r="F307" t="n">
-        <v>519.0</v>
+        <v>520.0</v>
       </c>
       <c r="G307" t="n">
         <v>2.0</v>
       </c>
       <c r="H307" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="308">
@@ -10343,7 +10343,7 @@
         <v>673</v>
       </c>
       <c r="F318" t="n">
-        <v>263.0</v>
+        <v>264.0</v>
       </c>
       <c r="G318" t="n">
         <v>0.0</v>
@@ -10447,7 +10447,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>372.0</v>
+        <v>376.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10655,7 +10655,7 @@
         <v>674</v>
       </c>
       <c r="F330" t="n">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="G330" t="n">
         <v>0.0</v>
@@ -11045,7 +11045,7 @@
         <v>674</v>
       </c>
       <c r="F345" t="n">
-        <v>504.0</v>
+        <v>505.0</v>
       </c>
       <c r="G345" t="n">
         <v>1.0</v>
@@ -11077,7 +11077,7 @@
         <v>1.0</v>
       </c>
       <c r="H346" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="347">
@@ -11097,10 +11097,10 @@
         <v>673</v>
       </c>
       <c r="F347" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G347" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H347" t="n">
         <v>0.0</v>
@@ -11669,7 +11669,7 @@
         <v>674</v>
       </c>
       <c r="F369" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G369" t="n">
         <v>0.0</v>
@@ -11721,7 +11721,7 @@
         <v>674</v>
       </c>
       <c r="F371" t="n">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="G371" t="n">
         <v>0.0</v>
@@ -11747,7 +11747,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>216.0</v>
+        <v>220.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -11981,7 +11981,7 @@
         <v>673</v>
       </c>
       <c r="F381" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G381" t="n">
         <v>1.0</v>
@@ -12085,7 +12085,7 @@
         <v>674</v>
       </c>
       <c r="F385" t="n">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12319,7 +12319,7 @@
         <v>674</v>
       </c>
       <c r="F394" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -12345,13 +12345,13 @@
         <v>673</v>
       </c>
       <c r="F395" t="n">
-        <v>281.0</v>
+        <v>284.0</v>
       </c>
       <c r="G395" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="H395" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="396">
@@ -12553,7 +12553,7 @@
         <v>673</v>
       </c>
       <c r="F403" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G403" t="n">
         <v>0.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>514.0</v>
+        <v>519.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13203,7 +13203,7 @@
         <v>673</v>
       </c>
       <c r="F428" t="n">
-        <v>183.0</v>
+        <v>185.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -13541,7 +13541,7 @@
         <v>673</v>
       </c>
       <c r="F441" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G441" t="n">
         <v>0.0</v>
@@ -13645,7 +13645,7 @@
         <v>673</v>
       </c>
       <c r="F445" t="n">
-        <v>517.0</v>
+        <v>519.0</v>
       </c>
       <c r="G445" t="n">
         <v>2.0</v>
@@ -13723,7 +13723,7 @@
         <v>673</v>
       </c>
       <c r="F448" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="G448" t="n">
         <v>7.0</v>
@@ -14035,7 +14035,7 @@
         <v>673</v>
       </c>
       <c r="F460" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G460" t="n">
         <v>0.0</v>
@@ -14113,7 +14113,7 @@
         <v>674</v>
       </c>
       <c r="F463" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G463" t="n">
         <v>1.0</v>
@@ -14425,10 +14425,10 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>518.0</v>
+        <v>527.0</v>
       </c>
       <c r="G475" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H475" t="n">
         <v>0.0</v>
@@ -14737,7 +14737,7 @@
         <v>673</v>
       </c>
       <c r="F487" t="n">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
       <c r="G487" t="n">
         <v>0.0</v>
@@ -14763,7 +14763,7 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2275.0</v>
+        <v>2279.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
@@ -14945,7 +14945,7 @@
         <v>673</v>
       </c>
       <c r="F495" t="n">
-        <v>60.0</v>
+        <v>62.0</v>
       </c>
       <c r="G495" t="n">
         <v>0.0</v>
@@ -15101,13 +15101,13 @@
         <v>673</v>
       </c>
       <c r="F501" t="n">
-        <v>394.0</v>
+        <v>395.0</v>
       </c>
       <c r="G501" t="n">
         <v>9.0</v>
       </c>
       <c r="H501" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="502">
@@ -15231,7 +15231,7 @@
         <v>673</v>
       </c>
       <c r="F506" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G506" t="n">
         <v>0.0</v>
@@ -15361,7 +15361,7 @@
         <v>674</v>
       </c>
       <c r="F511" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -15465,7 +15465,7 @@
         <v>674</v>
       </c>
       <c r="F515" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="G515" t="n">
         <v>1.0</v>
@@ -15517,13 +15517,13 @@
         <v>673</v>
       </c>
       <c r="F517" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
       </c>
       <c r="H517" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="518">
@@ -15543,7 +15543,7 @@
         <v>674</v>
       </c>
       <c r="F518" t="n">
-        <v>241.0</v>
+        <v>244.0</v>
       </c>
       <c r="G518" t="n">
         <v>0.0</v>
@@ -16037,7 +16037,7 @@
         <v>674</v>
       </c>
       <c r="F537" t="n">
-        <v>520.0</v>
+        <v>527.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16095,7 +16095,7 @@
         <v>0.0</v>
       </c>
       <c r="H539" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="540">
@@ -16115,7 +16115,7 @@
         <v>673</v>
       </c>
       <c r="F540" t="n">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
       <c r="G540" t="n">
         <v>1.0</v>
@@ -16297,7 +16297,7 @@
         <v>674</v>
       </c>
       <c r="F547" t="n">
-        <v>250.0</v>
+        <v>253.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16375,7 +16375,7 @@
         <v>673</v>
       </c>
       <c r="F550" t="n">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="G550" t="n">
         <v>1.0</v>
@@ -16453,7 +16453,7 @@
         <v>674</v>
       </c>
       <c r="F553" t="n">
-        <v>280.0</v>
+        <v>283.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16739,7 +16739,7 @@
         <v>673</v>
       </c>
       <c r="F564" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G564" t="n">
         <v>0.0</v>
@@ -16869,7 +16869,7 @@
         <v>673</v>
       </c>
       <c r="F569" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G569" t="n">
         <v>1.0</v>
@@ -16895,7 +16895,7 @@
         <v>674</v>
       </c>
       <c r="F570" t="n">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="G570" t="n">
         <v>0.0</v>
@@ -16947,7 +16947,7 @@
         <v>674</v>
       </c>
       <c r="F572" t="n">
-        <v>349.0</v>
+        <v>351.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17285,7 +17285,7 @@
         <v>674</v>
       </c>
       <c r="F585" t="n">
-        <v>336.0</v>
+        <v>338.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17597,7 +17597,7 @@
         <v>673</v>
       </c>
       <c r="F597" t="n">
-        <v>231.0</v>
+        <v>240.0</v>
       </c>
       <c r="G597" t="n">
         <v>0.0</v>
@@ -17759,7 +17759,7 @@
         <v>3.0</v>
       </c>
       <c r="H603" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="604">
@@ -17909,7 +17909,7 @@
         <v>673</v>
       </c>
       <c r="F609" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G609" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>674</v>
       </c>
       <c r="F620" t="n">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="G620" t="n">
         <v>0.0</v>
@@ -18409,7 +18409,7 @@
         <v>0.0</v>
       </c>
       <c r="H628" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="629">
@@ -18611,7 +18611,7 @@
         <v>673</v>
       </c>
       <c r="F636" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G636" t="n">
         <v>6.0</v>
@@ -18767,7 +18767,7 @@
         <v>674</v>
       </c>
       <c r="F642" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -19079,7 +19079,7 @@
         <v>674</v>
       </c>
       <c r="F654" t="n">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19105,7 +19105,7 @@
         <v>674</v>
       </c>
       <c r="F655" t="n">
-        <v>82.0</v>
+        <v>86.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19131,7 +19131,7 @@
         <v>674</v>
       </c>
       <c r="F656" t="n">
-        <v>101.0</v>
+        <v>105.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19157,7 +19157,7 @@
         <v>674</v>
       </c>
       <c r="F657" t="n">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="G657" t="n">
         <v>0.0</v>
@@ -19209,7 +19209,7 @@
         <v>674</v>
       </c>
       <c r="F659" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -19261,7 +19261,7 @@
         <v>673</v>
       </c>
       <c r="F661" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19287,7 +19287,7 @@
         <v>674</v>
       </c>
       <c r="F662" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19313,7 +19313,7 @@
         <v>673</v>
       </c>
       <c r="F663" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19339,7 +19339,7 @@
         <v>674</v>
       </c>
       <c r="F664" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G664" t="n">
         <v>1.0</v>
@@ -19365,7 +19365,7 @@
         <v>674</v>
       </c>
       <c r="F665" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G665" t="n">
         <v>0.0</v>
@@ -19391,7 +19391,7 @@
         <v>673</v>
       </c>
       <c r="F666" t="n">
-        <v>271.0</v>
+        <v>273.0</v>
       </c>
       <c r="G666" t="n">
         <v>2.0</v>
@@ -19443,7 +19443,7 @@
         <v>674</v>
       </c>
       <c r="F668" t="n">
-        <v>323.0</v>
+        <v>330.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3999,7 +3999,7 @@
         <v>673</v>
       </c>
       <c r="F74" t="n">
-        <v>340.0</v>
+        <v>341.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -5065,7 +5065,7 @@
         <v>673</v>
       </c>
       <c r="F115" t="n">
-        <v>409.0</v>
+        <v>410.0</v>
       </c>
       <c r="G115" t="n">
         <v>1.0</v>
@@ -5455,7 +5455,7 @@
         <v>673</v>
       </c>
       <c r="F130" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -5793,7 +5793,7 @@
         <v>674</v>
       </c>
       <c r="F143" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -9537,7 +9537,7 @@
         <v>673</v>
       </c>
       <c r="F287" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G287" t="n">
         <v>0.0</v>
@@ -9953,7 +9953,7 @@
         <v>673</v>
       </c>
       <c r="F303" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G303" t="n">
         <v>0.0</v>
@@ -11045,7 +11045,7 @@
         <v>674</v>
       </c>
       <c r="F345" t="n">
-        <v>505.0</v>
+        <v>506.0</v>
       </c>
       <c r="G345" t="n">
         <v>1.0</v>
@@ -12449,7 +12449,7 @@
         <v>673</v>
       </c>
       <c r="F399" t="n">
-        <v>174.0</v>
+        <v>178.0</v>
       </c>
       <c r="G399" t="n">
         <v>0.0</v>
@@ -15517,7 +15517,7 @@
         <v>673</v>
       </c>
       <c r="F517" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -15881,7 +15881,7 @@
         <v>673</v>
       </c>
       <c r="F531" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G531" t="n">
         <v>1.0</v>
@@ -19027,7 +19027,7 @@
         <v>673</v>
       </c>
       <c r="F652" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G652" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2127,7 +2127,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="G2" t="n">
         <v>2.0</v>
@@ -2393,7 +2393,7 @@
         <v>0.0</v>
       </c>
       <c r="H12" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="13">
@@ -2491,7 +2491,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>354.0</v>
+        <v>356.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>674</v>
       </c>
       <c r="F21" t="n">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2881,7 +2881,7 @@
         <v>674</v>
       </c>
       <c r="F31" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -2907,7 +2907,7 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>450.0</v>
+        <v>452.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3141,7 +3141,7 @@
         <v>673</v>
       </c>
       <c r="F41" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -3245,7 +3245,7 @@
         <v>673</v>
       </c>
       <c r="F45" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -3427,13 +3427,13 @@
         <v>673</v>
       </c>
       <c r="F52" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="53">
@@ -3895,7 +3895,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4811,7 +4811,7 @@
         <v>0.0</v>
       </c>
       <c r="H105" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="106">
@@ -4831,7 +4831,7 @@
         <v>673</v>
       </c>
       <c r="F106" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -5117,7 +5117,7 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>419.0</v>
+        <v>422.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5195,7 +5195,7 @@
         <v>674</v>
       </c>
       <c r="F120" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -5455,7 +5455,7 @@
         <v>673</v>
       </c>
       <c r="F130" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -5611,7 +5611,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>610.0</v>
+        <v>612.0</v>
       </c>
       <c r="G136" t="n">
         <v>1.0</v>
@@ -6261,7 +6261,7 @@
         <v>674</v>
       </c>
       <c r="F161" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6469,7 +6469,7 @@
         <v>673</v>
       </c>
       <c r="F169" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6495,7 +6495,7 @@
         <v>674</v>
       </c>
       <c r="F170" t="n">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6885,7 +6885,7 @@
         <v>673</v>
       </c>
       <c r="F185" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
       <c r="G185" t="n">
         <v>2.0</v>
@@ -9537,13 +9537,13 @@
         <v>673</v>
       </c>
       <c r="F287" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G287" t="n">
         <v>0.0</v>
       </c>
       <c r="H287" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="288">
@@ -11071,7 +11071,7 @@
         <v>673</v>
       </c>
       <c r="F346" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G346" t="n">
         <v>1.0</v>
@@ -11100,7 +11100,7 @@
         <v>90.0</v>
       </c>
       <c r="G347" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H347" t="n">
         <v>0.0</v>
@@ -13229,7 +13229,7 @@
         <v>673</v>
       </c>
       <c r="F429" t="n">
-        <v>751.0</v>
+        <v>753.0</v>
       </c>
       <c r="G429" t="n">
         <v>2.0</v>
@@ -13287,7 +13287,7 @@
         <v>0.0</v>
       </c>
       <c r="H431" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="432">
@@ -13541,7 +13541,7 @@
         <v>673</v>
       </c>
       <c r="F441" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G441" t="n">
         <v>0.0</v>
@@ -14113,7 +14113,7 @@
         <v>674</v>
       </c>
       <c r="F463" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G463" t="n">
         <v>1.0</v>
@@ -14763,7 +14763,7 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2279.0</v>
+        <v>2289.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
@@ -15361,7 +15361,7 @@
         <v>674</v>
       </c>
       <c r="F511" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -16115,7 +16115,7 @@
         <v>673</v>
       </c>
       <c r="F540" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G540" t="n">
         <v>1.0</v>
@@ -16453,7 +16453,7 @@
         <v>674</v>
       </c>
       <c r="F553" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16947,7 +16947,7 @@
         <v>674</v>
       </c>
       <c r="F572" t="n">
-        <v>351.0</v>
+        <v>355.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17597,7 +17597,7 @@
         <v>673</v>
       </c>
       <c r="F597" t="n">
-        <v>240.0</v>
+        <v>242.0</v>
       </c>
       <c r="G597" t="n">
         <v>0.0</v>
@@ -17915,7 +17915,7 @@
         <v>0.0</v>
       </c>
       <c r="H609" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="610">
@@ -18715,7 +18715,7 @@
         <v>673</v>
       </c>
       <c r="F640" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>674</v>
       </c>
       <c r="F643" t="n">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -18923,7 +18923,7 @@
         <v>674</v>
       </c>
       <c r="F648" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -19079,7 +19079,7 @@
         <v>674</v>
       </c>
       <c r="F654" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19131,7 +19131,7 @@
         <v>674</v>
       </c>
       <c r="F656" t="n">
-        <v>105.0</v>
+        <v>108.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19287,7 +19287,7 @@
         <v>674</v>
       </c>
       <c r="F662" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19313,7 +19313,7 @@
         <v>673</v>
       </c>
       <c r="F663" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19391,7 +19391,7 @@
         <v>673</v>
       </c>
       <c r="F666" t="n">
-        <v>273.0</v>
+        <v>275.0</v>
       </c>
       <c r="G666" t="n">
         <v>2.0</v>
@@ -19469,7 +19469,7 @@
         <v>673</v>
       </c>
       <c r="F669" t="n">
-        <v>177.0</v>
+        <v>179.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -6495,7 +6495,7 @@
         <v>674</v>
       </c>
       <c r="F170" t="n">
-        <v>463.0</v>
+        <v>465.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -15023,7 +15023,7 @@
         <v>673</v>
       </c>
       <c r="F498" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G498" t="n">
         <v>1.0</v>
@@ -19105,7 +19105,7 @@
         <v>674</v>
       </c>
       <c r="F655" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19131,7 +19131,7 @@
         <v>674</v>
       </c>
       <c r="F656" t="n">
-        <v>108.0</v>
+        <v>113.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19287,7 +19287,7 @@
         <v>674</v>
       </c>
       <c r="F662" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19339,7 +19339,7 @@
         <v>674</v>
       </c>
       <c r="F664" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G664" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2205,7 +2205,7 @@
         <v>673</v>
       </c>
       <c r="F5" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -2289,7 +2289,7 @@
         <v>1.0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
@@ -2647,7 +2647,7 @@
         <v>674</v>
       </c>
       <c r="F22" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3037,7 +3037,7 @@
         <v>673</v>
       </c>
       <c r="F37" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3687,7 +3687,7 @@
         <v>673</v>
       </c>
       <c r="F62" t="n">
-        <v>203.0</v>
+        <v>208.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -3791,10 +3791,10 @@
         <v>673</v>
       </c>
       <c r="F66" t="n">
-        <v>127.0</v>
+        <v>131.0</v>
       </c>
       <c r="G66" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -3973,7 +3973,7 @@
         <v>674</v>
       </c>
       <c r="F73" t="n">
-        <v>333.0</v>
+        <v>336.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -3999,7 +3999,7 @@
         <v>673</v>
       </c>
       <c r="F74" t="n">
-        <v>341.0</v>
+        <v>342.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4649,7 +4649,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -5143,7 +5143,7 @@
         <v>674</v>
       </c>
       <c r="F118" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G118" t="n">
         <v>0.0</v>
@@ -5221,7 +5221,7 @@
         <v>673</v>
       </c>
       <c r="F121" t="n">
-        <v>115.0</v>
+        <v>118.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>
@@ -5403,7 +5403,7 @@
         <v>674</v>
       </c>
       <c r="F128" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -6625,7 +6625,7 @@
         <v>674</v>
       </c>
       <c r="F175" t="n">
-        <v>545.0</v>
+        <v>546.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -6755,7 +6755,7 @@
         <v>674</v>
       </c>
       <c r="F180" t="n">
-        <v>618.0</v>
+        <v>620.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -7093,7 +7093,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>985.0</v>
+        <v>986.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -7249,7 +7249,7 @@
         <v>674</v>
       </c>
       <c r="F199" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>673</v>
       </c>
       <c r="F212" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -9173,7 +9173,7 @@
         <v>674</v>
       </c>
       <c r="F273" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G273" t="n">
         <v>0.0</v>
@@ -9901,7 +9901,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>460.0</v>
+        <v>462.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -9979,7 +9979,7 @@
         <v>673</v>
       </c>
       <c r="F304" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10057,13 +10057,13 @@
         <v>673</v>
       </c>
       <c r="F307" t="n">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="G307" t="n">
         <v>2.0</v>
       </c>
       <c r="H307" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="308">
@@ -10447,7 +10447,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11877,7 +11877,7 @@
         <v>673</v>
       </c>
       <c r="F377" t="n">
-        <v>59.0</v>
+        <v>63.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12085,7 +12085,7 @@
         <v>674</v>
       </c>
       <c r="F385" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12267,7 +12267,7 @@
         <v>674</v>
       </c>
       <c r="F392" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G392" t="n">
         <v>0.0</v>
@@ -12449,7 +12449,7 @@
         <v>673</v>
       </c>
       <c r="F399" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="G399" t="n">
         <v>0.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>519.0</v>
+        <v>520.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -14477,7 +14477,7 @@
         <v>674</v>
       </c>
       <c r="F477" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>674</v>
       </c>
       <c r="F480" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G480" t="n">
         <v>0.0</v>
@@ -15465,7 +15465,7 @@
         <v>674</v>
       </c>
       <c r="F515" t="n">
-        <v>306.0</v>
+        <v>308.0</v>
       </c>
       <c r="G515" t="n">
         <v>1.0</v>
@@ -15543,7 +15543,7 @@
         <v>674</v>
       </c>
       <c r="F518" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G518" t="n">
         <v>0.0</v>
@@ -15881,7 +15881,7 @@
         <v>673</v>
       </c>
       <c r="F531" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G531" t="n">
         <v>1.0</v>
@@ -15907,7 +15907,7 @@
         <v>673</v>
       </c>
       <c r="F532" t="n">
-        <v>342.0</v>
+        <v>343.0</v>
       </c>
       <c r="G532" t="n">
         <v>0.0</v>
@@ -16037,7 +16037,7 @@
         <v>674</v>
       </c>
       <c r="F537" t="n">
-        <v>527.0</v>
+        <v>529.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16297,7 +16297,7 @@
         <v>674</v>
       </c>
       <c r="F547" t="n">
-        <v>253.0</v>
+        <v>257.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -17285,7 +17285,7 @@
         <v>674</v>
       </c>
       <c r="F585" t="n">
-        <v>338.0</v>
+        <v>341.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17597,7 +17597,7 @@
         <v>673</v>
       </c>
       <c r="F597" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G597" t="n">
         <v>0.0</v>
@@ -17753,10 +17753,10 @@
         <v>673</v>
       </c>
       <c r="F603" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G603" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H603" t="n">
         <v>78.0</v>
@@ -17935,7 +17935,7 @@
         <v>674</v>
       </c>
       <c r="F610" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>674</v>
       </c>
       <c r="F643" t="n">
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -18897,7 +18897,7 @@
         <v>674</v>
       </c>
       <c r="F647" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19131,7 +19131,7 @@
         <v>674</v>
       </c>
       <c r="F656" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2286,7 +2286,7 @@
         <v>193.0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H8" t="n">
         <v>2.0</v>
@@ -3791,7 +3791,7 @@
         <v>673</v>
       </c>
       <c r="F66" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -4363,7 +4363,7 @@
         <v>673</v>
       </c>
       <c r="F88" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -8188,7 +8188,7 @@
         <v>84.0</v>
       </c>
       <c r="G235" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H235" t="n">
         <v>0.0</v>
@@ -9797,7 +9797,7 @@
         <v>673</v>
       </c>
       <c r="F297" t="n">
-        <v>939.0</v>
+        <v>940.0</v>
       </c>
       <c r="G297" t="n">
         <v>5.0</v>
@@ -10343,7 +10343,7 @@
         <v>673</v>
       </c>
       <c r="F318" t="n">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
       <c r="G318" t="n">
         <v>0.0</v>
@@ -10655,7 +10655,7 @@
         <v>674</v>
       </c>
       <c r="F330" t="n">
-        <v>45.0</v>
+        <v>50.0</v>
       </c>
       <c r="G330" t="n">
         <v>0.0</v>
@@ -11253,7 +11253,7 @@
         <v>674</v>
       </c>
       <c r="F353" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G353" t="n">
         <v>0.0</v>
@@ -12085,7 +12085,7 @@
         <v>674</v>
       </c>
       <c r="F385" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12345,7 +12345,7 @@
         <v>673</v>
       </c>
       <c r="F395" t="n">
-        <v>284.0</v>
+        <v>285.0</v>
       </c>
       <c r="G395" t="n">
         <v>9.0</v>
@@ -12553,7 +12553,7 @@
         <v>673</v>
       </c>
       <c r="F403" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G403" t="n">
         <v>0.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13229,7 +13229,7 @@
         <v>673</v>
       </c>
       <c r="F429" t="n">
-        <v>753.0</v>
+        <v>754.0</v>
       </c>
       <c r="G429" t="n">
         <v>2.0</v>
@@ -13287,7 +13287,7 @@
         <v>0.0</v>
       </c>
       <c r="H431" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="432">
@@ -13648,7 +13648,7 @@
         <v>519.0</v>
       </c>
       <c r="G445" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H445" t="n">
         <v>0.0</v>
@@ -14035,7 +14035,7 @@
         <v>673</v>
       </c>
       <c r="F460" t="n">
-        <v>141.0</v>
+        <v>144.0</v>
       </c>
       <c r="G460" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2231,7 +2231,7 @@
         <v>673</v>
       </c>
       <c r="F6" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -2985,7 +2985,7 @@
         <v>673</v>
       </c>
       <c r="F35" t="n">
-        <v>257.0</v>
+        <v>259.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3433,7 +3433,7 @@
         <v>0.0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="53">
@@ -3687,7 +3687,7 @@
         <v>673</v>
       </c>
       <c r="F62" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>673</v>
       </c>
       <c r="F66" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -4597,10 +4597,10 @@
         <v>674</v>
       </c>
       <c r="F97" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -4811,7 +4811,7 @@
         <v>0.0</v>
       </c>
       <c r="H105" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="106">
@@ -5461,7 +5461,7 @@
         <v>0.0</v>
       </c>
       <c r="H130" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="131">
@@ -6625,7 +6625,7 @@
         <v>674</v>
       </c>
       <c r="F175" t="n">
-        <v>546.0</v>
+        <v>548.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -9303,7 +9303,7 @@
         <v>673</v>
       </c>
       <c r="F278" t="n">
-        <v>532.0</v>
+        <v>533.0</v>
       </c>
       <c r="G278" t="n">
         <v>6.0</v>
@@ -9953,13 +9953,13 @@
         <v>673</v>
       </c>
       <c r="F303" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G303" t="n">
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="304">
@@ -10213,7 +10213,7 @@
         <v>673</v>
       </c>
       <c r="F313" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G313" t="n">
         <v>1.0</v>
@@ -11045,7 +11045,7 @@
         <v>674</v>
       </c>
       <c r="F345" t="n">
-        <v>506.0</v>
+        <v>507.0</v>
       </c>
       <c r="G345" t="n">
         <v>1.0</v>
@@ -12085,7 +12085,7 @@
         <v>674</v>
       </c>
       <c r="F385" t="n">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>521.0</v>
+        <v>525.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13125,7 +13125,7 @@
         <v>673</v>
       </c>
       <c r="F425" t="n">
-        <v>146.0</v>
+        <v>149.0</v>
       </c>
       <c r="G425" t="n">
         <v>0.0</v>
@@ -13281,7 +13281,7 @@
         <v>673</v>
       </c>
       <c r="F431" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G431" t="n">
         <v>0.0</v>
@@ -13359,7 +13359,7 @@
         <v>673</v>
       </c>
       <c r="F434" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G434" t="n">
         <v>0.0</v>
@@ -15517,13 +15517,13 @@
         <v>673</v>
       </c>
       <c r="F517" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
       </c>
       <c r="H517" t="n">
-        <v>36.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="518">
@@ -16895,7 +16895,7 @@
         <v>674</v>
       </c>
       <c r="F570" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
       <c r="G570" t="n">
         <v>0.0</v>
@@ -17915,7 +17915,7 @@
         <v>0.0</v>
       </c>
       <c r="H609" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="610">
@@ -18435,7 +18435,7 @@
         <v>0.0</v>
       </c>
       <c r="H629" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="630">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3999,7 +3999,7 @@
         <v>673</v>
       </c>
       <c r="F74" t="n">
-        <v>342.0</v>
+        <v>344.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4259,7 +4259,7 @@
         <v>673</v>
       </c>
       <c r="F84" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G84" t="n">
         <v>2.0</v>
@@ -4311,7 +4311,7 @@
         <v>673</v>
       </c>
       <c r="F86" t="n">
-        <v>465.0</v>
+        <v>466.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -5481,7 +5481,7 @@
         <v>673</v>
       </c>
       <c r="F131" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
@@ -8185,7 +8185,7 @@
         <v>673</v>
       </c>
       <c r="F235" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G235" t="n">
         <v>1.0</v>
@@ -9017,7 +9017,7 @@
         <v>673</v>
       </c>
       <c r="F267" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9049,7 +9049,7 @@
         <v>0.0</v>
       </c>
       <c r="H268" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="269">
@@ -9069,7 +9069,7 @@
         <v>673</v>
       </c>
       <c r="F269" t="n">
-        <v>492.0</v>
+        <v>493.0</v>
       </c>
       <c r="G269" t="n">
         <v>0.0</v>
@@ -9745,7 +9745,7 @@
         <v>673</v>
       </c>
       <c r="F295" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G295" t="n">
         <v>2.0</v>
@@ -9797,7 +9797,7 @@
         <v>673</v>
       </c>
       <c r="F297" t="n">
-        <v>940.0</v>
+        <v>941.0</v>
       </c>
       <c r="G297" t="n">
         <v>5.0</v>
@@ -12007,7 +12007,7 @@
         <v>673</v>
       </c>
       <c r="F382" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="G382" t="n">
         <v>1.0</v>
@@ -12059,7 +12059,7 @@
         <v>673</v>
       </c>
       <c r="F384" t="n">
-        <v>426.0</v>
+        <v>428.0</v>
       </c>
       <c r="G384" t="n">
         <v>1.0</v>
@@ -13099,7 +13099,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -14477,7 +14477,7 @@
         <v>674</v>
       </c>
       <c r="F477" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>674</v>
       </c>
       <c r="F480" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G480" t="n">
         <v>0.0</v>
@@ -14763,13 +14763,13 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2289.0</v>
+        <v>2292.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
       </c>
       <c r="H488" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
     </row>
     <row r="489">
@@ -14867,7 +14867,7 @@
         <v>673</v>
       </c>
       <c r="F492" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G492" t="n">
         <v>0.0</v>
@@ -15725,10 +15725,10 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>401.0</v>
+        <v>403.0</v>
       </c>
       <c r="G525" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H525" t="n">
         <v>0.0</v>
@@ -15751,7 +15751,7 @@
         <v>673</v>
       </c>
       <c r="F526" t="n">
-        <v>200.0</v>
+        <v>203.0</v>
       </c>
       <c r="G526" t="n">
         <v>0.0</v>
@@ -16115,7 +16115,7 @@
         <v>673</v>
       </c>
       <c r="F540" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G540" t="n">
         <v>1.0</v>
@@ -17077,7 +17077,7 @@
         <v>673</v>
       </c>
       <c r="F577" t="n">
-        <v>213.0</v>
+        <v>217.0</v>
       </c>
       <c r="G577" t="n">
         <v>0.0</v>
@@ -17285,7 +17285,7 @@
         <v>674</v>
       </c>
       <c r="F585" t="n">
-        <v>341.0</v>
+        <v>344.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17727,7 +17727,7 @@
         <v>673</v>
       </c>
       <c r="F602" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G602" t="n">
         <v>1.0</v>
@@ -18435,7 +18435,7 @@
         <v>0.0</v>
       </c>
       <c r="H629" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="630">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2127,10 +2127,10 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>521.0</v>
+        <v>525.0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H2" t="n">
         <v>0.0</v>
@@ -2439,10 +2439,10 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>415.0</v>
+        <v>417.0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H14" t="n">
         <v>2.0</v>
@@ -2491,7 +2491,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>356.0</v>
+        <v>359.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>674</v>
       </c>
       <c r="F21" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2907,7 +2907,7 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>452.0</v>
+        <v>455.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3609,7 +3609,7 @@
         <v>674</v>
       </c>
       <c r="F59" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -3765,7 +3765,7 @@
         <v>674</v>
       </c>
       <c r="F65" t="n">
-        <v>151.0</v>
+        <v>153.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3797,7 +3797,7 @@
         <v>2.0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="67">
@@ -3895,7 +3895,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>109.0</v>
+        <v>111.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4545,7 +4545,7 @@
         <v>674</v>
       </c>
       <c r="F95" t="n">
-        <v>369.0</v>
+        <v>372.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4649,10 +4649,10 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>2.0</v>
@@ -5117,7 +5117,7 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>422.0</v>
+        <v>424.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5611,7 +5611,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>612.0</v>
+        <v>614.0</v>
       </c>
       <c r="G136" t="n">
         <v>1.0</v>
@@ -6261,7 +6261,7 @@
         <v>674</v>
       </c>
       <c r="F161" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6313,7 +6313,7 @@
         <v>674</v>
       </c>
       <c r="F163" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6469,7 +6469,7 @@
         <v>673</v>
       </c>
       <c r="F169" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6495,7 +6495,7 @@
         <v>674</v>
       </c>
       <c r="F170" t="n">
-        <v>465.0</v>
+        <v>470.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6521,7 +6521,7 @@
         <v>674</v>
       </c>
       <c r="F171" t="n">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -6625,7 +6625,7 @@
         <v>674</v>
       </c>
       <c r="F175" t="n">
-        <v>548.0</v>
+        <v>549.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -9641,7 +9641,7 @@
         <v>674</v>
       </c>
       <c r="F291" t="n">
-        <v>384.0</v>
+        <v>386.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -9901,7 +9901,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>462.0</v>
+        <v>466.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10447,7 +10447,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>377.0</v>
+        <v>381.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11747,7 +11747,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -13541,7 +13541,7 @@
         <v>673</v>
       </c>
       <c r="F441" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G441" t="n">
         <v>0.0</v>
@@ -14425,7 +14425,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>527.0</v>
+        <v>531.0</v>
       </c>
       <c r="G475" t="n">
         <v>2.0</v>
@@ -16453,7 +16453,7 @@
         <v>674</v>
       </c>
       <c r="F553" t="n">
-        <v>284.0</v>
+        <v>286.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16947,7 +16947,7 @@
         <v>674</v>
       </c>
       <c r="F572" t="n">
-        <v>355.0</v>
+        <v>357.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17883,7 +17883,7 @@
         <v>673</v>
       </c>
       <c r="F608" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>674</v>
       </c>
       <c r="F620" t="n">
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
       <c r="G620" t="n">
         <v>0.0</v>
@@ -18562,7 +18562,7 @@
         <v>85.0</v>
       </c>
       <c r="G634" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H634" t="n">
         <v>0.0</v>
@@ -18715,7 +18715,7 @@
         <v>673</v>
       </c>
       <c r="F640" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>674</v>
       </c>
       <c r="F643" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -18897,7 +18897,7 @@
         <v>674</v>
       </c>
       <c r="F647" t="n">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -18923,7 +18923,7 @@
         <v>674</v>
       </c>
       <c r="F648" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -19079,7 +19079,7 @@
         <v>674</v>
       </c>
       <c r="F654" t="n">
-        <v>46.0</v>
+        <v>52.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19105,7 +19105,7 @@
         <v>674</v>
       </c>
       <c r="F655" t="n">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19131,7 +19131,7 @@
         <v>674</v>
       </c>
       <c r="F656" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19157,7 +19157,7 @@
         <v>674</v>
       </c>
       <c r="F657" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="G657" t="n">
         <v>0.0</v>
@@ -19235,10 +19235,10 @@
         <v>673</v>
       </c>
       <c r="F660" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G660" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H660" t="n">
         <v>0.0</v>
@@ -19313,7 +19313,7 @@
         <v>673</v>
       </c>
       <c r="F663" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19417,7 +19417,7 @@
         <v>674</v>
       </c>
       <c r="F667" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19443,7 +19443,7 @@
         <v>674</v>
       </c>
       <c r="F668" t="n">
-        <v>330.0</v>
+        <v>334.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>
@@ -19469,7 +19469,7 @@
         <v>673</v>
       </c>
       <c r="F669" t="n">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2413,7 +2413,7 @@
         <v>673</v>
       </c>
       <c r="F13" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -3583,13 +3583,13 @@
         <v>673</v>
       </c>
       <c r="F58" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
       </c>
       <c r="H58" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="59">
@@ -4337,7 +4337,7 @@
         <v>674</v>
       </c>
       <c r="F87" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -6781,7 +6781,7 @@
         <v>674</v>
       </c>
       <c r="F181" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7977,7 +7977,7 @@
         <v>674</v>
       </c>
       <c r="F227" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G227" t="n">
         <v>0.0</v>
@@ -9959,7 +9959,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="304">
@@ -12059,7 +12059,7 @@
         <v>673</v>
       </c>
       <c r="F384" t="n">
-        <v>428.0</v>
+        <v>430.0</v>
       </c>
       <c r="G384" t="n">
         <v>1.0</v>
@@ -14737,7 +14737,7 @@
         <v>673</v>
       </c>
       <c r="F487" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="G487" t="n">
         <v>0.0</v>
@@ -15523,7 +15523,7 @@
         <v>0.0</v>
       </c>
       <c r="H517" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="518">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="676">
   <si>
     <t>Regione</t>
   </si>
@@ -2034,6 +2034,9 @@
   </si>
   <si>
     <t>II</t>
+  </si>
+  <si>
+    <t>III</t>
   </si>
   <si>
     <t>I</t>
@@ -2280,7 +2283,7 @@
         <v>672</v>
       </c>
       <c r="E8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F8" t="n">
         <v>193.0</v>
@@ -2445,7 +2448,7 @@
         <v>5.0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15">
@@ -2494,7 +2497,7 @@
         <v>359.0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H16" t="n">
         <v>0.0</v>
@@ -2514,7 +2517,7 @@
         <v>672</v>
       </c>
       <c r="E17" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F17" t="n">
         <v>247.0</v>
@@ -2540,7 +2543,7 @@
         <v>672</v>
       </c>
       <c r="E18" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F18" t="n">
         <v>4.0</v>
@@ -2618,7 +2621,7 @@
         <v>672</v>
       </c>
       <c r="E21" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F21" t="n">
         <v>330.0</v>
@@ -2644,7 +2647,7 @@
         <v>672</v>
       </c>
       <c r="E22" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F22" t="n">
         <v>37.0</v>
@@ -2696,7 +2699,7 @@
         <v>672</v>
       </c>
       <c r="E24" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F24" t="n">
         <v>120.0</v>
@@ -2852,7 +2855,7 @@
         <v>672</v>
       </c>
       <c r="E30" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F30" t="n">
         <v>44.0</v>
@@ -2878,7 +2881,7 @@
         <v>672</v>
       </c>
       <c r="E31" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F31" t="n">
         <v>202.0</v>
@@ -3008,7 +3011,7 @@
         <v>672</v>
       </c>
       <c r="E36" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F36" t="n">
         <v>291.0</v>
@@ -3060,7 +3063,7 @@
         <v>672</v>
       </c>
       <c r="E38" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F38" t="n">
         <v>8.0</v>
@@ -3320,7 +3323,7 @@
         <v>672</v>
       </c>
       <c r="E48" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F48" t="n">
         <v>10.0</v>
@@ -3346,7 +3349,7 @@
         <v>672</v>
       </c>
       <c r="E49" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F49" t="n">
         <v>19.0</v>
@@ -3372,7 +3375,7 @@
         <v>672</v>
       </c>
       <c r="E50" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F50" t="n">
         <v>84.0</v>
@@ -3450,7 +3453,7 @@
         <v>672</v>
       </c>
       <c r="E53" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F53" t="n">
         <v>47.0</v>
@@ -3476,7 +3479,7 @@
         <v>672</v>
       </c>
       <c r="E54" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F54" t="n">
         <v>2.0</v>
@@ -3528,7 +3531,7 @@
         <v>672</v>
       </c>
       <c r="E56" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F56" t="n">
         <v>277.0</v>
@@ -3606,7 +3609,7 @@
         <v>672</v>
       </c>
       <c r="E59" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F59" t="n">
         <v>108.0</v>
@@ -3658,7 +3661,7 @@
         <v>672</v>
       </c>
       <c r="E61" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F61" t="n">
         <v>5.0</v>
@@ -3687,7 +3690,7 @@
         <v>673</v>
       </c>
       <c r="F62" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -3710,7 +3713,7 @@
         <v>672</v>
       </c>
       <c r="E63" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F63" t="n">
         <v>41.0</v>
@@ -3736,7 +3739,7 @@
         <v>672</v>
       </c>
       <c r="E64" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F64" t="n">
         <v>49.0</v>
@@ -3762,7 +3765,7 @@
         <v>672</v>
       </c>
       <c r="E65" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F65" t="n">
         <v>153.0</v>
@@ -3970,7 +3973,7 @@
         <v>672</v>
       </c>
       <c r="E73" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F73" t="n">
         <v>336.0</v>
@@ -3999,7 +4002,7 @@
         <v>673</v>
       </c>
       <c r="F74" t="n">
-        <v>344.0</v>
+        <v>346.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4074,7 +4077,7 @@
         <v>672</v>
       </c>
       <c r="E77" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F77" t="n">
         <v>51.0</v>
@@ -4308,10 +4311,10 @@
         <v>672</v>
       </c>
       <c r="E86" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F86" t="n">
-        <v>466.0</v>
+        <v>462.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -4334,7 +4337,7 @@
         <v>672</v>
       </c>
       <c r="E87" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F87" t="n">
         <v>108.0</v>
@@ -4386,7 +4389,7 @@
         <v>672</v>
       </c>
       <c r="E89" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F89" t="n">
         <v>2.0</v>
@@ -4441,7 +4444,7 @@
         <v>673</v>
       </c>
       <c r="F91" t="n">
-        <v>126.0</v>
+        <v>125.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -4490,7 +4493,7 @@
         <v>672</v>
       </c>
       <c r="E93" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
@@ -4542,7 +4545,7 @@
         <v>672</v>
       </c>
       <c r="E95" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F95" t="n">
         <v>372.0</v>
@@ -4594,7 +4597,7 @@
         <v>672</v>
       </c>
       <c r="E97" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F97" t="n">
         <v>139.0</v>
@@ -4724,7 +4727,7 @@
         <v>672</v>
       </c>
       <c r="E102" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F102" t="n">
         <v>38.0</v>
@@ -4776,7 +4779,7 @@
         <v>672</v>
       </c>
       <c r="E104" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F104" t="n">
         <v>12.0</v>
@@ -4854,7 +4857,7 @@
         <v>672</v>
       </c>
       <c r="E107" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F107" t="n">
         <v>69.0</v>
@@ -5062,10 +5065,10 @@
         <v>672</v>
       </c>
       <c r="E115" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F115" t="n">
-        <v>410.0</v>
+        <v>408.0</v>
       </c>
       <c r="G115" t="n">
         <v>1.0</v>
@@ -5140,7 +5143,7 @@
         <v>672</v>
       </c>
       <c r="E118" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F118" t="n">
         <v>50.0</v>
@@ -5192,10 +5195,10 @@
         <v>672</v>
       </c>
       <c r="E120" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F120" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -5322,7 +5325,7 @@
         <v>672</v>
       </c>
       <c r="E125" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F125" t="n">
         <v>283.0</v>
@@ -5400,10 +5403,10 @@
         <v>672</v>
       </c>
       <c r="E128" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F128" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -5530,10 +5533,10 @@
         <v>672</v>
       </c>
       <c r="E133" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F133" t="n">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="G133" t="n">
         <v>1.0</v>
@@ -5712,7 +5715,7 @@
         <v>672</v>
       </c>
       <c r="E140" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F140" t="n">
         <v>194.0</v>
@@ -5790,7 +5793,7 @@
         <v>672</v>
       </c>
       <c r="E143" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F143" t="n">
         <v>71.0</v>
@@ -5816,7 +5819,7 @@
         <v>672</v>
       </c>
       <c r="E144" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F144" t="n">
         <v>29.0</v>
@@ -5842,7 +5845,7 @@
         <v>672</v>
       </c>
       <c r="E145" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F145" t="n">
         <v>135.0</v>
@@ -5920,7 +5923,7 @@
         <v>672</v>
       </c>
       <c r="E148" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F148" t="n">
         <v>128.0</v>
@@ -5946,7 +5949,7 @@
         <v>672</v>
       </c>
       <c r="E149" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F149" t="n">
         <v>16.0</v>
@@ -5972,7 +5975,7 @@
         <v>672</v>
       </c>
       <c r="E150" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F150" t="n">
         <v>17.0</v>
@@ -6076,7 +6079,7 @@
         <v>672</v>
       </c>
       <c r="E154" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F154" t="n">
         <v>50.0</v>
@@ -6102,7 +6105,7 @@
         <v>672</v>
       </c>
       <c r="E155" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F155" t="n">
         <v>199.0</v>
@@ -6154,7 +6157,7 @@
         <v>672</v>
       </c>
       <c r="E157" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F157" t="n">
         <v>339.0</v>
@@ -6209,7 +6212,7 @@
         <v>673</v>
       </c>
       <c r="F159" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G159" t="n">
         <v>0.0</v>
@@ -6258,7 +6261,7 @@
         <v>672</v>
       </c>
       <c r="E161" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F161" t="n">
         <v>178.0</v>
@@ -6310,7 +6313,7 @@
         <v>672</v>
       </c>
       <c r="E163" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F163" t="n">
         <v>298.0</v>
@@ -6440,7 +6443,7 @@
         <v>672</v>
       </c>
       <c r="E168" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F168" t="n">
         <v>97.0</v>
@@ -6492,7 +6495,7 @@
         <v>672</v>
       </c>
       <c r="E170" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F170" t="n">
         <v>470.0</v>
@@ -6518,7 +6521,7 @@
         <v>672</v>
       </c>
       <c r="E171" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F171" t="n">
         <v>105.0</v>
@@ -6622,10 +6625,10 @@
         <v>672</v>
       </c>
       <c r="E175" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F175" t="n">
-        <v>549.0</v>
+        <v>550.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -6700,7 +6703,7 @@
         <v>672</v>
       </c>
       <c r="E178" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F178" t="n">
         <v>60.0</v>
@@ -6726,7 +6729,7 @@
         <v>672</v>
       </c>
       <c r="E179" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F179" t="n">
         <v>14.0</v>
@@ -6752,7 +6755,7 @@
         <v>672</v>
       </c>
       <c r="E180" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F180" t="n">
         <v>620.0</v>
@@ -6778,7 +6781,7 @@
         <v>672</v>
       </c>
       <c r="E181" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F181" t="n">
         <v>8.0</v>
@@ -6830,7 +6833,7 @@
         <v>672</v>
       </c>
       <c r="E183" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F183" t="n">
         <v>75.0</v>
@@ -6960,7 +6963,7 @@
         <v>672</v>
       </c>
       <c r="E188" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F188" t="n">
         <v>107.0</v>
@@ -6986,7 +6989,7 @@
         <v>672</v>
       </c>
       <c r="E189" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F189" t="n">
         <v>269.0</v>
@@ -7012,7 +7015,7 @@
         <v>672</v>
       </c>
       <c r="E190" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F190" t="n">
         <v>17.0</v>
@@ -7064,7 +7067,7 @@
         <v>672</v>
       </c>
       <c r="E192" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F192" t="n">
         <v>19.0</v>
@@ -7142,7 +7145,7 @@
         <v>672</v>
       </c>
       <c r="E195" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F195" t="n">
         <v>111.0</v>
@@ -7220,7 +7223,7 @@
         <v>672</v>
       </c>
       <c r="E198" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F198" t="n">
         <v>17.0</v>
@@ -7246,7 +7249,7 @@
         <v>672</v>
       </c>
       <c r="E199" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F199" t="n">
         <v>79.0</v>
@@ -7272,7 +7275,7 @@
         <v>672</v>
       </c>
       <c r="E200" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F200" t="n">
         <v>62.0</v>
@@ -7376,7 +7379,7 @@
         <v>672</v>
       </c>
       <c r="E204" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F204" t="n">
         <v>29.0</v>
@@ -7428,7 +7431,7 @@
         <v>672</v>
       </c>
       <c r="E206" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F206" t="n">
         <v>15.0</v>
@@ -7454,7 +7457,7 @@
         <v>672</v>
       </c>
       <c r="E207" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F207" t="n">
         <v>7.0</v>
@@ -7506,7 +7509,7 @@
         <v>672</v>
       </c>
       <c r="E209" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F209" t="n">
         <v>205.0</v>
@@ -7532,7 +7535,7 @@
         <v>672</v>
       </c>
       <c r="E210" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F210" t="n">
         <v>187.0</v>
@@ -7792,10 +7795,10 @@
         <v>672</v>
       </c>
       <c r="E220" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F220" t="n">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="G220" t="n">
         <v>0.0</v>
@@ -7844,7 +7847,7 @@
         <v>672</v>
       </c>
       <c r="E222" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F222" t="n">
         <v>15.0</v>
@@ -7948,7 +7951,7 @@
         <v>672</v>
       </c>
       <c r="E226" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F226" t="n">
         <v>94.0</v>
@@ -7974,7 +7977,7 @@
         <v>672</v>
       </c>
       <c r="E227" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F227" t="n">
         <v>32.0</v>
@@ -8000,7 +8003,7 @@
         <v>672</v>
       </c>
       <c r="E228" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F228" t="n">
         <v>51.0</v>
@@ -8026,7 +8029,7 @@
         <v>672</v>
       </c>
       <c r="E229" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F229" t="n">
         <v>25.0</v>
@@ -8078,7 +8081,7 @@
         <v>672</v>
       </c>
       <c r="E231" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F231" t="n">
         <v>0.0</v>
@@ -8130,7 +8133,7 @@
         <v>672</v>
       </c>
       <c r="E233" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F233" t="n">
         <v>87.0</v>
@@ -8182,7 +8185,7 @@
         <v>672</v>
       </c>
       <c r="E235" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F235" t="n">
         <v>86.0</v>
@@ -8364,7 +8367,7 @@
         <v>672</v>
       </c>
       <c r="E242" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F242" t="n">
         <v>6.0</v>
@@ -8523,7 +8526,7 @@
         <v>673</v>
       </c>
       <c r="F248" t="n">
-        <v>921.0</v>
+        <v>923.0</v>
       </c>
       <c r="G248" t="n">
         <v>16.0</v>
@@ -8676,7 +8679,7 @@
         <v>672</v>
       </c>
       <c r="E254" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F254" t="n">
         <v>4.0</v>
@@ -8731,7 +8734,7 @@
         <v>673</v>
       </c>
       <c r="F256" t="n">
-        <v>225.0</v>
+        <v>224.0</v>
       </c>
       <c r="G256" t="n">
         <v>0.0</v>
@@ -8991,7 +8994,7 @@
         <v>673</v>
       </c>
       <c r="F266" t="n">
-        <v>167.0</v>
+        <v>163.0</v>
       </c>
       <c r="G266" t="n">
         <v>0.0</v>
@@ -9014,7 +9017,7 @@
         <v>672</v>
       </c>
       <c r="E267" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F267" t="n">
         <v>111.0</v>
@@ -9092,7 +9095,7 @@
         <v>672</v>
       </c>
       <c r="E270" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F270" t="n">
         <v>90.0</v>
@@ -9118,7 +9121,7 @@
         <v>672</v>
       </c>
       <c r="E271" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F271" t="n">
         <v>0.0</v>
@@ -9144,7 +9147,7 @@
         <v>672</v>
       </c>
       <c r="E272" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F272" t="n">
         <v>70.0</v>
@@ -9170,7 +9173,7 @@
         <v>672</v>
       </c>
       <c r="E273" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F273" t="n">
         <v>78.0</v>
@@ -9196,7 +9199,7 @@
         <v>672</v>
       </c>
       <c r="E274" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F274" t="n">
         <v>66.0</v>
@@ -9352,7 +9355,7 @@
         <v>672</v>
       </c>
       <c r="E280" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F280" t="n">
         <v>282.0</v>
@@ -9430,7 +9433,7 @@
         <v>672</v>
       </c>
       <c r="E283" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F283" t="n">
         <v>11.0</v>
@@ -9482,7 +9485,7 @@
         <v>672</v>
       </c>
       <c r="E285" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F285" t="n">
         <v>206.0</v>
@@ -9586,7 +9589,7 @@
         <v>672</v>
       </c>
       <c r="E289" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F289" t="n">
         <v>63.0</v>
@@ -9638,7 +9641,7 @@
         <v>672</v>
       </c>
       <c r="E291" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F291" t="n">
         <v>386.0</v>
@@ -9664,7 +9667,7 @@
         <v>672</v>
       </c>
       <c r="E292" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F292" t="n">
         <v>59.0</v>
@@ -9872,7 +9875,7 @@
         <v>672</v>
       </c>
       <c r="E300" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F300" t="n">
         <v>12.0</v>
@@ -10106,7 +10109,7 @@
         <v>672</v>
       </c>
       <c r="E309" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F309" t="n">
         <v>66.0</v>
@@ -10158,7 +10161,7 @@
         <v>672</v>
       </c>
       <c r="E311" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F311" t="n">
         <v>7.0</v>
@@ -10288,7 +10291,7 @@
         <v>672</v>
       </c>
       <c r="E316" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F316" t="n">
         <v>6.0</v>
@@ -10522,7 +10525,7 @@
         <v>672</v>
       </c>
       <c r="E325" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F325" t="n">
         <v>191.0</v>
@@ -10574,7 +10577,7 @@
         <v>672</v>
       </c>
       <c r="E327" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F327" t="n">
         <v>0.0</v>
@@ -10652,7 +10655,7 @@
         <v>672</v>
       </c>
       <c r="E330" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F330" t="n">
         <v>50.0</v>
@@ -10678,7 +10681,7 @@
         <v>672</v>
       </c>
       <c r="E331" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F331" t="n">
         <v>123.0</v>
@@ -10704,7 +10707,7 @@
         <v>672</v>
       </c>
       <c r="E332" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F332" t="n">
         <v>28.0</v>
@@ -10730,7 +10733,7 @@
         <v>672</v>
       </c>
       <c r="E333" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F333" t="n">
         <v>20.0</v>
@@ -10782,7 +10785,7 @@
         <v>672</v>
       </c>
       <c r="E335" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F335" t="n">
         <v>37.0</v>
@@ -10808,7 +10811,7 @@
         <v>672</v>
       </c>
       <c r="E336" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F336" t="n">
         <v>0.0</v>
@@ -10860,7 +10863,7 @@
         <v>672</v>
       </c>
       <c r="E338" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F338" t="n">
         <v>2.0</v>
@@ -10886,7 +10889,7 @@
         <v>672</v>
       </c>
       <c r="E339" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F339" t="n">
         <v>8.0</v>
@@ -11042,7 +11045,7 @@
         <v>672</v>
       </c>
       <c r="E345" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F345" t="n">
         <v>507.0</v>
@@ -11123,7 +11126,7 @@
         <v>673</v>
       </c>
       <c r="F348" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G348" t="n">
         <v>0.0</v>
@@ -11250,7 +11253,7 @@
         <v>672</v>
       </c>
       <c r="E353" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F353" t="n">
         <v>93.0</v>
@@ -11354,7 +11357,7 @@
         <v>672</v>
       </c>
       <c r="E357" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F357" t="n">
         <v>163.0</v>
@@ -11380,7 +11383,7 @@
         <v>672</v>
       </c>
       <c r="E358" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F358" t="n">
         <v>14.0</v>
@@ -11432,7 +11435,7 @@
         <v>672</v>
       </c>
       <c r="E360" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F360" t="n">
         <v>23.0</v>
@@ -11458,7 +11461,7 @@
         <v>672</v>
       </c>
       <c r="E361" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F361" t="n">
         <v>59.0</v>
@@ -11484,7 +11487,7 @@
         <v>672</v>
       </c>
       <c r="E362" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F362" t="n">
         <v>4.0</v>
@@ -11536,7 +11539,7 @@
         <v>672</v>
       </c>
       <c r="E364" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F364" t="n">
         <v>93.0</v>
@@ -11588,7 +11591,7 @@
         <v>672</v>
       </c>
       <c r="E366" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F366" t="n">
         <v>6.0</v>
@@ -11666,7 +11669,7 @@
         <v>672</v>
       </c>
       <c r="E369" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F369" t="n">
         <v>112.0</v>
@@ -11718,7 +11721,7 @@
         <v>672</v>
       </c>
       <c r="E371" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F371" t="n">
         <v>31.0</v>
@@ -11770,7 +11773,7 @@
         <v>672</v>
       </c>
       <c r="E373" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F373" t="n">
         <v>1.0</v>
@@ -11796,7 +11799,7 @@
         <v>672</v>
       </c>
       <c r="E374" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F374" t="n">
         <v>13.0</v>
@@ -11822,7 +11825,7 @@
         <v>672</v>
       </c>
       <c r="E375" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F375" t="n">
         <v>20.0</v>
@@ -11952,7 +11955,7 @@
         <v>672</v>
       </c>
       <c r="E380" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F380" t="n">
         <v>17.0</v>
@@ -11981,7 +11984,7 @@
         <v>673</v>
       </c>
       <c r="F381" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G381" t="n">
         <v>1.0</v>
@@ -12082,10 +12085,10 @@
         <v>672</v>
       </c>
       <c r="E385" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F385" t="n">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12238,7 +12241,7 @@
         <v>672</v>
       </c>
       <c r="E391" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F391" t="n">
         <v>6.0</v>
@@ -12264,7 +12267,7 @@
         <v>672</v>
       </c>
       <c r="E392" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F392" t="n">
         <v>6.0</v>
@@ -12316,7 +12319,7 @@
         <v>672</v>
       </c>
       <c r="E394" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F394" t="n">
         <v>70.0</v>
@@ -12394,7 +12397,7 @@
         <v>672</v>
       </c>
       <c r="E397" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F397" t="n">
         <v>0.0</v>
@@ -12654,7 +12657,7 @@
         <v>672</v>
       </c>
       <c r="E407" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F407" t="n">
         <v>219.0</v>
@@ -12784,7 +12787,7 @@
         <v>672</v>
       </c>
       <c r="E412" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F412" t="n">
         <v>46.0</v>
@@ -12836,7 +12839,7 @@
         <v>672</v>
       </c>
       <c r="E414" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F414" t="n">
         <v>22.0</v>
@@ -12862,7 +12865,7 @@
         <v>672</v>
       </c>
       <c r="E415" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F415" t="n">
         <v>98.0</v>
@@ -12966,7 +12969,7 @@
         <v>672</v>
       </c>
       <c r="E419" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F419" t="n">
         <v>3.0</v>
@@ -13018,7 +13021,7 @@
         <v>672</v>
       </c>
       <c r="E421" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F421" t="n">
         <v>79.0</v>
@@ -13278,7 +13281,7 @@
         <v>672</v>
       </c>
       <c r="E431" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F431" t="n">
         <v>136.0</v>
@@ -13359,7 +13362,7 @@
         <v>673</v>
       </c>
       <c r="F434" t="n">
-        <v>62.0</v>
+        <v>61.0</v>
       </c>
       <c r="G434" t="n">
         <v>0.0</v>
@@ -13408,7 +13411,7 @@
         <v>672</v>
       </c>
       <c r="E436" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F436" t="n">
         <v>193.0</v>
@@ -13616,7 +13619,7 @@
         <v>672</v>
       </c>
       <c r="E444" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F444" t="n">
         <v>0.0</v>
@@ -13642,10 +13645,10 @@
         <v>672</v>
       </c>
       <c r="E445" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F445" t="n">
-        <v>519.0</v>
+        <v>518.0</v>
       </c>
       <c r="G445" t="n">
         <v>3.0</v>
@@ -13668,7 +13671,7 @@
         <v>672</v>
       </c>
       <c r="E446" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F446" t="n">
         <v>183.0</v>
@@ -13746,7 +13749,7 @@
         <v>672</v>
       </c>
       <c r="E449" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F449" t="n">
         <v>129.0</v>
@@ -13775,7 +13778,7 @@
         <v>673</v>
       </c>
       <c r="F450" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G450" t="n">
         <v>0.0</v>
@@ -13902,7 +13905,7 @@
         <v>672</v>
       </c>
       <c r="E455" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F455" t="n">
         <v>5.0</v>
@@ -13980,7 +13983,7 @@
         <v>672</v>
       </c>
       <c r="E458" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F458" t="n">
         <v>64.0</v>
@@ -14110,7 +14113,7 @@
         <v>672</v>
       </c>
       <c r="E463" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F463" t="n">
         <v>224.0</v>
@@ -14136,7 +14139,7 @@
         <v>672</v>
       </c>
       <c r="E464" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F464" t="n">
         <v>32.0</v>
@@ -14188,7 +14191,7 @@
         <v>672</v>
       </c>
       <c r="E466" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F466" t="n">
         <v>68.0</v>
@@ -14318,7 +14321,7 @@
         <v>672</v>
       </c>
       <c r="E471" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F471" t="n">
         <v>0.0</v>
@@ -14344,7 +14347,7 @@
         <v>672</v>
       </c>
       <c r="E472" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F472" t="n">
         <v>143.0</v>
@@ -14396,7 +14399,7 @@
         <v>672</v>
       </c>
       <c r="E474" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F474" t="n">
         <v>76.0</v>
@@ -14474,7 +14477,7 @@
         <v>672</v>
       </c>
       <c r="E477" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F477" t="n">
         <v>40.0</v>
@@ -14552,7 +14555,7 @@
         <v>672</v>
       </c>
       <c r="E480" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F480" t="n">
         <v>101.0</v>
@@ -14630,7 +14633,7 @@
         <v>672</v>
       </c>
       <c r="E483" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F483" t="n">
         <v>9.0</v>
@@ -14942,7 +14945,7 @@
         <v>672</v>
       </c>
       <c r="E495" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F495" t="n">
         <v>62.0</v>
@@ -14968,7 +14971,7 @@
         <v>672</v>
       </c>
       <c r="E496" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F496" t="n">
         <v>215.0</v>
@@ -15049,7 +15052,7 @@
         <v>673</v>
       </c>
       <c r="F499" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -15072,7 +15075,7 @@
         <v>672</v>
       </c>
       <c r="E500" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F500" t="n">
         <v>20.0</v>
@@ -15101,7 +15104,7 @@
         <v>673</v>
       </c>
       <c r="F501" t="n">
-        <v>395.0</v>
+        <v>399.0</v>
       </c>
       <c r="G501" t="n">
         <v>9.0</v>
@@ -15124,7 +15127,7 @@
         <v>672</v>
       </c>
       <c r="E502" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F502" t="n">
         <v>20.0</v>
@@ -15306,7 +15309,7 @@
         <v>672</v>
       </c>
       <c r="E509" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F509" t="n">
         <v>50.0</v>
@@ -15358,7 +15361,7 @@
         <v>672</v>
       </c>
       <c r="E511" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F511" t="n">
         <v>142.0</v>
@@ -15384,7 +15387,7 @@
         <v>672</v>
       </c>
       <c r="E512" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F512" t="n">
         <v>16.0</v>
@@ -15462,7 +15465,7 @@
         <v>672</v>
       </c>
       <c r="E515" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F515" t="n">
         <v>308.0</v>
@@ -15540,7 +15543,7 @@
         <v>672</v>
       </c>
       <c r="E518" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F518" t="n">
         <v>245.0</v>
@@ -15725,7 +15728,7 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>403.0</v>
+        <v>405.0</v>
       </c>
       <c r="G525" t="n">
         <v>3.0</v>
@@ -15748,7 +15751,7 @@
         <v>672</v>
       </c>
       <c r="E526" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F526" t="n">
         <v>203.0</v>
@@ -15800,7 +15803,7 @@
         <v>672</v>
       </c>
       <c r="E528" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F528" t="n">
         <v>129.0</v>
@@ -15907,7 +15910,7 @@
         <v>673</v>
       </c>
       <c r="F532" t="n">
-        <v>343.0</v>
+        <v>344.0</v>
       </c>
       <c r="G532" t="n">
         <v>0.0</v>
@@ -15930,7 +15933,7 @@
         <v>672</v>
       </c>
       <c r="E533" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F533" t="n">
         <v>2.0</v>
@@ -16008,7 +16011,7 @@
         <v>672</v>
       </c>
       <c r="E536" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F536" t="n">
         <v>47.0</v>
@@ -16034,7 +16037,7 @@
         <v>672</v>
       </c>
       <c r="E537" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F537" t="n">
         <v>529.0</v>
@@ -16060,7 +16063,7 @@
         <v>672</v>
       </c>
       <c r="E538" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F538" t="n">
         <v>92.0</v>
@@ -16069,7 +16072,7 @@
         <v>3.0</v>
       </c>
       <c r="H538" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="539">
@@ -16242,7 +16245,7 @@
         <v>672</v>
       </c>
       <c r="E545" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F545" t="n">
         <v>111.0</v>
@@ -16268,7 +16271,7 @@
         <v>672</v>
       </c>
       <c r="E546" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F546" t="n">
         <v>6.0</v>
@@ -16294,7 +16297,7 @@
         <v>672</v>
       </c>
       <c r="E547" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F547" t="n">
         <v>257.0</v>
@@ -16320,7 +16323,7 @@
         <v>672</v>
       </c>
       <c r="E548" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F548" t="n">
         <v>0.0</v>
@@ -16346,7 +16349,7 @@
         <v>672</v>
       </c>
       <c r="E549" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F549" t="n">
         <v>17.0</v>
@@ -16398,7 +16401,7 @@
         <v>672</v>
       </c>
       <c r="E551" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F551" t="n">
         <v>60.0</v>
@@ -16424,7 +16427,7 @@
         <v>672</v>
       </c>
       <c r="E552" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F552" t="n">
         <v>53.0</v>
@@ -16450,7 +16453,7 @@
         <v>672</v>
       </c>
       <c r="E553" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F553" t="n">
         <v>286.0</v>
@@ -16502,7 +16505,7 @@
         <v>672</v>
       </c>
       <c r="E555" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F555" t="n">
         <v>20.0</v>
@@ -16528,7 +16531,7 @@
         <v>672</v>
       </c>
       <c r="E556" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F556" t="n">
         <v>70.0</v>
@@ -16606,7 +16609,7 @@
         <v>672</v>
       </c>
       <c r="E559" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F559" t="n">
         <v>15.0</v>
@@ -16658,7 +16661,7 @@
         <v>672</v>
       </c>
       <c r="E561" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F561" t="n">
         <v>0.0</v>
@@ -16684,7 +16687,7 @@
         <v>672</v>
       </c>
       <c r="E562" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F562" t="n">
         <v>275.0</v>
@@ -16710,7 +16713,7 @@
         <v>672</v>
       </c>
       <c r="E563" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F563" t="n">
         <v>87.0</v>
@@ -16892,7 +16895,7 @@
         <v>672</v>
       </c>
       <c r="E570" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F570" t="n">
         <v>26.0</v>
@@ -16944,7 +16947,7 @@
         <v>672</v>
       </c>
       <c r="E572" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F572" t="n">
         <v>357.0</v>
@@ -17048,7 +17051,7 @@
         <v>672</v>
       </c>
       <c r="E576" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F576" t="n">
         <v>6.0</v>
@@ -17204,7 +17207,7 @@
         <v>672</v>
       </c>
       <c r="E582" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F582" t="n">
         <v>36.0</v>
@@ -17282,10 +17285,10 @@
         <v>672</v>
       </c>
       <c r="E585" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F585" t="n">
-        <v>344.0</v>
+        <v>347.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17334,7 +17337,7 @@
         <v>672</v>
       </c>
       <c r="E587" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F587" t="n">
         <v>1.0</v>
@@ -17412,7 +17415,7 @@
         <v>672</v>
       </c>
       <c r="E590" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F590" t="n">
         <v>1.0</v>
@@ -17464,7 +17467,7 @@
         <v>672</v>
       </c>
       <c r="E592" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F592" t="n">
         <v>66.0</v>
@@ -17620,7 +17623,7 @@
         <v>672</v>
       </c>
       <c r="E598" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F598" t="n">
         <v>15.0</v>
@@ -17646,7 +17649,7 @@
         <v>672</v>
       </c>
       <c r="E599" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F599" t="n">
         <v>78.0</v>
@@ -17698,7 +17701,7 @@
         <v>672</v>
       </c>
       <c r="E601" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F601" t="n">
         <v>21.0</v>
@@ -17776,7 +17779,7 @@
         <v>672</v>
       </c>
       <c r="E604" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F604" t="n">
         <v>35.0</v>
@@ -17828,7 +17831,7 @@
         <v>672</v>
       </c>
       <c r="E606" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F606" t="n">
         <v>171.0</v>
@@ -17854,7 +17857,7 @@
         <v>672</v>
       </c>
       <c r="E607" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F607" t="n">
         <v>18.0</v>
@@ -17932,7 +17935,7 @@
         <v>672</v>
       </c>
       <c r="E610" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F610" t="n">
         <v>80.0</v>
@@ -18088,7 +18091,7 @@
         <v>672</v>
       </c>
       <c r="E616" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F616" t="n">
         <v>3.0</v>
@@ -18140,7 +18143,7 @@
         <v>672</v>
       </c>
       <c r="E618" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F618" t="n">
         <v>17.0</v>
@@ -18192,7 +18195,7 @@
         <v>672</v>
       </c>
       <c r="E620" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F620" t="n">
         <v>50.0</v>
@@ -18322,7 +18325,7 @@
         <v>672</v>
       </c>
       <c r="E625" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F625" t="n">
         <v>0.0</v>
@@ -18634,7 +18637,7 @@
         <v>672</v>
       </c>
       <c r="E637" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F637" t="n">
         <v>60.0</v>
@@ -18660,7 +18663,7 @@
         <v>672</v>
       </c>
       <c r="E638" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F638" t="n">
         <v>105.0</v>
@@ -18738,7 +18741,7 @@
         <v>672</v>
       </c>
       <c r="E641" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F641" t="n">
         <v>92.0</v>
@@ -18764,7 +18767,7 @@
         <v>672</v>
       </c>
       <c r="E642" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F642" t="n">
         <v>106.0</v>
@@ -18790,7 +18793,7 @@
         <v>672</v>
       </c>
       <c r="E643" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F643" t="n">
         <v>53.0</v>
@@ -18816,7 +18819,7 @@
         <v>672</v>
       </c>
       <c r="E644" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F644" t="n">
         <v>102.0</v>
@@ -18842,7 +18845,7 @@
         <v>672</v>
       </c>
       <c r="E645" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F645" t="n">
         <v>42.0</v>
@@ -18868,7 +18871,7 @@
         <v>672</v>
       </c>
       <c r="E646" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F646" t="n">
         <v>43.0</v>
@@ -18894,7 +18897,7 @@
         <v>672</v>
       </c>
       <c r="E647" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F647" t="n">
         <v>48.0</v>
@@ -18920,7 +18923,7 @@
         <v>672</v>
       </c>
       <c r="E648" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F648" t="n">
         <v>70.0</v>
@@ -19050,7 +19053,7 @@
         <v>672</v>
       </c>
       <c r="E653" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F653" t="n">
         <v>50.0</v>
@@ -19076,7 +19079,7 @@
         <v>672</v>
       </c>
       <c r="E654" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F654" t="n">
         <v>52.0</v>
@@ -19102,7 +19105,7 @@
         <v>672</v>
       </c>
       <c r="E655" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F655" t="n">
         <v>89.0</v>
@@ -19128,7 +19131,7 @@
         <v>672</v>
       </c>
       <c r="E656" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F656" t="n">
         <v>115.0</v>
@@ -19154,7 +19157,7 @@
         <v>672</v>
       </c>
       <c r="E657" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F657" t="n">
         <v>49.0</v>
@@ -19206,7 +19209,7 @@
         <v>672</v>
       </c>
       <c r="E659" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F659" t="n">
         <v>37.0</v>
@@ -19284,7 +19287,7 @@
         <v>672</v>
       </c>
       <c r="E662" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F662" t="n">
         <v>53.0</v>
@@ -19336,7 +19339,7 @@
         <v>672</v>
       </c>
       <c r="E664" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F664" t="n">
         <v>146.0</v>
@@ -19362,7 +19365,7 @@
         <v>672</v>
       </c>
       <c r="E665" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F665" t="n">
         <v>46.0</v>
@@ -19414,7 +19417,7 @@
         <v>672</v>
       </c>
       <c r="E667" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F667" t="n">
         <v>124.0</v>
@@ -19440,7 +19443,7 @@
         <v>672</v>
       </c>
       <c r="E668" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F668" t="n">
         <v>334.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2260,7 +2260,7 @@
         <v>673</v>
       </c>
       <c r="F7" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -2442,7 +2442,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>417.0</v>
+        <v>420.0</v>
       </c>
       <c r="G14" t="n">
         <v>5.0</v>
@@ -2494,7 +2494,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2624,7 +2624,7 @@
         <v>675</v>
       </c>
       <c r="F21" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2731,7 +2731,7 @@
         <v>10.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H25" t="n">
         <v>6.0</v>
@@ -2910,7 +2910,7 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>455.0</v>
+        <v>456.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3014,7 +3014,7 @@
         <v>675</v>
       </c>
       <c r="F36" t="n">
-        <v>291.0</v>
+        <v>300.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -3404,7 +3404,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3560,7 +3560,7 @@
         <v>673</v>
       </c>
       <c r="F57" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -3898,7 +3898,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -3976,7 +3976,7 @@
         <v>675</v>
       </c>
       <c r="F73" t="n">
-        <v>336.0</v>
+        <v>338.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4054,7 +4054,7 @@
         <v>673</v>
       </c>
       <c r="F76" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G76" t="n">
         <v>15.0</v>
@@ -4109,7 +4109,7 @@
         <v>36.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -4548,7 +4548,7 @@
         <v>675</v>
       </c>
       <c r="F95" t="n">
-        <v>372.0</v>
+        <v>374.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4652,10 +4652,10 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>463.0</v>
+        <v>464.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H99" t="n">
         <v>2.0</v>
@@ -4912,7 +4912,7 @@
         <v>673</v>
       </c>
       <c r="F109" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -5614,10 +5614,10 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>614.0</v>
+        <v>617.0</v>
       </c>
       <c r="G136" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H136" t="n">
         <v>2.0</v>
@@ -5900,7 +5900,7 @@
         <v>673</v>
       </c>
       <c r="F147" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -5926,7 +5926,7 @@
         <v>675</v>
       </c>
       <c r="F148" t="n">
-        <v>128.0</v>
+        <v>133.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6602,13 +6602,13 @@
         <v>673</v>
       </c>
       <c r="F174" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G174" t="n">
         <v>1.0</v>
       </c>
       <c r="H174" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="175">
@@ -6758,7 +6758,7 @@
         <v>675</v>
       </c>
       <c r="F180" t="n">
-        <v>620.0</v>
+        <v>624.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -7229,7 +7229,7 @@
         <v>17.0</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H198" t="n">
         <v>0.0</v>
@@ -7590,7 +7590,7 @@
         <v>673</v>
       </c>
       <c r="F212" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -8266,7 +8266,7 @@
         <v>673</v>
       </c>
       <c r="F238" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G238" t="n">
         <v>0.0</v>
@@ -8916,7 +8916,7 @@
         <v>673</v>
       </c>
       <c r="F263" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -9546,7 +9546,7 @@
         <v>0.0</v>
       </c>
       <c r="H287" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="288">
@@ -9930,7 +9930,7 @@
         <v>673</v>
       </c>
       <c r="F302" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G302" t="n">
         <v>0.0</v>
@@ -9962,7 +9962,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="304">
@@ -11028,7 +11028,7 @@
         <v>0.0</v>
       </c>
       <c r="H344" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="345">
@@ -11620,7 +11620,7 @@
         <v>673</v>
       </c>
       <c r="F367" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="G367" t="n">
         <v>0.0</v>
@@ -11672,7 +11672,7 @@
         <v>675</v>
       </c>
       <c r="F369" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G369" t="n">
         <v>0.0</v>
@@ -12088,7 +12088,7 @@
         <v>675</v>
       </c>
       <c r="F385" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12348,7 +12348,7 @@
         <v>673</v>
       </c>
       <c r="F395" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G395" t="n">
         <v>9.0</v>
@@ -13206,7 +13206,7 @@
         <v>673</v>
       </c>
       <c r="F428" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -13726,7 +13726,7 @@
         <v>673</v>
       </c>
       <c r="F448" t="n">
-        <v>158.0</v>
+        <v>160.0</v>
       </c>
       <c r="G448" t="n">
         <v>7.0</v>
@@ -14038,7 +14038,7 @@
         <v>673</v>
       </c>
       <c r="F460" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G460" t="n">
         <v>0.0</v>
@@ -14298,7 +14298,7 @@
         <v>673</v>
       </c>
       <c r="F470" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="G470" t="n">
         <v>2.0</v>
@@ -14766,7 +14766,7 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2292.0</v>
+        <v>2294.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
@@ -15260,7 +15260,7 @@
         <v>673</v>
       </c>
       <c r="F507" t="n">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15546,7 +15546,7 @@
         <v>675</v>
       </c>
       <c r="F518" t="n">
-        <v>245.0</v>
+        <v>247.0</v>
       </c>
       <c r="G518" t="n">
         <v>0.0</v>
@@ -15598,7 +15598,7 @@
         <v>673</v>
       </c>
       <c r="F520" t="n">
-        <v>115.0</v>
+        <v>118.0</v>
       </c>
       <c r="G520" t="n">
         <v>1.0</v>
@@ -16040,7 +16040,7 @@
         <v>675</v>
       </c>
       <c r="F537" t="n">
-        <v>529.0</v>
+        <v>534.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16300,7 +16300,7 @@
         <v>675</v>
       </c>
       <c r="F547" t="n">
-        <v>257.0</v>
+        <v>259.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16950,7 +16950,7 @@
         <v>675</v>
       </c>
       <c r="F572" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17210,7 +17210,7 @@
         <v>675</v>
       </c>
       <c r="F582" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -17808,7 +17808,7 @@
         <v>673</v>
       </c>
       <c r="F605" t="n">
-        <v>153.0</v>
+        <v>157.0</v>
       </c>
       <c r="G605" t="n">
         <v>0.0</v>
@@ -17834,7 +17834,7 @@
         <v>675</v>
       </c>
       <c r="F606" t="n">
-        <v>171.0</v>
+        <v>178.0</v>
       </c>
       <c r="G606" t="n">
         <v>0.0</v>
@@ -18406,7 +18406,7 @@
         <v>673</v>
       </c>
       <c r="F628" t="n">
-        <v>99.0</v>
+        <v>106.0</v>
       </c>
       <c r="G628" t="n">
         <v>0.0</v>
@@ -18692,7 +18692,7 @@
         <v>673</v>
       </c>
       <c r="F639" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G639" t="n">
         <v>0.0</v>
@@ -18770,7 +18770,7 @@
         <v>675</v>
       </c>
       <c r="F642" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -19160,7 +19160,7 @@
         <v>675</v>
       </c>
       <c r="F657" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G657" t="n">
         <v>0.0</v>
@@ -19316,7 +19316,7 @@
         <v>673</v>
       </c>
       <c r="F663" t="n">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19394,7 +19394,7 @@
         <v>673</v>
       </c>
       <c r="F666" t="n">
-        <v>275.0</v>
+        <v>277.0</v>
       </c>
       <c r="G666" t="n">
         <v>2.0</v>
@@ -19446,7 +19446,7 @@
         <v>675</v>
       </c>
       <c r="F668" t="n">
-        <v>334.0</v>
+        <v>336.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2130,7 +2130,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>525.0</v>
+        <v>527.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2442,7 +2442,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
       <c r="G14" t="n">
         <v>5.0</v>
@@ -2494,7 +2494,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>360.0</v>
+        <v>363.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2520,7 +2520,7 @@
         <v>674</v>
       </c>
       <c r="F17" t="n">
-        <v>247.0</v>
+        <v>249.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -2910,13 +2910,13 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>456.0</v>
+        <v>457.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="33">
@@ -2936,7 +2936,7 @@
         <v>673</v>
       </c>
       <c r="F33" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -3898,7 +3898,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4340,7 +4340,7 @@
         <v>675</v>
       </c>
       <c r="F87" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -4548,7 +4548,7 @@
         <v>675</v>
       </c>
       <c r="F95" t="n">
-        <v>374.0</v>
+        <v>375.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4652,7 +4652,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>464.0</v>
+        <v>466.0</v>
       </c>
       <c r="G99" t="n">
         <v>2.0</v>
@@ -5614,7 +5614,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>617.0</v>
+        <v>620.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -5900,7 +5900,7 @@
         <v>673</v>
       </c>
       <c r="F147" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -6316,7 +6316,7 @@
         <v>673</v>
       </c>
       <c r="F163" t="n">
-        <v>298.0</v>
+        <v>299.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6472,7 +6472,7 @@
         <v>673</v>
       </c>
       <c r="F169" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6498,7 +6498,7 @@
         <v>675</v>
       </c>
       <c r="F170" t="n">
-        <v>470.0</v>
+        <v>475.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6524,7 +6524,7 @@
         <v>675</v>
       </c>
       <c r="F171" t="n">
-        <v>105.0</v>
+        <v>107.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -6608,7 +6608,7 @@
         <v>1.0</v>
       </c>
       <c r="H174" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="175">
@@ -6628,7 +6628,7 @@
         <v>675</v>
       </c>
       <c r="F175" t="n">
-        <v>550.0</v>
+        <v>553.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -7096,7 +7096,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>986.0</v>
+        <v>987.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -8188,7 +8188,7 @@
         <v>674</v>
       </c>
       <c r="F235" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G235" t="n">
         <v>1.0</v>
@@ -8526,7 +8526,7 @@
         <v>673</v>
       </c>
       <c r="F248" t="n">
-        <v>923.0</v>
+        <v>927.0</v>
       </c>
       <c r="G248" t="n">
         <v>16.0</v>
@@ -9020,7 +9020,7 @@
         <v>674</v>
       </c>
       <c r="F267" t="n">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9904,7 +9904,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>466.0</v>
+        <v>469.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -9956,7 +9956,7 @@
         <v>673</v>
       </c>
       <c r="F303" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G303" t="n">
         <v>0.0</v>
@@ -10063,7 +10063,7 @@
         <v>521.0</v>
       </c>
       <c r="G307" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H307" t="n">
         <v>7.0</v>
@@ -10216,7 +10216,7 @@
         <v>673</v>
       </c>
       <c r="F313" t="n">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="G313" t="n">
         <v>1.0</v>
@@ -10450,7 +10450,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>381.0</v>
+        <v>382.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11048,7 +11048,7 @@
         <v>675</v>
       </c>
       <c r="F345" t="n">
-        <v>507.0</v>
+        <v>508.0</v>
       </c>
       <c r="G345" t="n">
         <v>1.0</v>
@@ -11360,7 +11360,7 @@
         <v>675</v>
       </c>
       <c r="F357" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="G357" t="n">
         <v>0.0</v>
@@ -11750,7 +11750,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -12088,7 +12088,7 @@
         <v>675</v>
       </c>
       <c r="F385" t="n">
-        <v>57.0</v>
+        <v>60.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12354,7 +12354,7 @@
         <v>9.0</v>
       </c>
       <c r="H395" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="396">
@@ -13414,7 +13414,7 @@
         <v>674</v>
       </c>
       <c r="F436" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G436" t="n">
         <v>0.0</v>
@@ -14064,7 +14064,7 @@
         <v>673</v>
       </c>
       <c r="F461" t="n">
-        <v>530.0</v>
+        <v>531.0</v>
       </c>
       <c r="G461" t="n">
         <v>0.0</v>
@@ -14116,7 +14116,7 @@
         <v>675</v>
       </c>
       <c r="F463" t="n">
-        <v>224.0</v>
+        <v>226.0</v>
       </c>
       <c r="G463" t="n">
         <v>1.0</v>
@@ -14428,7 +14428,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>531.0</v>
+        <v>533.0</v>
       </c>
       <c r="G475" t="n">
         <v>2.0</v>
@@ -15026,7 +15026,7 @@
         <v>673</v>
       </c>
       <c r="F498" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G498" t="n">
         <v>1.0</v>
@@ -15416,7 +15416,7 @@
         <v>673</v>
       </c>
       <c r="F513" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G513" t="n">
         <v>0.0</v>
@@ -16456,7 +16456,7 @@
         <v>673</v>
       </c>
       <c r="F553" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -18874,7 +18874,7 @@
         <v>675</v>
       </c>
       <c r="F646" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -18926,7 +18926,7 @@
         <v>675</v>
       </c>
       <c r="F648" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -19082,7 +19082,7 @@
         <v>675</v>
       </c>
       <c r="F654" t="n">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19108,7 +19108,7 @@
         <v>675</v>
       </c>
       <c r="F655" t="n">
-        <v>89.0</v>
+        <v>91.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19134,7 +19134,7 @@
         <v>675</v>
       </c>
       <c r="F656" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19264,7 +19264,7 @@
         <v>673</v>
       </c>
       <c r="F661" t="n">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19290,7 +19290,7 @@
         <v>675</v>
       </c>
       <c r="F662" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19342,7 +19342,7 @@
         <v>675</v>
       </c>
       <c r="F664" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G664" t="n">
         <v>1.0</v>
@@ -19472,7 +19472,7 @@
         <v>673</v>
       </c>
       <c r="F669" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4990,7 +4990,7 @@
         <v>673</v>
       </c>
       <c r="F112" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G112" t="n">
         <v>0.0</v>
@@ -5770,7 +5770,7 @@
         <v>673</v>
       </c>
       <c r="F142" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -6212,7 +6212,7 @@
         <v>673</v>
       </c>
       <c r="F159" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G159" t="n">
         <v>0.0</v>
@@ -6576,7 +6576,7 @@
         <v>673</v>
       </c>
       <c r="F173" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G173" t="n">
         <v>0.0</v>
@@ -7096,7 +7096,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>987.0</v>
+        <v>988.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -7954,7 +7954,7 @@
         <v>675</v>
       </c>
       <c r="F226" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8526,7 +8526,7 @@
         <v>673</v>
       </c>
       <c r="F248" t="n">
-        <v>927.0</v>
+        <v>928.0</v>
       </c>
       <c r="G248" t="n">
         <v>16.0</v>
@@ -9020,7 +9020,7 @@
         <v>674</v>
       </c>
       <c r="F267" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9306,7 +9306,7 @@
         <v>673</v>
       </c>
       <c r="F278" t="n">
-        <v>533.0</v>
+        <v>534.0</v>
       </c>
       <c r="G278" t="n">
         <v>6.0</v>
@@ -9748,7 +9748,7 @@
         <v>673</v>
       </c>
       <c r="F295" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G295" t="n">
         <v>2.0</v>
@@ -11048,7 +11048,7 @@
         <v>675</v>
       </c>
       <c r="F345" t="n">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
       <c r="G345" t="n">
         <v>1.0</v>
@@ -11698,7 +11698,7 @@
         <v>673</v>
       </c>
       <c r="F370" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G370" t="n">
         <v>0.0</v>
@@ -12998,7 +12998,7 @@
         <v>673</v>
       </c>
       <c r="F420" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G420" t="n">
         <v>1.0</v>
@@ -14038,7 +14038,7 @@
         <v>673</v>
       </c>
       <c r="F460" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="G460" t="n">
         <v>0.0</v>
@@ -14480,7 +14480,7 @@
         <v>675</v>
       </c>
       <c r="F477" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -14766,7 +14766,7 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2294.0</v>
+        <v>2295.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
@@ -17288,7 +17288,7 @@
         <v>675</v>
       </c>
       <c r="F585" t="n">
-        <v>347.0</v>
+        <v>348.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -19342,7 +19342,7 @@
         <v>675</v>
       </c>
       <c r="F664" t="n">
-        <v>148.0</v>
+        <v>152.0</v>
       </c>
       <c r="G664" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -8656,7 +8656,7 @@
         <v>673</v>
       </c>
       <c r="F253" t="n">
-        <v>221.0</v>
+        <v>223.0</v>
       </c>
       <c r="G253" t="n">
         <v>0.0</v>
@@ -9052,7 +9052,7 @@
         <v>0.0</v>
       </c>
       <c r="H268" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="269">
@@ -9072,7 +9072,7 @@
         <v>673</v>
       </c>
       <c r="F269" t="n">
-        <v>493.0</v>
+        <v>494.0</v>
       </c>
       <c r="G269" t="n">
         <v>0.0</v>
@@ -9546,7 +9546,7 @@
         <v>0.0</v>
       </c>
       <c r="H287" t="n">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="288">
@@ -9962,7 +9962,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>28.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="304">
@@ -10482,7 +10482,7 @@
         <v>0.0</v>
       </c>
       <c r="H323" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="324">
@@ -12588,7 +12588,7 @@
         <v>0.0</v>
       </c>
       <c r="H404" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="405">
@@ -13732,7 +13732,7 @@
         <v>7.0</v>
       </c>
       <c r="H448" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="449">
@@ -14720,7 +14720,7 @@
         <v>0.0</v>
       </c>
       <c r="H486" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="487">
@@ -14740,7 +14740,7 @@
         <v>673</v>
       </c>
       <c r="F487" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="G487" t="n">
         <v>0.0</v>
@@ -15526,7 +15526,7 @@
         <v>0.0</v>
       </c>
       <c r="H517" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="518">
@@ -16098,7 +16098,7 @@
         <v>0.0</v>
       </c>
       <c r="H539" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="540">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2130,7 +2130,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2442,7 +2442,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>422.0</v>
+        <v>426.0</v>
       </c>
       <c r="G14" t="n">
         <v>5.0</v>
@@ -2468,7 +2468,7 @@
         <v>673</v>
       </c>
       <c r="F15" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="G15" t="n">
         <v>9.0</v>
@@ -2494,7 +2494,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>363.0</v>
+        <v>364.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2598,7 +2598,7 @@
         <v>673</v>
       </c>
       <c r="F20" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G20" t="n">
         <v>2.0</v>
@@ -3404,7 +3404,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3768,7 +3768,7 @@
         <v>675</v>
       </c>
       <c r="F65" t="n">
-        <v>153.0</v>
+        <v>156.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -4236,7 +4236,7 @@
         <v>673</v>
       </c>
       <c r="F83" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4444,7 +4444,7 @@
         <v>673</v>
       </c>
       <c r="F91" t="n">
-        <v>125.0</v>
+        <v>132.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -5120,7 +5120,7 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>424.0</v>
+        <v>426.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5614,7 +5614,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>620.0</v>
+        <v>621.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -5926,7 +5926,7 @@
         <v>675</v>
       </c>
       <c r="F148" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6264,7 +6264,7 @@
         <v>675</v>
       </c>
       <c r="F161" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6316,7 +6316,7 @@
         <v>673</v>
       </c>
       <c r="F163" t="n">
-        <v>299.0</v>
+        <v>300.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6368,7 +6368,7 @@
         <v>673</v>
       </c>
       <c r="F165" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="G165" t="n">
         <v>6.0</v>
@@ -7252,7 +7252,7 @@
         <v>675</v>
       </c>
       <c r="F199" t="n">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -7772,7 +7772,7 @@
         <v>673</v>
       </c>
       <c r="F219" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G219" t="n">
         <v>1.0</v>
@@ -8058,7 +8058,7 @@
         <v>673</v>
       </c>
       <c r="F230" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G230" t="n">
         <v>0.0</v>
@@ -9176,7 +9176,7 @@
         <v>675</v>
       </c>
       <c r="F273" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G273" t="n">
         <v>0.0</v>
@@ -9748,7 +9748,7 @@
         <v>673</v>
       </c>
       <c r="F295" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G295" t="n">
         <v>2.0</v>
@@ -9800,7 +9800,7 @@
         <v>673</v>
       </c>
       <c r="F297" t="n">
-        <v>941.0</v>
+        <v>945.0</v>
       </c>
       <c r="G297" t="n">
         <v>5.0</v>
@@ -9904,7 +9904,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10450,7 +10450,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>382.0</v>
+        <v>383.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11048,10 +11048,10 @@
         <v>675</v>
       </c>
       <c r="F345" t="n">
-        <v>509.0</v>
+        <v>510.0</v>
       </c>
       <c r="G345" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H345" t="n">
         <v>0.0</v>
@@ -11464,7 +11464,7 @@
         <v>675</v>
       </c>
       <c r="F361" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11750,7 +11750,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -11984,7 +11984,7 @@
         <v>673</v>
       </c>
       <c r="F381" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G381" t="n">
         <v>1.0</v>
@@ -12998,7 +12998,7 @@
         <v>673</v>
       </c>
       <c r="F420" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G420" t="n">
         <v>1.0</v>
@@ -13232,7 +13232,7 @@
         <v>673</v>
       </c>
       <c r="F429" t="n">
-        <v>754.0</v>
+        <v>755.0</v>
       </c>
       <c r="G429" t="n">
         <v>2.0</v>
@@ -13648,7 +13648,7 @@
         <v>674</v>
       </c>
       <c r="F445" t="n">
-        <v>518.0</v>
+        <v>520.0</v>
       </c>
       <c r="G445" t="n">
         <v>3.0</v>
@@ -14428,7 +14428,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>533.0</v>
+        <v>534.0</v>
       </c>
       <c r="G475" t="n">
         <v>2.0</v>
@@ -14766,13 +14766,13 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2295.0</v>
+        <v>2297.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
       </c>
       <c r="H488" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="489">
@@ -15260,7 +15260,7 @@
         <v>673</v>
       </c>
       <c r="F507" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15364,7 +15364,7 @@
         <v>675</v>
       </c>
       <c r="F511" t="n">
-        <v>142.0</v>
+        <v>144.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -15728,7 +15728,7 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>405.0</v>
+        <v>406.0</v>
       </c>
       <c r="G525" t="n">
         <v>3.0</v>
@@ -15806,7 +15806,7 @@
         <v>675</v>
       </c>
       <c r="F528" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G528" t="n">
         <v>1.0</v>
@@ -16456,7 +16456,7 @@
         <v>673</v>
       </c>
       <c r="F553" t="n">
-        <v>287.0</v>
+        <v>288.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16872,7 +16872,7 @@
         <v>673</v>
       </c>
       <c r="F569" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G569" t="n">
         <v>1.0</v>
@@ -16950,7 +16950,7 @@
         <v>675</v>
       </c>
       <c r="F572" t="n">
-        <v>358.0</v>
+        <v>360.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17288,7 +17288,7 @@
         <v>675</v>
       </c>
       <c r="F585" t="n">
-        <v>348.0</v>
+        <v>350.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -18692,7 +18692,7 @@
         <v>673</v>
       </c>
       <c r="F639" t="n">
-        <v>102.0</v>
+        <v>104.0</v>
       </c>
       <c r="G639" t="n">
         <v>0.0</v>
@@ -18874,7 +18874,7 @@
         <v>675</v>
       </c>
       <c r="F646" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -18900,7 +18900,7 @@
         <v>675</v>
       </c>
       <c r="F647" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19082,7 +19082,7 @@
         <v>675</v>
       </c>
       <c r="F654" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19420,7 +19420,7 @@
         <v>675</v>
       </c>
       <c r="F667" t="n">
-        <v>124.0</v>
+        <v>126.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19446,7 +19446,7 @@
         <v>675</v>
       </c>
       <c r="F668" t="n">
-        <v>336.0</v>
+        <v>338.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2650,7 +2650,7 @@
         <v>675</v>
       </c>
       <c r="F22" t="n">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3352,7 +3352,7 @@
         <v>675</v>
       </c>
       <c r="F49" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -3378,7 +3378,7 @@
         <v>675</v>
       </c>
       <c r="F50" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -3976,7 +3976,7 @@
         <v>675</v>
       </c>
       <c r="F73" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4314,7 +4314,7 @@
         <v>674</v>
       </c>
       <c r="F86" t="n">
-        <v>462.0</v>
+        <v>463.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -4626,7 +4626,7 @@
         <v>673</v>
       </c>
       <c r="F98" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -6758,7 +6758,7 @@
         <v>675</v>
       </c>
       <c r="F180" t="n">
-        <v>624.0</v>
+        <v>627.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -7096,7 +7096,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>988.0</v>
+        <v>989.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -9202,7 +9202,7 @@
         <v>675</v>
       </c>
       <c r="F274" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="G274" t="n">
         <v>0.0</v>
@@ -9546,7 +9546,7 @@
         <v>0.0</v>
       </c>
       <c r="H287" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="288">
@@ -12354,7 +12354,7 @@
         <v>9.0</v>
       </c>
       <c r="H395" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="396">
@@ -14766,7 +14766,7 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2297.0</v>
+        <v>2300.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
@@ -14870,7 +14870,7 @@
         <v>673</v>
       </c>
       <c r="F492" t="n">
-        <v>189.0</v>
+        <v>193.0</v>
       </c>
       <c r="G492" t="n">
         <v>0.0</v>
@@ -15286,7 +15286,7 @@
         <v>673</v>
       </c>
       <c r="F508" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G508" t="n">
         <v>0.0</v>
@@ -15468,7 +15468,7 @@
         <v>675</v>
       </c>
       <c r="F515" t="n">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
       <c r="G515" t="n">
         <v>1.0</v>
@@ -15598,7 +15598,7 @@
         <v>673</v>
       </c>
       <c r="F520" t="n">
-        <v>118.0</v>
+        <v>120.0</v>
       </c>
       <c r="G520" t="n">
         <v>1.0</v>
@@ -15910,7 +15910,7 @@
         <v>673</v>
       </c>
       <c r="F532" t="n">
-        <v>344.0</v>
+        <v>345.0</v>
       </c>
       <c r="G532" t="n">
         <v>0.0</v>
@@ -16040,7 +16040,7 @@
         <v>675</v>
       </c>
       <c r="F537" t="n">
-        <v>534.0</v>
+        <v>536.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16300,7 +16300,7 @@
         <v>675</v>
       </c>
       <c r="F547" t="n">
-        <v>259.0</v>
+        <v>261.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -18490,7 +18490,7 @@
         <v>0.0</v>
       </c>
       <c r="H631" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="632">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2130,7 +2130,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2208,7 +2208,7 @@
         <v>673</v>
       </c>
       <c r="F5" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -2494,7 +2494,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>364.0</v>
+        <v>366.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2624,7 +2624,7 @@
         <v>675</v>
       </c>
       <c r="F21" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2910,7 +2910,7 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>457.0</v>
+        <v>461.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3014,7 +3014,7 @@
         <v>675</v>
       </c>
       <c r="F36" t="n">
-        <v>300.0</v>
+        <v>302.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -3170,7 +3170,7 @@
         <v>673</v>
       </c>
       <c r="F42" t="n">
-        <v>284.0</v>
+        <v>285.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -3248,7 +3248,7 @@
         <v>673</v>
       </c>
       <c r="F45" t="n">
-        <v>21.0</v>
+        <v>25.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -3560,7 +3560,7 @@
         <v>673</v>
       </c>
       <c r="F57" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -3768,7 +3768,7 @@
         <v>675</v>
       </c>
       <c r="F65" t="n">
-        <v>156.0</v>
+        <v>158.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3898,7 +3898,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4548,7 +4548,7 @@
         <v>675</v>
       </c>
       <c r="F95" t="n">
-        <v>375.0</v>
+        <v>378.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4652,7 +4652,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>466.0</v>
+        <v>467.0</v>
       </c>
       <c r="G99" t="n">
         <v>2.0</v>
@@ -4782,7 +4782,7 @@
         <v>675</v>
       </c>
       <c r="F104" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -5614,7 +5614,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>621.0</v>
+        <v>623.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -5822,7 +5822,7 @@
         <v>675</v>
       </c>
       <c r="F144" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -6264,7 +6264,7 @@
         <v>675</v>
       </c>
       <c r="F161" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6498,7 +6498,7 @@
         <v>675</v>
       </c>
       <c r="F170" t="n">
-        <v>475.0</v>
+        <v>476.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6966,7 +6966,7 @@
         <v>675</v>
       </c>
       <c r="F188" t="n">
-        <v>107.0</v>
+        <v>109.0</v>
       </c>
       <c r="G188" t="n">
         <v>0.0</v>
@@ -7798,7 +7798,7 @@
         <v>675</v>
       </c>
       <c r="F220" t="n">
-        <v>223.0</v>
+        <v>231.0</v>
       </c>
       <c r="G220" t="n">
         <v>0.0</v>
@@ -7850,7 +7850,7 @@
         <v>675</v>
       </c>
       <c r="F222" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G222" t="n">
         <v>0.0</v>
@@ -8058,7 +8058,7 @@
         <v>673</v>
       </c>
       <c r="F230" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G230" t="n">
         <v>0.0</v>
@@ -8266,7 +8266,7 @@
         <v>673</v>
       </c>
       <c r="F238" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G238" t="n">
         <v>0.0</v>
@@ -8448,7 +8448,7 @@
         <v>673</v>
       </c>
       <c r="F245" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G245" t="n">
         <v>0.0</v>
@@ -9904,7 +9904,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>471.0</v>
+        <v>473.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10450,7 +10450,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>383.0</v>
+        <v>384.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11516,7 +11516,7 @@
         <v>673</v>
       </c>
       <c r="F363" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11984,7 +11984,7 @@
         <v>673</v>
       </c>
       <c r="F381" t="n">
-        <v>112.0</v>
+        <v>115.0</v>
       </c>
       <c r="G381" t="n">
         <v>1.0</v>
@@ -12062,7 +12062,7 @@
         <v>673</v>
       </c>
       <c r="F384" t="n">
-        <v>430.0</v>
+        <v>431.0</v>
       </c>
       <c r="G384" t="n">
         <v>1.0</v>
@@ -12348,7 +12348,7 @@
         <v>673</v>
       </c>
       <c r="F395" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="G395" t="n">
         <v>9.0</v>
@@ -13024,7 +13024,7 @@
         <v>675</v>
       </c>
       <c r="F421" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G421" t="n">
         <v>0.0</v>
@@ -13102,7 +13102,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -14116,7 +14116,7 @@
         <v>675</v>
       </c>
       <c r="F463" t="n">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
       <c r="G463" t="n">
         <v>1.0</v>
@@ -14194,7 +14194,7 @@
         <v>675</v>
       </c>
       <c r="F466" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G466" t="n">
         <v>0.0</v>
@@ -14428,7 +14428,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>534.0</v>
+        <v>539.0</v>
       </c>
       <c r="G475" t="n">
         <v>2.0</v>
@@ -15286,7 +15286,7 @@
         <v>673</v>
       </c>
       <c r="F508" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G508" t="n">
         <v>0.0</v>
@@ -15364,7 +15364,7 @@
         <v>675</v>
       </c>
       <c r="F511" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -16456,7 +16456,7 @@
         <v>673</v>
       </c>
       <c r="F553" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16872,7 +16872,7 @@
         <v>673</v>
       </c>
       <c r="F569" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G569" t="n">
         <v>1.0</v>
@@ -16950,7 +16950,7 @@
         <v>675</v>
       </c>
       <c r="F572" t="n">
-        <v>360.0</v>
+        <v>361.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17288,7 +17288,7 @@
         <v>675</v>
       </c>
       <c r="F585" t="n">
-        <v>350.0</v>
+        <v>353.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -18198,7 +18198,7 @@
         <v>675</v>
       </c>
       <c r="F620" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G620" t="n">
         <v>0.0</v>
@@ -18406,7 +18406,7 @@
         <v>673</v>
       </c>
       <c r="F628" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G628" t="n">
         <v>0.0</v>
@@ -18614,7 +18614,7 @@
         <v>673</v>
       </c>
       <c r="F636" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G636" t="n">
         <v>6.0</v>
@@ -18666,7 +18666,7 @@
         <v>675</v>
       </c>
       <c r="F638" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -18796,7 +18796,7 @@
         <v>675</v>
       </c>
       <c r="F643" t="n">
-        <v>53.0</v>
+        <v>56.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -18874,7 +18874,7 @@
         <v>675</v>
       </c>
       <c r="F646" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -18900,7 +18900,7 @@
         <v>675</v>
       </c>
       <c r="F647" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19082,7 +19082,7 @@
         <v>675</v>
       </c>
       <c r="F654" t="n">
-        <v>57.0</v>
+        <v>60.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19108,7 +19108,7 @@
         <v>675</v>
       </c>
       <c r="F655" t="n">
-        <v>91.0</v>
+        <v>93.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19134,7 +19134,7 @@
         <v>675</v>
       </c>
       <c r="F656" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19160,7 +19160,7 @@
         <v>675</v>
       </c>
       <c r="F657" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G657" t="n">
         <v>0.0</v>
@@ -19241,7 +19241,7 @@
         <v>13.0</v>
       </c>
       <c r="G660" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H660" t="n">
         <v>0.0</v>
@@ -19342,7 +19342,7 @@
         <v>675</v>
       </c>
       <c r="F664" t="n">
-        <v>152.0</v>
+        <v>155.0</v>
       </c>
       <c r="G664" t="n">
         <v>1.0</v>
@@ -19394,7 +19394,7 @@
         <v>673</v>
       </c>
       <c r="F666" t="n">
-        <v>277.0</v>
+        <v>280.0</v>
       </c>
       <c r="G666" t="n">
         <v>2.0</v>
@@ -19446,7 +19446,7 @@
         <v>675</v>
       </c>
       <c r="F668" t="n">
-        <v>338.0</v>
+        <v>341.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>
@@ -19472,7 +19472,7 @@
         <v>673</v>
       </c>
       <c r="F669" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2416,7 +2416,7 @@
         <v>673</v>
       </c>
       <c r="F13" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -3716,7 +3716,7 @@
         <v>675</v>
       </c>
       <c r="F63" t="n">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -4314,7 +4314,7 @@
         <v>674</v>
       </c>
       <c r="F86" t="n">
-        <v>463.0</v>
+        <v>464.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -4814,7 +4814,7 @@
         <v>0.0</v>
       </c>
       <c r="H105" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="106">
@@ -4834,7 +4834,7 @@
         <v>673</v>
       </c>
       <c r="F106" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -6576,7 +6576,7 @@
         <v>673</v>
       </c>
       <c r="F173" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G173" t="n">
         <v>0.0</v>
@@ -6888,7 +6888,7 @@
         <v>673</v>
       </c>
       <c r="F185" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="G185" t="n">
         <v>2.0</v>
@@ -7954,7 +7954,7 @@
         <v>675</v>
       </c>
       <c r="F226" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8656,7 +8656,7 @@
         <v>673</v>
       </c>
       <c r="F253" t="n">
-        <v>223.0</v>
+        <v>224.0</v>
       </c>
       <c r="G253" t="n">
         <v>0.0</v>
@@ -9072,7 +9072,7 @@
         <v>673</v>
       </c>
       <c r="F269" t="n">
-        <v>494.0</v>
+        <v>495.0</v>
       </c>
       <c r="G269" t="n">
         <v>0.0</v>
@@ -9306,7 +9306,7 @@
         <v>673</v>
       </c>
       <c r="F278" t="n">
-        <v>534.0</v>
+        <v>535.0</v>
       </c>
       <c r="G278" t="n">
         <v>6.0</v>
@@ -9491,7 +9491,7 @@
         <v>206.0</v>
       </c>
       <c r="G285" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H285" t="n">
         <v>0.0</v>
@@ -9800,7 +9800,7 @@
         <v>673</v>
       </c>
       <c r="F297" t="n">
-        <v>945.0</v>
+        <v>960.0</v>
       </c>
       <c r="G297" t="n">
         <v>5.0</v>
@@ -9930,7 +9930,7 @@
         <v>673</v>
       </c>
       <c r="F302" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G302" t="n">
         <v>0.0</v>
@@ -10060,13 +10060,13 @@
         <v>673</v>
       </c>
       <c r="F307" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="G307" t="n">
         <v>3.0</v>
       </c>
       <c r="H307" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="308">
@@ -11022,7 +11022,7 @@
         <v>673</v>
       </c>
       <c r="F344" t="n">
-        <v>156.0</v>
+        <v>159.0</v>
       </c>
       <c r="G344" t="n">
         <v>0.0</v>
@@ -11048,7 +11048,7 @@
         <v>675</v>
       </c>
       <c r="F345" t="n">
-        <v>510.0</v>
+        <v>511.0</v>
       </c>
       <c r="G345" t="n">
         <v>6.0</v>
@@ -12452,7 +12452,7 @@
         <v>673</v>
       </c>
       <c r="F399" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="G399" t="n">
         <v>0.0</v>
@@ -12530,7 +12530,7 @@
         <v>673</v>
       </c>
       <c r="F402" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G402" t="n">
         <v>0.0</v>
@@ -13232,7 +13232,7 @@
         <v>673</v>
       </c>
       <c r="F429" t="n">
-        <v>755.0</v>
+        <v>757.0</v>
       </c>
       <c r="G429" t="n">
         <v>2.0</v>
@@ -13570,7 +13570,7 @@
         <v>673</v>
       </c>
       <c r="F442" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G442" t="n">
         <v>0.0</v>
@@ -14558,7 +14558,7 @@
         <v>675</v>
       </c>
       <c r="F480" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G480" t="n">
         <v>0.0</v>
@@ -14720,7 +14720,7 @@
         <v>0.0</v>
       </c>
       <c r="H486" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="487">
@@ -14766,7 +14766,7 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2300.0</v>
+        <v>2303.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
@@ -15448,7 +15448,7 @@
         <v>0.0</v>
       </c>
       <c r="H514" t="n">
-        <v>46.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="515">
@@ -16118,7 +16118,7 @@
         <v>673</v>
       </c>
       <c r="F540" t="n">
-        <v>258.0</v>
+        <v>260.0</v>
       </c>
       <c r="G540" t="n">
         <v>1.0</v>
@@ -17574,7 +17574,7 @@
         <v>673</v>
       </c>
       <c r="F596" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G596" t="n">
         <v>0.0</v>
@@ -18458,7 +18458,7 @@
         <v>673</v>
       </c>
       <c r="F630" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G630" t="n">
         <v>0.0</v>
@@ -19342,7 +19342,7 @@
         <v>675</v>
       </c>
       <c r="F664" t="n">
-        <v>155.0</v>
+        <v>157.0</v>
       </c>
       <c r="G664" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2130,7 +2130,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>529.0</v>
+        <v>533.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2442,7 +2442,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>426.0</v>
+        <v>429.0</v>
       </c>
       <c r="G14" t="n">
         <v>5.0</v>
@@ -2494,7 +2494,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -3404,7 +3404,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3800,7 +3800,7 @@
         <v>2.0</v>
       </c>
       <c r="H66" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="67">
@@ -4652,7 +4652,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>467.0</v>
+        <v>470.0</v>
       </c>
       <c r="G99" t="n">
         <v>2.0</v>
@@ -5406,7 +5406,7 @@
         <v>675</v>
       </c>
       <c r="F128" t="n">
-        <v>174.0</v>
+        <v>176.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -5614,7 +5614,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>623.0</v>
+        <v>624.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -6238,7 +6238,7 @@
         <v>673</v>
       </c>
       <c r="F160" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -6264,7 +6264,7 @@
         <v>675</v>
       </c>
       <c r="F161" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6472,7 +6472,7 @@
         <v>673</v>
       </c>
       <c r="F169" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -7096,7 +7096,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>989.0</v>
+        <v>990.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -7252,7 +7252,7 @@
         <v>675</v>
       </c>
       <c r="F199" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -7954,7 +7954,7 @@
         <v>675</v>
       </c>
       <c r="F226" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -9904,7 +9904,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>473.0</v>
+        <v>476.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10450,7 +10450,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>384.0</v>
+        <v>385.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -14116,7 +14116,7 @@
         <v>675</v>
       </c>
       <c r="F463" t="n">
-        <v>227.0</v>
+        <v>229.0</v>
       </c>
       <c r="G463" t="n">
         <v>1.0</v>
@@ -14428,7 +14428,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>539.0</v>
+        <v>541.0</v>
       </c>
       <c r="G475" t="n">
         <v>2.0</v>
@@ -14480,7 +14480,7 @@
         <v>675</v>
       </c>
       <c r="F477" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -15364,7 +15364,7 @@
         <v>675</v>
       </c>
       <c r="F511" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -15728,7 +15728,7 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>406.0</v>
+        <v>407.0</v>
       </c>
       <c r="G525" t="n">
         <v>3.0</v>
@@ -17574,7 +17574,7 @@
         <v>673</v>
       </c>
       <c r="F596" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G596" t="n">
         <v>0.0</v>
@@ -18614,7 +18614,7 @@
         <v>673</v>
       </c>
       <c r="F636" t="n">
-        <v>111.0</v>
+        <v>114.0</v>
       </c>
       <c r="G636" t="n">
         <v>6.0</v>
@@ -18770,7 +18770,7 @@
         <v>675</v>
       </c>
       <c r="F642" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -18874,7 +18874,7 @@
         <v>675</v>
       </c>
       <c r="F646" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -19082,7 +19082,7 @@
         <v>675</v>
       </c>
       <c r="F654" t="n">
-        <v>60.0</v>
+        <v>62.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19264,7 +19264,7 @@
         <v>673</v>
       </c>
       <c r="F661" t="n">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19394,7 +19394,7 @@
         <v>673</v>
       </c>
       <c r="F666" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="G666" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -14772,7 +14772,7 @@
         <v>44.0</v>
       </c>
       <c r="H488" t="n">
-        <v>280.0</v>
+        <v>282.0</v>
       </c>
     </row>
     <row r="489">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2130,7 +2130,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>533.0</v>
+        <v>534.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2520,7 +2520,7 @@
         <v>674</v>
       </c>
       <c r="F17" t="n">
-        <v>249.0</v>
+        <v>252.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -3014,7 +3014,7 @@
         <v>675</v>
       </c>
       <c r="F36" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -3176,7 +3176,7 @@
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="43">
@@ -3404,7 +3404,7 @@
         <v>673</v>
       </c>
       <c r="F51" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -3800,7 +3800,7 @@
         <v>2.0</v>
       </c>
       <c r="H66" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="67">
@@ -3976,7 +3976,7 @@
         <v>675</v>
       </c>
       <c r="F73" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4548,7 +4548,7 @@
         <v>675</v>
       </c>
       <c r="F95" t="n">
-        <v>378.0</v>
+        <v>381.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4704,7 +4704,7 @@
         <v>673</v>
       </c>
       <c r="F101" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -4782,7 +4782,7 @@
         <v>675</v>
       </c>
       <c r="F104" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -5120,7 +5120,7 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>426.0</v>
+        <v>427.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5406,7 +5406,7 @@
         <v>675</v>
       </c>
       <c r="F128" t="n">
-        <v>176.0</v>
+        <v>179.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -5796,7 +5796,7 @@
         <v>675</v>
       </c>
       <c r="F143" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -5900,7 +5900,7 @@
         <v>673</v>
       </c>
       <c r="F147" t="n">
-        <v>197.0</v>
+        <v>199.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -5926,7 +5926,7 @@
         <v>675</v>
       </c>
       <c r="F148" t="n">
-        <v>134.0</v>
+        <v>136.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6316,7 +6316,7 @@
         <v>673</v>
       </c>
       <c r="F163" t="n">
-        <v>300.0</v>
+        <v>301.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6498,7 +6498,7 @@
         <v>675</v>
       </c>
       <c r="F170" t="n">
-        <v>476.0</v>
+        <v>479.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6758,7 +6758,7 @@
         <v>675</v>
       </c>
       <c r="F180" t="n">
-        <v>627.0</v>
+        <v>630.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -6888,7 +6888,7 @@
         <v>673</v>
       </c>
       <c r="F185" t="n">
-        <v>312.0</v>
+        <v>316.0</v>
       </c>
       <c r="G185" t="n">
         <v>2.0</v>
@@ -7252,7 +7252,7 @@
         <v>675</v>
       </c>
       <c r="F199" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -9696,7 +9696,7 @@
         <v>673</v>
       </c>
       <c r="F293" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G293" t="n">
         <v>0.0</v>
@@ -10450,7 +10450,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>385.0</v>
+        <v>386.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10736,7 +10736,7 @@
         <v>675</v>
       </c>
       <c r="F333" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G333" t="n">
         <v>0.0</v>
@@ -11672,7 +11672,7 @@
         <v>675</v>
       </c>
       <c r="F369" t="n">
-        <v>113.0</v>
+        <v>116.0</v>
       </c>
       <c r="G369" t="n">
         <v>0.0</v>
@@ -12088,7 +12088,7 @@
         <v>675</v>
       </c>
       <c r="F385" t="n">
-        <v>60.0</v>
+        <v>62.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12322,7 +12322,7 @@
         <v>675</v>
       </c>
       <c r="F394" t="n">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -13102,7 +13102,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>527.0</v>
+        <v>529.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13206,7 +13206,7 @@
         <v>673</v>
       </c>
       <c r="F428" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -13648,7 +13648,7 @@
         <v>674</v>
       </c>
       <c r="F445" t="n">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="G445" t="n">
         <v>3.0</v>
@@ -13726,7 +13726,7 @@
         <v>673</v>
       </c>
       <c r="F448" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="G448" t="n">
         <v>7.0</v>
@@ -13778,7 +13778,7 @@
         <v>673</v>
       </c>
       <c r="F450" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G450" t="n">
         <v>0.0</v>
@@ -14428,7 +14428,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>541.0</v>
+        <v>543.0</v>
       </c>
       <c r="G475" t="n">
         <v>2.0</v>
@@ -15364,7 +15364,7 @@
         <v>675</v>
       </c>
       <c r="F511" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -15468,7 +15468,7 @@
         <v>675</v>
       </c>
       <c r="F515" t="n">
-        <v>309.0</v>
+        <v>311.0</v>
       </c>
       <c r="G515" t="n">
         <v>1.0</v>
@@ -15546,7 +15546,7 @@
         <v>675</v>
       </c>
       <c r="F518" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="G518" t="n">
         <v>0.0</v>
@@ -15731,7 +15731,7 @@
         <v>407.0</v>
       </c>
       <c r="G525" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H525" t="n">
         <v>0.0</v>
@@ -16040,7 +16040,7 @@
         <v>675</v>
       </c>
       <c r="F537" t="n">
-        <v>536.0</v>
+        <v>537.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16300,7 +16300,7 @@
         <v>675</v>
       </c>
       <c r="F547" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16378,7 +16378,7 @@
         <v>673</v>
       </c>
       <c r="F550" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="G550" t="n">
         <v>1.0</v>
@@ -17002,7 +17002,7 @@
         <v>673</v>
       </c>
       <c r="F574" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G574" t="n">
         <v>0.0</v>
@@ -19186,7 +19186,7 @@
         <v>673</v>
       </c>
       <c r="F658" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -19316,7 +19316,7 @@
         <v>673</v>
       </c>
       <c r="F663" t="n">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19420,7 +19420,7 @@
         <v>675</v>
       </c>
       <c r="F667" t="n">
-        <v>126.0</v>
+        <v>128.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19446,7 +19446,7 @@
         <v>675</v>
       </c>
       <c r="F668" t="n">
-        <v>341.0</v>
+        <v>345.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2130,7 +2130,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>534.0</v>
+        <v>535.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2234,7 +2234,7 @@
         <v>673</v>
       </c>
       <c r="F6" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -2364,7 +2364,7 @@
         <v>673</v>
       </c>
       <c r="F11" t="n">
-        <v>295.0</v>
+        <v>297.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -2396,7 +2396,7 @@
         <v>0.0</v>
       </c>
       <c r="H12" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="13">
@@ -2442,7 +2442,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>429.0</v>
+        <v>431.0</v>
       </c>
       <c r="G14" t="n">
         <v>5.0</v>
@@ -2494,7 +2494,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>367.0</v>
+        <v>369.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -3144,7 +3144,7 @@
         <v>673</v>
       </c>
       <c r="F41" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -3768,7 +3768,7 @@
         <v>675</v>
       </c>
       <c r="F65" t="n">
-        <v>158.0</v>
+        <v>160.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3794,10 +3794,10 @@
         <v>673</v>
       </c>
       <c r="F66" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H66" t="n">
         <v>8.0</v>
@@ -4314,7 +4314,7 @@
         <v>674</v>
       </c>
       <c r="F86" t="n">
-        <v>464.0</v>
+        <v>465.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -4652,7 +4652,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>470.0</v>
+        <v>473.0</v>
       </c>
       <c r="G99" t="n">
         <v>2.0</v>
@@ -5406,7 +5406,7 @@
         <v>675</v>
       </c>
       <c r="F128" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -5458,13 +5458,13 @@
         <v>673</v>
       </c>
       <c r="F130" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
       </c>
       <c r="H130" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="131">
@@ -5614,7 +5614,7 @@
         <v>673</v>
       </c>
       <c r="F136" t="n">
-        <v>624.0</v>
+        <v>628.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -6212,7 +6212,7 @@
         <v>673</v>
       </c>
       <c r="F159" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G159" t="n">
         <v>0.0</v>
@@ -6264,7 +6264,7 @@
         <v>675</v>
       </c>
       <c r="F161" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6628,7 +6628,7 @@
         <v>675</v>
       </c>
       <c r="F175" t="n">
-        <v>553.0</v>
+        <v>555.0</v>
       </c>
       <c r="G175" t="n">
         <v>1.0</v>
@@ -6784,7 +6784,7 @@
         <v>675</v>
       </c>
       <c r="F181" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7252,7 +7252,7 @@
         <v>675</v>
       </c>
       <c r="F199" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -8734,7 +8734,7 @@
         <v>673</v>
       </c>
       <c r="F256" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="G256" t="n">
         <v>0.0</v>
@@ -9176,7 +9176,7 @@
         <v>675</v>
       </c>
       <c r="F273" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G273" t="n">
         <v>0.0</v>
@@ -9904,7 +9904,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>476.0</v>
+        <v>478.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -9962,7 +9962,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="304">
@@ -10924,7 +10924,7 @@
         <v>0.0</v>
       </c>
       <c r="H340" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="341">
@@ -11048,7 +11048,7 @@
         <v>675</v>
       </c>
       <c r="F345" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="G345" t="n">
         <v>6.0</v>
@@ -11126,7 +11126,7 @@
         <v>673</v>
       </c>
       <c r="F348" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G348" t="n">
         <v>0.0</v>
@@ -11360,7 +11360,7 @@
         <v>675</v>
       </c>
       <c r="F357" t="n">
-        <v>165.0</v>
+        <v>167.0</v>
       </c>
       <c r="G357" t="n">
         <v>0.0</v>
@@ -11750,7 +11750,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>224.0</v>
+        <v>226.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -12088,7 +12088,7 @@
         <v>675</v>
       </c>
       <c r="F385" t="n">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -12452,7 +12452,7 @@
         <v>673</v>
       </c>
       <c r="F399" t="n">
-        <v>180.0</v>
+        <v>182.0</v>
       </c>
       <c r="G399" t="n">
         <v>0.0</v>
@@ -14720,7 +14720,7 @@
         <v>0.0</v>
       </c>
       <c r="H486" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="487">
@@ -14740,7 +14740,7 @@
         <v>673</v>
       </c>
       <c r="F487" t="n">
-        <v>334.0</v>
+        <v>335.0</v>
       </c>
       <c r="G487" t="n">
         <v>0.0</v>
@@ -15364,7 +15364,7 @@
         <v>675</v>
       </c>
       <c r="F511" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -15448,7 +15448,7 @@
         <v>0.0</v>
       </c>
       <c r="H514" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="515">
@@ -17860,7 +17860,7 @@
         <v>675</v>
       </c>
       <c r="F607" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G607" t="n">
         <v>0.0</v>
@@ -17886,7 +17886,7 @@
         <v>673</v>
       </c>
       <c r="F608" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18198,7 +18198,7 @@
         <v>675</v>
       </c>
       <c r="F620" t="n">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="G620" t="n">
         <v>0.0</v>
@@ -18594,7 +18594,7 @@
         <v>0.0</v>
       </c>
       <c r="H635" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="636">
@@ -18796,7 +18796,7 @@
         <v>675</v>
       </c>
       <c r="F643" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -18900,7 +18900,7 @@
         <v>675</v>
       </c>
       <c r="F647" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -18926,7 +18926,7 @@
         <v>675</v>
       </c>
       <c r="F648" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -18955,7 +18955,7 @@
         <v>12.0</v>
       </c>
       <c r="G649" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H649" t="n">
         <v>0.0</v>
@@ -19082,7 +19082,7 @@
         <v>675</v>
       </c>
       <c r="F654" t="n">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19446,7 +19446,7 @@
         <v>675</v>
       </c>
       <c r="F668" t="n">
-        <v>345.0</v>
+        <v>348.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2445,7 +2445,7 @@
         <v>431.0</v>
       </c>
       <c r="G14" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H14" t="n">
         <v>3.0</v>
@@ -2494,7 +2494,7 @@
         <v>673</v>
       </c>
       <c r="F16" t="n">
-        <v>369.0</v>
+        <v>370.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2572,7 +2572,7 @@
         <v>673</v>
       </c>
       <c r="F19" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G19" t="n">
         <v>1.0</v>
@@ -2624,7 +2624,7 @@
         <v>675</v>
       </c>
       <c r="F21" t="n">
-        <v>333.0</v>
+        <v>335.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2936,7 +2936,7 @@
         <v>673</v>
       </c>
       <c r="F33" t="n">
-        <v>159.0</v>
+        <v>165.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -3014,7 +3014,7 @@
         <v>675</v>
       </c>
       <c r="F36" t="n">
-        <v>303.0</v>
+        <v>304.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -3898,7 +3898,7 @@
         <v>673</v>
       </c>
       <c r="F70" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4548,7 +4548,7 @@
         <v>675</v>
       </c>
       <c r="F95" t="n">
-        <v>381.0</v>
+        <v>383.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4912,7 +4912,7 @@
         <v>673</v>
       </c>
       <c r="F109" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -5120,7 +5120,7 @@
         <v>673</v>
       </c>
       <c r="F117" t="n">
-        <v>427.0</v>
+        <v>428.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -6316,7 +6316,7 @@
         <v>673</v>
       </c>
       <c r="F163" t="n">
-        <v>301.0</v>
+        <v>302.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6472,7 +6472,7 @@
         <v>673</v>
       </c>
       <c r="F169" t="n">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -9644,7 +9644,7 @@
         <v>675</v>
       </c>
       <c r="F291" t="n">
-        <v>386.0</v>
+        <v>387.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -9748,7 +9748,7 @@
         <v>673</v>
       </c>
       <c r="F295" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G295" t="n">
         <v>2.0</v>
@@ -9904,7 +9904,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>478.0</v>
+        <v>480.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10450,7 +10450,7 @@
         <v>673</v>
       </c>
       <c r="F322" t="n">
-        <v>386.0</v>
+        <v>387.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11750,7 +11750,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -12091,7 +12091,7 @@
         <v>64.0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H385" t="n">
         <v>0.0</v>
@@ -12530,7 +12530,7 @@
         <v>673</v>
       </c>
       <c r="F402" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G402" t="n">
         <v>0.0</v>
@@ -12588,7 +12588,7 @@
         <v>0.0</v>
       </c>
       <c r="H404" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="405">
@@ -13102,7 +13102,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>529.0</v>
+        <v>536.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13648,7 +13648,7 @@
         <v>674</v>
       </c>
       <c r="F445" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="G445" t="n">
         <v>3.0</v>
@@ -14116,7 +14116,7 @@
         <v>675</v>
       </c>
       <c r="F463" t="n">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
       <c r="G463" t="n">
         <v>1.0</v>
@@ -14428,7 +14428,7 @@
         <v>673</v>
       </c>
       <c r="F475" t="n">
-        <v>543.0</v>
+        <v>546.0</v>
       </c>
       <c r="G475" t="n">
         <v>2.0</v>
@@ -14720,7 +14720,7 @@
         <v>0.0</v>
       </c>
       <c r="H486" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="487">
@@ -14766,13 +14766,13 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2303.0</v>
+        <v>2314.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
       </c>
       <c r="H488" t="n">
-        <v>282.0</v>
+        <v>284.0</v>
       </c>
     </row>
     <row r="489">
@@ -15104,7 +15104,7 @@
         <v>673</v>
       </c>
       <c r="F501" t="n">
-        <v>399.0</v>
+        <v>402.0</v>
       </c>
       <c r="G501" t="n">
         <v>9.0</v>
@@ -15598,7 +15598,7 @@
         <v>673</v>
       </c>
       <c r="F520" t="n">
-        <v>120.0</v>
+        <v>124.0</v>
       </c>
       <c r="G520" t="n">
         <v>1.0</v>
@@ -16098,7 +16098,7 @@
         <v>0.0</v>
       </c>
       <c r="H539" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="540">
@@ -16456,7 +16456,7 @@
         <v>673</v>
       </c>
       <c r="F553" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -17808,7 +17808,7 @@
         <v>673</v>
       </c>
       <c r="F605" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="G605" t="n">
         <v>0.0</v>
@@ -18900,7 +18900,7 @@
         <v>675</v>
       </c>
       <c r="F647" t="n">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19108,7 +19108,7 @@
         <v>675</v>
       </c>
       <c r="F655" t="n">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19134,7 +19134,7 @@
         <v>675</v>
       </c>
       <c r="F656" t="n">
-        <v>117.0</v>
+        <v>120.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19264,7 +19264,7 @@
         <v>673</v>
       </c>
       <c r="F661" t="n">
-        <v>92.0</v>
+        <v>94.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19316,7 +19316,7 @@
         <v>673</v>
       </c>
       <c r="F663" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19342,7 +19342,7 @@
         <v>675</v>
       </c>
       <c r="F664" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="G664" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -5406,7 +5406,7 @@
         <v>675</v>
       </c>
       <c r="F128" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -6888,7 +6888,7 @@
         <v>673</v>
       </c>
       <c r="F185" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G185" t="n">
         <v>2.0</v>
@@ -7648,7 +7648,7 @@
         <v>0.0</v>
       </c>
       <c r="H214" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="215">
@@ -7668,7 +7668,7 @@
         <v>673</v>
       </c>
       <c r="F215" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="G215" t="n">
         <v>0.0</v>
@@ -10924,7 +10924,7 @@
         <v>0.0</v>
       </c>
       <c r="H340" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="341">
@@ -11048,7 +11048,7 @@
         <v>675</v>
       </c>
       <c r="F345" t="n">
-        <v>512.0</v>
+        <v>513.0</v>
       </c>
       <c r="G345" t="n">
         <v>6.0</v>
@@ -12088,7 +12088,7 @@
         <v>675</v>
       </c>
       <c r="F385" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G385" t="n">
         <v>1.0</v>
@@ -14772,7 +14772,7 @@
         <v>44.0</v>
       </c>
       <c r="H488" t="n">
-        <v>284.0</v>
+        <v>286.0</v>
       </c>
     </row>
     <row r="489">
@@ -14870,7 +14870,7 @@
         <v>673</v>
       </c>
       <c r="F492" t="n">
-        <v>193.0</v>
+        <v>195.0</v>
       </c>
       <c r="G492" t="n">
         <v>0.0</v>
@@ -15910,7 +15910,7 @@
         <v>673</v>
       </c>
       <c r="F532" t="n">
-        <v>345.0</v>
+        <v>347.0</v>
       </c>
       <c r="G532" t="n">
         <v>0.0</v>
@@ -17080,7 +17080,7 @@
         <v>673</v>
       </c>
       <c r="F577" t="n">
-        <v>217.0</v>
+        <v>219.0</v>
       </c>
       <c r="G577" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3800,7 +3800,7 @@
         <v>5.0</v>
       </c>
       <c r="H66" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="67">
@@ -12354,7 +12354,7 @@
         <v>9.0</v>
       </c>
       <c r="H395" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="396">
@@ -17762,7 +17762,7 @@
         <v>2.0</v>
       </c>
       <c r="H603" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="604">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2676,7 +2676,7 @@
         <v>673</v>
       </c>
       <c r="F23" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -3794,7 +3794,7 @@
         <v>673</v>
       </c>
       <c r="F66" t="n">
-        <v>135.0</v>
+        <v>138.0</v>
       </c>
       <c r="G66" t="n">
         <v>5.0</v>
@@ -5464,7 +5464,7 @@
         <v>0.0</v>
       </c>
       <c r="H130" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="131">
@@ -8870,7 +8870,7 @@
         <v>0.0</v>
       </c>
       <c r="H261" t="n">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="262">
@@ -10924,7 +10924,7 @@
         <v>0.0</v>
       </c>
       <c r="H340" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="341">
@@ -13102,7 +13102,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>536.0</v>
+        <v>537.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13648,7 +13648,7 @@
         <v>674</v>
       </c>
       <c r="F445" t="n">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
       <c r="G445" t="n">
         <v>3.0</v>
@@ -15728,7 +15728,7 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>407.0</v>
+        <v>408.0</v>
       </c>
       <c r="G525" t="n">
         <v>4.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3378,7 +3378,7 @@
         <v>675</v>
       </c>
       <c r="F50" t="n">
-        <v>86.0</v>
+        <v>90.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -5458,13 +5458,13 @@
         <v>673</v>
       </c>
       <c r="F130" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
       </c>
       <c r="H130" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="131">
@@ -5822,7 +5822,7 @@
         <v>675</v>
       </c>
       <c r="F144" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -6426,7 +6426,7 @@
         <v>0.0</v>
       </c>
       <c r="H167" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="168">
@@ -6732,7 +6732,7 @@
         <v>675</v>
       </c>
       <c r="F179" t="n">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -6758,7 +6758,7 @@
         <v>675</v>
       </c>
       <c r="F180" t="n">
-        <v>630.0</v>
+        <v>632.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -6784,7 +6784,7 @@
         <v>675</v>
       </c>
       <c r="F181" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7096,7 +7096,7 @@
         <v>673</v>
       </c>
       <c r="F193" t="n">
-        <v>990.0</v>
+        <v>991.0</v>
       </c>
       <c r="G193" t="n">
         <v>1.0</v>
@@ -8272,7 +8272,7 @@
         <v>0.0</v>
       </c>
       <c r="H238" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="239">
@@ -8994,7 +8994,7 @@
         <v>673</v>
       </c>
       <c r="F266" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G266" t="n">
         <v>0.0</v>
@@ -10918,7 +10918,7 @@
         <v>673</v>
       </c>
       <c r="F340" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G340" t="n">
         <v>0.0</v>
@@ -13102,7 +13102,7 @@
         <v>673</v>
       </c>
       <c r="F424" t="n">
-        <v>537.0</v>
+        <v>539.0</v>
       </c>
       <c r="G424" t="n">
         <v>3.0</v>
@@ -13518,7 +13518,7 @@
         <v>673</v>
       </c>
       <c r="F440" t="n">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
       <c r="G440" t="n">
         <v>0.0</v>
@@ -15182,7 +15182,7 @@
         <v>673</v>
       </c>
       <c r="F504" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
@@ -15468,7 +15468,7 @@
         <v>675</v>
       </c>
       <c r="F515" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="G515" t="n">
         <v>1.0</v>
@@ -15546,7 +15546,7 @@
         <v>675</v>
       </c>
       <c r="F518" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G518" t="n">
         <v>0.0</v>
@@ -16040,7 +16040,7 @@
         <v>675</v>
       </c>
       <c r="F537" t="n">
-        <v>537.0</v>
+        <v>541.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16300,7 +16300,7 @@
         <v>675</v>
       </c>
       <c r="F547" t="n">
-        <v>262.0</v>
+        <v>264.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2130,7 +2130,7 @@
         <v>673</v>
       </c>
       <c r="F2" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2442,7 +2442,7 @@
         <v>673</v>
       </c>
       <c r="F14" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
       <c r="G14" t="n">
         <v>6.0</v>
@@ -2910,7 +2910,7 @@
         <v>673</v>
       </c>
       <c r="F32" t="n">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -2936,7 +2936,7 @@
         <v>673</v>
       </c>
       <c r="F33" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -3014,7 +3014,7 @@
         <v>675</v>
       </c>
       <c r="F36" t="n">
-        <v>304.0</v>
+        <v>306.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -3768,7 +3768,7 @@
         <v>675</v>
       </c>
       <c r="F65" t="n">
-        <v>160.0</v>
+        <v>162.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3794,7 +3794,7 @@
         <v>673</v>
       </c>
       <c r="F66" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G66" t="n">
         <v>5.0</v>
@@ -3950,7 +3950,7 @@
         <v>673</v>
       </c>
       <c r="F72" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -4054,7 +4054,7 @@
         <v>673</v>
       </c>
       <c r="F76" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G76" t="n">
         <v>15.0</v>
@@ -4652,7 +4652,7 @@
         <v>673</v>
       </c>
       <c r="F99" t="n">
-        <v>473.0</v>
+        <v>474.0</v>
       </c>
       <c r="G99" t="n">
         <v>2.0</v>
@@ -4814,7 +4814,7 @@
         <v>0.0</v>
       </c>
       <c r="H105" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="106">
@@ -4834,7 +4834,7 @@
         <v>673</v>
       </c>
       <c r="F106" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -5198,7 +5198,7 @@
         <v>675</v>
       </c>
       <c r="F120" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -5900,7 +5900,7 @@
         <v>673</v>
       </c>
       <c r="F147" t="n">
-        <v>199.0</v>
+        <v>201.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -5926,7 +5926,7 @@
         <v>675</v>
       </c>
       <c r="F148" t="n">
-        <v>136.0</v>
+        <v>143.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6264,7 +6264,7 @@
         <v>675</v>
       </c>
       <c r="F161" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6524,7 +6524,7 @@
         <v>675</v>
       </c>
       <c r="F171" t="n">
-        <v>107.0</v>
+        <v>109.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -6576,7 +6576,7 @@
         <v>673</v>
       </c>
       <c r="F173" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G173" t="n">
         <v>0.0</v>
@@ -6602,7 +6602,7 @@
         <v>673</v>
       </c>
       <c r="F174" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G174" t="n">
         <v>1.0</v>
@@ -7226,7 +7226,7 @@
         <v>675</v>
       </c>
       <c r="F198" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G198" t="n">
         <v>1.0</v>
@@ -8292,7 +8292,7 @@
         <v>673</v>
       </c>
       <c r="F239" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G239" t="n">
         <v>1.0</v>
@@ -8656,7 +8656,7 @@
         <v>673</v>
       </c>
       <c r="F253" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="G253" t="n">
         <v>0.0</v>
@@ -9072,7 +9072,7 @@
         <v>673</v>
       </c>
       <c r="F269" t="n">
-        <v>495.0</v>
+        <v>496.0</v>
       </c>
       <c r="G269" t="n">
         <v>0.0</v>
@@ -9228,7 +9228,7 @@
         <v>673</v>
       </c>
       <c r="F275" t="n">
-        <v>244.0</v>
+        <v>248.0</v>
       </c>
       <c r="G275" t="n">
         <v>2.0</v>
@@ -9644,7 +9644,7 @@
         <v>675</v>
       </c>
       <c r="F291" t="n">
-        <v>387.0</v>
+        <v>389.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -9904,7 +9904,7 @@
         <v>673</v>
       </c>
       <c r="F301" t="n">
-        <v>480.0</v>
+        <v>481.0</v>
       </c>
       <c r="G301" t="n">
         <v>5.0</v>
@@ -10164,7 +10164,7 @@
         <v>675</v>
       </c>
       <c r="F311" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G311" t="n">
         <v>0.0</v>
@@ -11360,7 +11360,7 @@
         <v>675</v>
       </c>
       <c r="F357" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G357" t="n">
         <v>0.0</v>
@@ -11750,7 +11750,7 @@
         <v>673</v>
       </c>
       <c r="F372" t="n">
-        <v>227.0</v>
+        <v>229.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -11984,7 +11984,7 @@
         <v>673</v>
       </c>
       <c r="F381" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G381" t="n">
         <v>1.0</v>
@@ -12062,7 +12062,7 @@
         <v>673</v>
       </c>
       <c r="F384" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
       <c r="G384" t="n">
         <v>1.0</v>
@@ -12588,7 +12588,7 @@
         <v>0.0</v>
       </c>
       <c r="H404" t="n">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="405">
@@ -13726,7 +13726,7 @@
         <v>673</v>
       </c>
       <c r="F448" t="n">
-        <v>161.0</v>
+        <v>163.0</v>
       </c>
       <c r="G448" t="n">
         <v>7.0</v>
@@ -14246,7 +14246,7 @@
         <v>673</v>
       </c>
       <c r="F468" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G468" t="n">
         <v>0.0</v>
@@ -14720,7 +14720,7 @@
         <v>0.0</v>
       </c>
       <c r="H486" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="487">
@@ -14766,13 +14766,13 @@
         <v>673</v>
       </c>
       <c r="F488" t="n">
-        <v>2314.0</v>
+        <v>2317.0</v>
       </c>
       <c r="G488" t="n">
         <v>44.0</v>
       </c>
       <c r="H488" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
     </row>
     <row r="489">
@@ -15286,7 +15286,7 @@
         <v>673</v>
       </c>
       <c r="F508" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G508" t="n">
         <v>0.0</v>
@@ -15364,7 +15364,7 @@
         <v>675</v>
       </c>
       <c r="F511" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
@@ -15728,10 +15728,10 @@
         <v>673</v>
       </c>
       <c r="F525" t="n">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
       <c r="G525" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H525" t="n">
         <v>0.0</v>
@@ -16098,7 +16098,7 @@
         <v>0.0</v>
       </c>
       <c r="H539" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="540">
@@ -16118,7 +16118,7 @@
         <v>673</v>
       </c>
       <c r="F540" t="n">
-        <v>260.0</v>
+        <v>262.0</v>
       </c>
       <c r="G540" t="n">
         <v>1.0</v>
@@ -16456,7 +16456,7 @@
         <v>673</v>
       </c>
       <c r="F553" t="n">
-        <v>290.0</v>
+        <v>291.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16898,7 +16898,7 @@
         <v>675</v>
       </c>
       <c r="F570" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G570" t="n">
         <v>0.0</v>
@@ -16950,7 +16950,7 @@
         <v>675</v>
       </c>
       <c r="F572" t="n">
-        <v>361.0</v>
+        <v>363.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17600,7 +17600,7 @@
         <v>673</v>
       </c>
       <c r="F597" t="n">
-        <v>243.0</v>
+        <v>247.0</v>
       </c>
       <c r="G597" t="n">
         <v>0.0</v>
@@ -17886,7 +17886,7 @@
         <v>673</v>
       </c>
       <c r="F608" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18406,7 +18406,7 @@
         <v>673</v>
       </c>
       <c r="F628" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G628" t="n">
         <v>0.0</v>
@@ -18614,7 +18614,7 @@
         <v>673</v>
       </c>
       <c r="F636" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G636" t="n">
         <v>6.0</v>
@@ -18718,7 +18718,7 @@
         <v>673</v>
       </c>
       <c r="F640" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -18874,7 +18874,7 @@
         <v>675</v>
       </c>
       <c r="F646" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -19082,7 +19082,7 @@
         <v>675</v>
       </c>
       <c r="F654" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19108,7 +19108,7 @@
         <v>675</v>
       </c>
       <c r="F655" t="n">
-        <v>95.0</v>
+        <v>98.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19420,7 +19420,7 @@
         <v>675</v>
       </c>
       <c r="F667" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19446,7 +19446,7 @@
         <v>675</v>
       </c>
       <c r="F668" t="n">
-        <v>348.0</v>
+        <v>350.0</v>
       </c>
       <c r="G668" t="n">
         <v>1.0</v>
@@ -19472,7 +19472,7 @@
         <v>673</v>
       </c>
       <c r="F669" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3170,7 +3170,7 @@
         <v>699</v>
       </c>
       <c r="F39" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3592,7 +3592,7 @@
         <v>0.0</v>
       </c>
       <c r="H55" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="56">
@@ -5380,7 +5380,7 @@
         <v>699</v>
       </c>
       <c r="F124" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>
@@ -5614,7 +5614,7 @@
         <v>701</v>
       </c>
       <c r="F133" t="n">
-        <v>181.0</v>
+        <v>185.0</v>
       </c>
       <c r="G133" t="n">
         <v>0.0</v>
@@ -5698,7 +5698,7 @@
         <v>0.0</v>
       </c>
       <c r="H136" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="137">
@@ -6056,7 +6056,7 @@
         <v>701</v>
       </c>
       <c r="F150" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -7908,7 +7908,7 @@
         <v>0.0</v>
       </c>
       <c r="H221" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="222">
@@ -8792,7 +8792,7 @@
         <v>16.0</v>
       </c>
       <c r="H255" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="256">
@@ -9546,7 +9546,7 @@
         <v>1.0</v>
       </c>
       <c r="H284" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="285">
@@ -10248,7 +10248,7 @@
         <v>0.0</v>
       </c>
       <c r="H311" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="312">
@@ -10560,7 +10560,7 @@
         <v>0.0</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="324">
@@ -13862,7 +13862,7 @@
         <v>0.0</v>
       </c>
       <c r="H450" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="451">
@@ -16046,7 +16046,7 @@
         <v>0.0</v>
       </c>
       <c r="H534" t="n">
-        <v>44.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="535">
@@ -16670,7 +16670,7 @@
         <v>3.0</v>
       </c>
       <c r="H558" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="559">
@@ -18620,7 +18620,7 @@
         <v>0.0</v>
       </c>
       <c r="H633" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="634">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -18588,7 +18588,7 @@
         <v>699</v>
       </c>
       <c r="F632" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G632" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2494,7 +2494,7 @@
         <v>699</v>
       </c>
       <c r="F13" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -2702,7 +2702,7 @@
         <v>699</v>
       </c>
       <c r="F21" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G21" t="n">
         <v>2.0</v>
@@ -3014,7 +3014,7 @@
         <v>699</v>
       </c>
       <c r="F33" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -3508,7 +3508,7 @@
         <v>701</v>
       </c>
       <c r="F52" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -4158,7 +4158,7 @@
         <v>701</v>
       </c>
       <c r="F77" t="n">
-        <v>340.0</v>
+        <v>342.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4912,7 +4912,7 @@
         <v>699</v>
       </c>
       <c r="F106" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G106" t="n">
         <v>1.0</v>
@@ -5022,7 +5022,7 @@
         <v>0.0</v>
       </c>
       <c r="H110" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="111">
@@ -5698,7 +5698,7 @@
         <v>0.0</v>
       </c>
       <c r="H136" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="137">
@@ -5718,7 +5718,7 @@
         <v>699</v>
       </c>
       <c r="F137" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -6680,13 +6680,13 @@
         <v>699</v>
       </c>
       <c r="F174" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G174" t="n">
         <v>0.0</v>
       </c>
       <c r="H174" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="175">
@@ -6888,7 +6888,7 @@
         <v>701</v>
       </c>
       <c r="F182" t="n">
-        <v>555.0</v>
+        <v>556.0</v>
       </c>
       <c r="G182" t="n">
         <v>1.0</v>
@@ -6992,7 +6992,7 @@
         <v>701</v>
       </c>
       <c r="F186" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G186" t="n">
         <v>0.0</v>
@@ -7018,7 +7018,7 @@
         <v>701</v>
       </c>
       <c r="F187" t="n">
-        <v>632.0</v>
+        <v>636.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7044,7 +7044,7 @@
         <v>701</v>
       </c>
       <c r="F188" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="G188" t="n">
         <v>0.0</v>
@@ -7356,7 +7356,7 @@
         <v>699</v>
       </c>
       <c r="F200" t="n">
-        <v>992.0</v>
+        <v>993.0</v>
       </c>
       <c r="G200" t="n">
         <v>1.0</v>
@@ -7720,7 +7720,7 @@
         <v>701</v>
       </c>
       <c r="F214" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G214" t="n">
         <v>0.0</v>
@@ -8448,7 +8448,7 @@
         <v>700</v>
       </c>
       <c r="F242" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G242" t="n">
         <v>1.0</v>
@@ -8922,7 +8922,7 @@
         <v>0.0</v>
       </c>
       <c r="H260" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="261">
@@ -8942,7 +8942,7 @@
         <v>699</v>
       </c>
       <c r="F261" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
       <c r="G261" t="n">
         <v>0.0</v>
@@ -9020,7 +9020,7 @@
         <v>699</v>
       </c>
       <c r="F264" t="n">
-        <v>225.0</v>
+        <v>233.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9156,7 +9156,7 @@
         <v>0.0</v>
       </c>
       <c r="H269" t="n">
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="270">
@@ -9436,7 +9436,7 @@
         <v>701</v>
       </c>
       <c r="F280" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G280" t="n">
         <v>0.0</v>
@@ -10086,7 +10086,7 @@
         <v>699</v>
       </c>
       <c r="F305" t="n">
-        <v>960.0</v>
+        <v>970.0</v>
       </c>
       <c r="G305" t="n">
         <v>5.0</v>
@@ -11236,7 +11236,7 @@
         <v>0.0</v>
       </c>
       <c r="H349" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="350">
@@ -11360,7 +11360,7 @@
         <v>699</v>
       </c>
       <c r="F354" t="n">
-        <v>514.0</v>
+        <v>517.0</v>
       </c>
       <c r="G354" t="n">
         <v>6.0</v>
@@ -11932,7 +11932,7 @@
         <v>699</v>
       </c>
       <c r="F376" t="n">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -11984,7 +11984,7 @@
         <v>701</v>
       </c>
       <c r="F378" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G378" t="n">
         <v>0.0</v>
@@ -12374,7 +12374,7 @@
         <v>699</v>
       </c>
       <c r="F393" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G393" t="n">
         <v>1.0</v>
@@ -13440,7 +13440,7 @@
         <v>699</v>
       </c>
       <c r="F434" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G434" t="n">
         <v>1.0</v>
@@ -13986,7 +13986,7 @@
         <v>699</v>
       </c>
       <c r="F455" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G455" t="n">
         <v>0.0</v>
@@ -15286,13 +15286,13 @@
         <v>699</v>
       </c>
       <c r="F505" t="n">
-        <v>2317.0</v>
+        <v>2321.0</v>
       </c>
       <c r="G505" t="n">
         <v>44.0</v>
       </c>
       <c r="H505" t="n">
-        <v>287.0</v>
+        <v>289.0</v>
       </c>
     </row>
     <row r="506">
@@ -15754,7 +15754,7 @@
         <v>699</v>
       </c>
       <c r="F523" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G523" t="n">
         <v>0.0</v>
@@ -15988,7 +15988,7 @@
         <v>701</v>
       </c>
       <c r="F532" t="n">
-        <v>312.0</v>
+        <v>314.0</v>
       </c>
       <c r="G532" t="n">
         <v>1.0</v>
@@ -16066,7 +16066,7 @@
         <v>701</v>
       </c>
       <c r="F535" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -16352,7 +16352,7 @@
         <v>701</v>
       </c>
       <c r="F546" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G546" t="n">
         <v>1.0</v>
@@ -16638,7 +16638,7 @@
         <v>701</v>
       </c>
       <c r="F557" t="n">
-        <v>541.0</v>
+        <v>547.0</v>
       </c>
       <c r="G557" t="n">
         <v>1.0</v>
@@ -16924,7 +16924,7 @@
         <v>701</v>
       </c>
       <c r="F568" t="n">
-        <v>264.0</v>
+        <v>266.0</v>
       </c>
       <c r="G568" t="n">
         <v>0.0</v>
@@ -18146,7 +18146,7 @@
         <v>701</v>
       </c>
       <c r="F615" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -19296,7 +19296,7 @@
         <v>0.0</v>
       </c>
       <c r="H659" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="660">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2598,7 +2598,7 @@
         <v>700</v>
       </c>
       <c r="F17" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -3872,7 +3872,7 @@
         <v>699</v>
       </c>
       <c r="F66" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -5698,7 +5698,7 @@
         <v>0.0</v>
       </c>
       <c r="H136" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="137">
@@ -9774,7 +9774,7 @@
         <v>700</v>
       </c>
       <c r="F293" t="n">
-        <v>206.0</v>
+        <v>207.0</v>
       </c>
       <c r="G293" t="n">
         <v>4.0</v>
@@ -11236,7 +11236,7 @@
         <v>0.0</v>
       </c>
       <c r="H349" t="n">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="350">
@@ -13440,7 +13440,7 @@
         <v>699</v>
       </c>
       <c r="F434" t="n">
-        <v>220.0</v>
+        <v>219.0</v>
       </c>
       <c r="G434" t="n">
         <v>1.0</v>
@@ -18640,7 +18640,7 @@
         <v>701</v>
       </c>
       <c r="F634" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2474,7 +2474,7 @@
         <v>0.0</v>
       </c>
       <c r="H12" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="13">
@@ -2523,7 +2523,7 @@
         <v>432.0</v>
       </c>
       <c r="G14" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H14" t="n">
         <v>3.0</v>
@@ -3144,7 +3144,7 @@
         <v>699</v>
       </c>
       <c r="F38" t="n">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
       <c r="G38" t="n">
         <v>1.0</v>
@@ -4863,7 +4863,7 @@
         <v>474.0</v>
       </c>
       <c r="G104" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H104" t="n">
         <v>2.0</v>
@@ -5692,7 +5692,7 @@
         <v>699</v>
       </c>
       <c r="F136" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -7590,7 +7590,7 @@
         <v>699</v>
       </c>
       <c r="F209" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="G209" t="n">
         <v>0.0</v>
@@ -8214,7 +8214,7 @@
         <v>701</v>
       </c>
       <c r="F233" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G233" t="n">
         <v>0.0</v>
@@ -8942,7 +8942,7 @@
         <v>699</v>
       </c>
       <c r="F261" t="n">
-        <v>226.0</v>
+        <v>229.0</v>
       </c>
       <c r="G261" t="n">
         <v>0.0</v>
@@ -9338,7 +9338,7 @@
         <v>0.0</v>
       </c>
       <c r="H276" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="277">
@@ -9358,7 +9358,7 @@
         <v>699</v>
       </c>
       <c r="F277" t="n">
-        <v>496.0</v>
+        <v>497.0</v>
       </c>
       <c r="G277" t="n">
         <v>0.0</v>
@@ -10034,7 +10034,7 @@
         <v>699</v>
       </c>
       <c r="F303" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G303" t="n">
         <v>2.0</v>
@@ -10190,10 +10190,10 @@
         <v>699</v>
       </c>
       <c r="F309" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
       <c r="G309" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H309" t="n">
         <v>0.0</v>
@@ -10794,7 +10794,7 @@
         <v>0.0</v>
       </c>
       <c r="H332" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="333">
@@ -11230,7 +11230,7 @@
         <v>699</v>
       </c>
       <c r="F349" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G349" t="n">
         <v>0.0</v>
@@ -11360,7 +11360,7 @@
         <v>699</v>
       </c>
       <c r="F354" t="n">
-        <v>517.0</v>
+        <v>518.0</v>
       </c>
       <c r="G354" t="n">
         <v>6.0</v>
@@ -11672,7 +11672,7 @@
         <v>701</v>
       </c>
       <c r="F366" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G366" t="n">
         <v>0.0</v>
@@ -14220,7 +14220,7 @@
         <v>699</v>
       </c>
       <c r="F464" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G464" t="n">
         <v>7.0</v>
@@ -15240,7 +15240,7 @@
         <v>0.0</v>
       </c>
       <c r="H503" t="n">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="504">
@@ -16696,7 +16696,7 @@
         <v>0.0</v>
       </c>
       <c r="H559" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="560">
@@ -16716,7 +16716,7 @@
         <v>699</v>
       </c>
       <c r="F560" t="n">
-        <v>262.0</v>
+        <v>265.0</v>
       </c>
       <c r="G560" t="n">
         <v>1.0</v>
@@ -19267,7 +19267,7 @@
         <v>85.0</v>
       </c>
       <c r="G658" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H658" t="n">
         <v>0.0</v>
@@ -19319,7 +19319,7 @@
         <v>115.0</v>
       </c>
       <c r="G660" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="H660" t="n">
         <v>0.0</v>
@@ -19472,7 +19472,7 @@
         <v>701</v>
       </c>
       <c r="F666" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -19735,7 +19735,7 @@
         <v>54.0</v>
       </c>
       <c r="G676" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="H676" t="n">
         <v>2.0</v>
@@ -19836,7 +19836,7 @@
         <v>701</v>
       </c>
       <c r="F680" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -19966,7 +19966,7 @@
         <v>701</v>
       </c>
       <c r="F685" t="n">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -20200,7 +20200,7 @@
         <v>701</v>
       </c>
       <c r="F694" t="n">
-        <v>350.0</v>
+        <v>362.0</v>
       </c>
       <c r="G694" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2754,7 +2754,7 @@
         <v>701</v>
       </c>
       <c r="F23" t="n">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -3482,7 +3482,7 @@
         <v>701</v>
       </c>
       <c r="F51" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -3976,10 +3976,10 @@
         <v>699</v>
       </c>
       <c r="F70" t="n">
-        <v>139.0</v>
+        <v>142.0</v>
       </c>
       <c r="G70" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H70" t="n">
         <v>10.0</v>
@@ -4158,7 +4158,7 @@
         <v>701</v>
       </c>
       <c r="F77" t="n">
-        <v>342.0</v>
+        <v>343.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4522,7 +4522,7 @@
         <v>700</v>
       </c>
       <c r="F91" t="n">
-        <v>466.0</v>
+        <v>467.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -6108,10 +6108,10 @@
         <v>699</v>
       </c>
       <c r="F152" t="n">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -7018,7 +7018,7 @@
         <v>701</v>
       </c>
       <c r="F187" t="n">
-        <v>636.0</v>
+        <v>640.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7148,7 +7148,7 @@
         <v>699</v>
       </c>
       <c r="F192" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="G192" t="n">
         <v>2.0</v>
@@ -7356,7 +7356,7 @@
         <v>699</v>
       </c>
       <c r="F200" t="n">
-        <v>993.0</v>
+        <v>994.0</v>
       </c>
       <c r="G200" t="n">
         <v>1.0</v>
@@ -8032,7 +8032,7 @@
         <v>699</v>
       </c>
       <c r="F226" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G226" t="n">
         <v>1.0</v>
@@ -8318,7 +8318,7 @@
         <v>699</v>
       </c>
       <c r="F237" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -10086,7 +10086,7 @@
         <v>699</v>
       </c>
       <c r="F305" t="n">
-        <v>970.0</v>
+        <v>971.0</v>
       </c>
       <c r="G305" t="n">
         <v>5.0</v>
@@ -11568,7 +11568,7 @@
         <v>701</v>
       </c>
       <c r="F362" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G362" t="n">
         <v>0.0</v>
@@ -11984,7 +11984,7 @@
         <v>701</v>
       </c>
       <c r="F378" t="n">
-        <v>117.0</v>
+        <v>119.0</v>
       </c>
       <c r="G378" t="n">
         <v>0.0</v>
@@ -12322,7 +12322,7 @@
         <v>699</v>
       </c>
       <c r="F391" t="n">
-        <v>182.0</v>
+        <v>184.0</v>
       </c>
       <c r="G391" t="n">
         <v>7.0</v>
@@ -15286,13 +15286,13 @@
         <v>699</v>
       </c>
       <c r="F505" t="n">
-        <v>2321.0</v>
+        <v>2330.0</v>
       </c>
       <c r="G505" t="n">
         <v>44.0</v>
       </c>
       <c r="H505" t="n">
-        <v>289.0</v>
+        <v>294.0</v>
       </c>
     </row>
     <row r="506">
@@ -16118,7 +16118,7 @@
         <v>699</v>
       </c>
       <c r="F537" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16144,7 +16144,7 @@
         <v>699</v>
       </c>
       <c r="F538" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G538" t="n">
         <v>0.0</v>
@@ -16274,7 +16274,7 @@
         <v>699</v>
       </c>
       <c r="F543" t="n">
-        <v>409.0</v>
+        <v>410.0</v>
       </c>
       <c r="G543" t="n">
         <v>3.0</v>
@@ -16638,7 +16638,7 @@
         <v>701</v>
       </c>
       <c r="F557" t="n">
-        <v>547.0</v>
+        <v>548.0</v>
       </c>
       <c r="G557" t="n">
         <v>1.0</v>
@@ -16924,7 +16924,7 @@
         <v>701</v>
       </c>
       <c r="F568" t="n">
-        <v>266.0</v>
+        <v>268.0</v>
       </c>
       <c r="G568" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3306,7 +3306,7 @@
         <v>1.0</v>
       </c>
       <c r="H44" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="45">
@@ -11418,7 +11418,7 @@
         <v>7.0</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="357">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3098,7 +3098,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="37">
@@ -5074,7 +5074,7 @@
         <v>0.0</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="113">
@@ -17600,7 +17600,7 @@
         <v>701</v>
       </c>
       <c r="F594" t="n">
-        <v>363.0</v>
+        <v>366.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
@@ -19316,7 +19316,7 @@
         <v>699</v>
       </c>
       <c r="F660" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G660" t="n">
         <v>13.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3478" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="702">
   <si>
     <t>Regione</t>
   </si>
@@ -3098,7 +3098,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="37">
@@ -3306,7 +3306,7 @@
         <v>1.0</v>
       </c>
       <c r="H44" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="45">
@@ -3976,10 +3976,10 @@
         <v>699</v>
       </c>
       <c r="F70" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G70" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="H70" t="n">
         <v>10.0</v>
@@ -4548,7 +4548,7 @@
         <v>701</v>
       </c>
       <c r="F92" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -5224,7 +5224,7 @@
         <v>699</v>
       </c>
       <c r="F118" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G118" t="n">
         <v>0.0</v>
@@ -6686,7 +6686,7 @@
         <v>0.0</v>
       </c>
       <c r="H174" t="n">
-        <v>16.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="175">
@@ -6836,7 +6836,7 @@
         <v>699</v>
       </c>
       <c r="F180" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -8786,7 +8786,7 @@
         <v>699</v>
       </c>
       <c r="F255" t="n">
-        <v>929.0</v>
+        <v>930.0</v>
       </c>
       <c r="G255" t="n">
         <v>16.0</v>
@@ -10086,7 +10086,7 @@
         <v>699</v>
       </c>
       <c r="F305" t="n">
-        <v>971.0</v>
+        <v>972.0</v>
       </c>
       <c r="G305" t="n">
         <v>5.0</v>
@@ -11256,24 +11256,24 @@
         <v>699</v>
       </c>
       <c r="F350" t="n">
-        <v>120.0</v>
+        <v>0.0</v>
       </c>
       <c r="G350" t="n">
         <v>0.0</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B351" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C351" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D351" t="s">
         <v>698</v>
@@ -11282,7 +11282,7 @@
         <v>699</v>
       </c>
       <c r="F351" t="n">
-        <v>12.0</v>
+        <v>120.0</v>
       </c>
       <c r="G351" t="n">
         <v>0.0</v>
@@ -11299,7 +11299,7 @@
         <v>22</v>
       </c>
       <c r="C352" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D352" t="s">
         <v>698</v>
@@ -11308,24 +11308,24 @@
         <v>699</v>
       </c>
       <c r="F352" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="G352" t="n">
         <v>0.0</v>
       </c>
       <c r="H352" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B353" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C353" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D353" t="s">
         <v>698</v>
@@ -11334,24 +11334,24 @@
         <v>699</v>
       </c>
       <c r="F353" t="n">
-        <v>159.0</v>
+        <v>13.0</v>
       </c>
       <c r="G353" t="n">
         <v>0.0</v>
       </c>
       <c r="H353" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B354" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C354" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D354" t="s">
         <v>698</v>
@@ -11360,24 +11360,24 @@
         <v>699</v>
       </c>
       <c r="F354" t="n">
-        <v>518.0</v>
+        <v>159.0</v>
       </c>
       <c r="G354" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B355" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C355" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D355" t="s">
         <v>698</v>
@@ -11386,24 +11386,24 @@
         <v>699</v>
       </c>
       <c r="F355" t="n">
-        <v>54.0</v>
+        <v>519.0</v>
       </c>
       <c r="G355" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H355" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B356" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C356" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D356" t="s">
         <v>698</v>
@@ -11412,24 +11412,24 @@
         <v>699</v>
       </c>
       <c r="F356" t="n">
-        <v>90.0</v>
+        <v>54.0</v>
       </c>
       <c r="G356" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H356" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B357" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C357" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D357" t="s">
         <v>698</v>
@@ -11438,24 +11438,24 @@
         <v>699</v>
       </c>
       <c r="F357" t="n">
-        <v>98.0</v>
+        <v>90.0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B358" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C358" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D358" t="s">
         <v>698</v>
@@ -11464,24 +11464,24 @@
         <v>699</v>
       </c>
       <c r="F358" t="n">
-        <v>19.0</v>
+        <v>98.0</v>
       </c>
       <c r="G358" t="n">
         <v>0.0</v>
       </c>
       <c r="H358" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B359" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C359" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D359" t="s">
         <v>698</v>
@@ -11490,13 +11490,13 @@
         <v>699</v>
       </c>
       <c r="F359" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G359" t="n">
         <v>0.0</v>
       </c>
       <c r="H359" t="n">
-        <v>18.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="360">
@@ -11507,7 +11507,7 @@
         <v>15</v>
       </c>
       <c r="C360" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D360" t="s">
         <v>698</v>
@@ -11516,13 +11516,13 @@
         <v>699</v>
       </c>
       <c r="F360" t="n">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="G360" t="n">
         <v>0.0</v>
       </c>
       <c r="H360" t="n">
-        <v>8.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="361">
@@ -11533,7 +11533,7 @@
         <v>15</v>
       </c>
       <c r="C361" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D361" t="s">
         <v>698</v>
@@ -11542,76 +11542,76 @@
         <v>699</v>
       </c>
       <c r="F361" t="n">
-        <v>28.0</v>
+        <v>22.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
       </c>
       <c r="H361" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B362" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C362" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D362" t="s">
         <v>698</v>
       </c>
       <c r="E362" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F362" t="n">
-        <v>94.0</v>
+        <v>28.0</v>
       </c>
       <c r="G362" t="n">
         <v>0.0</v>
       </c>
       <c r="H362" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B363" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C363" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D363" t="s">
         <v>698</v>
       </c>
       <c r="E363" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F363" t="n">
-        <v>15.0</v>
+        <v>94.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
       </c>
       <c r="H363" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B364" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C364" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D364" t="s">
         <v>698</v>
@@ -11620,7 +11620,7 @@
         <v>699</v>
       </c>
       <c r="F364" t="n">
-        <v>48.0</v>
+        <v>15.0</v>
       </c>
       <c r="G364" t="n">
         <v>0.0</v>
@@ -11631,13 +11631,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B365" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C365" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D365" t="s">
         <v>698</v>
@@ -11646,7 +11646,7 @@
         <v>699</v>
       </c>
       <c r="F365" t="n">
-        <v>104.0</v>
+        <v>48.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -11663,22 +11663,22 @@
         <v>18</v>
       </c>
       <c r="C366" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D366" t="s">
         <v>698</v>
       </c>
       <c r="E366" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F366" t="n">
-        <v>169.0</v>
+        <v>104.0</v>
       </c>
       <c r="G366" t="n">
         <v>0.0</v>
       </c>
       <c r="H366" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="367">
@@ -11686,25 +11686,25 @@
         <v>9</v>
       </c>
       <c r="B367" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C367" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D367" t="s">
         <v>698</v>
       </c>
       <c r="E367" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F367" t="n">
-        <v>14.0</v>
+        <v>169.0</v>
       </c>
       <c r="G367" t="n">
         <v>0.0</v>
       </c>
       <c r="H367" t="n">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="368">
@@ -11715,22 +11715,22 @@
         <v>15</v>
       </c>
       <c r="C368" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D368" t="s">
         <v>698</v>
       </c>
       <c r="E368" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F368" t="n">
-        <v>128.0</v>
+        <v>14.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
       </c>
       <c r="H368" t="n">
-        <v>7.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="369">
@@ -11741,22 +11741,22 @@
         <v>15</v>
       </c>
       <c r="C369" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D369" t="s">
         <v>698</v>
       </c>
       <c r="E369" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F369" t="n">
-        <v>23.0</v>
+        <v>128.0</v>
       </c>
       <c r="G369" t="n">
         <v>0.0</v>
       </c>
       <c r="H369" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="370">
@@ -11764,19 +11764,19 @@
         <v>9</v>
       </c>
       <c r="B370" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C370" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D370" t="s">
         <v>698</v>
       </c>
       <c r="E370" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F370" t="n">
-        <v>60.0</v>
+        <v>23.0</v>
       </c>
       <c r="G370" t="n">
         <v>0.0</v>
@@ -11787,22 +11787,22 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B371" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C371" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D371" t="s">
         <v>698</v>
       </c>
       <c r="E371" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F371" t="n">
-        <v>4.0</v>
+        <v>60.0</v>
       </c>
       <c r="G371" t="n">
         <v>0.0</v>
@@ -11813,22 +11813,22 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B372" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C372" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D372" t="s">
         <v>698</v>
       </c>
       <c r="E372" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F372" t="n">
-        <v>29.0</v>
+        <v>4.0</v>
       </c>
       <c r="G372" t="n">
         <v>0.0</v>
@@ -11839,13 +11839,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B373" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C373" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D373" t="s">
         <v>698</v>
@@ -11854,7 +11854,7 @@
         <v>699</v>
       </c>
       <c r="F373" t="n">
-        <v>96.0</v>
+        <v>29.0</v>
       </c>
       <c r="G373" t="n">
         <v>0.0</v>
@@ -11865,13 +11865,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B374" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C374" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D374" t="s">
         <v>698</v>
@@ -11880,39 +11880,39 @@
         <v>699</v>
       </c>
       <c r="F374" t="n">
-        <v>71.0</v>
+        <v>96.0</v>
       </c>
       <c r="G374" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H374" t="n">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B375" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C375" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D375" t="s">
         <v>698</v>
       </c>
       <c r="E375" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F375" t="n">
-        <v>6.0</v>
+        <v>71.0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H375" t="n">
-        <v>0.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="376">
@@ -11923,16 +11923,16 @@
         <v>22</v>
       </c>
       <c r="C376" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D376" t="s">
         <v>698</v>
       </c>
       <c r="E376" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F376" t="n">
-        <v>26.0</v>
+        <v>6.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -11943,13 +11943,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B377" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C377" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D377" t="s">
         <v>698</v>
@@ -11958,91 +11958,91 @@
         <v>699</v>
       </c>
       <c r="F377" t="n">
-        <v>99.0</v>
+        <v>26.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
       </c>
       <c r="H377" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B378" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C378" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D378" t="s">
         <v>698</v>
       </c>
       <c r="E378" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F378" t="n">
-        <v>119.0</v>
+        <v>99.0</v>
       </c>
       <c r="G378" t="n">
         <v>0.0</v>
       </c>
       <c r="H378" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B379" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C379" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D379" t="s">
         <v>698</v>
       </c>
       <c r="E379" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F379" t="n">
-        <v>32.0</v>
+        <v>119.0</v>
       </c>
       <c r="G379" t="n">
         <v>0.0</v>
       </c>
       <c r="H379" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B380" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C380" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D380" t="s">
         <v>698</v>
       </c>
       <c r="E380" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F380" t="n">
-        <v>115.0</v>
+        <v>32.0</v>
       </c>
       <c r="G380" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H380" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="381">
@@ -12050,10 +12050,10 @@
         <v>9</v>
       </c>
       <c r="B381" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C381" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D381" t="s">
         <v>698</v>
@@ -12062,10 +12062,10 @@
         <v>701</v>
       </c>
       <c r="F381" t="n">
-        <v>31.0</v>
+        <v>115.0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H381" t="n">
         <v>0.0</v>
@@ -12073,54 +12073,54 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B382" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C382" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D382" t="s">
         <v>698</v>
       </c>
       <c r="E382" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F382" t="n">
-        <v>229.0</v>
+        <v>31.0</v>
       </c>
       <c r="G382" t="n">
         <v>0.0</v>
       </c>
       <c r="H382" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B383" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C383" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D383" t="s">
         <v>698</v>
       </c>
       <c r="E383" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F383" t="n">
+        <v>229.0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H383" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G383" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H383" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="384">
@@ -12128,10 +12128,10 @@
         <v>9</v>
       </c>
       <c r="B384" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C384" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D384" t="s">
         <v>698</v>
@@ -12140,7 +12140,7 @@
         <v>701</v>
       </c>
       <c r="F384" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="G384" t="n">
         <v>0.0</v>
@@ -12157,7 +12157,7 @@
         <v>21</v>
       </c>
       <c r="C385" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D385" t="s">
         <v>698</v>
@@ -12177,13 +12177,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B386" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C386" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D386" t="s">
         <v>698</v>
@@ -12203,13 +12203,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B387" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C387" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D387" t="s">
         <v>698</v>
@@ -12218,7 +12218,7 @@
         <v>701</v>
       </c>
       <c r="F387" t="n">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="G387" t="n">
         <v>0.0</v>
@@ -12229,39 +12229,39 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B388" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C388" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D388" t="s">
         <v>698</v>
       </c>
       <c r="E388" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F388" t="n">
-        <v>69.0</v>
+        <v>20.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
       </c>
       <c r="H388" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B389" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C389" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D389" t="s">
         <v>698</v>
@@ -12270,24 +12270,24 @@
         <v>699</v>
       </c>
       <c r="F389" t="n">
-        <v>63.0</v>
+        <v>69.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
       </c>
       <c r="H389" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B390" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C390" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D390" t="s">
         <v>698</v>
@@ -12296,13 +12296,13 @@
         <v>699</v>
       </c>
       <c r="F390" t="n">
-        <v>138.0</v>
+        <v>63.0</v>
       </c>
       <c r="G390" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H390" t="n">
-        <v>36.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="391">
@@ -12313,7 +12313,7 @@
         <v>17</v>
       </c>
       <c r="C391" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D391" t="s">
         <v>698</v>
@@ -12322,65 +12322,65 @@
         <v>699</v>
       </c>
       <c r="F391" t="n">
-        <v>184.0</v>
+        <v>138.0</v>
       </c>
       <c r="G391" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="H391" t="n">
-        <v>2.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B392" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C392" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D392" t="s">
         <v>698</v>
       </c>
       <c r="E392" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F392" t="n">
-        <v>17.0</v>
+        <v>184.0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H392" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B393" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C393" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D393" t="s">
         <v>698</v>
       </c>
       <c r="E393" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F393" t="n">
-        <v>117.0</v>
+        <v>17.0</v>
       </c>
       <c r="G393" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H393" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="394">
@@ -12388,10 +12388,10 @@
         <v>11</v>
       </c>
       <c r="B394" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C394" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D394" t="s">
         <v>698</v>
@@ -12400,24 +12400,24 @@
         <v>699</v>
       </c>
       <c r="F394" t="n">
-        <v>140.0</v>
+        <v>117.0</v>
       </c>
       <c r="G394" t="n">
         <v>1.0</v>
       </c>
       <c r="H394" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B395" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C395" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D395" t="s">
         <v>698</v>
@@ -12426,10 +12426,10 @@
         <v>699</v>
       </c>
       <c r="F395" t="n">
-        <v>0.0</v>
+        <v>140.0</v>
       </c>
       <c r="G395" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H395" t="n">
         <v>3.0</v>
@@ -12452,33 +12452,33 @@
         <v>699</v>
       </c>
       <c r="F396" t="n">
-        <v>432.0</v>
+        <v>0.0</v>
       </c>
       <c r="G396" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H396" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B397" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C397" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D397" t="s">
         <v>698</v>
       </c>
       <c r="E397" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F397" t="n">
-        <v>65.0</v>
+        <v>432.0</v>
       </c>
       <c r="G397" t="n">
         <v>1.0</v>
@@ -12489,39 +12489,39 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B398" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C398" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D398" t="s">
         <v>698</v>
       </c>
       <c r="E398" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F398" t="n">
-        <v>39.0</v>
+        <v>65.0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H398" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B399" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C399" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D399" t="s">
         <v>698</v>
@@ -12530,13 +12530,13 @@
         <v>699</v>
       </c>
       <c r="F399" t="n">
-        <v>6.0</v>
+        <v>39.0</v>
       </c>
       <c r="G399" t="n">
         <v>0.0</v>
       </c>
       <c r="H399" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="400">
@@ -12547,7 +12547,7 @@
         <v>15</v>
       </c>
       <c r="C400" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D400" t="s">
         <v>698</v>
@@ -12556,24 +12556,24 @@
         <v>699</v>
       </c>
       <c r="F400" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G400" t="n">
         <v>0.0</v>
       </c>
       <c r="H400" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B401" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C401" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D401" t="s">
         <v>698</v>
@@ -12582,24 +12582,24 @@
         <v>699</v>
       </c>
       <c r="F401" t="n">
-        <v>32.0</v>
+        <v>8.0</v>
       </c>
       <c r="G401" t="n">
         <v>0.0</v>
       </c>
       <c r="H401" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B402" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C402" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D402" t="s">
         <v>698</v>
@@ -12608,13 +12608,13 @@
         <v>699</v>
       </c>
       <c r="F402" t="n">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="G402" t="n">
         <v>0.0</v>
       </c>
       <c r="H402" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="403">
@@ -12622,25 +12622,25 @@
         <v>9</v>
       </c>
       <c r="B403" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C403" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D403" t="s">
         <v>698</v>
       </c>
       <c r="E403" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F403" t="n">
-        <v>6.0</v>
+        <v>36.0</v>
       </c>
       <c r="G403" t="n">
         <v>0.0</v>
       </c>
       <c r="H403" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="404">
@@ -12648,10 +12648,10 @@
         <v>9</v>
       </c>
       <c r="B404" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C404" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D404" t="s">
         <v>698</v>
@@ -12674,25 +12674,25 @@
         <v>9</v>
       </c>
       <c r="B405" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C405" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D405" t="s">
         <v>698</v>
       </c>
       <c r="E405" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F405" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G405" t="n">
         <v>0.0</v>
       </c>
       <c r="H405" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="406">
@@ -12700,62 +12700,62 @@
         <v>9</v>
       </c>
       <c r="B406" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C406" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D406" t="s">
         <v>698</v>
       </c>
       <c r="E406" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F406" t="n">
-        <v>73.0</v>
+        <v>2.0</v>
       </c>
       <c r="G406" t="n">
         <v>0.0</v>
       </c>
       <c r="H406" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B407" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C407" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D407" t="s">
         <v>698</v>
       </c>
       <c r="E407" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F407" t="n">
-        <v>287.0</v>
+        <v>73.0</v>
       </c>
       <c r="G407" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="H407" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B408" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C408" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D408" t="s">
         <v>698</v>
@@ -12764,33 +12764,33 @@
         <v>699</v>
       </c>
       <c r="F408" t="n">
-        <v>88.0</v>
+        <v>287.0</v>
       </c>
       <c r="G408" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B409" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C409" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D409" t="s">
         <v>698</v>
       </c>
       <c r="E409" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F409" t="n">
-        <v>0.0</v>
+        <v>88.0</v>
       </c>
       <c r="G409" t="n">
         <v>0.0</v>
@@ -12801,28 +12801,28 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B410" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C410" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D410" t="s">
         <v>698</v>
       </c>
       <c r="E410" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F410" t="n">
-        <v>88.0</v>
+        <v>0.0</v>
       </c>
       <c r="G410" t="n">
         <v>0.0</v>
       </c>
       <c r="H410" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="411">
@@ -12833,7 +12833,7 @@
         <v>15</v>
       </c>
       <c r="C411" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D411" t="s">
         <v>698</v>
@@ -12842,13 +12842,13 @@
         <v>699</v>
       </c>
       <c r="F411" t="n">
-        <v>182.0</v>
+        <v>88.0</v>
       </c>
       <c r="G411" t="n">
         <v>0.0</v>
       </c>
       <c r="H411" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="412">
@@ -12859,7 +12859,7 @@
         <v>15</v>
       </c>
       <c r="C412" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D412" t="s">
         <v>698</v>
@@ -12868,13 +12868,13 @@
         <v>699</v>
       </c>
       <c r="F412" t="n">
-        <v>8.0</v>
+        <v>182.0</v>
       </c>
       <c r="G412" t="n">
         <v>0.0</v>
       </c>
       <c r="H412" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="413">
@@ -12885,7 +12885,7 @@
         <v>15</v>
       </c>
       <c r="C413" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D413" t="s">
         <v>698</v>
@@ -12894,7 +12894,7 @@
         <v>699</v>
       </c>
       <c r="F413" t="n">
-        <v>122.0</v>
+        <v>8.0</v>
       </c>
       <c r="G413" t="n">
         <v>0.0</v>
@@ -12905,13 +12905,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B414" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C414" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D414" t="s">
         <v>698</v>
@@ -12920,24 +12920,24 @@
         <v>699</v>
       </c>
       <c r="F414" t="n">
-        <v>71.0</v>
+        <v>122.0</v>
       </c>
       <c r="G414" t="n">
         <v>0.0</v>
       </c>
       <c r="H414" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B415" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C415" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D415" t="s">
         <v>698</v>
@@ -12946,24 +12946,24 @@
         <v>699</v>
       </c>
       <c r="F415" t="n">
-        <v>38.0</v>
+        <v>71.0</v>
       </c>
       <c r="G415" t="n">
         <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B416" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C416" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D416" t="s">
         <v>698</v>
@@ -12972,13 +12972,13 @@
         <v>699</v>
       </c>
       <c r="F416" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="G416" t="n">
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>36.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="417">
@@ -12998,24 +12998,24 @@
         <v>699</v>
       </c>
       <c r="F417" t="n">
-        <v>268.0</v>
+        <v>0.0</v>
       </c>
       <c r="G417" t="n">
         <v>0.0</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B418" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C418" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D418" t="s">
         <v>698</v>
@@ -13024,39 +13024,39 @@
         <v>699</v>
       </c>
       <c r="F418" t="n">
-        <v>39.0</v>
+        <v>268.0</v>
       </c>
       <c r="G418" t="n">
         <v>0.0</v>
       </c>
       <c r="H418" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B419" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C419" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D419" t="s">
         <v>698</v>
       </c>
       <c r="E419" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F419" t="n">
-        <v>219.0</v>
+        <v>39.0</v>
       </c>
       <c r="G419" t="n">
         <v>0.0</v>
       </c>
       <c r="H419" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="420">
@@ -13067,16 +13067,16 @@
         <v>19</v>
       </c>
       <c r="C420" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D420" t="s">
         <v>698</v>
       </c>
       <c r="E420" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F420" t="n">
-        <v>35.0</v>
+        <v>219.0</v>
       </c>
       <c r="G420" t="n">
         <v>0.0</v>
@@ -13087,13 +13087,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B421" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C421" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D421" t="s">
         <v>698</v>
@@ -13102,7 +13102,7 @@
         <v>699</v>
       </c>
       <c r="F421" t="n">
-        <v>14.0</v>
+        <v>35.0</v>
       </c>
       <c r="G421" t="n">
         <v>0.0</v>
@@ -13113,13 +13113,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B422" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C422" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D422" t="s">
         <v>698</v>
@@ -13128,7 +13128,7 @@
         <v>699</v>
       </c>
       <c r="F422" t="n">
-        <v>34.0</v>
+        <v>14.0</v>
       </c>
       <c r="G422" t="n">
         <v>0.0</v>
@@ -13145,7 +13145,7 @@
         <v>22</v>
       </c>
       <c r="C423" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D423" t="s">
         <v>698</v>
@@ -13154,39 +13154,39 @@
         <v>699</v>
       </c>
       <c r="F423" t="n">
-        <v>49.0</v>
+        <v>34.0</v>
       </c>
       <c r="G423" t="n">
         <v>0.0</v>
       </c>
       <c r="H423" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B424" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C424" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D424" t="s">
         <v>698</v>
       </c>
       <c r="E424" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F424" t="n">
-        <v>14.0</v>
+        <v>49.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
       </c>
       <c r="H424" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="425">
@@ -13197,7 +13197,7 @@
         <v>21</v>
       </c>
       <c r="C425" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D425" t="s">
         <v>698</v>
@@ -13206,7 +13206,7 @@
         <v>701</v>
       </c>
       <c r="F425" t="n">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="G425" t="n">
         <v>0.0</v>
@@ -13220,19 +13220,19 @@
         <v>9</v>
       </c>
       <c r="B426" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C426" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D426" t="s">
         <v>698</v>
       </c>
       <c r="E426" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F426" t="n">
-        <v>46.0</v>
+        <v>21.0</v>
       </c>
       <c r="G426" t="n">
         <v>0.0</v>
@@ -13243,48 +13243,48 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B427" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C427" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D427" t="s">
         <v>698</v>
       </c>
       <c r="E427" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F427" t="n">
-        <v>93.0</v>
+        <v>46.0</v>
       </c>
       <c r="G427" t="n">
         <v>0.0</v>
       </c>
       <c r="H427" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B428" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C428" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D428" t="s">
         <v>698</v>
       </c>
       <c r="E428" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F428" t="n">
-        <v>22.0</v>
+        <v>93.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -13295,13 +13295,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B429" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C429" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D429" t="s">
         <v>698</v>
@@ -13310,39 +13310,39 @@
         <v>701</v>
       </c>
       <c r="F429" t="n">
-        <v>98.0</v>
+        <v>22.0</v>
       </c>
       <c r="G429" t="n">
         <v>0.0</v>
       </c>
       <c r="H429" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B430" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C430" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D430" t="s">
         <v>698</v>
       </c>
       <c r="E430" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F430" t="n">
-        <v>26.0</v>
+        <v>98.0</v>
       </c>
       <c r="G430" t="n">
         <v>0.0</v>
       </c>
       <c r="H430" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="431">
@@ -13353,7 +13353,7 @@
         <v>22</v>
       </c>
       <c r="C431" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D431" t="s">
         <v>698</v>
@@ -13362,24 +13362,24 @@
         <v>699</v>
       </c>
       <c r="F431" t="n">
-        <v>84.0</v>
+        <v>26.0</v>
       </c>
       <c r="G431" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H431" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B432" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C432" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D432" t="s">
         <v>698</v>
@@ -13388,76 +13388,76 @@
         <v>699</v>
       </c>
       <c r="F432" t="n">
-        <v>105.0</v>
+        <v>84.0</v>
       </c>
       <c r="G432" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H432" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B433" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C433" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D433" t="s">
         <v>698</v>
       </c>
       <c r="E433" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F433" t="n">
-        <v>3.0</v>
+        <v>105.0</v>
       </c>
       <c r="G433" t="n">
         <v>0.0</v>
       </c>
       <c r="H433" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B434" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C434" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D434" t="s">
         <v>698</v>
       </c>
       <c r="E434" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F434" t="n">
-        <v>219.0</v>
+        <v>3.0</v>
       </c>
       <c r="G434" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H434" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B435" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C435" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D435" t="s">
         <v>698</v>
@@ -13466,13 +13466,13 @@
         <v>699</v>
       </c>
       <c r="F435" t="n">
-        <v>80.0</v>
+        <v>219.0</v>
       </c>
       <c r="G435" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H435" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="436">
@@ -13480,10 +13480,10 @@
         <v>9</v>
       </c>
       <c r="B436" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C436" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D436" t="s">
         <v>698</v>
@@ -13492,7 +13492,7 @@
         <v>699</v>
       </c>
       <c r="F436" t="n">
-        <v>1.0</v>
+        <v>80.0</v>
       </c>
       <c r="G436" t="n">
         <v>0.0</v>
@@ -13509,7 +13509,7 @@
         <v>15</v>
       </c>
       <c r="C437" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D437" t="s">
         <v>698</v>
@@ -13518,7 +13518,7 @@
         <v>699</v>
       </c>
       <c r="F437" t="n">
-        <v>23.0</v>
+        <v>1.0</v>
       </c>
       <c r="G437" t="n">
         <v>0.0</v>
@@ -13529,13 +13529,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B438" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C438" t="s">
-        <v>23</v>
+        <v>451</v>
       </c>
       <c r="D438" t="s">
         <v>698</v>
@@ -13544,10 +13544,10 @@
         <v>699</v>
       </c>
       <c r="F438" t="n">
-        <v>539.0</v>
+        <v>23.0</v>
       </c>
       <c r="G438" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H438" t="n">
         <v>0.0</v>
@@ -13558,10 +13558,10 @@
         <v>11</v>
       </c>
       <c r="B439" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C439" t="s">
-        <v>452</v>
+        <v>23</v>
       </c>
       <c r="D439" t="s">
         <v>698</v>
@@ -13570,24 +13570,24 @@
         <v>699</v>
       </c>
       <c r="F439" t="n">
-        <v>150.0</v>
+        <v>539.0</v>
       </c>
       <c r="G439" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H439" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B440" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C440" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D440" t="s">
         <v>698</v>
@@ -13596,24 +13596,24 @@
         <v>699</v>
       </c>
       <c r="F440" t="n">
-        <v>135.0</v>
+        <v>150.0</v>
       </c>
       <c r="G440" t="n">
         <v>0.0</v>
       </c>
       <c r="H440" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B441" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C441" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D441" t="s">
         <v>698</v>
@@ -13622,24 +13622,24 @@
         <v>699</v>
       </c>
       <c r="F441" t="n">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="G441" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H441" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B442" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C442" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D442" t="s">
         <v>698</v>
@@ -13648,24 +13648,24 @@
         <v>699</v>
       </c>
       <c r="F442" t="n">
-        <v>187.0</v>
+        <v>121.0</v>
       </c>
       <c r="G442" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H442" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B443" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C443" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D443" t="s">
         <v>698</v>
@@ -13674,13 +13674,13 @@
         <v>699</v>
       </c>
       <c r="F443" t="n">
-        <v>758.0</v>
+        <v>187.0</v>
       </c>
       <c r="G443" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H443" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="444">
@@ -13688,10 +13688,10 @@
         <v>11</v>
       </c>
       <c r="B444" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C444" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D444" t="s">
         <v>698</v>
@@ -13700,39 +13700,39 @@
         <v>699</v>
       </c>
       <c r="F444" t="n">
-        <v>59.0</v>
+        <v>758.0</v>
       </c>
       <c r="G444" t="n">
         <v>2.0</v>
       </c>
       <c r="H444" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B445" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C445" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D445" t="s">
         <v>698</v>
       </c>
       <c r="E445" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F445" t="n">
-        <v>136.0</v>
+        <v>59.0</v>
       </c>
       <c r="G445" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H445" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="446">
@@ -13743,22 +13743,22 @@
         <v>15</v>
       </c>
       <c r="C446" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D446" t="s">
         <v>698</v>
       </c>
       <c r="E446" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F446" t="n">
-        <v>32.0</v>
+        <v>136.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
       </c>
       <c r="H446" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="447">
@@ -13769,7 +13769,7 @@
         <v>15</v>
       </c>
       <c r="C447" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D447" t="s">
         <v>698</v>
@@ -13778,13 +13778,13 @@
         <v>699</v>
       </c>
       <c r="F447" t="n">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
       </c>
       <c r="H447" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="448">
@@ -13792,10 +13792,10 @@
         <v>9</v>
       </c>
       <c r="B448" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C448" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D448" t="s">
         <v>698</v>
@@ -13804,24 +13804,24 @@
         <v>699</v>
       </c>
       <c r="F448" t="n">
-        <v>61.0</v>
+        <v>27.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
       </c>
       <c r="H448" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B449" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C449" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D449" t="s">
         <v>698</v>
@@ -13830,39 +13830,39 @@
         <v>699</v>
       </c>
       <c r="F449" t="n">
-        <v>122.0</v>
+        <v>61.0</v>
       </c>
       <c r="G449" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H449" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B450" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C450" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D450" t="s">
         <v>698</v>
       </c>
       <c r="E450" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F450" t="n">
-        <v>194.0</v>
+        <v>122.0</v>
       </c>
       <c r="G450" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H450" t="n">
-        <v>2.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="451">
@@ -13873,33 +13873,33 @@
         <v>18</v>
       </c>
       <c r="C451" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D451" t="s">
         <v>698</v>
       </c>
       <c r="E451" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F451" t="n">
-        <v>377.0</v>
+        <v>194.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
       </c>
       <c r="H451" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B452" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C452" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D452" t="s">
         <v>698</v>
@@ -13908,24 +13908,24 @@
         <v>699</v>
       </c>
       <c r="F452" t="n">
-        <v>58.0</v>
+        <v>377.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
       </c>
       <c r="H452" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B453" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C453" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D453" t="s">
         <v>698</v>
@@ -13934,59 +13934,59 @@
         <v>699</v>
       </c>
       <c r="F453" t="n">
-        <v>16.0</v>
+        <v>58.0</v>
       </c>
       <c r="G453" t="n">
         <v>0.0</v>
       </c>
       <c r="H453" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B454" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C454" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D454" t="s">
         <v>698</v>
       </c>
       <c r="E454" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F454" t="n">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="G454" t="n">
         <v>0.0</v>
       </c>
       <c r="H454" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B455" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C455" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D455" t="s">
         <v>698</v>
       </c>
       <c r="E455" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F455" t="n">
-        <v>33.0</v>
+        <v>11.0</v>
       </c>
       <c r="G455" t="n">
         <v>0.0</v>
@@ -13997,13 +13997,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B456" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C456" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D456" t="s">
         <v>698</v>
@@ -14012,24 +14012,24 @@
         <v>699</v>
       </c>
       <c r="F456" t="n">
-        <v>131.0</v>
+        <v>33.0</v>
       </c>
       <c r="G456" t="n">
         <v>0.0</v>
       </c>
       <c r="H456" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B457" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C457" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D457" t="s">
         <v>698</v>
@@ -14038,13 +14038,13 @@
         <v>699</v>
       </c>
       <c r="F457" t="n">
-        <v>53.0</v>
+        <v>131.0</v>
       </c>
       <c r="G457" t="n">
         <v>0.0</v>
       </c>
       <c r="H457" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="458">
@@ -14055,16 +14055,16 @@
         <v>19</v>
       </c>
       <c r="C458" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D458" t="s">
         <v>698</v>
       </c>
       <c r="E458" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F458" t="n">
-        <v>204.0</v>
+        <v>53.0</v>
       </c>
       <c r="G458" t="n">
         <v>0.0</v>
@@ -14075,28 +14075,28 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B459" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C459" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D459" t="s">
         <v>698</v>
       </c>
       <c r="E459" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F459" t="n">
-        <v>18.0</v>
+        <v>204.0</v>
       </c>
       <c r="G459" t="n">
         <v>0.0</v>
       </c>
       <c r="H459" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="460">
@@ -14107,22 +14107,22 @@
         <v>15</v>
       </c>
       <c r="C460" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D460" t="s">
         <v>698</v>
       </c>
       <c r="E460" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F460" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="G460" t="n">
         <v>0.0</v>
       </c>
       <c r="H460" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="461">
@@ -14130,22 +14130,22 @@
         <v>9</v>
       </c>
       <c r="B461" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C461" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D461" t="s">
         <v>698</v>
       </c>
       <c r="E461" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F461" t="n">
-        <v>523.0</v>
+        <v>0.0</v>
       </c>
       <c r="G461" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H461" t="n">
         <v>0.0</v>
@@ -14153,25 +14153,25 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B462" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C462" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D462" t="s">
         <v>698</v>
       </c>
       <c r="E462" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F462" t="n">
-        <v>182.0</v>
+        <v>523.0</v>
       </c>
       <c r="G462" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H462" t="n">
         <v>0.0</v>
@@ -14182,36 +14182,36 @@
         <v>11</v>
       </c>
       <c r="B463" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C463" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D463" t="s">
         <v>698</v>
       </c>
       <c r="E463" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F463" t="n">
-        <v>32.0</v>
+        <v>182.0</v>
       </c>
       <c r="G463" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H463" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B464" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C464" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D464" t="s">
         <v>698</v>
@@ -14220,76 +14220,76 @@
         <v>699</v>
       </c>
       <c r="F464" t="n">
-        <v>164.0</v>
+        <v>32.0</v>
       </c>
       <c r="G464" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H464" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B465" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C465" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D465" t="s">
         <v>698</v>
       </c>
       <c r="E465" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F465" t="n">
-        <v>129.0</v>
+        <v>164.0</v>
       </c>
       <c r="G465" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H465" t="n">
-        <v>44.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B466" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C466" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D466" t="s">
         <v>698</v>
       </c>
       <c r="E466" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F466" t="n">
-        <v>94.0</v>
+        <v>129.0</v>
       </c>
       <c r="G466" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H466" t="n">
-        <v>0.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B467" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C467" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D467" t="s">
         <v>698</v>
@@ -14298,7 +14298,7 @@
         <v>699</v>
       </c>
       <c r="F467" t="n">
-        <v>13.0</v>
+        <v>94.0</v>
       </c>
       <c r="G467" t="n">
         <v>0.0</v>
@@ -14315,7 +14315,7 @@
         <v>22</v>
       </c>
       <c r="C468" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D468" t="s">
         <v>698</v>
@@ -14324,7 +14324,7 @@
         <v>699</v>
       </c>
       <c r="F468" t="n">
-        <v>23.0</v>
+        <v>13.0</v>
       </c>
       <c r="G468" t="n">
         <v>0.0</v>
@@ -14335,13 +14335,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B469" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C469" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D469" t="s">
         <v>698</v>
@@ -14350,13 +14350,13 @@
         <v>699</v>
       </c>
       <c r="F469" t="n">
-        <v>218.0</v>
+        <v>23.0</v>
       </c>
       <c r="G469" t="n">
         <v>0.0</v>
       </c>
       <c r="H469" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="470">
@@ -14364,10 +14364,10 @@
         <v>9</v>
       </c>
       <c r="B470" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C470" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D470" t="s">
         <v>698</v>
@@ -14376,13 +14376,13 @@
         <v>699</v>
       </c>
       <c r="F470" t="n">
-        <v>165.0</v>
+        <v>218.0</v>
       </c>
       <c r="G470" t="n">
         <v>0.0</v>
       </c>
       <c r="H470" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="471">
@@ -14390,19 +14390,19 @@
         <v>9</v>
       </c>
       <c r="B471" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C471" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D471" t="s">
         <v>698</v>
       </c>
       <c r="E471" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F471" t="n">
-        <v>5.0</v>
+        <v>165.0</v>
       </c>
       <c r="G471" t="n">
         <v>0.0</v>
@@ -14419,22 +14419,22 @@
         <v>15</v>
       </c>
       <c r="C472" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D472" t="s">
         <v>698</v>
       </c>
       <c r="E472" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F472" t="n">
-        <v>96.0</v>
+        <v>5.0</v>
       </c>
       <c r="G472" t="n">
         <v>0.0</v>
       </c>
       <c r="H472" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="473">
@@ -14445,7 +14445,7 @@
         <v>15</v>
       </c>
       <c r="C473" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D473" t="s">
         <v>698</v>
@@ -14454,13 +14454,13 @@
         <v>699</v>
       </c>
       <c r="F473" t="n">
-        <v>1.0</v>
+        <v>96.0</v>
       </c>
       <c r="G473" t="n">
         <v>0.0</v>
       </c>
       <c r="H473" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="474">
@@ -14471,59 +14471,59 @@
         <v>15</v>
       </c>
       <c r="C474" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D474" t="s">
         <v>698</v>
       </c>
       <c r="E474" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F474" t="n">
-        <v>64.0</v>
+        <v>1.0</v>
       </c>
       <c r="G474" t="n">
         <v>0.0</v>
       </c>
       <c r="H474" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B475" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C475" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D475" t="s">
         <v>698</v>
       </c>
       <c r="E475" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F475" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G475" t="n">
         <v>0.0</v>
       </c>
       <c r="H475" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B476" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C476" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D476" t="s">
         <v>698</v>
@@ -14532,7 +14532,7 @@
         <v>699</v>
       </c>
       <c r="F476" t="n">
-        <v>147.0</v>
+        <v>63.0</v>
       </c>
       <c r="G476" t="n">
         <v>0.0</v>
@@ -14549,7 +14549,7 @@
         <v>18</v>
       </c>
       <c r="C477" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D477" t="s">
         <v>698</v>
@@ -14558,24 +14558,24 @@
         <v>699</v>
       </c>
       <c r="F477" t="n">
-        <v>531.0</v>
+        <v>147.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
       </c>
       <c r="H477" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B478" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C478" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D478" t="s">
         <v>698</v>
@@ -14584,24 +14584,24 @@
         <v>699</v>
       </c>
       <c r="F478" t="n">
-        <v>74.0</v>
+        <v>531.0</v>
       </c>
       <c r="G478" t="n">
         <v>0.0</v>
       </c>
       <c r="H478" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B479" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C479" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D479" t="s">
         <v>698</v>
@@ -14610,10 +14610,10 @@
         <v>699</v>
       </c>
       <c r="F479" t="n">
-        <v>230.0</v>
+        <v>74.0</v>
       </c>
       <c r="G479" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H479" t="n">
         <v>0.0</v>
@@ -14621,25 +14621,25 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B480" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C480" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D480" t="s">
         <v>698</v>
       </c>
       <c r="E480" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F480" t="n">
-        <v>32.0</v>
+        <v>230.0</v>
       </c>
       <c r="G480" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H480" t="n">
         <v>0.0</v>
@@ -14647,74 +14647,74 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B481" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C481" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D481" t="s">
         <v>698</v>
       </c>
       <c r="E481" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F481" t="n">
-        <v>119.0</v>
+        <v>32.0</v>
       </c>
       <c r="G481" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H481" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B482" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C482" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D482" t="s">
         <v>698</v>
       </c>
       <c r="E482" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F482" t="n">
-        <v>69.0</v>
+        <v>119.0</v>
       </c>
       <c r="G482" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H482" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B483" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C483" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D483" t="s">
         <v>698</v>
       </c>
       <c r="E483" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F483" t="n">
-        <v>10.0</v>
+        <v>69.0</v>
       </c>
       <c r="G483" t="n">
         <v>0.0</v>
@@ -14725,13 +14725,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B484" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C484" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D484" t="s">
         <v>698</v>
@@ -14740,24 +14740,24 @@
         <v>699</v>
       </c>
       <c r="F484" t="n">
-        <v>44.0</v>
+        <v>10.0</v>
       </c>
       <c r="G484" t="n">
         <v>0.0</v>
       </c>
       <c r="H484" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B485" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C485" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D485" t="s">
         <v>698</v>
@@ -14766,24 +14766,24 @@
         <v>699</v>
       </c>
       <c r="F485" t="n">
-        <v>33.0</v>
+        <v>44.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
       </c>
       <c r="H485" t="n">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B486" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C486" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D486" t="s">
         <v>698</v>
@@ -14792,39 +14792,39 @@
         <v>699</v>
       </c>
       <c r="F486" t="n">
-        <v>379.0</v>
+        <v>33.0</v>
       </c>
       <c r="G486" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H486" t="n">
-        <v>39.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B487" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C487" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D487" t="s">
         <v>698</v>
       </c>
       <c r="E487" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F487" t="n">
-        <v>0.0</v>
+        <v>379.0</v>
       </c>
       <c r="G487" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H487" t="n">
-        <v>0.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="488">
@@ -14835,16 +14835,16 @@
         <v>15</v>
       </c>
       <c r="C488" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D488" t="s">
         <v>698</v>
       </c>
       <c r="E488" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F488" t="n">
-        <v>143.0</v>
+        <v>0.0</v>
       </c>
       <c r="G488" t="n">
         <v>0.0</v>
@@ -14858,19 +14858,19 @@
         <v>9</v>
       </c>
       <c r="B489" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C489" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D489" t="s">
         <v>698</v>
       </c>
       <c r="E489" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F489" t="n">
-        <v>6.0</v>
+        <v>143.0</v>
       </c>
       <c r="G489" t="n">
         <v>0.0</v>
@@ -14884,19 +14884,19 @@
         <v>9</v>
       </c>
       <c r="B490" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C490" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D490" t="s">
         <v>698</v>
       </c>
       <c r="E490" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F490" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G490" t="n">
         <v>0.0</v>
@@ -14907,13 +14907,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B491" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C491" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D491" t="s">
         <v>698</v>
@@ -14922,50 +14922,50 @@
         <v>701</v>
       </c>
       <c r="F491" t="n">
-        <v>76.0</v>
+        <v>4.0</v>
       </c>
       <c r="G491" t="n">
         <v>0.0</v>
       </c>
       <c r="H491" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B492" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C492" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D492" t="s">
         <v>698</v>
       </c>
       <c r="E492" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F492" t="n">
-        <v>546.0</v>
+        <v>76.0</v>
       </c>
       <c r="G492" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H492" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B493" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C493" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D493" t="s">
         <v>698</v>
@@ -14974,13 +14974,13 @@
         <v>699</v>
       </c>
       <c r="F493" t="n">
-        <v>22.0</v>
+        <v>546.0</v>
       </c>
       <c r="G493" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H493" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="494">
@@ -14991,22 +14991,22 @@
         <v>15</v>
       </c>
       <c r="C494" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D494" t="s">
         <v>698</v>
       </c>
       <c r="E494" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F494" t="n">
-        <v>42.0</v>
+        <v>22.0</v>
       </c>
       <c r="G494" t="n">
         <v>0.0</v>
       </c>
       <c r="H494" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="495">
@@ -15017,33 +15017,33 @@
         <v>15</v>
       </c>
       <c r="C495" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D495" t="s">
         <v>698</v>
       </c>
       <c r="E495" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F495" t="n">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="G495" t="n">
         <v>0.0</v>
       </c>
       <c r="H495" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B496" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C496" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D496" t="s">
         <v>698</v>
@@ -15052,39 +15052,39 @@
         <v>699</v>
       </c>
       <c r="F496" t="n">
-        <v>190.0</v>
+        <v>43.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
       </c>
       <c r="H496" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B497" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C497" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D497" t="s">
         <v>698</v>
       </c>
       <c r="E497" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F497" t="n">
-        <v>102.0</v>
+        <v>190.0</v>
       </c>
       <c r="G497" t="n">
         <v>0.0</v>
       </c>
       <c r="H497" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="498">
@@ -15095,33 +15095,33 @@
         <v>15</v>
       </c>
       <c r="C498" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D498" t="s">
         <v>698</v>
       </c>
       <c r="E498" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F498" t="n">
-        <v>1.0</v>
+        <v>102.0</v>
       </c>
       <c r="G498" t="n">
         <v>0.0</v>
       </c>
       <c r="H498" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B499" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C499" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D499" t="s">
         <v>698</v>
@@ -15130,76 +15130,76 @@
         <v>699</v>
       </c>
       <c r="F499" t="n">
-        <v>96.0</v>
+        <v>1.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
       </c>
       <c r="H499" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B500" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C500" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D500" t="s">
         <v>698</v>
       </c>
       <c r="E500" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F500" t="n">
-        <v>9.0</v>
+        <v>96.0</v>
       </c>
       <c r="G500" t="n">
         <v>0.0</v>
       </c>
       <c r="H500" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B501" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C501" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D501" t="s">
         <v>698</v>
       </c>
       <c r="E501" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F501" t="n">
-        <v>69.0</v>
+        <v>9.0</v>
       </c>
       <c r="G501" t="n">
         <v>0.0</v>
       </c>
       <c r="H501" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B502" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C502" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D502" t="s">
         <v>698</v>
@@ -15208,24 +15208,24 @@
         <v>699</v>
       </c>
       <c r="F502" t="n">
-        <v>184.0</v>
+        <v>69.0</v>
       </c>
       <c r="G502" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H502" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B503" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C503" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D503" t="s">
         <v>698</v>
@@ -15234,13 +15234,13 @@
         <v>699</v>
       </c>
       <c r="F503" t="n">
-        <v>0.0</v>
+        <v>184.0</v>
       </c>
       <c r="G503" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H503" t="n">
-        <v>33.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="504">
@@ -15260,24 +15260,24 @@
         <v>699</v>
       </c>
       <c r="F504" t="n">
-        <v>335.0</v>
+        <v>0.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
       </c>
       <c r="H504" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B505" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C505" t="s">
-        <v>17</v>
+        <v>516</v>
       </c>
       <c r="D505" t="s">
         <v>698</v>
@@ -15286,24 +15286,24 @@
         <v>699</v>
       </c>
       <c r="F505" t="n">
-        <v>2330.0</v>
+        <v>335.0</v>
       </c>
       <c r="G505" t="n">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
       <c r="H505" t="n">
-        <v>294.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B506" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C506" t="s">
-        <v>517</v>
+        <v>17</v>
       </c>
       <c r="D506" t="s">
         <v>698</v>
@@ -15312,24 +15312,24 @@
         <v>699</v>
       </c>
       <c r="F506" t="n">
-        <v>171.0</v>
+        <v>2330.0</v>
       </c>
       <c r="G506" t="n">
-        <v>1.0</v>
+        <v>44.0</v>
       </c>
       <c r="H506" t="n">
-        <v>26.0</v>
+        <v>294.0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B507" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C507" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D507" t="s">
         <v>698</v>
@@ -15338,13 +15338,13 @@
         <v>699</v>
       </c>
       <c r="F507" t="n">
-        <v>203.0</v>
+        <v>171.0</v>
       </c>
       <c r="G507" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H507" t="n">
-        <v>6.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="508">
@@ -15355,7 +15355,7 @@
         <v>15</v>
       </c>
       <c r="C508" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D508" t="s">
         <v>698</v>
@@ -15364,13 +15364,13 @@
         <v>699</v>
       </c>
       <c r="F508" t="n">
-        <v>30.0</v>
+        <v>203.0</v>
       </c>
       <c r="G508" t="n">
         <v>0.0</v>
       </c>
       <c r="H508" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="509">
@@ -15381,7 +15381,7 @@
         <v>15</v>
       </c>
       <c r="C509" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D509" t="s">
         <v>698</v>
@@ -15390,24 +15390,24 @@
         <v>699</v>
       </c>
       <c r="F509" t="n">
-        <v>195.0</v>
+        <v>30.0</v>
       </c>
       <c r="G509" t="n">
         <v>0.0</v>
       </c>
       <c r="H509" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B510" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C510" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D510" t="s">
         <v>698</v>
@@ -15416,24 +15416,24 @@
         <v>699</v>
       </c>
       <c r="F510" t="n">
-        <v>0.0</v>
+        <v>195.0</v>
       </c>
       <c r="G510" t="n">
         <v>0.0</v>
       </c>
       <c r="H510" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B511" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C511" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D511" t="s">
         <v>698</v>
@@ -15442,13 +15442,13 @@
         <v>699</v>
       </c>
       <c r="F511" t="n">
-        <v>112.0</v>
+        <v>0.0</v>
       </c>
       <c r="G511" t="n">
         <v>0.0</v>
       </c>
       <c r="H511" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="512">
@@ -15456,25 +15456,25 @@
         <v>9</v>
       </c>
       <c r="B512" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C512" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D512" t="s">
         <v>698</v>
       </c>
       <c r="E512" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F512" t="n">
-        <v>62.0</v>
+        <v>112.0</v>
       </c>
       <c r="G512" t="n">
         <v>0.0</v>
       </c>
       <c r="H512" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="513">
@@ -15482,10 +15482,10 @@
         <v>9</v>
       </c>
       <c r="B513" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C513" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D513" t="s">
         <v>698</v>
@@ -15494,13 +15494,13 @@
         <v>700</v>
       </c>
       <c r="F513" t="n">
-        <v>215.0</v>
+        <v>62.0</v>
       </c>
       <c r="G513" t="n">
         <v>0.0</v>
       </c>
       <c r="H513" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="514">
@@ -15511,33 +15511,33 @@
         <v>15</v>
       </c>
       <c r="C514" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D514" t="s">
         <v>698</v>
       </c>
       <c r="E514" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F514" t="n">
-        <v>80.0</v>
+        <v>215.0</v>
       </c>
       <c r="G514" t="n">
         <v>0.0</v>
       </c>
       <c r="H514" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B515" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C515" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D515" t="s">
         <v>698</v>
@@ -15546,24 +15546,24 @@
         <v>699</v>
       </c>
       <c r="F515" t="n">
-        <v>66.0</v>
+        <v>80.0</v>
       </c>
       <c r="G515" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H515" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B516" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C516" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D516" t="s">
         <v>698</v>
@@ -15572,13 +15572,13 @@
         <v>699</v>
       </c>
       <c r="F516" t="n">
-        <v>24.0</v>
+        <v>66.0</v>
       </c>
       <c r="G516" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H516" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="517">
@@ -15589,74 +15589,74 @@
         <v>15</v>
       </c>
       <c r="C517" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D517" t="s">
         <v>698</v>
       </c>
       <c r="E517" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F517" t="n">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
       </c>
       <c r="H517" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B518" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C518" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D518" t="s">
         <v>698</v>
       </c>
       <c r="E518" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F518" t="n">
-        <v>403.0</v>
+        <v>20.0</v>
       </c>
       <c r="G518" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="H518" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B519" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C519" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D519" t="s">
         <v>698</v>
       </c>
       <c r="E519" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F519" t="n">
-        <v>20.0</v>
+        <v>404.0</v>
       </c>
       <c r="G519" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H519" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="520">
@@ -15667,22 +15667,22 @@
         <v>22</v>
       </c>
       <c r="C520" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D520" t="s">
         <v>698</v>
       </c>
       <c r="E520" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F520" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G520" t="n">
         <v>0.0</v>
       </c>
       <c r="H520" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="521">
@@ -15693,7 +15693,7 @@
         <v>22</v>
       </c>
       <c r="C521" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D521" t="s">
         <v>698</v>
@@ -15702,13 +15702,13 @@
         <v>699</v>
       </c>
       <c r="F521" t="n">
-        <v>63.0</v>
+        <v>5.0</v>
       </c>
       <c r="G521" t="n">
         <v>0.0</v>
       </c>
       <c r="H521" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="522">
@@ -15719,7 +15719,7 @@
         <v>22</v>
       </c>
       <c r="C522" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D522" t="s">
         <v>698</v>
@@ -15728,24 +15728,24 @@
         <v>699</v>
       </c>
       <c r="F522" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H522" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G522" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H522" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B523" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C523" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D523" t="s">
         <v>698</v>
@@ -15754,24 +15754,24 @@
         <v>699</v>
       </c>
       <c r="F523" t="n">
-        <v>194.0</v>
+        <v>1.0</v>
       </c>
       <c r="G523" t="n">
         <v>0.0</v>
       </c>
       <c r="H523" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B524" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C524" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D524" t="s">
         <v>698</v>
@@ -15780,24 +15780,24 @@
         <v>699</v>
       </c>
       <c r="F524" t="n">
-        <v>76.0</v>
+        <v>194.0</v>
       </c>
       <c r="G524" t="n">
         <v>0.0</v>
       </c>
       <c r="H524" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B525" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C525" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D525" t="s">
         <v>698</v>
@@ -15806,13 +15806,13 @@
         <v>699</v>
       </c>
       <c r="F525" t="n">
-        <v>37.0</v>
+        <v>76.0</v>
       </c>
       <c r="G525" t="n">
         <v>0.0</v>
       </c>
       <c r="H525" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="526">
@@ -15820,19 +15820,19 @@
         <v>9</v>
       </c>
       <c r="B526" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C526" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D526" t="s">
         <v>698</v>
       </c>
       <c r="E526" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F526" t="n">
-        <v>50.0</v>
+        <v>37.0</v>
       </c>
       <c r="G526" t="n">
         <v>0.0</v>
@@ -15849,111 +15849,111 @@
         <v>15</v>
       </c>
       <c r="C527" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D527" t="s">
         <v>698</v>
       </c>
       <c r="E527" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F527" t="n">
-        <v>29.0</v>
+        <v>50.0</v>
       </c>
       <c r="G527" t="n">
         <v>0.0</v>
       </c>
       <c r="H527" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B528" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C528" t="s">
-        <v>13</v>
+        <v>538</v>
       </c>
       <c r="D528" t="s">
         <v>698</v>
       </c>
       <c r="E528" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F528" t="n">
-        <v>150.0</v>
+        <v>29.0</v>
       </c>
       <c r="G528" t="n">
         <v>0.0</v>
       </c>
       <c r="H528" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B529" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C529" t="s">
-        <v>539</v>
+        <v>13</v>
       </c>
       <c r="D529" t="s">
         <v>698</v>
       </c>
       <c r="E529" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F529" t="n">
-        <v>16.0</v>
+        <v>150.0</v>
       </c>
       <c r="G529" t="n">
         <v>0.0</v>
       </c>
       <c r="H529" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B530" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C530" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D530" t="s">
         <v>698</v>
       </c>
       <c r="E530" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F530" t="n">
-        <v>87.0</v>
+        <v>16.0</v>
       </c>
       <c r="G530" t="n">
         <v>0.0</v>
       </c>
       <c r="H530" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B531" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C531" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D531" t="s">
         <v>698</v>
@@ -15962,76 +15962,76 @@
         <v>699</v>
       </c>
       <c r="F531" t="n">
-        <v>25.0</v>
+        <v>87.0</v>
       </c>
       <c r="G531" t="n">
         <v>0.0</v>
       </c>
       <c r="H531" t="n">
-        <v>51.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B532" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C532" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D532" t="s">
         <v>698</v>
       </c>
       <c r="E532" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F532" t="n">
-        <v>314.0</v>
+        <v>25.0</v>
       </c>
       <c r="G532" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H532" t="n">
-        <v>1.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B533" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C533" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D533" t="s">
         <v>698</v>
       </c>
       <c r="E533" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F533" t="n">
-        <v>75.0</v>
+        <v>314.0</v>
       </c>
       <c r="G533" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H533" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B534" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C534" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D534" t="s">
         <v>698</v>
@@ -16040,76 +16040,76 @@
         <v>699</v>
       </c>
       <c r="F534" t="n">
-        <v>53.0</v>
+        <v>76.0</v>
       </c>
       <c r="G534" t="n">
         <v>0.0</v>
       </c>
       <c r="H534" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B535" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C535" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D535" t="s">
         <v>698</v>
       </c>
       <c r="E535" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F535" t="n">
-        <v>250.0</v>
+        <v>53.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
       </c>
       <c r="H535" t="n">
-        <v>1.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B536" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C536" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D536" t="s">
         <v>698</v>
       </c>
       <c r="E536" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F536" t="n">
-        <v>72.0</v>
+        <v>250.0</v>
       </c>
       <c r="G536" t="n">
         <v>0.0</v>
       </c>
       <c r="H536" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B537" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C537" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D537" t="s">
         <v>698</v>
@@ -16118,24 +16118,24 @@
         <v>699</v>
       </c>
       <c r="F537" t="n">
-        <v>125.0</v>
+        <v>72.0</v>
       </c>
       <c r="G537" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H537" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B538" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C538" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D538" t="s">
         <v>698</v>
@@ -16144,39 +16144,39 @@
         <v>699</v>
       </c>
       <c r="F538" t="n">
-        <v>23.0</v>
+        <v>125.0</v>
       </c>
       <c r="G538" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H538" t="n">
-        <v>130.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B539" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C539" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D539" t="s">
         <v>698</v>
       </c>
       <c r="E539" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F539" t="n">
-        <v>8.0</v>
+        <v>23.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
       </c>
       <c r="H539" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="540">
@@ -16184,25 +16184,25 @@
         <v>9</v>
       </c>
       <c r="B540" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C540" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D540" t="s">
         <v>698</v>
       </c>
       <c r="E540" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F540" t="n">
-        <v>86.0</v>
+        <v>8.0</v>
       </c>
       <c r="G540" t="n">
         <v>0.0</v>
       </c>
       <c r="H540" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="541">
@@ -16213,7 +16213,7 @@
         <v>15</v>
       </c>
       <c r="C541" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D541" t="s">
         <v>698</v>
@@ -16222,13 +16222,13 @@
         <v>699</v>
       </c>
       <c r="F541" t="n">
-        <v>7.0</v>
+        <v>86.0</v>
       </c>
       <c r="G541" t="n">
         <v>0.0</v>
       </c>
       <c r="H541" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="542">
@@ -16236,10 +16236,10 @@
         <v>9</v>
       </c>
       <c r="B542" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C542" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D542" t="s">
         <v>698</v>
@@ -16248,13 +16248,13 @@
         <v>699</v>
       </c>
       <c r="F542" t="n">
-        <v>168.0</v>
+        <v>7.0</v>
       </c>
       <c r="G542" t="n">
         <v>0.0</v>
       </c>
       <c r="H542" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="543">
@@ -16262,10 +16262,10 @@
         <v>9</v>
       </c>
       <c r="B543" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C543" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D543" t="s">
         <v>698</v>
@@ -16274,10 +16274,10 @@
         <v>699</v>
       </c>
       <c r="F543" t="n">
-        <v>410.0</v>
+        <v>168.0</v>
       </c>
       <c r="G543" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H543" t="n">
         <v>0.0</v>
@@ -16288,74 +16288,74 @@
         <v>9</v>
       </c>
       <c r="B544" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C544" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D544" t="s">
         <v>698</v>
       </c>
       <c r="E544" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F544" t="n">
-        <v>203.0</v>
+        <v>411.0</v>
       </c>
       <c r="G544" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H544" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B545" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C545" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D545" t="s">
         <v>698</v>
       </c>
       <c r="E545" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F545" t="n">
-        <v>102.0</v>
+        <v>203.0</v>
       </c>
       <c r="G545" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H545" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B546" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C546" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D546" t="s">
         <v>698</v>
       </c>
       <c r="E546" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F546" t="n">
-        <v>131.0</v>
+        <v>102.0</v>
       </c>
       <c r="G546" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H546" t="n">
         <v>0.0</v>
@@ -16366,19 +16366,19 @@
         <v>9</v>
       </c>
       <c r="B547" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C547" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D547" t="s">
         <v>698</v>
       </c>
       <c r="E547" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F547" t="n">
-        <v>18.0</v>
+        <v>131.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -16395,7 +16395,7 @@
         <v>15</v>
       </c>
       <c r="C548" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D548" t="s">
         <v>698</v>
@@ -16404,13 +16404,13 @@
         <v>699</v>
       </c>
       <c r="F548" t="n">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="G548" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H548" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="549">
@@ -16421,7 +16421,7 @@
         <v>15</v>
       </c>
       <c r="C549" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D549" t="s">
         <v>698</v>
@@ -16430,13 +16430,13 @@
         <v>699</v>
       </c>
       <c r="F549" t="n">
-        <v>222.0</v>
+        <v>6.0</v>
       </c>
       <c r="G549" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H549" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H549" t="n">
-        <v>29.0</v>
       </c>
     </row>
     <row r="550">
@@ -16447,7 +16447,7 @@
         <v>15</v>
       </c>
       <c r="C550" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D550" t="s">
         <v>698</v>
@@ -16456,13 +16456,13 @@
         <v>699</v>
       </c>
       <c r="F550" t="n">
-        <v>347.0</v>
+        <v>222.0</v>
       </c>
       <c r="G550" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H550" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="551">
@@ -16473,16 +16473,16 @@
         <v>15</v>
       </c>
       <c r="C551" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D551" t="s">
         <v>698</v>
       </c>
       <c r="E551" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F551" t="n">
-        <v>2.0</v>
+        <v>347.0</v>
       </c>
       <c r="G551" t="n">
         <v>0.0</v>
@@ -16496,10 +16496,10 @@
         <v>9</v>
       </c>
       <c r="B552" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C552" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D552" t="s">
         <v>698</v>
@@ -16508,7 +16508,7 @@
         <v>701</v>
       </c>
       <c r="F552" t="n">
-        <v>54.0</v>
+        <v>2.0</v>
       </c>
       <c r="G552" t="n">
         <v>0.0</v>
@@ -16525,7 +16525,7 @@
         <v>21</v>
       </c>
       <c r="C553" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D553" t="s">
         <v>698</v>
@@ -16534,7 +16534,7 @@
         <v>701</v>
       </c>
       <c r="F553" t="n">
-        <v>12.0</v>
+        <v>54.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -16545,22 +16545,22 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B554" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C554" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D554" t="s">
         <v>698</v>
       </c>
       <c r="E554" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F554" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="G554" t="n">
         <v>0.0</v>
@@ -16571,13 +16571,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B555" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C555" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D555" t="s">
         <v>698</v>
@@ -16586,39 +16586,39 @@
         <v>699</v>
       </c>
       <c r="F555" t="n">
-        <v>30.0</v>
+        <v>4.0</v>
       </c>
       <c r="G555" t="n">
         <v>0.0</v>
       </c>
       <c r="H555" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B556" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C556" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D556" t="s">
         <v>698</v>
       </c>
       <c r="E556" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F556" t="n">
-        <v>47.0</v>
+        <v>30.0</v>
       </c>
       <c r="G556" t="n">
         <v>0.0</v>
       </c>
       <c r="H556" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="557">
@@ -16626,10 +16626,10 @@
         <v>12</v>
       </c>
       <c r="B557" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C557" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D557" t="s">
         <v>698</v>
@@ -16638,10 +16638,10 @@
         <v>701</v>
       </c>
       <c r="F557" t="n">
-        <v>548.0</v>
+        <v>47.0</v>
       </c>
       <c r="G557" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H557" t="n">
         <v>0.0</v>
@@ -16649,54 +16649,54 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B558" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C558" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D558" t="s">
         <v>698</v>
       </c>
       <c r="E558" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F558" t="n">
-        <v>92.0</v>
+        <v>548.0</v>
       </c>
       <c r="G558" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H558" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B559" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C559" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D559" t="s">
         <v>698</v>
       </c>
       <c r="E559" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F559" t="n">
-        <v>0.0</v>
+        <v>92.0</v>
       </c>
       <c r="G559" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H559" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="560">
@@ -16716,24 +16716,24 @@
         <v>699</v>
       </c>
       <c r="F560" t="n">
-        <v>265.0</v>
+        <v>0.0</v>
       </c>
       <c r="G560" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H560" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B561" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C561" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D561" t="s">
         <v>698</v>
@@ -16742,24 +16742,24 @@
         <v>699</v>
       </c>
       <c r="F561" t="n">
-        <v>1.0</v>
+        <v>265.0</v>
       </c>
       <c r="G561" t="n">
         <v>1.0</v>
       </c>
       <c r="H561" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B562" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C562" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D562" t="s">
         <v>698</v>
@@ -16768,24 +16768,24 @@
         <v>699</v>
       </c>
       <c r="F562" t="n">
-        <v>54.0</v>
+        <v>1.0</v>
       </c>
       <c r="G562" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H562" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B563" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C563" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D563" t="s">
         <v>698</v>
@@ -16794,39 +16794,39 @@
         <v>699</v>
       </c>
       <c r="F563" t="n">
-        <v>42.0</v>
+        <v>54.0</v>
       </c>
       <c r="G563" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H563" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B564" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C564" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D564" t="s">
         <v>698</v>
       </c>
       <c r="E564" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F564" t="n">
-        <v>11.0</v>
+        <v>42.0</v>
       </c>
       <c r="G564" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H564" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="565">
@@ -16834,51 +16834,51 @@
         <v>9</v>
       </c>
       <c r="B565" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C565" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D565" t="s">
         <v>698</v>
       </c>
       <c r="E565" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F565" t="n">
-        <v>26.0</v>
+        <v>11.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
       </c>
       <c r="H565" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B566" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C566" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D566" t="s">
         <v>698</v>
       </c>
       <c r="E566" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F566" t="n">
-        <v>111.0</v>
+        <v>26.0</v>
       </c>
       <c r="G566" t="n">
         <v>0.0</v>
       </c>
       <c r="H566" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="567">
@@ -16889,7 +16889,7 @@
         <v>22</v>
       </c>
       <c r="C567" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D567" t="s">
         <v>698</v>
@@ -16898,7 +16898,7 @@
         <v>701</v>
       </c>
       <c r="F567" t="n">
-        <v>6.0</v>
+        <v>111.0</v>
       </c>
       <c r="G567" t="n">
         <v>0.0</v>
@@ -16915,7 +16915,7 @@
         <v>22</v>
       </c>
       <c r="C568" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D568" t="s">
         <v>698</v>
@@ -16924,7 +16924,7 @@
         <v>701</v>
       </c>
       <c r="F568" t="n">
-        <v>268.0</v>
+        <v>6.0</v>
       </c>
       <c r="G568" t="n">
         <v>0.0</v>
@@ -16935,13 +16935,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B569" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C569" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D569" t="s">
         <v>698</v>
@@ -16950,7 +16950,7 @@
         <v>701</v>
       </c>
       <c r="F569" t="n">
-        <v>0.0</v>
+        <v>268.0</v>
       </c>
       <c r="G569" t="n">
         <v>0.0</v>
@@ -16961,13 +16961,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B570" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C570" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D570" t="s">
         <v>698</v>
@@ -16976,7 +16976,7 @@
         <v>701</v>
       </c>
       <c r="F570" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G570" t="n">
         <v>0.0</v>
@@ -16987,25 +16987,25 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B571" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C571" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D571" t="s">
         <v>698</v>
       </c>
       <c r="E571" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F571" t="n">
-        <v>67.0</v>
+        <v>17.0</v>
       </c>
       <c r="G571" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H571" t="n">
         <v>0.0</v>
@@ -17013,13 +17013,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B572" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C572" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D572" t="s">
         <v>698</v>
@@ -17028,10 +17028,10 @@
         <v>699</v>
       </c>
       <c r="F572" t="n">
-        <v>60.0</v>
+        <v>67.0</v>
       </c>
       <c r="G572" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H572" t="n">
         <v>0.0</v>
@@ -17042,19 +17042,19 @@
         <v>9</v>
       </c>
       <c r="B573" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C573" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D573" t="s">
         <v>698</v>
       </c>
       <c r="E573" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F573" t="n">
-        <v>53.0</v>
+        <v>60.0</v>
       </c>
       <c r="G573" t="n">
         <v>0.0</v>
@@ -17065,22 +17065,22 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B574" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C574" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D574" t="s">
         <v>698</v>
       </c>
       <c r="E574" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F574" t="n">
-        <v>291.0</v>
+        <v>53.0</v>
       </c>
       <c r="G574" t="n">
         <v>0.0</v>
@@ -17091,13 +17091,13 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B575" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C575" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D575" t="s">
         <v>698</v>
@@ -17106,7 +17106,7 @@
         <v>699</v>
       </c>
       <c r="F575" t="n">
-        <v>10.0</v>
+        <v>291.0</v>
       </c>
       <c r="G575" t="n">
         <v>0.0</v>
@@ -17120,19 +17120,19 @@
         <v>9</v>
       </c>
       <c r="B576" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C576" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D576" t="s">
         <v>698</v>
       </c>
       <c r="E576" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F576" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
@@ -17146,10 +17146,10 @@
         <v>9</v>
       </c>
       <c r="B577" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C577" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D577" t="s">
         <v>698</v>
@@ -17169,22 +17169,22 @@
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B578" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C578" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D578" t="s">
         <v>698</v>
       </c>
       <c r="E578" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F578" t="n">
-        <v>66.0</v>
+        <v>20.0</v>
       </c>
       <c r="G578" t="n">
         <v>0.0</v>
@@ -17198,10 +17198,10 @@
         <v>11</v>
       </c>
       <c r="B579" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C579" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D579" t="s">
         <v>698</v>
@@ -17210,7 +17210,7 @@
         <v>699</v>
       </c>
       <c r="F579" t="n">
-        <v>85.0</v>
+        <v>66.0</v>
       </c>
       <c r="G579" t="n">
         <v>0.0</v>
@@ -17221,13 +17221,13 @@
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B580" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C580" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D580" t="s">
         <v>698</v>
@@ -17236,39 +17236,39 @@
         <v>699</v>
       </c>
       <c r="F580" t="n">
-        <v>49.0</v>
+        <v>85.0</v>
       </c>
       <c r="G580" t="n">
         <v>0.0</v>
       </c>
       <c r="H580" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B581" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C581" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D581" t="s">
         <v>698</v>
       </c>
       <c r="E581" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F581" t="n">
-        <v>15.0</v>
+        <v>49.0</v>
       </c>
       <c r="G581" t="n">
         <v>0.0</v>
       </c>
       <c r="H581" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="582">
@@ -17279,22 +17279,22 @@
         <v>22</v>
       </c>
       <c r="C582" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D582" t="s">
         <v>698</v>
       </c>
       <c r="E582" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F582" t="n">
-        <v>77.0</v>
+        <v>15.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
       </c>
       <c r="H582" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="583">
@@ -17305,42 +17305,42 @@
         <v>22</v>
       </c>
       <c r="C583" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D583" t="s">
         <v>698</v>
       </c>
       <c r="E583" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F583" t="n">
-        <v>0.0</v>
+        <v>77.0</v>
       </c>
       <c r="G583" t="n">
         <v>0.0</v>
       </c>
       <c r="H583" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B584" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C584" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D584" t="s">
         <v>698</v>
       </c>
       <c r="E584" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F584" t="n">
-        <v>275.0</v>
+        <v>0.0</v>
       </c>
       <c r="G584" t="n">
         <v>0.0</v>
@@ -17351,22 +17351,22 @@
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B585" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C585" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D585" t="s">
         <v>698</v>
       </c>
       <c r="E585" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F585" t="n">
-        <v>89.0</v>
+        <v>275.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17380,19 +17380,19 @@
         <v>11</v>
       </c>
       <c r="B586" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C586" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D586" t="s">
         <v>698</v>
       </c>
       <c r="E586" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F586" t="n">
-        <v>32.0</v>
+        <v>89.0</v>
       </c>
       <c r="G586" t="n">
         <v>0.0</v>
@@ -17403,13 +17403,13 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B587" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C587" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D587" t="s">
         <v>698</v>
@@ -17418,7 +17418,7 @@
         <v>699</v>
       </c>
       <c r="F587" t="n">
-        <v>24.0</v>
+        <v>32.0</v>
       </c>
       <c r="G587" t="n">
         <v>0.0</v>
@@ -17429,13 +17429,13 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B588" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C588" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D588" t="s">
         <v>698</v>
@@ -17444,24 +17444,24 @@
         <v>699</v>
       </c>
       <c r="F588" t="n">
-        <v>177.0</v>
+        <v>24.0</v>
       </c>
       <c r="G588" t="n">
         <v>0.0</v>
       </c>
       <c r="H588" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B589" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C589" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D589" t="s">
         <v>698</v>
@@ -17470,24 +17470,24 @@
         <v>699</v>
       </c>
       <c r="F589" t="n">
+        <v>177.0</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H589" t="n">
         <v>9.0</v>
-      </c>
-      <c r="G589" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H589" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B590" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C590" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D590" t="s">
         <v>698</v>
@@ -17496,24 +17496,24 @@
         <v>699</v>
       </c>
       <c r="F590" t="n">
-        <v>345.0</v>
+        <v>9.0</v>
       </c>
       <c r="G590" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H590" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B591" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C591" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D591" t="s">
         <v>698</v>
@@ -17522,39 +17522,39 @@
         <v>699</v>
       </c>
       <c r="F591" t="n">
-        <v>252.0</v>
+        <v>345.0</v>
       </c>
       <c r="G591" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="H591" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B592" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C592" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D592" t="s">
         <v>698</v>
       </c>
       <c r="E592" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F592" t="n">
-        <v>27.0</v>
+        <v>252.0</v>
       </c>
       <c r="G592" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H592" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="593">
@@ -17562,71 +17562,71 @@
         <v>9</v>
       </c>
       <c r="B593" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C593" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D593" t="s">
         <v>698</v>
       </c>
       <c r="E593" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F593" t="n">
-        <v>19.0</v>
+        <v>27.0</v>
       </c>
       <c r="G593" t="n">
         <v>0.0</v>
       </c>
       <c r="H593" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B594" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C594" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D594" t="s">
         <v>698</v>
       </c>
       <c r="E594" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F594" t="n">
-        <v>366.0</v>
+        <v>19.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
       </c>
       <c r="H594" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B595" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C595" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D595" t="s">
         <v>698</v>
       </c>
       <c r="E595" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F595" t="n">
-        <v>10.0</v>
+        <v>366.0</v>
       </c>
       <c r="G595" t="n">
         <v>0.0</v>
@@ -17637,13 +17637,13 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B596" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C596" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D596" t="s">
         <v>698</v>
@@ -17652,24 +17652,24 @@
         <v>699</v>
       </c>
       <c r="F596" t="n">
-        <v>32.0</v>
+        <v>10.0</v>
       </c>
       <c r="G596" t="n">
         <v>0.0</v>
       </c>
       <c r="H596" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B597" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C597" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D597" t="s">
         <v>698</v>
@@ -17678,50 +17678,50 @@
         <v>699</v>
       </c>
       <c r="F597" t="n">
-        <v>210.0</v>
+        <v>32.0</v>
       </c>
       <c r="G597" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H597" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B598" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C598" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D598" t="s">
         <v>698</v>
       </c>
       <c r="E598" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F598" t="n">
-        <v>4.0</v>
+        <v>210.0</v>
       </c>
       <c r="G598" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H598" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B599" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C599" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D599" t="s">
         <v>698</v>
@@ -17730,50 +17730,50 @@
         <v>701</v>
       </c>
       <c r="F599" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
       </c>
       <c r="H599" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B600" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C600" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D600" t="s">
         <v>698</v>
       </c>
       <c r="E600" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F600" t="n">
-        <v>219.0</v>
+        <v>6.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
       </c>
       <c r="H600" t="n">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B601" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C601" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D601" t="s">
         <v>698</v>
@@ -17782,24 +17782,24 @@
         <v>699</v>
       </c>
       <c r="F601" t="n">
-        <v>64.0</v>
+        <v>219.0</v>
       </c>
       <c r="G601" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H601" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B602" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C602" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D602" t="s">
         <v>698</v>
@@ -17808,13 +17808,13 @@
         <v>699</v>
       </c>
       <c r="F602" t="n">
-        <v>16.0</v>
+        <v>64.0</v>
       </c>
       <c r="G602" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H602" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="603">
@@ -17825,7 +17825,7 @@
         <v>15</v>
       </c>
       <c r="C603" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D603" t="s">
         <v>698</v>
@@ -17834,13 +17834,13 @@
         <v>699</v>
       </c>
       <c r="F603" t="n">
-        <v>93.0</v>
+        <v>16.0</v>
       </c>
       <c r="G603" t="n">
         <v>0.0</v>
       </c>
       <c r="H603" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="604">
@@ -17851,7 +17851,7 @@
         <v>15</v>
       </c>
       <c r="C604" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D604" t="s">
         <v>698</v>
@@ -17860,59 +17860,59 @@
         <v>699</v>
       </c>
       <c r="F604" t="n">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="G604" t="n">
         <v>0.0</v>
       </c>
       <c r="H604" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B605" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C605" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D605" t="s">
         <v>698</v>
       </c>
       <c r="E605" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F605" t="n">
-        <v>37.0</v>
+        <v>90.0</v>
       </c>
       <c r="G605" t="n">
         <v>0.0</v>
       </c>
       <c r="H605" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B606" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C606" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D606" t="s">
         <v>698</v>
       </c>
       <c r="E606" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F606" t="n">
-        <v>121.0</v>
+        <v>37.0</v>
       </c>
       <c r="G606" t="n">
         <v>0.0</v>
@@ -17923,13 +17923,13 @@
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B607" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C607" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D607" t="s">
         <v>698</v>
@@ -17938,39 +17938,39 @@
         <v>699</v>
       </c>
       <c r="F607" t="n">
-        <v>23.0</v>
+        <v>121.0</v>
       </c>
       <c r="G607" t="n">
         <v>0.0</v>
       </c>
       <c r="H607" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B608" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C608" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D608" t="s">
         <v>698</v>
       </c>
       <c r="E608" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F608" t="n">
-        <v>353.0</v>
+        <v>23.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
       </c>
       <c r="H608" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="609">
@@ -17981,85 +17981,85 @@
         <v>15</v>
       </c>
       <c r="C609" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D609" t="s">
         <v>698</v>
       </c>
       <c r="E609" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F609" t="n">
-        <v>24.0</v>
+        <v>353.0</v>
       </c>
       <c r="G609" t="n">
         <v>0.0</v>
       </c>
       <c r="H609" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B610" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C610" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D610" t="s">
         <v>698</v>
       </c>
       <c r="E610" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F610" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="G610" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H610" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G610" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H610" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B611" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C611" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D611" t="s">
         <v>698</v>
       </c>
       <c r="E611" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F611" t="n">
-        <v>212.0</v>
+        <v>1.0</v>
       </c>
       <c r="G611" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H611" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B612" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C612" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D612" t="s">
         <v>698</v>
@@ -18068,13 +18068,13 @@
         <v>699</v>
       </c>
       <c r="F612" t="n">
-        <v>12.0</v>
+        <v>212.0</v>
       </c>
       <c r="G612" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H612" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="613">
@@ -18082,19 +18082,19 @@
         <v>9</v>
       </c>
       <c r="B613" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C613" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D613" t="s">
         <v>698</v>
       </c>
       <c r="E613" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F613" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G613" t="n">
         <v>0.0</v>
@@ -18105,22 +18105,22 @@
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B614" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C614" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D614" t="s">
         <v>698</v>
       </c>
       <c r="E614" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F614" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G614" t="n">
         <v>0.0</v>
@@ -18137,48 +18137,48 @@
         <v>22</v>
       </c>
       <c r="C615" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D615" t="s">
         <v>698</v>
       </c>
       <c r="E615" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F615" t="n">
-        <v>67.0</v>
+        <v>4.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
       </c>
       <c r="H615" t="n">
-        <v>1851.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B616" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C616" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D616" t="s">
         <v>698</v>
       </c>
       <c r="E616" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F616" t="n">
-        <v>41.0</v>
+        <v>67.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
       </c>
       <c r="H616" t="n">
-        <v>0.0</v>
+        <v>1851.0</v>
       </c>
     </row>
     <row r="617">
@@ -18186,10 +18186,10 @@
         <v>8</v>
       </c>
       <c r="B617" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C617" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D617" t="s">
         <v>698</v>
@@ -18198,24 +18198,24 @@
         <v>699</v>
       </c>
       <c r="F617" t="n">
-        <v>18.0</v>
+        <v>41.0</v>
       </c>
       <c r="G617" t="n">
         <v>0.0</v>
       </c>
       <c r="H617" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B618" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C618" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D618" t="s">
         <v>698</v>
@@ -18224,24 +18224,24 @@
         <v>699</v>
       </c>
       <c r="F618" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="G618" t="n">
         <v>0.0</v>
       </c>
       <c r="H618" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B619" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C619" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D619" t="s">
         <v>698</v>
@@ -18250,13 +18250,13 @@
         <v>699</v>
       </c>
       <c r="F619" t="n">
-        <v>69.0</v>
+        <v>10.0</v>
       </c>
       <c r="G619" t="n">
         <v>0.0</v>
       </c>
       <c r="H619" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="620">
@@ -18264,10 +18264,10 @@
         <v>9</v>
       </c>
       <c r="B620" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C620" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D620" t="s">
         <v>698</v>
@@ -18276,13 +18276,13 @@
         <v>699</v>
       </c>
       <c r="F620" t="n">
-        <v>247.0</v>
+        <v>69.0</v>
       </c>
       <c r="G620" t="n">
         <v>0.0</v>
       </c>
       <c r="H620" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="621">
@@ -18290,19 +18290,19 @@
         <v>9</v>
       </c>
       <c r="B621" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C621" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D621" t="s">
         <v>698</v>
       </c>
       <c r="E621" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F621" t="n">
-        <v>15.0</v>
+        <v>247.0</v>
       </c>
       <c r="G621" t="n">
         <v>0.0</v>
@@ -18319,7 +18319,7 @@
         <v>18</v>
       </c>
       <c r="C622" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D622" t="s">
         <v>698</v>
@@ -18328,7 +18328,7 @@
         <v>700</v>
       </c>
       <c r="F622" t="n">
-        <v>78.0</v>
+        <v>15.0</v>
       </c>
       <c r="G622" t="n">
         <v>0.0</v>
@@ -18342,74 +18342,74 @@
         <v>9</v>
       </c>
       <c r="B623" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C623" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D623" t="s">
         <v>698</v>
       </c>
       <c r="E623" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F623" t="n">
-        <v>73.0</v>
+        <v>78.0</v>
       </c>
       <c r="G623" t="n">
         <v>0.0</v>
       </c>
       <c r="H623" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B624" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C624" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D624" t="s">
         <v>698</v>
       </c>
       <c r="E624" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F624" t="n">
-        <v>21.0</v>
+        <v>73.0</v>
       </c>
       <c r="G624" t="n">
         <v>0.0</v>
       </c>
       <c r="H624" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B625" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C625" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D625" t="s">
         <v>698</v>
       </c>
       <c r="E625" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F625" t="n">
-        <v>94.0</v>
+        <v>21.0</v>
       </c>
       <c r="G625" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H625" t="n">
         <v>0.0</v>
@@ -18423,7 +18423,7 @@
         <v>19</v>
       </c>
       <c r="C626" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D626" t="s">
         <v>698</v>
@@ -18432,50 +18432,50 @@
         <v>699</v>
       </c>
       <c r="F626" t="n">
-        <v>143.0</v>
+        <v>94.0</v>
       </c>
       <c r="G626" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H626" t="n">
-        <v>79.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B627" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C627" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D627" t="s">
         <v>698</v>
       </c>
       <c r="E627" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F627" t="n">
-        <v>35.0</v>
+        <v>143.0</v>
       </c>
       <c r="G627" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H627" t="n">
-        <v>1.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B628" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C628" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D628" t="s">
         <v>698</v>
@@ -18484,13 +18484,13 @@
         <v>701</v>
       </c>
       <c r="F628" t="n">
-        <v>23.0</v>
+        <v>35.0</v>
       </c>
       <c r="G628" t="n">
         <v>0.0</v>
       </c>
       <c r="H628" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="629">
@@ -18498,19 +18498,19 @@
         <v>9</v>
       </c>
       <c r="B629" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C629" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D629" t="s">
         <v>698</v>
       </c>
       <c r="E629" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F629" t="n">
-        <v>159.0</v>
+        <v>23.0</v>
       </c>
       <c r="G629" t="n">
         <v>0.0</v>
@@ -18521,39 +18521,39 @@
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B630" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C630" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D630" t="s">
         <v>698</v>
       </c>
       <c r="E630" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F630" t="n">
-        <v>178.0</v>
+        <v>159.0</v>
       </c>
       <c r="G630" t="n">
         <v>0.0</v>
       </c>
       <c r="H630" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B631" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C631" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D631" t="s">
         <v>698</v>
@@ -18562,33 +18562,33 @@
         <v>701</v>
       </c>
       <c r="F631" t="n">
-        <v>19.0</v>
+        <v>178.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
       </c>
       <c r="H631" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B632" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C632" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D632" t="s">
         <v>698</v>
       </c>
       <c r="E632" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F632" t="n">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="G632" t="n">
         <v>0.0</v>
@@ -18605,7 +18605,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D633" t="s">
         <v>698</v>
@@ -18614,39 +18614,39 @@
         <v>699</v>
       </c>
       <c r="F633" t="n">
-        <v>55.0</v>
+        <v>12.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
       </c>
       <c r="H633" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B634" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C634" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D634" t="s">
         <v>698</v>
       </c>
       <c r="E634" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F634" t="n">
-        <v>82.0</v>
+        <v>55.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="635">
@@ -18657,33 +18657,33 @@
         <v>15</v>
       </c>
       <c r="C635" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D635" t="s">
         <v>698</v>
       </c>
       <c r="E635" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F635" t="n">
-        <v>176.0</v>
+        <v>82.0</v>
       </c>
       <c r="G635" t="n">
         <v>0.0</v>
       </c>
       <c r="H635" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B636" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C636" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D636" t="s">
         <v>698</v>
@@ -18692,24 +18692,24 @@
         <v>699</v>
       </c>
       <c r="F636" t="n">
-        <v>6.0</v>
+        <v>176.0</v>
       </c>
       <c r="G636" t="n">
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B637" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C637" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D637" t="s">
         <v>698</v>
@@ -18718,24 +18718,24 @@
         <v>699</v>
       </c>
       <c r="F637" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G637" t="n">
         <v>0.0</v>
       </c>
       <c r="H637" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B638" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C638" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D638" t="s">
         <v>698</v>
@@ -18744,7 +18744,7 @@
         <v>699</v>
       </c>
       <c r="F638" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -18755,13 +18755,13 @@
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B639" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C639" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D639" t="s">
         <v>698</v>
@@ -18770,7 +18770,7 @@
         <v>699</v>
       </c>
       <c r="F639" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="G639" t="n">
         <v>0.0</v>
@@ -18787,16 +18787,16 @@
         <v>22</v>
       </c>
       <c r="C640" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D640" t="s">
         <v>698</v>
       </c>
       <c r="E640" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F640" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -18813,137 +18813,137 @@
         <v>22</v>
       </c>
       <c r="C641" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D641" t="s">
         <v>698</v>
       </c>
       <c r="E641" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F641" t="n">
-        <v>132.0</v>
+        <v>3.0</v>
       </c>
       <c r="G641" t="n">
         <v>0.0</v>
       </c>
       <c r="H641" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B642" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C642" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D642" t="s">
         <v>698</v>
       </c>
       <c r="E642" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F642" t="n">
-        <v>17.0</v>
+        <v>132.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
       </c>
       <c r="H642" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B643" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C643" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D643" t="s">
         <v>698</v>
       </c>
       <c r="E643" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F643" t="n">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G643" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H643" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B644" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C644" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D644" t="s">
         <v>698</v>
       </c>
       <c r="E644" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F644" t="n">
-        <v>55.0</v>
+        <v>19.0</v>
       </c>
       <c r="G644" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H644" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B645" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C645" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D645" t="s">
         <v>698</v>
       </c>
       <c r="E645" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F645" t="n">
-        <v>24.0</v>
+        <v>55.0</v>
       </c>
       <c r="G645" t="n">
         <v>0.0</v>
       </c>
       <c r="H645" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B646" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C646" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D646" t="s">
         <v>698</v>
@@ -18952,24 +18952,24 @@
         <v>699</v>
       </c>
       <c r="F646" t="n">
-        <v>94.0</v>
+        <v>24.0</v>
       </c>
       <c r="G646" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H646" t="n">
-        <v>44.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B647" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C647" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D647" t="s">
         <v>698</v>
@@ -18978,24 +18978,24 @@
         <v>699</v>
       </c>
       <c r="F647" t="n">
-        <v>4.0</v>
+        <v>94.0</v>
       </c>
       <c r="G647" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H647" t="n">
-        <v>0.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B648" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C648" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D648" t="s">
         <v>698</v>
@@ -19004,7 +19004,7 @@
         <v>699</v>
       </c>
       <c r="F648" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -19015,22 +19015,22 @@
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B649" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C649" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D649" t="s">
         <v>698</v>
       </c>
       <c r="E649" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F649" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G649" t="n">
         <v>0.0</v>
@@ -19041,19 +19041,19 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B650" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C650" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D650" t="s">
         <v>698</v>
       </c>
       <c r="E650" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F650" t="n">
         <v>0.0</v>
@@ -19062,7 +19062,7 @@
         <v>0.0</v>
       </c>
       <c r="H650" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="651">
@@ -19082,24 +19082,24 @@
         <v>699</v>
       </c>
       <c r="F651" t="n">
-        <v>55.0</v>
+        <v>0.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
       </c>
       <c r="H651" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B652" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C652" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D652" t="s">
         <v>698</v>
@@ -19108,24 +19108,24 @@
         <v>699</v>
       </c>
       <c r="F652" t="n">
-        <v>108.0</v>
+        <v>55.0</v>
       </c>
       <c r="G652" t="n">
         <v>0.0</v>
       </c>
       <c r="H652" t="n">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B653" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C653" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D653" t="s">
         <v>698</v>
@@ -19134,13 +19134,13 @@
         <v>699</v>
       </c>
       <c r="F653" t="n">
-        <v>0.0</v>
+        <v>108.0</v>
       </c>
       <c r="G653" t="n">
         <v>0.0</v>
       </c>
       <c r="H653" t="n">
-        <v>5.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="654">
@@ -19160,24 +19160,24 @@
         <v>699</v>
       </c>
       <c r="F654" t="n">
-        <v>170.0</v>
+        <v>0.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
       </c>
       <c r="H654" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B655" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C655" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D655" t="s">
         <v>698</v>
@@ -19186,13 +19186,13 @@
         <v>699</v>
       </c>
       <c r="F655" t="n">
-        <v>0.0</v>
+        <v>171.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
       </c>
       <c r="H655" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="656">
@@ -19212,13 +19212,13 @@
         <v>699</v>
       </c>
       <c r="F656" t="n">
-        <v>214.0</v>
+        <v>0.0</v>
       </c>
       <c r="G656" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H656" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="657">
@@ -19229,7 +19229,7 @@
         <v>25</v>
       </c>
       <c r="C657" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D657" t="s">
         <v>698</v>
@@ -19238,10 +19238,10 @@
         <v>699</v>
       </c>
       <c r="F657" t="n">
-        <v>55.0</v>
+        <v>214.0</v>
       </c>
       <c r="G657" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H657" t="n">
         <v>0.0</v>
@@ -19255,7 +19255,7 @@
         <v>25</v>
       </c>
       <c r="C658" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D658" t="s">
         <v>698</v>
@@ -19264,10 +19264,10 @@
         <v>699</v>
       </c>
       <c r="F658" t="n">
-        <v>85.0</v>
+        <v>55.0</v>
       </c>
       <c r="G658" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H658" t="n">
         <v>0.0</v>
@@ -19281,7 +19281,7 @@
         <v>25</v>
       </c>
       <c r="C659" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D659" t="s">
         <v>698</v>
@@ -19290,13 +19290,13 @@
         <v>699</v>
       </c>
       <c r="F659" t="n">
-        <v>0.0</v>
+        <v>85.0</v>
       </c>
       <c r="G659" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H659" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="660">
@@ -19316,13 +19316,13 @@
         <v>699</v>
       </c>
       <c r="F660" t="n">
-        <v>116.0</v>
+        <v>0.0</v>
       </c>
       <c r="G660" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H660" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="661">
@@ -19333,19 +19333,19 @@
         <v>25</v>
       </c>
       <c r="C661" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D661" t="s">
         <v>698</v>
       </c>
       <c r="E661" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F661" t="n">
-        <v>60.0</v>
+        <v>116.0</v>
       </c>
       <c r="G661" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H661" t="n">
         <v>0.0</v>
@@ -19359,7 +19359,7 @@
         <v>25</v>
       </c>
       <c r="C662" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D662" t="s">
         <v>698</v>
@@ -19368,7 +19368,7 @@
         <v>701</v>
       </c>
       <c r="F662" t="n">
-        <v>106.0</v>
+        <v>60.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19385,16 +19385,16 @@
         <v>25</v>
       </c>
       <c r="C663" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D663" t="s">
         <v>698</v>
       </c>
       <c r="E663" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F663" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19411,7 +19411,7 @@
         <v>25</v>
       </c>
       <c r="C664" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D664" t="s">
         <v>698</v>
@@ -19420,7 +19420,7 @@
         <v>699</v>
       </c>
       <c r="F664" t="n">
-        <v>50.0</v>
+        <v>104.0</v>
       </c>
       <c r="G664" t="n">
         <v>0.0</v>
@@ -19437,16 +19437,16 @@
         <v>25</v>
       </c>
       <c r="C665" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D665" t="s">
         <v>698</v>
       </c>
       <c r="E665" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F665" t="n">
-        <v>92.0</v>
+        <v>50.0</v>
       </c>
       <c r="G665" t="n">
         <v>0.0</v>
@@ -19463,7 +19463,7 @@
         <v>25</v>
       </c>
       <c r="C666" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D666" t="s">
         <v>698</v>
@@ -19472,7 +19472,7 @@
         <v>701</v>
       </c>
       <c r="F666" t="n">
-        <v>109.0</v>
+        <v>92.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -19489,7 +19489,7 @@
         <v>25</v>
       </c>
       <c r="C667" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D667" t="s">
         <v>698</v>
@@ -19498,7 +19498,7 @@
         <v>701</v>
       </c>
       <c r="F667" t="n">
-        <v>7.0</v>
+        <v>109.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19515,7 +19515,7 @@
         <v>25</v>
       </c>
       <c r="C668" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D668" t="s">
         <v>698</v>
@@ -19524,7 +19524,7 @@
         <v>701</v>
       </c>
       <c r="F668" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -19541,7 +19541,7 @@
         <v>25</v>
       </c>
       <c r="C669" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D669" t="s">
         <v>698</v>
@@ -19550,7 +19550,7 @@
         <v>701</v>
       </c>
       <c r="F669" t="n">
-        <v>60.0</v>
+        <v>9.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -19567,7 +19567,7 @@
         <v>25</v>
       </c>
       <c r="C670" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D670" t="s">
         <v>698</v>
@@ -19576,7 +19576,7 @@
         <v>701</v>
       </c>
       <c r="F670" t="n">
-        <v>102.0</v>
+        <v>60.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19593,7 +19593,7 @@
         <v>25</v>
       </c>
       <c r="C671" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D671" t="s">
         <v>698</v>
@@ -19602,7 +19602,7 @@
         <v>701</v>
       </c>
       <c r="F671" t="n">
-        <v>42.0</v>
+        <v>102.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19619,7 +19619,7 @@
         <v>25</v>
       </c>
       <c r="C672" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D672" t="s">
         <v>698</v>
@@ -19628,7 +19628,7 @@
         <v>701</v>
       </c>
       <c r="F672" t="n">
-        <v>48.0</v>
+        <v>42.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19645,7 +19645,7 @@
         <v>25</v>
       </c>
       <c r="C673" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D673" t="s">
         <v>698</v>
@@ -19654,7 +19654,7 @@
         <v>701</v>
       </c>
       <c r="F673" t="n">
-        <v>54.0</v>
+        <v>48.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19671,7 +19671,7 @@
         <v>25</v>
       </c>
       <c r="C674" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D674" t="s">
         <v>698</v>
@@ -19680,7 +19680,7 @@
         <v>701</v>
       </c>
       <c r="F674" t="n">
-        <v>72.0</v>
+        <v>54.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19694,22 +19694,22 @@
         <v>8</v>
       </c>
       <c r="B675" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C675" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D675" t="s">
         <v>698</v>
       </c>
       <c r="E675" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F675" t="n">
-        <v>12.0</v>
+        <v>72.0</v>
       </c>
       <c r="G675" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H675" t="n">
         <v>0.0</v>
@@ -19723,7 +19723,7 @@
         <v>26</v>
       </c>
       <c r="C676" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D676" t="s">
         <v>698</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="F676" t="n">
-        <v>54.0</v>
+        <v>12.0</v>
       </c>
       <c r="G676" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="H676" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="677">
@@ -19749,7 +19749,7 @@
         <v>26</v>
       </c>
       <c r="C677" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D677" t="s">
         <v>698</v>
@@ -19758,24 +19758,24 @@
         <v>699</v>
       </c>
       <c r="F677" t="n">
-        <v>4.0</v>
+        <v>54.0</v>
       </c>
       <c r="G677" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H677" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B678" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C678" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D678" t="s">
         <v>698</v>
@@ -19784,7 +19784,7 @@
         <v>699</v>
       </c>
       <c r="F678" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="G678" t="n">
         <v>0.0</v>
@@ -19795,22 +19795,22 @@
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B679" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C679" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D679" t="s">
         <v>698</v>
       </c>
       <c r="E679" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F679" t="n">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -19827,7 +19827,7 @@
         <v>26</v>
       </c>
       <c r="C680" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D680" t="s">
         <v>698</v>
@@ -19836,7 +19836,7 @@
         <v>701</v>
       </c>
       <c r="F680" t="n">
-        <v>66.0</v>
+        <v>50.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -19853,7 +19853,7 @@
         <v>26</v>
       </c>
       <c r="C681" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D681" t="s">
         <v>698</v>
@@ -19862,7 +19862,7 @@
         <v>701</v>
       </c>
       <c r="F681" t="n">
-        <v>98.0</v>
+        <v>66.0</v>
       </c>
       <c r="G681" t="n">
         <v>0.0</v>
@@ -19879,7 +19879,7 @@
         <v>26</v>
       </c>
       <c r="C682" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D682" t="s">
         <v>698</v>
@@ -19888,7 +19888,7 @@
         <v>701</v>
       </c>
       <c r="F682" t="n">
-        <v>120.0</v>
+        <v>98.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -19905,7 +19905,7 @@
         <v>26</v>
       </c>
       <c r="C683" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D683" t="s">
         <v>698</v>
@@ -19914,7 +19914,7 @@
         <v>701</v>
       </c>
       <c r="F683" t="n">
-        <v>51.0</v>
+        <v>120.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -19931,16 +19931,16 @@
         <v>26</v>
       </c>
       <c r="C684" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D684" t="s">
         <v>698</v>
       </c>
       <c r="E684" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F684" t="n">
-        <v>87.0</v>
+        <v>51.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -19957,16 +19957,16 @@
         <v>26</v>
       </c>
       <c r="C685" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D685" t="s">
         <v>698</v>
       </c>
       <c r="E685" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F685" t="n">
-        <v>40.0</v>
+        <v>87.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -19983,19 +19983,19 @@
         <v>26</v>
       </c>
       <c r="C686" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D686" t="s">
         <v>698</v>
       </c>
       <c r="E686" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F686" t="n">
-        <v>13.0</v>
+        <v>40.0</v>
       </c>
       <c r="G686" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H686" t="n">
         <v>0.0</v>
@@ -20009,7 +20009,7 @@
         <v>26</v>
       </c>
       <c r="C687" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D687" t="s">
         <v>698</v>
@@ -20018,10 +20018,10 @@
         <v>699</v>
       </c>
       <c r="F687" t="n">
-        <v>94.0</v>
+        <v>13.0</v>
       </c>
       <c r="G687" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H687" t="n">
         <v>0.0</v>
@@ -20035,16 +20035,16 @@
         <v>26</v>
       </c>
       <c r="C688" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D688" t="s">
         <v>698</v>
       </c>
       <c r="E688" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F688" t="n">
-        <v>54.0</v>
+        <v>94.0</v>
       </c>
       <c r="G688" t="n">
         <v>0.0</v>
@@ -20061,16 +20061,16 @@
         <v>26</v>
       </c>
       <c r="C689" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D689" t="s">
         <v>698</v>
       </c>
       <c r="E689" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F689" t="n">
-        <v>94.0</v>
+        <v>54.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20081,25 +20081,25 @@
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B690" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C690" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D690" t="s">
         <v>698</v>
       </c>
       <c r="E690" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F690" t="n">
-        <v>158.0</v>
+        <v>94.0</v>
       </c>
       <c r="G690" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H690" t="n">
         <v>0.0</v>
@@ -20107,13 +20107,13 @@
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B691" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C691" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D691" t="s">
         <v>698</v>
@@ -20122,10 +20122,10 @@
         <v>701</v>
       </c>
       <c r="F691" t="n">
-        <v>46.0</v>
+        <v>158.0</v>
       </c>
       <c r="G691" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H691" t="n">
         <v>0.0</v>
@@ -20136,22 +20136,22 @@
         <v>8</v>
       </c>
       <c r="B692" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C692" t="s">
-        <v>14</v>
+        <v>696</v>
       </c>
       <c r="D692" t="s">
         <v>698</v>
       </c>
       <c r="E692" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F692" t="n">
-        <v>281.0</v>
+        <v>46.0</v>
       </c>
       <c r="G692" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H692" t="n">
         <v>0.0</v>
@@ -20165,19 +20165,19 @@
         <v>14</v>
       </c>
       <c r="C693" t="s">
-        <v>697</v>
+        <v>14</v>
       </c>
       <c r="D693" t="s">
         <v>698</v>
       </c>
       <c r="E693" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F693" t="n">
-        <v>129.0</v>
+        <v>281.0</v>
       </c>
       <c r="G693" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H693" t="n">
         <v>0.0</v>
@@ -20191,7 +20191,7 @@
         <v>14</v>
       </c>
       <c r="C694" t="s">
-        <v>14</v>
+        <v>697</v>
       </c>
       <c r="D694" t="s">
         <v>698</v>
@@ -20200,10 +20200,10 @@
         <v>701</v>
       </c>
       <c r="F694" t="n">
-        <v>362.0</v>
+        <v>129.0</v>
       </c>
       <c r="G694" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H694" t="n">
         <v>0.0</v>
@@ -20217,21 +20217,47 @@
         <v>14</v>
       </c>
       <c r="C695" t="s">
+        <v>14</v>
+      </c>
+      <c r="D695" t="s">
+        <v>698</v>
+      </c>
+      <c r="E695" t="s">
+        <v>701</v>
+      </c>
+      <c r="F695" t="n">
+        <v>362.0</v>
+      </c>
+      <c r="G695" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H695" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="s">
+        <v>8</v>
+      </c>
+      <c r="B696" t="s">
+        <v>14</v>
+      </c>
+      <c r="C696" t="s">
         <v>697</v>
       </c>
-      <c r="D695" t="s">
-        <v>698</v>
-      </c>
-      <c r="E695" t="s">
-        <v>699</v>
-      </c>
-      <c r="F695" t="n">
+      <c r="D696" t="s">
+        <v>698</v>
+      </c>
+      <c r="E696" t="s">
+        <v>699</v>
+      </c>
+      <c r="F696" t="n">
         <v>184.0</v>
       </c>
-      <c r="G695" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H695" t="n">
+      <c r="G696" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H696" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3982,7 +3982,7 @@
         <v>9.0</v>
       </c>
       <c r="H70" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="71">
@@ -10086,7 +10086,7 @@
         <v>699</v>
       </c>
       <c r="F305" t="n">
-        <v>972.0</v>
+        <v>973.0</v>
       </c>
       <c r="G305" t="n">
         <v>5.0</v>
@@ -15780,7 +15780,7 @@
         <v>699</v>
       </c>
       <c r="F524" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G524" t="n">
         <v>0.0</v>
@@ -16306,7 +16306,7 @@
         <v>3.0</v>
       </c>
       <c r="H544" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -17132,7 +17132,7 @@
         <v>699</v>
       </c>
       <c r="F576" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
@@ -17652,7 +17652,7 @@
         <v>699</v>
       </c>
       <c r="F596" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G596" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -19218,7 +19218,7 @@
         <v>0.0</v>
       </c>
       <c r="H656" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="657">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3280,7 +3280,7 @@
         <v>0.0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="44">
@@ -3976,10 +3976,10 @@
         <v>699</v>
       </c>
       <c r="F70" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
       <c r="G70" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="H70" t="n">
         <v>11.0</v>
@@ -5458,7 +5458,7 @@
         <v>699</v>
       </c>
       <c r="F127" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
@@ -5588,7 +5588,7 @@
         <v>699</v>
       </c>
       <c r="F132" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -6686,7 +6686,7 @@
         <v>0.0</v>
       </c>
       <c r="H174" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="175">
@@ -8318,7 +8318,7 @@
         <v>699</v>
       </c>
       <c r="F237" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -9774,7 +9774,7 @@
         <v>700</v>
       </c>
       <c r="F293" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
       <c r="G293" t="n">
         <v>4.0</v>
@@ -10346,10 +10346,10 @@
         <v>699</v>
       </c>
       <c r="F315" t="n">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
       <c r="G315" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H315" t="n">
         <v>8.0</v>
@@ -18432,7 +18432,7 @@
         <v>699</v>
       </c>
       <c r="F626" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G626" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2312,7 +2312,7 @@
         <v>699</v>
       </c>
       <c r="F6" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -3982,7 +3982,7 @@
         <v>7.0</v>
       </c>
       <c r="H70" t="n">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="71">
@@ -7018,7 +7018,7 @@
         <v>701</v>
       </c>
       <c r="F187" t="n">
-        <v>640.0</v>
+        <v>645.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7954,7 +7954,7 @@
         <v>699</v>
       </c>
       <c r="F223" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="G223" t="n">
         <v>1.0</v>
@@ -9598,7 +9598,7 @@
         <v>6.0</v>
       </c>
       <c r="H286" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="287">
@@ -9777,7 +9777,7 @@
         <v>208.0</v>
       </c>
       <c r="G293" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H293" t="n">
         <v>0.0</v>
@@ -10086,7 +10086,7 @@
         <v>699</v>
       </c>
       <c r="F305" t="n">
-        <v>973.0</v>
+        <v>993.0</v>
       </c>
       <c r="G305" t="n">
         <v>5.0</v>
@@ -10216,7 +10216,7 @@
         <v>699</v>
       </c>
       <c r="F310" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G310" t="n">
         <v>0.0</v>
@@ -11444,7 +11444,7 @@
         <v>7.0</v>
       </c>
       <c r="H357" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="358">
@@ -13284,7 +13284,7 @@
         <v>699</v>
       </c>
       <c r="F428" t="n">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -13472,7 +13472,7 @@
         <v>1.0</v>
       </c>
       <c r="H435" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="436">
@@ -13570,7 +13570,7 @@
         <v>699</v>
       </c>
       <c r="F439" t="n">
-        <v>539.0</v>
+        <v>540.0</v>
       </c>
       <c r="G439" t="n">
         <v>3.0</v>
@@ -14012,7 +14012,7 @@
         <v>699</v>
       </c>
       <c r="F456" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
       <c r="G456" t="n">
         <v>0.0</v>
@@ -14662,7 +14662,7 @@
         <v>701</v>
       </c>
       <c r="F481" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G481" t="n">
         <v>0.0</v>
@@ -15312,7 +15312,7 @@
         <v>699</v>
       </c>
       <c r="F506" t="n">
-        <v>2330.0</v>
+        <v>2333.0</v>
       </c>
       <c r="G506" t="n">
         <v>44.0</v>
@@ -16144,7 +16144,7 @@
         <v>699</v>
       </c>
       <c r="F538" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G538" t="n">
         <v>1.0</v>
@@ -16664,7 +16664,7 @@
         <v>701</v>
       </c>
       <c r="F558" t="n">
-        <v>548.0</v>
+        <v>550.0</v>
       </c>
       <c r="G558" t="n">
         <v>1.0</v>
@@ -16950,7 +16950,7 @@
         <v>701</v>
       </c>
       <c r="F569" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="G569" t="n">
         <v>0.0</v>
@@ -18536,7 +18536,7 @@
         <v>699</v>
       </c>
       <c r="F630" t="n">
-        <v>159.0</v>
+        <v>163.0</v>
       </c>
       <c r="G630" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3017,7 +3017,7 @@
         <v>203.0</v>
       </c>
       <c r="G33" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -5406,7 +5406,7 @@
         <v>699</v>
       </c>
       <c r="F125" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="G125" t="n">
         <v>1.0</v>
@@ -5744,7 +5744,7 @@
         <v>699</v>
       </c>
       <c r="F138" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -6082,7 +6082,7 @@
         <v>701</v>
       </c>
       <c r="F151" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G151" t="n">
         <v>0.0</v>
@@ -6888,7 +6888,7 @@
         <v>701</v>
       </c>
       <c r="F182" t="n">
-        <v>556.0</v>
+        <v>558.0</v>
       </c>
       <c r="G182" t="n">
         <v>1.0</v>
@@ -7356,7 +7356,7 @@
         <v>699</v>
       </c>
       <c r="F200" t="n">
-        <v>994.0</v>
+        <v>995.0</v>
       </c>
       <c r="G200" t="n">
         <v>1.0</v>
@@ -9780,7 +9780,7 @@
         <v>5.0</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="294">
@@ -10294,7 +10294,7 @@
         <v>699</v>
       </c>
       <c r="F313" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G313" t="n">
         <v>0.0</v>
@@ -11262,7 +11262,7 @@
         <v>0.0</v>
       </c>
       <c r="H350" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="351">
@@ -11444,7 +11444,7 @@
         <v>7.0</v>
       </c>
       <c r="H357" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="358">
@@ -13908,7 +13908,7 @@
         <v>699</v>
       </c>
       <c r="F452" t="n">
-        <v>377.0</v>
+        <v>378.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -16722,7 +16722,7 @@
         <v>0.0</v>
       </c>
       <c r="H560" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="561">
@@ -18666,7 +18666,7 @@
         <v>701</v>
       </c>
       <c r="F635" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G635" t="n">
         <v>0.0</v>
@@ -19166,7 +19166,7 @@
         <v>0.0</v>
       </c>
       <c r="H654" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="655">
@@ -19186,7 +19186,7 @@
         <v>699</v>
       </c>
       <c r="F655" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2208,7 +2208,7 @@
         <v>699</v>
       </c>
       <c r="F2" t="n">
-        <v>536.0</v>
+        <v>554.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2318,7 +2318,7 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="7">
@@ -2520,10 +2520,10 @@
         <v>699</v>
       </c>
       <c r="F14" t="n">
-        <v>432.0</v>
+        <v>444.0</v>
       </c>
       <c r="G14" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="H14" t="n">
         <v>3.0</v>
@@ -2572,7 +2572,7 @@
         <v>699</v>
       </c>
       <c r="F16" t="n">
-        <v>370.0</v>
+        <v>383.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2728,7 +2728,7 @@
         <v>701</v>
       </c>
       <c r="F22" t="n">
-        <v>335.0</v>
+        <v>342.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3040,10 +3040,10 @@
         <v>699</v>
       </c>
       <c r="F34" t="n">
-        <v>463.0</v>
+        <v>477.0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H34" t="n">
         <v>3.0</v>
@@ -3066,7 +3066,7 @@
         <v>699</v>
       </c>
       <c r="F35" t="n">
-        <v>166.0</v>
+        <v>172.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3144,7 +3144,7 @@
         <v>699</v>
       </c>
       <c r="F38" t="n">
-        <v>307.0</v>
+        <v>311.0</v>
       </c>
       <c r="G38" t="n">
         <v>1.0</v>
@@ -3378,7 +3378,7 @@
         <v>699</v>
       </c>
       <c r="F47" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -3560,7 +3560,7 @@
         <v>699</v>
       </c>
       <c r="F54" t="n">
-        <v>117.0</v>
+        <v>121.0</v>
       </c>
       <c r="G54" t="n">
         <v>1.0</v>
@@ -3950,7 +3950,7 @@
         <v>701</v>
       </c>
       <c r="F69" t="n">
-        <v>162.0</v>
+        <v>174.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -4080,7 +4080,7 @@
         <v>699</v>
       </c>
       <c r="F74" t="n">
-        <v>116.0</v>
+        <v>119.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4314,7 +4314,7 @@
         <v>699</v>
       </c>
       <c r="F83" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G83" t="n">
         <v>1.0</v>
@@ -4444,7 +4444,7 @@
         <v>699</v>
       </c>
       <c r="F88" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -4756,7 +4756,7 @@
         <v>701</v>
       </c>
       <c r="F100" t="n">
-        <v>383.0</v>
+        <v>398.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -4860,7 +4860,7 @@
         <v>699</v>
       </c>
       <c r="F104" t="n">
-        <v>474.0</v>
+        <v>485.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -4990,7 +4990,7 @@
         <v>701</v>
       </c>
       <c r="F109" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -5328,7 +5328,7 @@
         <v>699</v>
       </c>
       <c r="F122" t="n">
-        <v>428.0</v>
+        <v>436.0</v>
       </c>
       <c r="G122" t="n">
         <v>1.0</v>
@@ -5698,7 +5698,7 @@
         <v>0.0</v>
       </c>
       <c r="H136" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="137">
@@ -5848,7 +5848,7 @@
         <v>699</v>
       </c>
       <c r="F142" t="n">
-        <v>628.0</v>
+        <v>640.0</v>
       </c>
       <c r="G142" t="n">
         <v>2.0</v>
@@ -6160,7 +6160,7 @@
         <v>699</v>
       </c>
       <c r="F154" t="n">
-        <v>201.0</v>
+        <v>206.0</v>
       </c>
       <c r="G154" t="n">
         <v>0.0</v>
@@ -6524,7 +6524,7 @@
         <v>701</v>
       </c>
       <c r="F168" t="n">
-        <v>183.0</v>
+        <v>187.0</v>
       </c>
       <c r="G168" t="n">
         <v>0.0</v>
@@ -6576,7 +6576,7 @@
         <v>699</v>
       </c>
       <c r="F170" t="n">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6732,7 +6732,7 @@
         <v>699</v>
       </c>
       <c r="F176" t="n">
-        <v>263.0</v>
+        <v>267.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -6758,7 +6758,7 @@
         <v>701</v>
       </c>
       <c r="F177" t="n">
-        <v>479.0</v>
+        <v>493.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7512,7 +7512,7 @@
         <v>701</v>
       </c>
       <c r="F206" t="n">
-        <v>84.0</v>
+        <v>89.0</v>
       </c>
       <c r="G206" t="n">
         <v>0.0</v>
@@ -7590,7 +7590,7 @@
         <v>699</v>
       </c>
       <c r="F209" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G209" t="n">
         <v>0.0</v>
@@ -8214,7 +8214,7 @@
         <v>701</v>
       </c>
       <c r="F233" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G233" t="n">
         <v>0.0</v>
@@ -8526,7 +8526,7 @@
         <v>699</v>
       </c>
       <c r="F245" t="n">
-        <v>134.0</v>
+        <v>145.0</v>
       </c>
       <c r="G245" t="n">
         <v>0.0</v>
@@ -8682,7 +8682,7 @@
         <v>699</v>
       </c>
       <c r="F251" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G251" t="n">
         <v>1.0</v>
@@ -9514,7 +9514,7 @@
         <v>699</v>
       </c>
       <c r="F283" t="n">
-        <v>248.0</v>
+        <v>250.0</v>
       </c>
       <c r="G283" t="n">
         <v>2.0</v>
@@ -9930,7 +9930,7 @@
         <v>699</v>
       </c>
       <c r="F299" t="n">
-        <v>388.0</v>
+        <v>395.0</v>
       </c>
       <c r="G299" t="n">
         <v>0.0</v>
@@ -10190,7 +10190,7 @@
         <v>699</v>
       </c>
       <c r="F309" t="n">
-        <v>482.0</v>
+        <v>484.0</v>
       </c>
       <c r="G309" t="n">
         <v>6.0</v>
@@ -10528,7 +10528,7 @@
         <v>699</v>
       </c>
       <c r="F322" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G322" t="n">
         <v>2.0</v>
@@ -10736,7 +10736,7 @@
         <v>699</v>
       </c>
       <c r="F330" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G330" t="n">
         <v>0.0</v>
@@ -10762,7 +10762,7 @@
         <v>699</v>
       </c>
       <c r="F331" t="n">
-        <v>387.0</v>
+        <v>393.0</v>
       </c>
       <c r="G331" t="n">
         <v>0.0</v>
@@ -11438,7 +11438,7 @@
         <v>699</v>
       </c>
       <c r="F357" t="n">
-        <v>90.0</v>
+        <v>98.0</v>
       </c>
       <c r="G357" t="n">
         <v>7.0</v>
@@ -11698,7 +11698,7 @@
         <v>701</v>
       </c>
       <c r="F367" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G367" t="n">
         <v>0.0</v>
@@ -12114,7 +12114,7 @@
         <v>699</v>
       </c>
       <c r="F383" t="n">
-        <v>229.0</v>
+        <v>233.0</v>
       </c>
       <c r="G383" t="n">
         <v>0.0</v>
@@ -12348,7 +12348,7 @@
         <v>699</v>
       </c>
       <c r="F392" t="n">
-        <v>184.0</v>
+        <v>187.0</v>
       </c>
       <c r="G392" t="n">
         <v>7.0</v>
@@ -12400,7 +12400,7 @@
         <v>699</v>
       </c>
       <c r="F394" t="n">
-        <v>117.0</v>
+        <v>124.0</v>
       </c>
       <c r="G394" t="n">
         <v>1.0</v>
@@ -12764,7 +12764,7 @@
         <v>699</v>
       </c>
       <c r="F408" t="n">
-        <v>287.0</v>
+        <v>288.0</v>
       </c>
       <c r="G408" t="n">
         <v>9.0</v>
@@ -14038,7 +14038,7 @@
         <v>699</v>
       </c>
       <c r="F457" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G457" t="n">
         <v>0.0</v>
@@ -14246,7 +14246,7 @@
         <v>699</v>
       </c>
       <c r="F465" t="n">
-        <v>164.0</v>
+        <v>172.0</v>
       </c>
       <c r="G465" t="n">
         <v>7.0</v>
@@ -14636,7 +14636,7 @@
         <v>699</v>
       </c>
       <c r="F480" t="n">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="G480" t="n">
         <v>1.0</v>
@@ -14974,7 +14974,7 @@
         <v>699</v>
       </c>
       <c r="F493" t="n">
-        <v>546.0</v>
+        <v>570.0</v>
       </c>
       <c r="G493" t="n">
         <v>2.0</v>
@@ -15266,7 +15266,7 @@
         <v>0.0</v>
       </c>
       <c r="H504" t="n">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="505">
@@ -15312,13 +15312,13 @@
         <v>699</v>
       </c>
       <c r="F506" t="n">
-        <v>2333.0</v>
+        <v>2334.0</v>
       </c>
       <c r="G506" t="n">
         <v>44.0</v>
       </c>
       <c r="H506" t="n">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
     </row>
     <row r="507">
@@ -15910,7 +15910,7 @@
         <v>701</v>
       </c>
       <c r="F529" t="n">
-        <v>150.0</v>
+        <v>156.0</v>
       </c>
       <c r="G529" t="n">
         <v>0.0</v>
@@ -15994,7 +15994,7 @@
         <v>0.0</v>
       </c>
       <c r="H532" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="533">
@@ -16144,7 +16144,7 @@
         <v>699</v>
       </c>
       <c r="F538" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G538" t="n">
         <v>1.0</v>
@@ -16768,7 +16768,7 @@
         <v>699</v>
       </c>
       <c r="F562" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G562" t="n">
         <v>1.0</v>
@@ -17106,7 +17106,7 @@
         <v>699</v>
       </c>
       <c r="F575" t="n">
-        <v>291.0</v>
+        <v>301.0</v>
       </c>
       <c r="G575" t="n">
         <v>0.0</v>
@@ -17626,7 +17626,7 @@
         <v>701</v>
       </c>
       <c r="F595" t="n">
-        <v>366.0</v>
+        <v>377.0</v>
       </c>
       <c r="G595" t="n">
         <v>0.0</v>
@@ -18068,7 +18068,7 @@
         <v>699</v>
       </c>
       <c r="F612" t="n">
-        <v>212.0</v>
+        <v>215.0</v>
       </c>
       <c r="G612" t="n">
         <v>2.0</v>
@@ -18198,7 +18198,7 @@
         <v>699</v>
       </c>
       <c r="F617" t="n">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
       <c r="G617" t="n">
         <v>0.0</v>
@@ -18926,7 +18926,7 @@
         <v>701</v>
       </c>
       <c r="F645" t="n">
-        <v>55.0</v>
+        <v>83.0</v>
       </c>
       <c r="G645" t="n">
         <v>0.0</v>
@@ -19134,7 +19134,7 @@
         <v>699</v>
       </c>
       <c r="F653" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G653" t="n">
         <v>0.0</v>
@@ -19166,7 +19166,7 @@
         <v>0.0</v>
       </c>
       <c r="H654" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="655">
@@ -19186,7 +19186,7 @@
         <v>699</v>
       </c>
       <c r="F655" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19238,7 +19238,7 @@
         <v>699</v>
       </c>
       <c r="F657" t="n">
-        <v>214.0</v>
+        <v>216.0</v>
       </c>
       <c r="G657" t="n">
         <v>1.0</v>
@@ -19290,7 +19290,7 @@
         <v>699</v>
       </c>
       <c r="F659" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G659" t="n">
         <v>2.0</v>
@@ -19394,7 +19394,7 @@
         <v>701</v>
       </c>
       <c r="F663" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19446,7 +19446,7 @@
         <v>699</v>
       </c>
       <c r="F665" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="G665" t="n">
         <v>0.0</v>
@@ -19472,7 +19472,7 @@
         <v>701</v>
       </c>
       <c r="F666" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -19498,7 +19498,7 @@
         <v>701</v>
       </c>
       <c r="F667" t="n">
-        <v>109.0</v>
+        <v>115.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19550,7 +19550,7 @@
         <v>701</v>
       </c>
       <c r="F669" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -19576,7 +19576,7 @@
         <v>701</v>
       </c>
       <c r="F670" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19602,7 +19602,7 @@
         <v>701</v>
       </c>
       <c r="F671" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19680,7 +19680,7 @@
         <v>701</v>
       </c>
       <c r="F674" t="n">
-        <v>54.0</v>
+        <v>58.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19706,7 +19706,7 @@
         <v>701</v>
       </c>
       <c r="F675" t="n">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19862,7 +19862,7 @@
         <v>701</v>
       </c>
       <c r="F681" t="n">
-        <v>66.0</v>
+        <v>85.0</v>
       </c>
       <c r="G681" t="n">
         <v>0.0</v>
@@ -19888,7 +19888,7 @@
         <v>701</v>
       </c>
       <c r="F682" t="n">
-        <v>98.0</v>
+        <v>116.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -19914,7 +19914,7 @@
         <v>701</v>
       </c>
       <c r="F683" t="n">
-        <v>120.0</v>
+        <v>132.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -19940,7 +19940,7 @@
         <v>701</v>
       </c>
       <c r="F684" t="n">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -19966,7 +19966,7 @@
         <v>699</v>
       </c>
       <c r="F685" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -20044,7 +20044,7 @@
         <v>699</v>
       </c>
       <c r="F688" t="n">
-        <v>94.0</v>
+        <v>102.0</v>
       </c>
       <c r="G688" t="n">
         <v>0.0</v>
@@ -20070,7 +20070,7 @@
         <v>701</v>
       </c>
       <c r="F689" t="n">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20096,7 +20096,7 @@
         <v>699</v>
       </c>
       <c r="F690" t="n">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20174,7 +20174,7 @@
         <v>699</v>
       </c>
       <c r="F693" t="n">
-        <v>281.0</v>
+        <v>297.0</v>
       </c>
       <c r="G693" t="n">
         <v>2.0</v>
@@ -20200,7 +20200,7 @@
         <v>701</v>
       </c>
       <c r="F694" t="n">
-        <v>129.0</v>
+        <v>137.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20226,7 +20226,7 @@
         <v>701</v>
       </c>
       <c r="F695" t="n">
-        <v>362.0</v>
+        <v>373.0</v>
       </c>
       <c r="G695" t="n">
         <v>1.0</v>
@@ -20252,7 +20252,7 @@
         <v>699</v>
       </c>
       <c r="F696" t="n">
-        <v>184.0</v>
+        <v>189.0</v>
       </c>
       <c r="G696" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3748,7 +3748,7 @@
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="62">
@@ -19212,7 +19212,7 @@
         <v>699</v>
       </c>
       <c r="F656" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19244,7 +19244,7 @@
         <v>0.0</v>
       </c>
       <c r="H657" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="658">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3378,7 +3378,7 @@
         <v>699</v>
       </c>
       <c r="F47" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -5068,13 +5068,13 @@
         <v>701</v>
       </c>
       <c r="F112" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G112" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H112" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="113">
@@ -10372,7 +10372,7 @@
         <v>699</v>
       </c>
       <c r="F316" t="n">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
       <c r="G316" t="n">
         <v>2.0</v>
@@ -11412,7 +11412,7 @@
         <v>699</v>
       </c>
       <c r="F356" t="n">
-        <v>519.0</v>
+        <v>520.0</v>
       </c>
       <c r="G356" t="n">
         <v>6.0</v>
@@ -13498,7 +13498,7 @@
         <v>1.0</v>
       </c>
       <c r="H436" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="437">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2208,7 +2208,7 @@
         <v>699</v>
       </c>
       <c r="F2" t="n">
-        <v>554.0</v>
+        <v>556.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2520,7 +2520,7 @@
         <v>699</v>
       </c>
       <c r="F14" t="n">
-        <v>444.0</v>
+        <v>446.0</v>
       </c>
       <c r="G14" t="n">
         <v>9.0</v>
@@ -2728,7 +2728,7 @@
         <v>701</v>
       </c>
       <c r="F22" t="n">
-        <v>342.0</v>
+        <v>344.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3040,7 +3040,7 @@
         <v>699</v>
       </c>
       <c r="F34" t="n">
-        <v>477.0</v>
+        <v>478.0</v>
       </c>
       <c r="G34" t="n">
         <v>1.0</v>
@@ -3748,7 +3748,7 @@
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="62">
@@ -4080,7 +4080,7 @@
         <v>699</v>
       </c>
       <c r="F74" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4158,7 +4158,7 @@
         <v>701</v>
       </c>
       <c r="F77" t="n">
-        <v>343.0</v>
+        <v>345.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4756,7 +4756,7 @@
         <v>701</v>
       </c>
       <c r="F100" t="n">
-        <v>398.0</v>
+        <v>402.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -4860,7 +4860,7 @@
         <v>699</v>
       </c>
       <c r="F104" t="n">
-        <v>485.0</v>
+        <v>488.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5198,7 +5198,7 @@
         <v>699</v>
       </c>
       <c r="F117" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G117" t="n">
         <v>0.0</v>
@@ -5328,7 +5328,7 @@
         <v>699</v>
       </c>
       <c r="F122" t="n">
-        <v>436.0</v>
+        <v>437.0</v>
       </c>
       <c r="G122" t="n">
         <v>1.0</v>
@@ -5614,7 +5614,7 @@
         <v>701</v>
       </c>
       <c r="F133" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G133" t="n">
         <v>0.0</v>
@@ -6056,7 +6056,7 @@
         <v>701</v>
       </c>
       <c r="F150" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -6160,7 +6160,7 @@
         <v>699</v>
       </c>
       <c r="F154" t="n">
-        <v>206.0</v>
+        <v>207.0</v>
       </c>
       <c r="G154" t="n">
         <v>0.0</v>
@@ -6186,7 +6186,7 @@
         <v>701</v>
       </c>
       <c r="F155" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -6576,7 +6576,7 @@
         <v>699</v>
       </c>
       <c r="F170" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6758,7 +6758,7 @@
         <v>701</v>
       </c>
       <c r="F177" t="n">
-        <v>493.0</v>
+        <v>494.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7018,7 +7018,7 @@
         <v>701</v>
       </c>
       <c r="F187" t="n">
-        <v>645.0</v>
+        <v>647.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7382,7 +7382,7 @@
         <v>699</v>
       </c>
       <c r="F201" t="n">
-        <v>995.0</v>
+        <v>996.0</v>
       </c>
       <c r="G201" t="n">
         <v>1.0</v>
@@ -7538,7 +7538,7 @@
         <v>701</v>
       </c>
       <c r="F207" t="n">
-        <v>89.0</v>
+        <v>91.0</v>
       </c>
       <c r="G207" t="n">
         <v>0.0</v>
@@ -7616,7 +7616,7 @@
         <v>699</v>
       </c>
       <c r="F210" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G210" t="n">
         <v>0.0</v>
@@ -7876,7 +7876,7 @@
         <v>699</v>
       </c>
       <c r="F220" t="n">
-        <v>123.0</v>
+        <v>125.0</v>
       </c>
       <c r="G220" t="n">
         <v>0.0</v>
@@ -8552,7 +8552,7 @@
         <v>699</v>
       </c>
       <c r="F246" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G246" t="n">
         <v>0.0</v>
@@ -9956,7 +9956,7 @@
         <v>699</v>
       </c>
       <c r="F300" t="n">
-        <v>395.0</v>
+        <v>396.0</v>
       </c>
       <c r="G300" t="n">
         <v>0.0</v>
@@ -10060,7 +10060,7 @@
         <v>699</v>
       </c>
       <c r="F304" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G304" t="n">
         <v>2.0</v>
@@ -10788,7 +10788,7 @@
         <v>699</v>
       </c>
       <c r="F332" t="n">
-        <v>393.0</v>
+        <v>395.0</v>
       </c>
       <c r="G332" t="n">
         <v>0.0</v>
@@ -12140,7 +12140,7 @@
         <v>699</v>
       </c>
       <c r="F384" t="n">
-        <v>233.0</v>
+        <v>236.0</v>
       </c>
       <c r="G384" t="n">
         <v>0.0</v>
@@ -13908,7 +13908,7 @@
         <v>700</v>
       </c>
       <c r="F452" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -14038,7 +14038,7 @@
         <v>699</v>
       </c>
       <c r="F457" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G457" t="n">
         <v>0.0</v>
@@ -14324,7 +14324,7 @@
         <v>699</v>
       </c>
       <c r="F468" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G468" t="n">
         <v>0.0</v>
@@ -14350,7 +14350,7 @@
         <v>699</v>
       </c>
       <c r="F469" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G469" t="n">
         <v>0.0</v>
@@ -15000,7 +15000,7 @@
         <v>699</v>
       </c>
       <c r="F494" t="n">
-        <v>570.0</v>
+        <v>573.0</v>
       </c>
       <c r="G494" t="n">
         <v>2.0</v>
@@ -15130,7 +15130,7 @@
         <v>701</v>
       </c>
       <c r="F499" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -15832,7 +15832,7 @@
         <v>699</v>
       </c>
       <c r="F526" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G526" t="n">
         <v>0.0</v>
@@ -16040,7 +16040,7 @@
         <v>701</v>
       </c>
       <c r="F534" t="n">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
       <c r="G534" t="n">
         <v>1.0</v>
@@ -16092,7 +16092,7 @@
         <v>699</v>
       </c>
       <c r="F536" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G536" t="n">
         <v>0.0</v>
@@ -16118,7 +16118,7 @@
         <v>701</v>
       </c>
       <c r="F537" t="n">
-        <v>250.0</v>
+        <v>253.0</v>
       </c>
       <c r="G537" t="n">
         <v>0.0</v>
@@ -16690,7 +16690,7 @@
         <v>701</v>
       </c>
       <c r="F559" t="n">
-        <v>550.0</v>
+        <v>554.0</v>
       </c>
       <c r="G559" t="n">
         <v>1.0</v>
@@ -16976,7 +16976,7 @@
         <v>701</v>
       </c>
       <c r="F570" t="n">
-        <v>269.0</v>
+        <v>271.0</v>
       </c>
       <c r="G570" t="n">
         <v>0.0</v>
@@ -17132,7 +17132,7 @@
         <v>699</v>
       </c>
       <c r="F576" t="n">
-        <v>301.0</v>
+        <v>304.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
@@ -18016,7 +18016,7 @@
         <v>701</v>
       </c>
       <c r="F610" t="n">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
@@ -18224,7 +18224,7 @@
         <v>699</v>
       </c>
       <c r="F618" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G618" t="n">
         <v>0.0</v>
@@ -18692,7 +18692,7 @@
         <v>701</v>
       </c>
       <c r="F636" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G636" t="n">
         <v>0.0</v>
@@ -18952,7 +18952,7 @@
         <v>701</v>
       </c>
       <c r="F646" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -19706,7 +19706,7 @@
         <v>701</v>
       </c>
       <c r="F675" t="n">
-        <v>58.0</v>
+        <v>62.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19888,7 +19888,7 @@
         <v>701</v>
       </c>
       <c r="F682" t="n">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -19914,7 +19914,7 @@
         <v>701</v>
       </c>
       <c r="F683" t="n">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -19966,7 +19966,7 @@
         <v>701</v>
       </c>
       <c r="F685" t="n">
-        <v>53.0</v>
+        <v>56.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -20018,7 +20018,7 @@
         <v>701</v>
       </c>
       <c r="F687" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G687" t="n">
         <v>0.0</v>
@@ -20044,7 +20044,7 @@
         <v>699</v>
       </c>
       <c r="F688" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G688" t="n">
         <v>2.0</v>
@@ -20122,7 +20122,7 @@
         <v>699</v>
       </c>
       <c r="F691" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="G691" t="n">
         <v>0.0</v>
@@ -20200,7 +20200,7 @@
         <v>699</v>
       </c>
       <c r="F694" t="n">
-        <v>297.0</v>
+        <v>299.0</v>
       </c>
       <c r="G694" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2318,7 +2318,7 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="7">
@@ -3098,7 +3098,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="37">
@@ -3872,7 +3872,7 @@
         <v>699</v>
       </c>
       <c r="F66" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -4106,7 +4106,7 @@
         <v>699</v>
       </c>
       <c r="F75" t="n">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -4652,7 +4652,7 @@
         <v>699</v>
       </c>
       <c r="F96" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -5068,10 +5068,10 @@
         <v>701</v>
       </c>
       <c r="F112" t="n">
-        <v>71.0</v>
+        <v>74.0</v>
       </c>
       <c r="G112" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H112" t="n">
         <v>2.0</v>
@@ -5120,7 +5120,7 @@
         <v>699</v>
       </c>
       <c r="F114" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -5406,7 +5406,7 @@
         <v>699</v>
       </c>
       <c r="F125" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G125" t="n">
         <v>1.0</v>
@@ -5698,7 +5698,7 @@
         <v>0.0</v>
       </c>
       <c r="H136" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="137">
@@ -6296,7 +6296,7 @@
         <v>0.0</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="160">
@@ -6686,7 +6686,7 @@
         <v>0.0</v>
       </c>
       <c r="H174" t="n">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="175">
@@ -6888,7 +6888,7 @@
         <v>701</v>
       </c>
       <c r="F182" t="n">
-        <v>558.0</v>
+        <v>559.0</v>
       </c>
       <c r="G182" t="n">
         <v>1.0</v>
@@ -9182,7 +9182,7 @@
         <v>0.0</v>
       </c>
       <c r="H270" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="271">
@@ -9306,7 +9306,7 @@
         <v>699</v>
       </c>
       <c r="F275" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -9364,7 +9364,7 @@
         <v>0.0</v>
       </c>
       <c r="H277" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="278">
@@ -10112,7 +10112,7 @@
         <v>699</v>
       </c>
       <c r="F306" t="n">
-        <v>993.0</v>
+        <v>999.0</v>
       </c>
       <c r="G306" t="n">
         <v>5.0</v>
@@ -10372,7 +10372,7 @@
         <v>699</v>
       </c>
       <c r="F316" t="n">
-        <v>527.0</v>
+        <v>533.0</v>
       </c>
       <c r="G316" t="n">
         <v>2.0</v>
@@ -11288,7 +11288,7 @@
         <v>0.0</v>
       </c>
       <c r="H351" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="352">
@@ -11412,7 +11412,7 @@
         <v>699</v>
       </c>
       <c r="F356" t="n">
-        <v>520.0</v>
+        <v>522.0</v>
       </c>
       <c r="G356" t="n">
         <v>6.0</v>
@@ -11724,7 +11724,7 @@
         <v>701</v>
       </c>
       <c r="F368" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -13521,7 +13521,7 @@
         <v>80.0</v>
       </c>
       <c r="G437" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H437" t="n">
         <v>0.0</v>
@@ -15292,7 +15292,7 @@
         <v>0.0</v>
       </c>
       <c r="H505" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="506">
@@ -15806,7 +15806,7 @@
         <v>699</v>
       </c>
       <c r="F525" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G525" t="n">
         <v>0.0</v>
@@ -16748,7 +16748,7 @@
         <v>0.0</v>
       </c>
       <c r="H561" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="562">
@@ -17600,7 +17600,7 @@
         <v>701</v>
       </c>
       <c r="F594" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
@@ -18539,7 +18539,7 @@
         <v>23.0</v>
       </c>
       <c r="G630" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H630" t="n">
         <v>0.0</v>
@@ -18562,7 +18562,7 @@
         <v>699</v>
       </c>
       <c r="F631" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -19192,7 +19192,7 @@
         <v>0.0</v>
       </c>
       <c r="H655" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="656">
@@ -19212,7 +19212,7 @@
         <v>699</v>
       </c>
       <c r="F656" t="n">
-        <v>174.0</v>
+        <v>175.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19244,7 +19244,7 @@
         <v>0.0</v>
       </c>
       <c r="H657" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="658">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2442,7 +2442,7 @@
         <v>699</v>
       </c>
       <c r="F11" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -2702,7 +2702,7 @@
         <v>699</v>
       </c>
       <c r="F21" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G21" t="n">
         <v>2.0</v>
@@ -3066,7 +3066,7 @@
         <v>699</v>
       </c>
       <c r="F35" t="n">
-        <v>172.0</v>
+        <v>177.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3982,7 +3982,7 @@
         <v>7.0</v>
       </c>
       <c r="H70" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="71">
@@ -4912,7 +4912,7 @@
         <v>699</v>
       </c>
       <c r="F106" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G106" t="n">
         <v>1.0</v>
@@ -9540,7 +9540,7 @@
         <v>699</v>
       </c>
       <c r="F284" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G284" t="n">
         <v>2.0</v>
@@ -9800,10 +9800,10 @@
         <v>700</v>
       </c>
       <c r="F294" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="G294" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H294" t="n">
         <v>1.0</v>
@@ -12972,7 +12972,7 @@
         <v>699</v>
       </c>
       <c r="F416" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G416" t="n">
         <v>0.0</v>
@@ -13310,7 +13310,7 @@
         <v>699</v>
       </c>
       <c r="F429" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G429" t="n">
         <v>0.0</v>
@@ -13596,7 +13596,7 @@
         <v>699</v>
       </c>
       <c r="F440" t="n">
-        <v>540.0</v>
+        <v>541.0</v>
       </c>
       <c r="G440" t="n">
         <v>3.0</v>
@@ -14844,7 +14844,7 @@
         <v>699</v>
       </c>
       <c r="F488" t="n">
-        <v>379.0</v>
+        <v>380.0</v>
       </c>
       <c r="G488" t="n">
         <v>2.0</v>
@@ -15338,13 +15338,13 @@
         <v>699</v>
       </c>
       <c r="F507" t="n">
-        <v>2334.0</v>
+        <v>2341.0</v>
       </c>
       <c r="G507" t="n">
         <v>44.0</v>
       </c>
       <c r="H507" t="n">
-        <v>295.0</v>
+        <v>298.0</v>
       </c>
     </row>
     <row r="508">
@@ -17054,7 +17054,7 @@
         <v>699</v>
       </c>
       <c r="F573" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G573" t="n">
         <v>1.0</v>
@@ -17548,7 +17548,7 @@
         <v>699</v>
       </c>
       <c r="F592" t="n">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
       <c r="G592" t="n">
         <v>11.0</v>
@@ -19192,7 +19192,7 @@
         <v>0.0</v>
       </c>
       <c r="H655" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="656">
@@ -19244,7 +19244,7 @@
         <v>0.0</v>
       </c>
       <c r="H657" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="658">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3306,7 +3306,7 @@
         <v>1.0</v>
       </c>
       <c r="H44" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="45">
@@ -6056,7 +6056,7 @@
         <v>701</v>
       </c>
       <c r="F150" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -12796,7 +12796,7 @@
         <v>9.0</v>
       </c>
       <c r="H409" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="410">
@@ -19192,7 +19192,7 @@
         <v>0.0</v>
       </c>
       <c r="H655" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="656">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2494,7 +2494,7 @@
         <v>699</v>
       </c>
       <c r="F13" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -3982,7 +3982,7 @@
         <v>7.0</v>
       </c>
       <c r="H70" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="71">
@@ -8968,7 +8968,7 @@
         <v>699</v>
       </c>
       <c r="F262" t="n">
-        <v>229.0</v>
+        <v>231.0</v>
       </c>
       <c r="G262" t="n">
         <v>0.0</v>
@@ -9384,7 +9384,7 @@
         <v>699</v>
       </c>
       <c r="F278" t="n">
-        <v>497.0</v>
+        <v>498.0</v>
       </c>
       <c r="G278" t="n">
         <v>0.0</v>
@@ -9624,7 +9624,7 @@
         <v>6.0</v>
       </c>
       <c r="H287" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="288">
@@ -10872,7 +10872,7 @@
         <v>0.0</v>
       </c>
       <c r="H335" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="336">
@@ -12504,7 +12504,7 @@
         <v>699</v>
       </c>
       <c r="F398" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
       <c r="G398" t="n">
         <v>1.0</v>
@@ -19212,7 +19212,7 @@
         <v>699</v>
       </c>
       <c r="F656" t="n">
-        <v>175.0</v>
+        <v>177.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2318,7 +2318,7 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="7">
@@ -2676,7 +2676,7 @@
         <v>699</v>
       </c>
       <c r="F20" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G20" t="n">
         <v>1.0</v>
@@ -3306,7 +3306,7 @@
         <v>1.0</v>
       </c>
       <c r="H44" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="45">
@@ -3872,7 +3872,7 @@
         <v>699</v>
       </c>
       <c r="F66" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -4132,7 +4132,7 @@
         <v>699</v>
       </c>
       <c r="F76" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -6966,10 +6966,10 @@
         <v>701</v>
       </c>
       <c r="F185" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -7382,7 +7382,7 @@
         <v>699</v>
       </c>
       <c r="F201" t="n">
-        <v>996.0</v>
+        <v>997.0</v>
       </c>
       <c r="G201" t="n">
         <v>1.0</v>
@@ -8812,7 +8812,7 @@
         <v>699</v>
       </c>
       <c r="F256" t="n">
-        <v>930.0</v>
+        <v>933.0</v>
       </c>
       <c r="G256" t="n">
         <v>16.0</v>
@@ -9696,7 +9696,7 @@
         <v>699</v>
       </c>
       <c r="F290" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="G290" t="n">
         <v>0.0</v>
@@ -10710,7 +10710,7 @@
         <v>699</v>
       </c>
       <c r="F329" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G329" t="n">
         <v>0.0</v>
@@ -12816,7 +12816,7 @@
         <v>699</v>
       </c>
       <c r="F410" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G410" t="n">
         <v>0.0</v>
@@ -13365,7 +13365,7 @@
         <v>98.0</v>
       </c>
       <c r="G431" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H431" t="n">
         <v>0.0</v>
@@ -13596,7 +13596,7 @@
         <v>699</v>
       </c>
       <c r="F440" t="n">
-        <v>541.0</v>
+        <v>542.0</v>
       </c>
       <c r="G440" t="n">
         <v>3.0</v>
@@ -14324,7 +14324,7 @@
         <v>699</v>
       </c>
       <c r="F468" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G468" t="n">
         <v>0.0</v>
@@ -15676,7 +15676,7 @@
         <v>699</v>
       </c>
       <c r="F520" t="n">
-        <v>404.0</v>
+        <v>409.0</v>
       </c>
       <c r="G520" t="n">
         <v>9.0</v>
@@ -17054,7 +17054,7 @@
         <v>699</v>
       </c>
       <c r="F573" t="n">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
       <c r="G573" t="n">
         <v>1.0</v>
@@ -18100,7 +18100,7 @@
         <v>2.0</v>
       </c>
       <c r="H613" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="614">
@@ -18536,10 +18536,10 @@
         <v>701</v>
       </c>
       <c r="F630" t="n">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
       <c r="G630" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H630" t="n">
         <v>0.0</v>
@@ -18692,7 +18692,7 @@
         <v>701</v>
       </c>
       <c r="F636" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G636" t="n">
         <v>0.0</v>
@@ -19244,7 +19244,7 @@
         <v>0.0</v>
       </c>
       <c r="H657" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="658">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2676,7 +2676,7 @@
         <v>699</v>
       </c>
       <c r="F20" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G20" t="n">
         <v>1.0</v>
@@ -2702,7 +2702,7 @@
         <v>699</v>
       </c>
       <c r="F21" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G21" t="n">
         <v>2.0</v>
@@ -3046,7 +3046,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="35">
@@ -3098,7 +3098,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="37">
@@ -3508,7 +3508,7 @@
         <v>701</v>
       </c>
       <c r="F52" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -5120,7 +5120,7 @@
         <v>699</v>
       </c>
       <c r="F114" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -6972,7 +6972,7 @@
         <v>2.0</v>
       </c>
       <c r="H185" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="186">
@@ -7018,7 +7018,7 @@
         <v>701</v>
       </c>
       <c r="F187" t="n">
-        <v>647.0</v>
+        <v>650.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7278,7 +7278,7 @@
         <v>701</v>
       </c>
       <c r="F197" t="n">
-        <v>269.0</v>
+        <v>271.0</v>
       </c>
       <c r="G197" t="n">
         <v>1.0</v>
@@ -8422,7 +8422,7 @@
         <v>701</v>
       </c>
       <c r="F241" t="n">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
       <c r="G241" t="n">
         <v>0.0</v>
@@ -8532,7 +8532,7 @@
         <v>0.0</v>
       </c>
       <c r="H245" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="246">
@@ -9618,7 +9618,7 @@
         <v>699</v>
       </c>
       <c r="F287" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
       <c r="G287" t="n">
         <v>6.0</v>
@@ -10112,7 +10112,7 @@
         <v>699</v>
       </c>
       <c r="F306" t="n">
-        <v>999.0</v>
+        <v>1000.0</v>
       </c>
       <c r="G306" t="n">
         <v>5.0</v>
@@ -12484,7 +12484,7 @@
         <v>0.0</v>
       </c>
       <c r="H397" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="398">
@@ -13368,7 +13368,7 @@
         <v>1.0</v>
       </c>
       <c r="H431" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="432">
@@ -16118,7 +16118,7 @@
         <v>701</v>
       </c>
       <c r="F537" t="n">
-        <v>253.0</v>
+        <v>257.0</v>
       </c>
       <c r="G537" t="n">
         <v>0.0</v>
@@ -16976,7 +16976,7 @@
         <v>701</v>
       </c>
       <c r="F570" t="n">
-        <v>271.0</v>
+        <v>273.0</v>
       </c>
       <c r="G570" t="n">
         <v>0.0</v>
@@ -17054,7 +17054,7 @@
         <v>699</v>
       </c>
       <c r="F573" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G573" t="n">
         <v>1.0</v>
@@ -19192,7 +19192,7 @@
         <v>0.0</v>
       </c>
       <c r="H655" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="656">
@@ -19244,7 +19244,7 @@
         <v>0.0</v>
       </c>
       <c r="H657" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="658">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2145,7 +2145,7 @@
         <v>678</v>
       </c>
       <c r="F2" t="n">
-        <v>565.0</v>
+        <v>567.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2457,7 +2457,7 @@
         <v>678</v>
       </c>
       <c r="F14" t="n">
-        <v>448.0</v>
+        <v>450.0</v>
       </c>
       <c r="G14" t="n">
         <v>9.0</v>
@@ -2509,7 +2509,7 @@
         <v>678</v>
       </c>
       <c r="F16" t="n">
-        <v>385.0</v>
+        <v>388.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2977,7 +2977,7 @@
         <v>678</v>
       </c>
       <c r="F34" t="n">
-        <v>177.0</v>
+        <v>182.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -3055,7 +3055,7 @@
         <v>679</v>
       </c>
       <c r="F37" t="n">
-        <v>114.0</v>
+        <v>117.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3107,7 +3107,7 @@
         <v>678</v>
       </c>
       <c r="F39" t="n">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3783,7 +3783,7 @@
         <v>679</v>
       </c>
       <c r="F65" t="n">
-        <v>176.0</v>
+        <v>178.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>678</v>
       </c>
       <c r="F70" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4355,7 +4355,7 @@
         <v>680</v>
       </c>
       <c r="F87" t="n">
-        <v>467.0</v>
+        <v>468.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -4589,7 +4589,7 @@
         <v>679</v>
       </c>
       <c r="F96" t="n">
-        <v>407.0</v>
+        <v>409.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -4693,7 +4693,7 @@
         <v>678</v>
       </c>
       <c r="F100" t="n">
-        <v>494.0</v>
+        <v>495.0</v>
       </c>
       <c r="G100" t="n">
         <v>3.0</v>
@@ -4904,7 +4904,7 @@
         <v>74.0</v>
       </c>
       <c r="G108" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H108" t="n">
         <v>2.0</v>
@@ -5161,7 +5161,7 @@
         <v>678</v>
       </c>
       <c r="F118" t="n">
-        <v>443.0</v>
+        <v>445.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -5499,7 +5499,7 @@
         <v>678</v>
       </c>
       <c r="F131" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
@@ -5629,7 +5629,7 @@
         <v>678</v>
       </c>
       <c r="F136" t="n">
-        <v>645.0</v>
+        <v>646.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -6253,7 +6253,7 @@
         <v>679</v>
       </c>
       <c r="F160" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -6305,7 +6305,7 @@
         <v>678</v>
       </c>
       <c r="F162" t="n">
-        <v>308.0</v>
+        <v>310.0</v>
       </c>
       <c r="G162" t="n">
         <v>0.0</v>
@@ -6487,7 +6487,7 @@
         <v>678</v>
       </c>
       <c r="F169" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6513,7 +6513,7 @@
         <v>679</v>
       </c>
       <c r="F170" t="n">
-        <v>496.0</v>
+        <v>499.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6877,7 +6877,7 @@
         <v>678</v>
       </c>
       <c r="F184" t="n">
-        <v>318.0</v>
+        <v>320.0</v>
       </c>
       <c r="G184" t="n">
         <v>2.0</v>
@@ -7839,7 +7839,7 @@
         <v>679</v>
       </c>
       <c r="F221" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8391,7 +8391,7 @@
         <v>16.0</v>
       </c>
       <c r="H242" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="243">
@@ -9711,7 +9711,7 @@
         <v>678</v>
       </c>
       <c r="F293" t="n">
-        <v>315.0</v>
+        <v>317.0</v>
       </c>
       <c r="G293" t="n">
         <v>4.0</v>
@@ -9893,7 +9893,7 @@
         <v>678</v>
       </c>
       <c r="F300" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
       <c r="G300" t="n">
         <v>0.0</v>
@@ -10130,7 +10130,7 @@
         <v>67.0</v>
       </c>
       <c r="G309" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H309" t="n">
         <v>0.0</v>
@@ -11063,7 +11063,7 @@
         <v>678</v>
       </c>
       <c r="F345" t="n">
-        <v>522.0</v>
+        <v>525.0</v>
       </c>
       <c r="G345" t="n">
         <v>6.0</v>
@@ -11739,7 +11739,7 @@
         <v>678</v>
       </c>
       <c r="F371" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="G371" t="n">
         <v>0.0</v>
@@ -11947,7 +11947,7 @@
         <v>678</v>
       </c>
       <c r="F379" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G379" t="n">
         <v>7.0</v>
@@ -13845,7 +13845,7 @@
         <v>678</v>
       </c>
       <c r="F452" t="n">
-        <v>96.0</v>
+        <v>99.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -14911,13 +14911,13 @@
         <v>678</v>
       </c>
       <c r="F493" t="n">
-        <v>2341.0</v>
+        <v>2350.0</v>
       </c>
       <c r="G493" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="H493" t="n">
-        <v>298.0</v>
+        <v>302.0</v>
       </c>
     </row>
     <row r="494">
@@ -15457,7 +15457,7 @@
         <v>679</v>
       </c>
       <c r="F514" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="G514" t="n">
         <v>0.0</v>
@@ -16705,7 +16705,7 @@
         <v>678</v>
       </c>
       <c r="F562" t="n">
-        <v>304.0</v>
+        <v>305.0</v>
       </c>
       <c r="G562" t="n">
         <v>0.0</v>
@@ -17095,7 +17095,7 @@
         <v>678</v>
       </c>
       <c r="F577" t="n">
-        <v>346.0</v>
+        <v>347.0</v>
       </c>
       <c r="G577" t="n">
         <v>11.0</v>
@@ -17693,7 +17693,7 @@
         <v>678</v>
       </c>
       <c r="F600" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -18343,7 +18343,7 @@
         <v>679</v>
       </c>
       <c r="F625" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G625" t="n">
         <v>0.0</v>
@@ -18635,7 +18635,7 @@
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>18.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="637">
@@ -19279,7 +19279,7 @@
         <v>679</v>
       </c>
       <c r="F661" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19331,7 +19331,7 @@
         <v>679</v>
       </c>
       <c r="F663" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19357,7 +19357,7 @@
         <v>679</v>
       </c>
       <c r="F664" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G664" t="n">
         <v>0.0</v>
@@ -19409,7 +19409,7 @@
         <v>679</v>
       </c>
       <c r="F666" t="n">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -19461,7 +19461,7 @@
         <v>678</v>
       </c>
       <c r="F668" t="n">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -19487,7 +19487,7 @@
         <v>679</v>
       </c>
       <c r="F669" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -19513,7 +19513,7 @@
         <v>678</v>
       </c>
       <c r="F670" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19591,7 +19591,7 @@
         <v>678</v>
       </c>
       <c r="F673" t="n">
-        <v>300.0</v>
+        <v>302.0</v>
       </c>
       <c r="G673" t="n">
         <v>2.0</v>
@@ -19617,7 +19617,7 @@
         <v>679</v>
       </c>
       <c r="F674" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19643,7 +19643,7 @@
         <v>679</v>
       </c>
       <c r="F675" t="n">
-        <v>376.0</v>
+        <v>378.0</v>
       </c>
       <c r="G675" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2255,7 +2255,7 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="7">
@@ -2431,7 +2431,7 @@
         <v>678</v>
       </c>
       <c r="F13" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -6149,7 +6149,7 @@
         <v>678</v>
       </c>
       <c r="F156" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -7059,7 +7059,7 @@
         <v>679</v>
       </c>
       <c r="F191" t="n">
-        <v>997.0</v>
+        <v>999.0</v>
       </c>
       <c r="G191" t="n">
         <v>1.0</v>
@@ -8099,7 +8099,7 @@
         <v>678</v>
       </c>
       <c r="F231" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G231" t="n">
         <v>0.0</v>
@@ -8385,7 +8385,7 @@
         <v>678</v>
       </c>
       <c r="F242" t="n">
-        <v>933.0</v>
+        <v>936.0</v>
       </c>
       <c r="G242" t="n">
         <v>16.0</v>
@@ -8541,7 +8541,7 @@
         <v>678</v>
       </c>
       <c r="F248" t="n">
-        <v>231.0</v>
+        <v>233.0</v>
       </c>
       <c r="G248" t="n">
         <v>0.0</v>
@@ -9685,7 +9685,7 @@
         <v>678</v>
       </c>
       <c r="F292" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G292" t="n">
         <v>2.0</v>
@@ -10569,7 +10569,7 @@
         <v>678</v>
       </c>
       <c r="F326" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G326" t="n">
         <v>0.0</v>
@@ -11349,7 +11349,7 @@
         <v>679</v>
       </c>
       <c r="F356" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G356" t="n">
         <v>0.0</v>
@@ -12551,7 +12551,7 @@
         <v>0.0</v>
       </c>
       <c r="H402" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="403">
@@ -13143,7 +13143,7 @@
         <v>678</v>
       </c>
       <c r="F425" t="n">
-        <v>542.0</v>
+        <v>544.0</v>
       </c>
       <c r="G425" t="n">
         <v>3.0</v>
@@ -13273,7 +13273,7 @@
         <v>678</v>
       </c>
       <c r="F430" t="n">
-        <v>758.0</v>
+        <v>759.0</v>
       </c>
       <c r="G430" t="n">
         <v>2.0</v>
@@ -14865,7 +14865,7 @@
         <v>0.0</v>
       </c>
       <c r="H491" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="492">
@@ -14917,7 +14917,7 @@
         <v>45.0</v>
       </c>
       <c r="H493" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
     </row>
     <row r="494">
@@ -15613,7 +15613,7 @@
         <v>678</v>
       </c>
       <c r="F520" t="n">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="G520" t="n">
         <v>0.0</v>
@@ -16003,7 +16003,7 @@
         <v>678</v>
       </c>
       <c r="F535" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G535" t="n">
         <v>1.0</v>
@@ -16081,7 +16081,7 @@
         <v>679</v>
       </c>
       <c r="F538" t="n">
-        <v>347.0</v>
+        <v>349.0</v>
       </c>
       <c r="G538" t="n">
         <v>0.0</v>
@@ -17875,7 +17875,7 @@
         <v>678</v>
       </c>
       <c r="F607" t="n">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
       <c r="G607" t="n">
         <v>0.0</v>
@@ -18583,7 +18583,7 @@
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="635">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2411,7 +2411,7 @@
         <v>0.0</v>
       </c>
       <c r="H12" t="n">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="13">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2457,7 +2457,7 @@
         <v>678</v>
       </c>
       <c r="F14" t="n">
-        <v>450.0</v>
+        <v>452.0</v>
       </c>
       <c r="G14" t="n">
         <v>9.0</v>
@@ -2509,7 +2509,7 @@
         <v>678</v>
       </c>
       <c r="F16" t="n">
-        <v>388.0</v>
+        <v>389.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2665,7 +2665,7 @@
         <v>679</v>
       </c>
       <c r="F22" t="n">
-        <v>346.0</v>
+        <v>347.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2951,7 +2951,7 @@
         <v>678</v>
       </c>
       <c r="F33" t="n">
-        <v>486.0</v>
+        <v>490.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -3214,7 +3214,7 @@
         <v>287.0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H43" t="n">
         <v>8.0</v>
@@ -3581,7 +3581,7 @@
         <v>0.0</v>
       </c>
       <c r="H57" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="58">
@@ -3783,7 +3783,7 @@
         <v>679</v>
       </c>
       <c r="F65" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>678</v>
       </c>
       <c r="F70" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4589,7 +4589,7 @@
         <v>679</v>
       </c>
       <c r="F96" t="n">
-        <v>409.0</v>
+        <v>413.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -4823,7 +4823,7 @@
         <v>679</v>
       </c>
       <c r="F105" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -6305,7 +6305,7 @@
         <v>678</v>
       </c>
       <c r="F162" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
       <c r="G162" t="n">
         <v>0.0</v>
@@ -6695,10 +6695,10 @@
         <v>678</v>
       </c>
       <c r="F177" t="n">
-        <v>61.0</v>
+        <v>63.0</v>
       </c>
       <c r="G177" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H177" t="n">
         <v>1.0</v>
@@ -7059,7 +7059,7 @@
         <v>679</v>
       </c>
       <c r="F191" t="n">
-        <v>999.0</v>
+        <v>1000.0</v>
       </c>
       <c r="G191" t="n">
         <v>1.0</v>
@@ -7215,7 +7215,7 @@
         <v>679</v>
       </c>
       <c r="F197" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G197" t="n">
         <v>0.0</v>
@@ -7709,7 +7709,7 @@
         <v>678</v>
       </c>
       <c r="F216" t="n">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="G216" t="n">
         <v>0.0</v>
@@ -9243,7 +9243,7 @@
         <v>678</v>
       </c>
       <c r="F275" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -9581,7 +9581,7 @@
         <v>678</v>
       </c>
       <c r="F288" t="n">
-        <v>397.0</v>
+        <v>399.0</v>
       </c>
       <c r="G288" t="n">
         <v>0.0</v>
@@ -9867,7 +9867,7 @@
         <v>678</v>
       </c>
       <c r="F299" t="n">
-        <v>485.0</v>
+        <v>487.0</v>
       </c>
       <c r="G299" t="n">
         <v>6.0</v>
@@ -11349,7 +11349,7 @@
         <v>679</v>
       </c>
       <c r="F356" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G356" t="n">
         <v>0.0</v>
@@ -12883,13 +12883,13 @@
         <v>678</v>
       </c>
       <c r="F415" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G415" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="416">
@@ -14521,7 +14521,7 @@
         <v>678</v>
       </c>
       <c r="F478" t="n">
-        <v>577.0</v>
+        <v>580.0</v>
       </c>
       <c r="G478" t="n">
         <v>2.0</v>
@@ -17173,7 +17173,7 @@
         <v>679</v>
       </c>
       <c r="F580" t="n">
-        <v>379.0</v>
+        <v>382.0</v>
       </c>
       <c r="G580" t="n">
         <v>0.0</v>
@@ -17693,7 +17693,7 @@
         <v>678</v>
       </c>
       <c r="F600" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -18005,10 +18005,10 @@
         <v>678</v>
       </c>
       <c r="F612" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G612" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H612" t="n">
         <v>0.0</v>
@@ -18343,7 +18343,7 @@
         <v>679</v>
       </c>
       <c r="F625" t="n">
-        <v>87.0</v>
+        <v>91.0</v>
       </c>
       <c r="G625" t="n">
         <v>0.0</v>
@@ -18635,7 +18635,7 @@
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="637">
@@ -19019,7 +19019,7 @@
         <v>679</v>
       </c>
       <c r="F651" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -19071,7 +19071,7 @@
         <v>679</v>
       </c>
       <c r="F653" t="n">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
       <c r="G653" t="n">
         <v>0.0</v>
@@ -19097,7 +19097,7 @@
         <v>679</v>
       </c>
       <c r="F654" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19279,7 +19279,7 @@
         <v>679</v>
       </c>
       <c r="F661" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19331,7 +19331,7 @@
         <v>679</v>
       </c>
       <c r="F663" t="n">
-        <v>138.0</v>
+        <v>141.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19617,7 +19617,7 @@
         <v>679</v>
       </c>
       <c r="F674" t="n">
-        <v>141.0</v>
+        <v>144.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2957,7 +2957,7 @@
         <v>1.0</v>
       </c>
       <c r="H33" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="34">
@@ -3107,7 +3107,7 @@
         <v>678</v>
       </c>
       <c r="F39" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3581,7 +3581,7 @@
         <v>0.0</v>
       </c>
       <c r="H57" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="58">
@@ -3991,7 +3991,7 @@
         <v>679</v>
       </c>
       <c r="F73" t="n">
-        <v>345.0</v>
+        <v>348.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4173,7 +4173,7 @@
         <v>678</v>
       </c>
       <c r="F80" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -4745,7 +4745,7 @@
         <v>678</v>
       </c>
       <c r="F102" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>
@@ -5031,7 +5031,7 @@
         <v>678</v>
       </c>
       <c r="F113" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -6149,10 +6149,10 @@
         <v>678</v>
       </c>
       <c r="F156" t="n">
-        <v>340.0</v>
+        <v>341.0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -6747,7 +6747,7 @@
         <v>679</v>
       </c>
       <c r="F179" t="n">
-        <v>650.0</v>
+        <v>661.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7501,7 +7501,7 @@
         <v>678</v>
       </c>
       <c r="F208" t="n">
-        <v>125.0</v>
+        <v>128.0</v>
       </c>
       <c r="G208" t="n">
         <v>0.0</v>
@@ -7735,7 +7735,7 @@
         <v>678</v>
       </c>
       <c r="F217" t="n">
-        <v>133.0</v>
+        <v>137.0</v>
       </c>
       <c r="G217" t="n">
         <v>0.0</v>
@@ -7917,7 +7917,7 @@
         <v>678</v>
       </c>
       <c r="F224" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G224" t="n">
         <v>0.0</v>
@@ -9113,7 +9113,7 @@
         <v>678</v>
       </c>
       <c r="F270" t="n">
-        <v>251.0</v>
+        <v>254.0</v>
       </c>
       <c r="G270" t="n">
         <v>2.0</v>
@@ -9269,7 +9269,7 @@
         <v>678</v>
       </c>
       <c r="F276" t="n">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="G276" t="n">
         <v>0.0</v>
@@ -9321,7 +9321,7 @@
         <v>678</v>
       </c>
       <c r="F278" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
       <c r="G278" t="n">
         <v>0.0</v>
@@ -10127,10 +10127,10 @@
         <v>678</v>
       </c>
       <c r="F309" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G309" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H309" t="n">
         <v>0.0</v>
@@ -11121,7 +11121,7 @@
         <v>7.0</v>
       </c>
       <c r="H347" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="348">
@@ -11661,7 +11661,7 @@
         <v>679</v>
       </c>
       <c r="F368" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -11687,7 +11687,7 @@
         <v>678</v>
       </c>
       <c r="F369" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G369" t="n">
         <v>0.0</v>
@@ -13273,7 +13273,7 @@
         <v>678</v>
       </c>
       <c r="F430" t="n">
-        <v>759.0</v>
+        <v>760.0</v>
       </c>
       <c r="G430" t="n">
         <v>2.0</v>
@@ -13637,7 +13637,7 @@
         <v>678</v>
       </c>
       <c r="F444" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
@@ -13845,7 +13845,7 @@
         <v>678</v>
       </c>
       <c r="F452" t="n">
-        <v>99.0</v>
+        <v>101.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -14911,7 +14911,7 @@
         <v>678</v>
       </c>
       <c r="F493" t="n">
-        <v>2350.0</v>
+        <v>2357.0</v>
       </c>
       <c r="G493" t="n">
         <v>45.0</v>
@@ -15587,7 +15587,7 @@
         <v>679</v>
       </c>
       <c r="F519" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G519" t="n">
         <v>1.0</v>
@@ -16029,7 +16029,7 @@
         <v>678</v>
       </c>
       <c r="F536" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G536" t="n">
         <v>0.0</v>
@@ -16523,7 +16523,7 @@
         <v>679</v>
       </c>
       <c r="F555" t="n">
-        <v>273.0</v>
+        <v>275.0</v>
       </c>
       <c r="G555" t="n">
         <v>0.0</v>
@@ -17043,7 +17043,7 @@
         <v>678</v>
       </c>
       <c r="F575" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="G575" t="n">
         <v>0.0</v>
@@ -18635,7 +18635,7 @@
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="637">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2145,7 +2145,7 @@
         <v>678</v>
       </c>
       <c r="F2" t="n">
-        <v>567.0</v>
+        <v>573.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2509,7 +2509,7 @@
         <v>678</v>
       </c>
       <c r="F16" t="n">
-        <v>389.0</v>
+        <v>391.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2639,7 +2639,7 @@
         <v>678</v>
       </c>
       <c r="F21" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G21" t="n">
         <v>2.0</v>
@@ -2665,7 +2665,7 @@
         <v>679</v>
       </c>
       <c r="F22" t="n">
-        <v>347.0</v>
+        <v>349.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2951,7 +2951,7 @@
         <v>678</v>
       </c>
       <c r="F33" t="n">
-        <v>490.0</v>
+        <v>491.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -2977,7 +2977,7 @@
         <v>678</v>
       </c>
       <c r="F34" t="n">
-        <v>182.0</v>
+        <v>185.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -3217,7 +3217,7 @@
         <v>3.0</v>
       </c>
       <c r="H43" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="44">
@@ -3783,7 +3783,7 @@
         <v>679</v>
       </c>
       <c r="F65" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3809,10 +3809,10 @@
         <v>678</v>
       </c>
       <c r="F66" t="n">
-        <v>145.0</v>
+        <v>149.0</v>
       </c>
       <c r="G66" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H66" t="n">
         <v>18.0</v>
@@ -3913,7 +3913,7 @@
         <v>678</v>
       </c>
       <c r="F70" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4147,7 +4147,7 @@
         <v>678</v>
       </c>
       <c r="F79" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -4381,7 +4381,7 @@
         <v>679</v>
       </c>
       <c r="F88" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -4693,7 +4693,7 @@
         <v>678</v>
       </c>
       <c r="F100" t="n">
-        <v>495.0</v>
+        <v>496.0</v>
       </c>
       <c r="G100" t="n">
         <v>3.0</v>
@@ -5161,7 +5161,7 @@
         <v>678</v>
       </c>
       <c r="F118" t="n">
-        <v>445.0</v>
+        <v>447.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -5629,7 +5629,7 @@
         <v>678</v>
       </c>
       <c r="F136" t="n">
-        <v>646.0</v>
+        <v>649.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -5915,7 +5915,7 @@
         <v>678</v>
       </c>
       <c r="F147" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -6305,7 +6305,7 @@
         <v>678</v>
       </c>
       <c r="F162" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="G162" t="n">
         <v>0.0</v>
@@ -6461,7 +6461,7 @@
         <v>679</v>
       </c>
       <c r="F168" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G168" t="n">
         <v>0.0</v>
@@ -6487,7 +6487,7 @@
         <v>678</v>
       </c>
       <c r="F169" t="n">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6513,7 +6513,7 @@
         <v>679</v>
       </c>
       <c r="F170" t="n">
-        <v>499.0</v>
+        <v>503.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -7839,7 +7839,7 @@
         <v>679</v>
       </c>
       <c r="F221" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8801,7 +8801,7 @@
         <v>678</v>
       </c>
       <c r="F258" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G258" t="n">
         <v>0.0</v>
@@ -9737,7 +9737,7 @@
         <v>678</v>
       </c>
       <c r="F294" t="n">
-        <v>1000.0</v>
+        <v>1001.0</v>
       </c>
       <c r="G294" t="n">
         <v>5.0</v>
@@ -10491,7 +10491,7 @@
         <v>678</v>
       </c>
       <c r="F323" t="n">
-        <v>402.0</v>
+        <v>403.0</v>
       </c>
       <c r="G323" t="n">
         <v>0.0</v>
@@ -11739,7 +11739,7 @@
         <v>678</v>
       </c>
       <c r="F371" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="G371" t="n">
         <v>0.0</v>
@@ -12311,13 +12311,13 @@
         <v>678</v>
       </c>
       <c r="F393" t="n">
-        <v>291.0</v>
+        <v>292.0</v>
       </c>
       <c r="G393" t="n">
         <v>9.0</v>
       </c>
       <c r="H393" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="394">
@@ -13143,7 +13143,7 @@
         <v>678</v>
       </c>
       <c r="F425" t="n">
-        <v>544.0</v>
+        <v>552.0</v>
       </c>
       <c r="G425" t="n">
         <v>3.0</v>
@@ -13617,7 +13617,7 @@
         <v>0.0</v>
       </c>
       <c r="H443" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="444">
@@ -14521,7 +14521,7 @@
         <v>678</v>
       </c>
       <c r="F478" t="n">
-        <v>580.0</v>
+        <v>583.0</v>
       </c>
       <c r="G478" t="n">
         <v>2.0</v>
@@ -15457,7 +15457,7 @@
         <v>679</v>
       </c>
       <c r="F514" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="G514" t="n">
         <v>0.0</v>
@@ -16627,7 +16627,7 @@
         <v>678</v>
       </c>
       <c r="F559" t="n">
-        <v>73.0</v>
+        <v>83.0</v>
       </c>
       <c r="G559" t="n">
         <v>1.0</v>
@@ -16705,7 +16705,7 @@
         <v>678</v>
       </c>
       <c r="F562" t="n">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="G562" t="n">
         <v>0.0</v>
@@ -17693,7 +17693,7 @@
         <v>678</v>
       </c>
       <c r="F600" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -18635,7 +18635,7 @@
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="637">
@@ -18655,7 +18655,7 @@
         <v>678</v>
       </c>
       <c r="F637" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
       <c r="G637" t="n">
         <v>1.0</v>
@@ -18681,7 +18681,7 @@
         <v>678</v>
       </c>
       <c r="F638" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -18785,7 +18785,7 @@
         <v>679</v>
       </c>
       <c r="F642" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -18837,7 +18837,7 @@
         <v>678</v>
       </c>
       <c r="F644" t="n">
-        <v>106.0</v>
+        <v>109.0</v>
       </c>
       <c r="G644" t="n">
         <v>0.0</v>
@@ -18863,7 +18863,7 @@
         <v>678</v>
       </c>
       <c r="F645" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G645" t="n">
         <v>0.0</v>
@@ -18993,7 +18993,7 @@
         <v>679</v>
       </c>
       <c r="F650" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G650" t="n">
         <v>0.0</v>
@@ -19019,7 +19019,7 @@
         <v>679</v>
       </c>
       <c r="F651" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -19123,7 +19123,7 @@
         <v>679</v>
       </c>
       <c r="F655" t="n">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19279,7 +19279,7 @@
         <v>679</v>
       </c>
       <c r="F661" t="n">
-        <v>94.0</v>
+        <v>97.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19305,7 +19305,7 @@
         <v>679</v>
       </c>
       <c r="F662" t="n">
-        <v>123.0</v>
+        <v>125.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19331,7 +19331,7 @@
         <v>679</v>
       </c>
       <c r="F663" t="n">
-        <v>141.0</v>
+        <v>144.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19357,7 +19357,7 @@
         <v>679</v>
       </c>
       <c r="F664" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G664" t="n">
         <v>0.0</v>
@@ -19383,7 +19383,7 @@
         <v>678</v>
       </c>
       <c r="F665" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G665" t="n">
         <v>0.0</v>
@@ -19409,7 +19409,7 @@
         <v>679</v>
       </c>
       <c r="F666" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -19545,7 +19545,7 @@
         <v>1.0</v>
       </c>
       <c r="H671" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="672">
@@ -19643,7 +19643,7 @@
         <v>679</v>
       </c>
       <c r="F675" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="G675" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2411,7 +2411,7 @@
         <v>0.0</v>
       </c>
       <c r="H12" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="13">
@@ -2431,7 +2431,7 @@
         <v>678</v>
       </c>
       <c r="F13" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -5031,7 +5031,7 @@
         <v>678</v>
       </c>
       <c r="F113" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -5057,7 +5057,7 @@
         <v>678</v>
       </c>
       <c r="F114" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -6019,7 +6019,7 @@
         <v>678</v>
       </c>
       <c r="F151" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G151" t="n">
         <v>0.0</v>
@@ -8879,7 +8879,7 @@
         <v>678</v>
       </c>
       <c r="F261" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G261" t="n">
         <v>0.0</v>
@@ -9113,7 +9113,7 @@
         <v>678</v>
       </c>
       <c r="F270" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="G270" t="n">
         <v>2.0</v>
@@ -10939,7 +10939,7 @@
         <v>0.0</v>
       </c>
       <c r="H340" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="341">
@@ -11063,7 +11063,7 @@
         <v>678</v>
       </c>
       <c r="F345" t="n">
-        <v>525.0</v>
+        <v>527.0</v>
       </c>
       <c r="G345" t="n">
         <v>6.0</v>
@@ -11947,7 +11947,7 @@
         <v>678</v>
       </c>
       <c r="F379" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G379" t="n">
         <v>7.0</v>
@@ -12077,7 +12077,7 @@
         <v>678</v>
       </c>
       <c r="F384" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="G384" t="n">
         <v>1.0</v>
@@ -13143,7 +13143,7 @@
         <v>678</v>
       </c>
       <c r="F425" t="n">
-        <v>552.0</v>
+        <v>555.0</v>
       </c>
       <c r="G425" t="n">
         <v>3.0</v>
@@ -13715,7 +13715,7 @@
         <v>680</v>
       </c>
       <c r="F447" t="n">
-        <v>523.0</v>
+        <v>524.0</v>
       </c>
       <c r="G447" t="n">
         <v>3.0</v>
@@ -14911,13 +14911,13 @@
         <v>678</v>
       </c>
       <c r="F493" t="n">
-        <v>2357.0</v>
+        <v>2359.0</v>
       </c>
       <c r="G493" t="n">
         <v>45.0</v>
       </c>
       <c r="H493" t="n">
-        <v>303.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="494">
@@ -16055,7 +16055,7 @@
         <v>678</v>
       </c>
       <c r="F537" t="n">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16627,7 +16627,7 @@
         <v>678</v>
       </c>
       <c r="F559" t="n">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="G559" t="n">
         <v>1.0</v>
@@ -18583,7 +18583,7 @@
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="635">
@@ -18635,7 +18635,7 @@
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="637">
@@ -19227,7 +19227,7 @@
         <v>678</v>
       </c>
       <c r="F659" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -19545,7 +19545,7 @@
         <v>1.0</v>
       </c>
       <c r="H671" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="672">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2145,7 +2145,7 @@
         <v>678</v>
       </c>
       <c r="F2" t="n">
-        <v>573.0</v>
+        <v>574.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2457,7 +2457,7 @@
         <v>678</v>
       </c>
       <c r="F14" t="n">
-        <v>452.0</v>
+        <v>456.0</v>
       </c>
       <c r="G14" t="n">
         <v>9.0</v>
@@ -2665,7 +2665,7 @@
         <v>679</v>
       </c>
       <c r="F22" t="n">
-        <v>349.0</v>
+        <v>351.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2951,7 +2951,7 @@
         <v>678</v>
       </c>
       <c r="F33" t="n">
-        <v>491.0</v>
+        <v>495.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -3578,7 +3578,7 @@
         <v>171.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H57" t="n">
         <v>15.0</v>
@@ -3783,7 +3783,7 @@
         <v>679</v>
       </c>
       <c r="F65" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>678</v>
       </c>
       <c r="F70" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -3991,7 +3991,7 @@
         <v>679</v>
       </c>
       <c r="F73" t="n">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4407,7 +4407,7 @@
         <v>678</v>
       </c>
       <c r="F89" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -4589,7 +4589,7 @@
         <v>679</v>
       </c>
       <c r="F96" t="n">
-        <v>413.0</v>
+        <v>417.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -4693,7 +4693,7 @@
         <v>678</v>
       </c>
       <c r="F100" t="n">
-        <v>496.0</v>
+        <v>499.0</v>
       </c>
       <c r="G100" t="n">
         <v>3.0</v>
@@ -5109,7 +5109,7 @@
         <v>680</v>
       </c>
       <c r="F116" t="n">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -5161,7 +5161,7 @@
         <v>678</v>
       </c>
       <c r="F118" t="n">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -5629,7 +5629,7 @@
         <v>678</v>
       </c>
       <c r="F136" t="n">
-        <v>649.0</v>
+        <v>652.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -5915,7 +5915,7 @@
         <v>678</v>
       </c>
       <c r="F147" t="n">
-        <v>209.0</v>
+        <v>211.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -6253,7 +6253,7 @@
         <v>679</v>
       </c>
       <c r="F160" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -6513,7 +6513,7 @@
         <v>679</v>
       </c>
       <c r="F170" t="n">
-        <v>503.0</v>
+        <v>504.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6747,7 +6747,7 @@
         <v>679</v>
       </c>
       <c r="F179" t="n">
-        <v>661.0</v>
+        <v>664.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -8021,7 +8021,7 @@
         <v>678</v>
       </c>
       <c r="F228" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G228" t="n">
         <v>1.0</v>
@@ -8128,7 +8128,7 @@
         <v>146.0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H232" t="n">
         <v>1.0</v>
@@ -8749,7 +8749,7 @@
         <v>678</v>
       </c>
       <c r="F256" t="n">
-        <v>610.0</v>
+        <v>611.0</v>
       </c>
       <c r="G256" t="n">
         <v>0.0</v>
@@ -8963,7 +8963,7 @@
         <v>0.0</v>
       </c>
       <c r="H264" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="265">
@@ -9243,7 +9243,7 @@
         <v>678</v>
       </c>
       <c r="F275" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -10491,7 +10491,7 @@
         <v>678</v>
       </c>
       <c r="F323" t="n">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="G323" t="n">
         <v>0.0</v>
@@ -11739,7 +11739,7 @@
         <v>678</v>
       </c>
       <c r="F371" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="G371" t="n">
         <v>0.0</v>
@@ -12311,13 +12311,13 @@
         <v>678</v>
       </c>
       <c r="F393" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="G393" t="n">
         <v>9.0</v>
       </c>
       <c r="H393" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="394">
@@ -12551,7 +12551,7 @@
         <v>0.0</v>
       </c>
       <c r="H402" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="403">
@@ -13247,7 +13247,7 @@
         <v>678</v>
       </c>
       <c r="F429" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G429" t="n">
         <v>0.0</v>
@@ -13585,7 +13585,7 @@
         <v>678</v>
       </c>
       <c r="F442" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G442" t="n">
         <v>0.0</v>
@@ -14157,7 +14157,7 @@
         <v>678</v>
       </c>
       <c r="F464" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G464" t="n">
         <v>1.0</v>
@@ -15535,7 +15535,7 @@
         <v>678</v>
       </c>
       <c r="F517" t="n">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -15665,7 +15665,7 @@
         <v>679</v>
       </c>
       <c r="F522" t="n">
-        <v>257.0</v>
+        <v>259.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -15876,7 +15876,7 @@
         <v>411.0</v>
       </c>
       <c r="G530" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H530" t="n">
         <v>2.0</v>
@@ -15899,7 +15899,7 @@
         <v>680</v>
       </c>
       <c r="F531" t="n">
-        <v>203.0</v>
+        <v>205.0</v>
       </c>
       <c r="G531" t="n">
         <v>0.0</v>
@@ -16159,7 +16159,7 @@
         <v>679</v>
       </c>
       <c r="F541" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G541" t="n">
         <v>0.0</v>
@@ -17303,7 +17303,7 @@
         <v>678</v>
       </c>
       <c r="F585" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17589,7 +17589,7 @@
         <v>678</v>
       </c>
       <c r="F596" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
       <c r="G596" t="n">
         <v>2.0</v>
@@ -18343,7 +18343,7 @@
         <v>679</v>
       </c>
       <c r="F625" t="n">
-        <v>91.0</v>
+        <v>98.0</v>
       </c>
       <c r="G625" t="n">
         <v>0.0</v>
@@ -18840,7 +18840,7 @@
         <v>109.0</v>
       </c>
       <c r="G644" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H644" t="n">
         <v>0.0</v>
@@ -18993,7 +18993,7 @@
         <v>679</v>
       </c>
       <c r="F650" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="G650" t="n">
         <v>0.0</v>
@@ -19305,7 +19305,7 @@
         <v>679</v>
       </c>
       <c r="F662" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19331,7 +19331,7 @@
         <v>679</v>
       </c>
       <c r="F663" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19383,7 +19383,7 @@
         <v>678</v>
       </c>
       <c r="F665" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G665" t="n">
         <v>0.0</v>
@@ -19409,7 +19409,7 @@
         <v>679</v>
       </c>
       <c r="F666" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -19591,7 +19591,7 @@
         <v>678</v>
       </c>
       <c r="F673" t="n">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="G673" t="n">
         <v>2.0</v>
@@ -19617,7 +19617,7 @@
         <v>679</v>
       </c>
       <c r="F674" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19643,7 +19643,7 @@
         <v>679</v>
       </c>
       <c r="F675" t="n">
-        <v>379.0</v>
+        <v>380.0</v>
       </c>
       <c r="G675" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3055,7 +3055,7 @@
         <v>679</v>
       </c>
       <c r="F37" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3289,7 +3289,7 @@
         <v>678</v>
       </c>
       <c r="F46" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -3809,7 +3809,7 @@
         <v>678</v>
       </c>
       <c r="F66" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G66" t="n">
         <v>3.0</v>
@@ -3965,7 +3965,7 @@
         <v>678</v>
       </c>
       <c r="F72" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -5346,7 +5346,7 @@
         <v>282.0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -10231,7 +10231,7 @@
         <v>678</v>
       </c>
       <c r="F313" t="n">
-        <v>44.0</v>
+        <v>52.0</v>
       </c>
       <c r="G313" t="n">
         <v>1.0</v>
@@ -10569,10 +10569,10 @@
         <v>678</v>
       </c>
       <c r="F326" t="n">
-        <v>186.0</v>
+        <v>189.0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H326" t="n">
         <v>1.0</v>
@@ -11716,7 +11716,7 @@
         <v>115.0</v>
       </c>
       <c r="G370" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H370" t="n">
         <v>0.0</v>
@@ -13143,7 +13143,7 @@
         <v>678</v>
       </c>
       <c r="F425" t="n">
-        <v>555.0</v>
+        <v>556.0</v>
       </c>
       <c r="G425" t="n">
         <v>3.0</v>
@@ -13715,7 +13715,7 @@
         <v>680</v>
       </c>
       <c r="F447" t="n">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="G447" t="n">
         <v>3.0</v>
@@ -14131,7 +14131,7 @@
         <v>678</v>
       </c>
       <c r="F463" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G463" t="n">
         <v>0.0</v>
@@ -16783,7 +16783,7 @@
         <v>678</v>
       </c>
       <c r="F565" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -17329,7 +17329,7 @@
         <v>678</v>
       </c>
       <c r="F586" t="n">
-        <v>64.0</v>
+        <v>70.0</v>
       </c>
       <c r="G586" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3991,7 +3991,7 @@
         <v>679</v>
       </c>
       <c r="F73" t="n">
-        <v>349.0</v>
+        <v>351.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4407,7 +4407,7 @@
         <v>678</v>
       </c>
       <c r="F89" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -6019,7 +6019,7 @@
         <v>678</v>
       </c>
       <c r="F151" t="n">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="G151" t="n">
         <v>0.0</v>
@@ -6415,7 +6415,7 @@
         <v>0.0</v>
       </c>
       <c r="H166" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="167">
@@ -6747,7 +6747,7 @@
         <v>679</v>
       </c>
       <c r="F179" t="n">
-        <v>664.0</v>
+        <v>668.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -6877,7 +6877,7 @@
         <v>678</v>
       </c>
       <c r="F184" t="n">
-        <v>320.0</v>
+        <v>322.0</v>
       </c>
       <c r="G184" t="n">
         <v>2.0</v>
@@ -7917,7 +7917,7 @@
         <v>678</v>
       </c>
       <c r="F224" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G224" t="n">
         <v>0.0</v>
@@ -8385,7 +8385,7 @@
         <v>678</v>
       </c>
       <c r="F242" t="n">
-        <v>936.0</v>
+        <v>937.0</v>
       </c>
       <c r="G242" t="n">
         <v>16.0</v>
@@ -9217,7 +9217,7 @@
         <v>678</v>
       </c>
       <c r="F274" t="n">
-        <v>536.0</v>
+        <v>538.0</v>
       </c>
       <c r="G274" t="n">
         <v>6.0</v>
@@ -9477,7 +9477,7 @@
         <v>678</v>
       </c>
       <c r="F284" t="n">
-        <v>15.0</v>
+        <v>22.0</v>
       </c>
       <c r="G284" t="n">
         <v>0.0</v>
@@ -9737,7 +9737,7 @@
         <v>678</v>
       </c>
       <c r="F294" t="n">
-        <v>1001.0</v>
+        <v>1002.0</v>
       </c>
       <c r="G294" t="n">
         <v>5.0</v>
@@ -9763,7 +9763,7 @@
         <v>678</v>
       </c>
       <c r="F295" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G295" t="n">
         <v>0.0</v>
@@ -10523,7 +10523,7 @@
         <v>0.0</v>
       </c>
       <c r="H324" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="325">
@@ -11661,7 +11661,7 @@
         <v>679</v>
       </c>
       <c r="F368" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -11947,7 +11947,7 @@
         <v>678</v>
       </c>
       <c r="F379" t="n">
-        <v>189.0</v>
+        <v>195.0</v>
       </c>
       <c r="G379" t="n">
         <v>7.0</v>
@@ -13247,7 +13247,7 @@
         <v>678</v>
       </c>
       <c r="F429" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G429" t="n">
         <v>0.0</v>
@@ -13637,7 +13637,7 @@
         <v>678</v>
       </c>
       <c r="F444" t="n">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
@@ -14833,7 +14833,7 @@
         <v>678</v>
       </c>
       <c r="F490" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
       <c r="G490" t="n">
         <v>2.0</v>
@@ -14911,7 +14911,7 @@
         <v>678</v>
       </c>
       <c r="F493" t="n">
-        <v>2359.0</v>
+        <v>2371.0</v>
       </c>
       <c r="G493" t="n">
         <v>45.0</v>
@@ -14937,7 +14937,7 @@
         <v>678</v>
       </c>
       <c r="F494" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G494" t="n">
         <v>1.0</v>
@@ -15353,7 +15353,7 @@
         <v>678</v>
       </c>
       <c r="F510" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="G510" t="n">
         <v>0.0</v>
@@ -15613,7 +15613,7 @@
         <v>678</v>
       </c>
       <c r="F520" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G520" t="n">
         <v>0.0</v>
@@ -15665,7 +15665,7 @@
         <v>679</v>
       </c>
       <c r="F522" t="n">
-        <v>259.0</v>
+        <v>261.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -16523,7 +16523,7 @@
         <v>679</v>
       </c>
       <c r="F555" t="n">
-        <v>275.0</v>
+        <v>277.0</v>
       </c>
       <c r="G555" t="n">
         <v>0.0</v>
@@ -17251,7 +17251,7 @@
         <v>678</v>
       </c>
       <c r="F583" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="G583" t="n">
         <v>3.0</v>
@@ -18635,7 +18635,7 @@
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="637">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2145,7 +2145,7 @@
         <v>678</v>
       </c>
       <c r="F2" t="n">
-        <v>574.0</v>
+        <v>580.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2509,7 +2509,7 @@
         <v>678</v>
       </c>
       <c r="F16" t="n">
-        <v>391.0</v>
+        <v>392.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2665,7 +2665,7 @@
         <v>679</v>
       </c>
       <c r="F22" t="n">
-        <v>351.0</v>
+        <v>353.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2977,7 +2977,7 @@
         <v>678</v>
       </c>
       <c r="F34" t="n">
-        <v>185.0</v>
+        <v>187.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -3055,7 +3055,7 @@
         <v>679</v>
       </c>
       <c r="F37" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3081,7 +3081,7 @@
         <v>678</v>
       </c>
       <c r="F38" t="n">
-        <v>314.0</v>
+        <v>321.0</v>
       </c>
       <c r="G38" t="n">
         <v>1.0</v>
@@ -3107,7 +3107,7 @@
         <v>678</v>
       </c>
       <c r="F39" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3217,7 +3217,7 @@
         <v>3.0</v>
       </c>
       <c r="H43" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="44">
@@ -3783,7 +3783,7 @@
         <v>679</v>
       </c>
       <c r="F65" t="n">
-        <v>181.0</v>
+        <v>183.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>678</v>
       </c>
       <c r="F70" t="n">
-        <v>126.0</v>
+        <v>128.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -4095,7 +4095,7 @@
         <v>678</v>
       </c>
       <c r="F77" t="n">
-        <v>182.0</v>
+        <v>185.0</v>
       </c>
       <c r="G77" t="n">
         <v>15.0</v>
@@ -4589,7 +4589,7 @@
         <v>679</v>
       </c>
       <c r="F96" t="n">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -4745,7 +4745,7 @@
         <v>678</v>
       </c>
       <c r="F102" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>
@@ -4823,7 +4823,7 @@
         <v>679</v>
       </c>
       <c r="F105" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -4855,7 +4855,7 @@
         <v>0.0</v>
       </c>
       <c r="H106" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="107">
@@ -5161,7 +5161,7 @@
         <v>678</v>
       </c>
       <c r="F118" t="n">
-        <v>448.0</v>
+        <v>449.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -5213,7 +5213,7 @@
         <v>678</v>
       </c>
       <c r="F120" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -5499,7 +5499,7 @@
         <v>678</v>
       </c>
       <c r="F131" t="n">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
@@ -5629,7 +5629,7 @@
         <v>678</v>
       </c>
       <c r="F136" t="n">
-        <v>652.0</v>
+        <v>654.0</v>
       </c>
       <c r="G136" t="n">
         <v>2.0</v>
@@ -5733,7 +5733,7 @@
         <v>678</v>
       </c>
       <c r="F140" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G140" t="n">
         <v>0.0</v>
@@ -5915,7 +5915,7 @@
         <v>678</v>
       </c>
       <c r="F147" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -6487,7 +6487,7 @@
         <v>678</v>
       </c>
       <c r="F169" t="n">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6513,7 +6513,7 @@
         <v>679</v>
       </c>
       <c r="F170" t="n">
-        <v>504.0</v>
+        <v>508.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6591,7 +6591,7 @@
         <v>679</v>
       </c>
       <c r="F173" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G173" t="n">
         <v>0.0</v>
@@ -6623,7 +6623,7 @@
         <v>1.0</v>
       </c>
       <c r="H174" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="175">
@@ -7215,7 +7215,7 @@
         <v>679</v>
       </c>
       <c r="F197" t="n">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="G197" t="n">
         <v>0.0</v>
@@ -7839,7 +7839,7 @@
         <v>679</v>
       </c>
       <c r="F221" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8645,7 +8645,7 @@
         <v>678</v>
       </c>
       <c r="F252" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G252" t="n">
         <v>0.0</v>
@@ -9867,7 +9867,7 @@
         <v>678</v>
       </c>
       <c r="F299" t="n">
-        <v>487.0</v>
+        <v>491.0</v>
       </c>
       <c r="G299" t="n">
         <v>6.0</v>
@@ -10939,7 +10939,7 @@
         <v>0.0</v>
       </c>
       <c r="H340" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="341">
@@ -11115,7 +11115,7 @@
         <v>678</v>
       </c>
       <c r="F347" t="n">
-        <v>98.0</v>
+        <v>101.0</v>
       </c>
       <c r="G347" t="n">
         <v>7.0</v>
@@ -11739,7 +11739,7 @@
         <v>678</v>
       </c>
       <c r="F371" t="n">
-        <v>242.0</v>
+        <v>244.0</v>
       </c>
       <c r="G371" t="n">
         <v>0.0</v>
@@ -12311,7 +12311,7 @@
         <v>678</v>
       </c>
       <c r="F393" t="n">
-        <v>293.0</v>
+        <v>295.0</v>
       </c>
       <c r="G393" t="n">
         <v>9.0</v>
@@ -13143,7 +13143,7 @@
         <v>678</v>
       </c>
       <c r="F425" t="n">
-        <v>556.0</v>
+        <v>559.0</v>
       </c>
       <c r="G425" t="n">
         <v>3.0</v>
@@ -13793,7 +13793,7 @@
         <v>678</v>
       </c>
       <c r="F450" t="n">
-        <v>172.0</v>
+        <v>174.0</v>
       </c>
       <c r="G450" t="n">
         <v>7.0</v>
@@ -14131,7 +14131,7 @@
         <v>678</v>
       </c>
       <c r="F463" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G463" t="n">
         <v>0.0</v>
@@ -14157,7 +14157,7 @@
         <v>678</v>
       </c>
       <c r="F464" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="G464" t="n">
         <v>1.0</v>
@@ -14521,7 +14521,7 @@
         <v>678</v>
       </c>
       <c r="F478" t="n">
-        <v>583.0</v>
+        <v>585.0</v>
       </c>
       <c r="G478" t="n">
         <v>2.0</v>
@@ -14865,7 +14865,7 @@
         <v>0.0</v>
       </c>
       <c r="H491" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="492">
@@ -14917,7 +14917,7 @@
         <v>45.0</v>
       </c>
       <c r="H493" t="n">
-        <v>304.0</v>
+        <v>305.0</v>
       </c>
     </row>
     <row r="494">
@@ -15873,10 +15873,10 @@
         <v>678</v>
       </c>
       <c r="F530" t="n">
-        <v>411.0</v>
+        <v>412.0</v>
       </c>
       <c r="G530" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H530" t="n">
         <v>2.0</v>
@@ -16295,7 +16295,7 @@
         <v>0.0</v>
       </c>
       <c r="H546" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="547">
@@ -16627,7 +16627,7 @@
         <v>678</v>
       </c>
       <c r="F559" t="n">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
       <c r="G559" t="n">
         <v>1.0</v>
@@ -16705,7 +16705,7 @@
         <v>678</v>
       </c>
       <c r="F562" t="n">
-        <v>307.0</v>
+        <v>309.0</v>
       </c>
       <c r="G562" t="n">
         <v>0.0</v>
@@ -16965,7 +16965,7 @@
         <v>679</v>
       </c>
       <c r="F572" t="n">
-        <v>89.0</v>
+        <v>93.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
@@ -17173,7 +17173,7 @@
         <v>679</v>
       </c>
       <c r="F580" t="n">
-        <v>382.0</v>
+        <v>384.0</v>
       </c>
       <c r="G580" t="n">
         <v>0.0</v>
@@ -17693,7 +17693,7 @@
         <v>678</v>
       </c>
       <c r="F600" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -18343,7 +18343,7 @@
         <v>679</v>
       </c>
       <c r="F625" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
       <c r="G625" t="n">
         <v>0.0</v>
@@ -18583,7 +18583,7 @@
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="635">
@@ -18635,7 +18635,7 @@
         <v>0.0</v>
       </c>
       <c r="H636" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="637">
@@ -18993,7 +18993,7 @@
         <v>679</v>
       </c>
       <c r="F650" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="G650" t="n">
         <v>0.0</v>
@@ -19071,7 +19071,7 @@
         <v>679</v>
       </c>
       <c r="F653" t="n">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
       <c r="G653" t="n">
         <v>0.0</v>
@@ -19097,7 +19097,7 @@
         <v>679</v>
       </c>
       <c r="F654" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19279,7 +19279,7 @@
         <v>679</v>
       </c>
       <c r="F661" t="n">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19305,7 +19305,7 @@
         <v>679</v>
       </c>
       <c r="F662" t="n">
-        <v>126.0</v>
+        <v>129.0</v>
       </c>
       <c r="G662" t="n">
         <v>0.0</v>
@@ -19357,7 +19357,7 @@
         <v>679</v>
       </c>
       <c r="F664" t="n">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
       <c r="G664" t="n">
         <v>0.0</v>
@@ -19461,7 +19461,7 @@
         <v>678</v>
       </c>
       <c r="F668" t="n">
-        <v>105.0</v>
+        <v>108.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -19617,7 +19617,7 @@
         <v>679</v>
       </c>
       <c r="F674" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19643,7 +19643,7 @@
         <v>679</v>
       </c>
       <c r="F675" t="n">
-        <v>380.0</v>
+        <v>382.0</v>
       </c>
       <c r="G675" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -32,10 +32,10 @@
     <t>Negativo</t>
   </si>
   <si>
+    <t>Positivo</t>
+  </si>
+  <si>
     <t>Non idoneo</t>
-  </si>
-  <si>
-    <t>Positivo</t>
   </si>
   <si>
     <t>EMILIA ROMAGNA</t>
@@ -2148,10 +2148,10 @@
         <v>580.0</v>
       </c>
       <c r="G2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H2" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -2174,10 +2174,10 @@
         <v>59.0</v>
       </c>
       <c r="G3" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="H3" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>42.0</v>
       </c>
     </row>
     <row r="4">
@@ -2200,10 +2200,10 @@
         <v>90.0</v>
       </c>
       <c r="G4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -2226,10 +2226,10 @@
         <v>124.0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -2252,10 +2252,10 @@
         <v>30.0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H6" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -2278,10 +2278,10 @@
         <v>97.0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="H7" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -2330,10 +2330,10 @@
         <v>14.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -2356,10 +2356,10 @@
         <v>21.0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H10" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -2379,13 +2379,13 @@
         <v>678</v>
       </c>
       <c r="F11" t="n">
-        <v>298.0</v>
+        <v>299.0</v>
       </c>
       <c r="G11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H11" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -2408,10 +2408,10 @@
         <v>0.0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="H12" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -2457,13 +2457,13 @@
         <v>678</v>
       </c>
       <c r="F14" t="n">
-        <v>456.0</v>
+        <v>459.0</v>
       </c>
       <c r="G14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H14" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="15">
@@ -2486,10 +2486,10 @@
         <v>235.0</v>
       </c>
       <c r="G15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H15" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="16">
@@ -2509,13 +2509,13 @@
         <v>678</v>
       </c>
       <c r="F16" t="n">
-        <v>392.0</v>
+        <v>394.0</v>
       </c>
       <c r="G16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -2590,10 +2590,10 @@
         <v>4.0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>1191.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1191.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -2616,10 +2616,10 @@
         <v>145.0</v>
       </c>
       <c r="G20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -2642,10 +2642,10 @@
         <v>76.0</v>
       </c>
       <c r="G21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H21" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -2665,7 +2665,7 @@
         <v>679</v>
       </c>
       <c r="F22" t="n">
-        <v>353.0</v>
+        <v>355.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2772,10 +2772,10 @@
         <v>10.0</v>
       </c>
       <c r="G26" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H26" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="27">
@@ -2798,10 +2798,10 @@
         <v>11.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -2824,10 +2824,10 @@
         <v>39.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -2876,10 +2876,10 @@
         <v>118.0</v>
       </c>
       <c r="G30" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H30" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="31">
@@ -2902,10 +2902,10 @@
         <v>21.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H31" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -2928,10 +2928,10 @@
         <v>203.0</v>
       </c>
       <c r="G32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H32" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -2951,13 +2951,13 @@
         <v>678</v>
       </c>
       <c r="F33" t="n">
-        <v>495.0</v>
+        <v>499.0</v>
       </c>
       <c r="G33" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H33" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>5.0</v>
       </c>
     </row>
     <row r="34">
@@ -3006,10 +3006,10 @@
         <v>0.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="H35" t="n">
-        <v>33.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -3084,10 +3084,10 @@
         <v>321.0</v>
       </c>
       <c r="G38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H38" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -3110,10 +3110,10 @@
         <v>65.0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H39" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -3136,10 +3136,10 @@
         <v>146.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H40" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -3162,10 +3162,10 @@
         <v>45.0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="H41" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -3188,10 +3188,10 @@
         <v>59.0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -3214,10 +3214,10 @@
         <v>287.0</v>
       </c>
       <c r="G43" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H43" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="44">
@@ -3240,10 +3240,10 @@
         <v>182.0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H44" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -3266,10 +3266,10 @@
         <v>31.0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -3318,10 +3318,10 @@
         <v>102.0</v>
       </c>
       <c r="G47" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H47" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>8.0</v>
       </c>
     </row>
     <row r="48">
@@ -3370,10 +3370,10 @@
         <v>21.0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -3396,10 +3396,10 @@
         <v>199.0</v>
       </c>
       <c r="G50" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H50" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -3422,10 +3422,10 @@
         <v>122.0</v>
       </c>
       <c r="G51" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="H51" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>52.0</v>
       </c>
     </row>
     <row r="52">
@@ -3448,10 +3448,10 @@
         <v>82.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H52" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -3526,10 +3526,10 @@
         <v>268.0</v>
       </c>
       <c r="G55" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H55" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>8.0</v>
       </c>
     </row>
     <row r="56">
@@ -3578,10 +3578,10 @@
         <v>171.0</v>
       </c>
       <c r="G57" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="H57" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>15.0</v>
       </c>
     </row>
     <row r="58">
@@ -3604,10 +3604,10 @@
         <v>27.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
       <c r="H58" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -3656,10 +3656,10 @@
         <v>24.0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H60" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -3783,7 +3783,7 @@
         <v>679</v>
       </c>
       <c r="F65" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -3812,10 +3812,10 @@
         <v>150.0</v>
       </c>
       <c r="G66" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="H66" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>18.0</v>
       </c>
     </row>
     <row r="67">
@@ -3864,10 +3864,10 @@
         <v>35.0</v>
       </c>
       <c r="G68" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="H68" t="n">
         <v>31.0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>27.0</v>
       </c>
     </row>
     <row r="69">
@@ -3968,10 +3968,10 @@
         <v>147.0</v>
       </c>
       <c r="G72" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H72" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -3994,10 +3994,10 @@
         <v>351.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -4020,10 +4020,10 @@
         <v>350.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -4098,10 +4098,10 @@
         <v>185.0</v>
       </c>
       <c r="G77" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="H77" t="n">
         <v>15.0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>81.0</v>
       </c>
     </row>
     <row r="78">
@@ -4150,10 +4150,10 @@
         <v>38.0</v>
       </c>
       <c r="G79" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H79" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -4176,10 +4176,10 @@
         <v>34.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H80" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -4202,10 +4202,10 @@
         <v>41.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H81" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -4254,10 +4254,10 @@
         <v>63.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H83" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -4280,10 +4280,10 @@
         <v>73.0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H84" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -4306,10 +4306,10 @@
         <v>110.0</v>
       </c>
       <c r="G85" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H85" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>16.0</v>
       </c>
     </row>
     <row r="86">
@@ -4358,10 +4358,10 @@
         <v>468.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H87" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -4410,10 +4410,10 @@
         <v>135.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H89" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -4462,10 +4462,10 @@
         <v>16.0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H91" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="92">
@@ -4514,10 +4514,10 @@
         <v>47.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="H93" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -4566,10 +4566,10 @@
         <v>51.0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H95" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -4589,7 +4589,7 @@
         <v>679</v>
       </c>
       <c r="F96" t="n">
-        <v>418.0</v>
+        <v>421.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -4618,10 +4618,10 @@
         <v>25.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="H97" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="98">
@@ -4670,10 +4670,10 @@
         <v>39.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -4693,13 +4693,13 @@
         <v>678</v>
       </c>
       <c r="F100" t="n">
-        <v>499.0</v>
+        <v>501.0</v>
       </c>
       <c r="G100" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H100" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="101">
@@ -4722,10 +4722,10 @@
         <v>9.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H101" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -4748,10 +4748,10 @@
         <v>84.0</v>
       </c>
       <c r="G102" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H102" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="103">
@@ -4774,10 +4774,10 @@
         <v>38.0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H103" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -4852,10 +4852,10 @@
         <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H106" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -4904,10 +4904,10 @@
         <v>74.0</v>
       </c>
       <c r="G108" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H108" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="109">
@@ -4927,13 +4927,13 @@
         <v>678</v>
       </c>
       <c r="F109" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G109" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="H109" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>24.0</v>
       </c>
     </row>
     <row r="110">
@@ -4956,10 +4956,10 @@
         <v>240.0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H110" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -4982,10 +4982,10 @@
         <v>0.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="H111" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
@@ -5086,10 +5086,10 @@
         <v>34.0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H115" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -5112,10 +5112,10 @@
         <v>409.0</v>
       </c>
       <c r="G116" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H116" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="117">
@@ -5138,10 +5138,10 @@
         <v>16.0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="H117" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -5164,10 +5164,10 @@
         <v>449.0</v>
       </c>
       <c r="G118" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H118" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>12.0</v>
       </c>
     </row>
     <row r="119">
@@ -5216,10 +5216,10 @@
         <v>250.0</v>
       </c>
       <c r="G120" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H120" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -5242,10 +5242,10 @@
         <v>118.0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H121" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -5294,10 +5294,10 @@
         <v>222.0</v>
       </c>
       <c r="G123" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H123" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="124">
@@ -5320,10 +5320,10 @@
         <v>79.0</v>
       </c>
       <c r="G124" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H124" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="125">
@@ -5343,13 +5343,13 @@
         <v>679</v>
       </c>
       <c r="F125" t="n">
-        <v>282.0</v>
+        <v>283.0</v>
       </c>
       <c r="G125" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H125" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="126">
@@ -5372,10 +5372,10 @@
         <v>101.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H126" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -5398,10 +5398,10 @@
         <v>74.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H127" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -5476,10 +5476,10 @@
         <v>64.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H130" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -5528,10 +5528,10 @@
         <v>110.0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H132" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="133">
@@ -5554,10 +5554,10 @@
         <v>132.0</v>
       </c>
       <c r="G133" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H133" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="134">
@@ -5580,10 +5580,10 @@
         <v>63.0</v>
       </c>
       <c r="G134" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="H134" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>25.0</v>
       </c>
     </row>
     <row r="135">
@@ -5606,10 +5606,10 @@
         <v>35.0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H135" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="136">
@@ -5658,10 +5658,10 @@
         <v>43.0</v>
       </c>
       <c r="G137" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H137" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="138">
@@ -5710,10 +5710,10 @@
         <v>273.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="H139" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="140">
@@ -5736,10 +5736,10 @@
         <v>48.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H140" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="141">
@@ -5762,10 +5762,10 @@
         <v>194.0</v>
       </c>
       <c r="G141" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H141" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="142">
@@ -5837,7 +5837,7 @@
         <v>679</v>
       </c>
       <c r="F144" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -5866,10 +5866,10 @@
         <v>140.0</v>
       </c>
       <c r="G145" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H145" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="146">
@@ -5918,10 +5918,10 @@
         <v>212.0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H147" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="148">
@@ -5996,10 +5996,10 @@
         <v>62.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H150" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="151">
@@ -6022,10 +6022,10 @@
         <v>35.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H151" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="152">
@@ -6126,10 +6126,10 @@
         <v>60.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="H155" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="156">
@@ -6152,10 +6152,10 @@
         <v>341.0</v>
       </c>
       <c r="G156" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H156" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="157">
@@ -6178,10 +6178,10 @@
         <v>53.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H157" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="158">
@@ -6230,10 +6230,10 @@
         <v>8.0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="160">
@@ -6253,13 +6253,13 @@
         <v>679</v>
       </c>
       <c r="F160" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H160" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="161">
@@ -6282,10 +6282,10 @@
         <v>64.0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H161" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="162">
@@ -6308,7 +6308,7 @@
         <v>312.0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H162" t="n">
         <v>1.0</v>
@@ -6360,10 +6360,10 @@
         <v>247.0</v>
       </c>
       <c r="G164" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="H164" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H164" t="n">
-        <v>56.0</v>
       </c>
     </row>
     <row r="165">
@@ -6386,10 +6386,10 @@
         <v>102.0</v>
       </c>
       <c r="G165" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H165" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="166">
@@ -6412,10 +6412,10 @@
         <v>19.0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="H166" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="167">
@@ -6438,10 +6438,10 @@
         <v>94.0</v>
       </c>
       <c r="G167" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H167" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="168">
@@ -6487,13 +6487,13 @@
         <v>678</v>
       </c>
       <c r="F169" t="n">
-        <v>271.0</v>
+        <v>272.0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H169" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="170">
@@ -6568,10 +6568,10 @@
         <v>104.0</v>
       </c>
       <c r="G172" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="H172" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H172" t="n">
-        <v>40.0</v>
       </c>
     </row>
     <row r="173">
@@ -6620,10 +6620,10 @@
         <v>120.0</v>
       </c>
       <c r="G174" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="H174" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H174" t="n">
-        <v>17.0</v>
       </c>
     </row>
     <row r="175">
@@ -6646,10 +6646,10 @@
         <v>14.0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H175" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="176">
@@ -6698,10 +6698,10 @@
         <v>63.0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H177" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="178">
@@ -6750,10 +6750,10 @@
         <v>668.0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H179" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="180">
@@ -6854,10 +6854,10 @@
         <v>162.0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H183" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="184">
@@ -6880,10 +6880,10 @@
         <v>322.0</v>
       </c>
       <c r="G184" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H184" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="185">
@@ -6932,10 +6932,10 @@
         <v>0.0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H186" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="187">
@@ -6984,10 +6984,10 @@
         <v>271.0</v>
       </c>
       <c r="G188" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H188" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H188" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="189">
@@ -7059,13 +7059,13 @@
         <v>679</v>
       </c>
       <c r="F191" t="n">
-        <v>1000.0</v>
+        <v>1004.0</v>
       </c>
       <c r="G191" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H191" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H191" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="192">
@@ -7088,10 +7088,10 @@
         <v>21.0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H192" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="193">
@@ -7140,10 +7140,10 @@
         <v>97.0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H194" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="195">
@@ -7166,10 +7166,10 @@
         <v>21.0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H195" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="196">
@@ -7192,10 +7192,10 @@
         <v>18.0</v>
       </c>
       <c r="G196" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H196" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H196" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="197">
@@ -7215,7 +7215,7 @@
         <v>679</v>
       </c>
       <c r="F197" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G197" t="n">
         <v>0.0</v>
@@ -7270,10 +7270,10 @@
         <v>23.0</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H199" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="200">
@@ -7296,10 +7296,10 @@
         <v>50.0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H200" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="201">
@@ -7322,10 +7322,10 @@
         <v>32.0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H201" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="202">
@@ -7374,10 +7374,10 @@
         <v>26.0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H203" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="204">
@@ -7400,10 +7400,10 @@
         <v>27.0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H204" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="205">
@@ -7478,10 +7478,10 @@
         <v>91.0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H207" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="208">
@@ -7530,10 +7530,10 @@
         <v>0.0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H209" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="210">
@@ -7556,10 +7556,10 @@
         <v>165.0</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H210" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="211">
@@ -7582,10 +7582,10 @@
         <v>216.0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H211" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="212">
@@ -7608,10 +7608,10 @@
         <v>260.0</v>
       </c>
       <c r="G212" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H212" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H212" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="213">
@@ -7660,10 +7660,10 @@
         <v>280.0</v>
       </c>
       <c r="G214" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="H214" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H214" t="n">
-        <v>20.0</v>
       </c>
     </row>
     <row r="215">
@@ -7686,10 +7686,10 @@
         <v>135.0</v>
       </c>
       <c r="G215" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H215" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H215" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="216">
@@ -7764,10 +7764,10 @@
         <v>0.0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H218" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="219">
@@ -7787,13 +7787,13 @@
         <v>678</v>
       </c>
       <c r="F219" t="n">
-        <v>394.0</v>
+        <v>395.0</v>
       </c>
       <c r="G219" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H219" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H219" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="220">
@@ -7865,7 +7865,7 @@
         <v>679</v>
       </c>
       <c r="F222" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G222" t="n">
         <v>0.0</v>
@@ -7894,10 +7894,10 @@
         <v>51.0</v>
       </c>
       <c r="G223" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H223" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H223" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="224">
@@ -7998,10 +7998,10 @@
         <v>89.0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.0</v>
+        <v>9735.0</v>
       </c>
       <c r="H227" t="n">
-        <v>9735.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="228">
@@ -8024,10 +8024,10 @@
         <v>234.0</v>
       </c>
       <c r="G228" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H228" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H228" t="n">
-        <v>10.0</v>
       </c>
     </row>
     <row r="229">
@@ -8050,10 +8050,10 @@
         <v>88.0</v>
       </c>
       <c r="G229" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H229" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H229" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="230">
@@ -8102,10 +8102,10 @@
         <v>140.0</v>
       </c>
       <c r="G231" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H231" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="232">
@@ -8125,7 +8125,7 @@
         <v>678</v>
       </c>
       <c r="F232" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G232" t="n">
         <v>1.0</v>
@@ -8154,10 +8154,10 @@
         <v>34.0</v>
       </c>
       <c r="G233" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H233" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H233" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="234">
@@ -8180,10 +8180,10 @@
         <v>26.0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H234" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="235">
@@ -8206,10 +8206,10 @@
         <v>149.0</v>
       </c>
       <c r="G235" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H235" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H235" t="n">
-        <v>16.0</v>
       </c>
     </row>
     <row r="236">
@@ -8258,10 +8258,10 @@
         <v>47.0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H237" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="238">
@@ -8284,10 +8284,10 @@
         <v>80.0</v>
       </c>
       <c r="G238" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="H238" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H238" t="n">
-        <v>29.0</v>
       </c>
     </row>
     <row r="239">
@@ -8310,10 +8310,10 @@
         <v>58.0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H239" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="240">
@@ -8336,10 +8336,10 @@
         <v>55.0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H240" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="241">
@@ -8362,10 +8362,10 @@
         <v>44.0</v>
       </c>
       <c r="G241" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="H241" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H241" t="n">
-        <v>54.0</v>
       </c>
     </row>
     <row r="242">
@@ -8388,10 +8388,10 @@
         <v>937.0</v>
       </c>
       <c r="G242" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="H242" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H242" t="n">
-        <v>23.0</v>
       </c>
     </row>
     <row r="243">
@@ -8414,10 +8414,10 @@
         <v>18.0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H243" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="244">
@@ -8466,10 +8466,10 @@
         <v>78.0</v>
       </c>
       <c r="G245" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H245" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H245" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="246">
@@ -8492,10 +8492,10 @@
         <v>34.0</v>
       </c>
       <c r="G246" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="H246" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H246" t="n">
-        <v>14.0</v>
       </c>
     </row>
     <row r="247">
@@ -8518,10 +8518,10 @@
         <v>0.0</v>
       </c>
       <c r="G247" t="n">
-        <v>0.0</v>
+        <v>70.0</v>
       </c>
       <c r="H247" t="n">
-        <v>70.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="248">
@@ -8596,10 +8596,10 @@
         <v>25.0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H250" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="251">
@@ -8648,10 +8648,10 @@
         <v>234.0</v>
       </c>
       <c r="G252" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H252" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="253">
@@ -8674,10 +8674,10 @@
         <v>37.0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H253" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="254">
@@ -8700,10 +8700,10 @@
         <v>57.0</v>
       </c>
       <c r="G254" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="H254" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H254" t="n">
-        <v>37.0</v>
       </c>
     </row>
     <row r="255">
@@ -8726,10 +8726,10 @@
         <v>56.0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="H255" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="256">
@@ -8752,10 +8752,10 @@
         <v>611.0</v>
       </c>
       <c r="G256" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="H256" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="257">
@@ -8778,10 +8778,10 @@
         <v>33.0</v>
       </c>
       <c r="G257" t="n">
-        <v>0.0</v>
+        <v>52.0</v>
       </c>
       <c r="H257" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="258">
@@ -8830,10 +8830,10 @@
         <v>70.0</v>
       </c>
       <c r="G259" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H259" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H259" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="260">
@@ -8856,10 +8856,10 @@
         <v>27.0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H260" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="261">
@@ -8882,10 +8882,10 @@
         <v>38.0</v>
       </c>
       <c r="G261" t="n">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="H261" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="262">
@@ -8908,10 +8908,10 @@
         <v>165.0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H262" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="263">
@@ -8960,10 +8960,10 @@
         <v>0.0</v>
       </c>
       <c r="G264" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H264" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="265">
@@ -9064,10 +9064,10 @@
         <v>71.0</v>
       </c>
       <c r="G268" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H268" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="269">
@@ -9116,10 +9116,10 @@
         <v>255.0</v>
       </c>
       <c r="G270" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H270" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H270" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="271">
@@ -9142,10 +9142,10 @@
         <v>234.0</v>
       </c>
       <c r="G271" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H271" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H271" t="n">
-        <v>8.0</v>
       </c>
     </row>
     <row r="272">
@@ -9194,10 +9194,10 @@
         <v>42.0</v>
       </c>
       <c r="G273" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H273" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H273" t="n">
-        <v>13.0</v>
       </c>
     </row>
     <row r="274">
@@ -9220,10 +9220,10 @@
         <v>538.0</v>
       </c>
       <c r="G274" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="H274" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H274" t="n">
-        <v>38.0</v>
       </c>
     </row>
     <row r="275">
@@ -9272,10 +9272,10 @@
         <v>47.0</v>
       </c>
       <c r="G276" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H276" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="277">
@@ -9298,10 +9298,10 @@
         <v>282.0</v>
       </c>
       <c r="G277" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H277" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H277" t="n">
-        <v>13.0</v>
       </c>
     </row>
     <row r="278">
@@ -9324,10 +9324,10 @@
         <v>237.0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H278" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="279">
@@ -9350,10 +9350,10 @@
         <v>82.0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H279" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="280">
@@ -9402,10 +9402,10 @@
         <v>94.0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H281" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="282">
@@ -9428,10 +9428,10 @@
         <v>209.0</v>
       </c>
       <c r="G282" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H282" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H282" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="283">
@@ -9454,10 +9454,10 @@
         <v>74.0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H283" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="284">
@@ -9480,10 +9480,10 @@
         <v>22.0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.0</v>
+        <v>48.0</v>
       </c>
       <c r="H284" t="n">
-        <v>48.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="285">
@@ -9506,10 +9506,10 @@
         <v>90.0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H285" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="286">
@@ -9558,10 +9558,10 @@
         <v>35.0</v>
       </c>
       <c r="G287" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H287" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="288">
@@ -9636,10 +9636,10 @@
         <v>58.0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H290" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="291">
@@ -9688,10 +9688,10 @@
         <v>123.0</v>
       </c>
       <c r="G292" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H292" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H292" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="293">
@@ -9714,10 +9714,10 @@
         <v>317.0</v>
       </c>
       <c r="G293" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H293" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H293" t="n">
-        <v>16.0</v>
       </c>
     </row>
     <row r="294">
@@ -9740,10 +9740,10 @@
         <v>1002.0</v>
       </c>
       <c r="G294" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="H294" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H294" t="n">
-        <v>20.0</v>
       </c>
     </row>
     <row r="295">
@@ -9766,10 +9766,10 @@
         <v>145.0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H295" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="296">
@@ -9792,10 +9792,10 @@
         <v>6.0</v>
       </c>
       <c r="G296" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H296" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H296" t="n">
-        <v>8.0</v>
       </c>
     </row>
     <row r="297">
@@ -9818,10 +9818,10 @@
         <v>12.0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H297" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="298">
@@ -9870,10 +9870,10 @@
         <v>491.0</v>
       </c>
       <c r="G299" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H299" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H299" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="300">
@@ -9896,10 +9896,10 @@
         <v>185.0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H300" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="301">
@@ -9922,10 +9922,10 @@
         <v>23.0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="H301" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="302">
@@ -9948,10 +9948,10 @@
         <v>20.0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H302" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="303">
@@ -9974,10 +9974,10 @@
         <v>102.0</v>
       </c>
       <c r="G303" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H303" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="304">
@@ -10052,10 +10052,10 @@
         <v>533.0</v>
       </c>
       <c r="G306" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H306" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H306" t="n">
-        <v>8.0</v>
       </c>
     </row>
     <row r="307">
@@ -10104,10 +10104,10 @@
         <v>14.0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H308" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="309">
@@ -10130,10 +10130,10 @@
         <v>68.0</v>
       </c>
       <c r="G309" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H309" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H309" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="310">
@@ -10208,10 +10208,10 @@
         <v>34.0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="H312" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="313">
@@ -10234,10 +10234,10 @@
         <v>52.0</v>
       </c>
       <c r="G313" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H313" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H313" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="314">
@@ -10260,10 +10260,10 @@
         <v>31.0</v>
       </c>
       <c r="G314" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H314" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H314" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="315">
@@ -10286,10 +10286,10 @@
         <v>51.0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H315" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="316">
@@ -10312,10 +10312,10 @@
         <v>2.0</v>
       </c>
       <c r="G316" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H316" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H316" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="317">
@@ -10364,10 +10364,10 @@
         <v>143.0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H318" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="319">
@@ -10390,10 +10390,10 @@
         <v>265.0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H319" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="320">
@@ -10416,10 +10416,10 @@
         <v>78.0</v>
       </c>
       <c r="G320" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H320" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="321">
@@ -10442,10 +10442,10 @@
         <v>16.0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H321" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="322">
@@ -10491,13 +10491,13 @@
         <v>678</v>
       </c>
       <c r="F323" t="n">
-        <v>404.0</v>
+        <v>405.0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H323" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="324">
@@ -10520,10 +10520,10 @@
         <v>47.0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H324" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="325">
@@ -10546,10 +10546,10 @@
         <v>0.0</v>
       </c>
       <c r="G325" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H325" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H325" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="326">
@@ -10572,10 +10572,10 @@
         <v>189.0</v>
       </c>
       <c r="G326" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H326" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H326" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="327">
@@ -10650,10 +10650,10 @@
         <v>5.0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H329" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="330">
@@ -10676,10 +10676,10 @@
         <v>12.0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H330" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="331">
@@ -10728,10 +10728,10 @@
         <v>123.0</v>
       </c>
       <c r="G332" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H332" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H332" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="333">
@@ -10806,10 +10806,10 @@
         <v>37.0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H335" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="336">
@@ -10858,10 +10858,10 @@
         <v>138.0</v>
       </c>
       <c r="G337" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H337" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H337" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="338">
@@ -10910,10 +10910,10 @@
         <v>25.0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H339" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="340">
@@ -10936,10 +10936,10 @@
         <v>0.0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H340" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="341">
@@ -11014,10 +11014,10 @@
         <v>13.0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H343" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="344">
@@ -11040,10 +11040,10 @@
         <v>159.0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H344" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="345">
@@ -11066,10 +11066,10 @@
         <v>527.0</v>
       </c>
       <c r="G345" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H345" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H345" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="346">
@@ -11092,10 +11092,10 @@
         <v>54.0</v>
       </c>
       <c r="G346" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H346" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H346" t="n">
-        <v>10.0</v>
       </c>
     </row>
     <row r="347">
@@ -11118,10 +11118,10 @@
         <v>101.0</v>
       </c>
       <c r="G347" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H347" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H347" t="n">
-        <v>5.0</v>
       </c>
     </row>
     <row r="348">
@@ -11141,7 +11141,7 @@
         <v>679</v>
       </c>
       <c r="F348" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G348" t="n">
         <v>0.0</v>
@@ -11170,10 +11170,10 @@
         <v>19.0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H349" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="350">
@@ -11196,10 +11196,10 @@
         <v>20.0</v>
       </c>
       <c r="G350" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H350" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="351">
@@ -11222,10 +11222,10 @@
         <v>22.0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H351" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="352">
@@ -11248,10 +11248,10 @@
         <v>28.0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H352" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="353">
@@ -11274,10 +11274,10 @@
         <v>15.0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H353" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="354">
@@ -11300,10 +11300,10 @@
         <v>48.0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H354" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="355">
@@ -11326,10 +11326,10 @@
         <v>104.0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H355" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="356">
@@ -11378,10 +11378,10 @@
         <v>14.0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="H357" t="n">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="358">
@@ -11404,10 +11404,10 @@
         <v>128.0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H358" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="359">
@@ -11560,10 +11560,10 @@
         <v>71.0</v>
       </c>
       <c r="G364" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="H364" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H364" t="n">
-        <v>34.0</v>
       </c>
     </row>
     <row r="365">
@@ -11638,10 +11638,10 @@
         <v>99.0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H367" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="368">
@@ -11690,10 +11690,10 @@
         <v>33.0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H369" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="370">
@@ -11716,10 +11716,10 @@
         <v>115.0</v>
       </c>
       <c r="G370" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H370" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H370" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="371">
@@ -11739,13 +11739,13 @@
         <v>678</v>
       </c>
       <c r="F371" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H371" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="372">
@@ -11872,10 +11872,10 @@
         <v>69.0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H376" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="377">
@@ -11924,10 +11924,10 @@
         <v>138.0</v>
       </c>
       <c r="G378" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="H378" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H378" t="n">
-        <v>36.0</v>
       </c>
     </row>
     <row r="379">
@@ -11950,10 +11950,10 @@
         <v>195.0</v>
       </c>
       <c r="G379" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H379" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H379" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="380">
@@ -11999,7 +11999,7 @@
         <v>678</v>
       </c>
       <c r="F381" t="n">
-        <v>124.0</v>
+        <v>126.0</v>
       </c>
       <c r="G381" t="n">
         <v>1.0</v>
@@ -12028,10 +12028,10 @@
         <v>140.0</v>
       </c>
       <c r="G382" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H382" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H382" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="383">
@@ -12054,10 +12054,10 @@
         <v>0.0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H383" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="384">
@@ -12080,10 +12080,10 @@
         <v>434.0</v>
       </c>
       <c r="G384" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H384" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H384" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="385">
@@ -12106,10 +12106,10 @@
         <v>63.0</v>
       </c>
       <c r="G385" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H385" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H385" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="386">
@@ -12132,10 +12132,10 @@
         <v>39.0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H386" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="387">
@@ -12184,10 +12184,10 @@
         <v>8.0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H388" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="389">
@@ -12236,10 +12236,10 @@
         <v>36.0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H390" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="391">
@@ -12288,10 +12288,10 @@
         <v>2.0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H392" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="393">
@@ -12311,13 +12311,13 @@
         <v>678</v>
       </c>
       <c r="F393" t="n">
-        <v>295.0</v>
+        <v>298.0</v>
       </c>
       <c r="G393" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="H393" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H393" t="n">
-        <v>27.0</v>
       </c>
     </row>
     <row r="394">
@@ -12392,10 +12392,10 @@
         <v>88.0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H396" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="397">
@@ -12418,10 +12418,10 @@
         <v>182.0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H397" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="398">
@@ -12496,10 +12496,10 @@
         <v>72.0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H400" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="401">
@@ -12548,10 +12548,10 @@
         <v>0.0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="H402" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="403">
@@ -12600,10 +12600,10 @@
         <v>39.0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H404" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="405">
@@ -12730,10 +12730,10 @@
         <v>49.0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H409" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="410">
@@ -12834,10 +12834,10 @@
         <v>96.0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H413" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="414">
@@ -12860,10 +12860,10 @@
         <v>22.0</v>
       </c>
       <c r="G414" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H414" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="415">
@@ -12886,10 +12886,10 @@
         <v>99.0</v>
       </c>
       <c r="G415" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H415" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="416">
@@ -12912,10 +12912,10 @@
         <v>26.0</v>
       </c>
       <c r="G416" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H416" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="417">
@@ -12964,10 +12964,10 @@
         <v>84.0</v>
       </c>
       <c r="G418" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H418" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H418" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="419">
@@ -12990,10 +12990,10 @@
         <v>105.0</v>
       </c>
       <c r="G419" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H419" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="420">
@@ -13042,10 +13042,10 @@
         <v>220.0</v>
       </c>
       <c r="G421" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H421" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H421" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="422">
@@ -13068,10 +13068,10 @@
         <v>80.0</v>
       </c>
       <c r="G422" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H422" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H422" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="423">
@@ -13146,10 +13146,10 @@
         <v>559.0</v>
       </c>
       <c r="G425" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H425" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H425" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="426">
@@ -13172,10 +13172,10 @@
         <v>150.0</v>
       </c>
       <c r="G426" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H426" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="427">
@@ -13198,10 +13198,10 @@
         <v>135.0</v>
       </c>
       <c r="G427" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H427" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="428">
@@ -13224,10 +13224,10 @@
         <v>121.0</v>
       </c>
       <c r="G428" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H428" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H428" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="429">
@@ -13250,10 +13250,10 @@
         <v>189.0</v>
       </c>
       <c r="G429" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H429" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="430">
@@ -13276,10 +13276,10 @@
         <v>760.0</v>
       </c>
       <c r="G430" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H430" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H430" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="431">
@@ -13302,10 +13302,10 @@
         <v>59.0</v>
       </c>
       <c r="G431" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H431" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H431" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="432">
@@ -13354,10 +13354,10 @@
         <v>32.0</v>
       </c>
       <c r="G433" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H433" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="434">
@@ -13380,10 +13380,10 @@
         <v>27.0</v>
       </c>
       <c r="G434" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H434" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="435">
@@ -13432,10 +13432,10 @@
         <v>122.0</v>
       </c>
       <c r="G436" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="H436" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H436" t="n">
-        <v>24.0</v>
       </c>
     </row>
     <row r="437">
@@ -13458,10 +13458,10 @@
         <v>195.0</v>
       </c>
       <c r="G437" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H437" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="438">
@@ -13510,10 +13510,10 @@
         <v>58.0</v>
       </c>
       <c r="G439" t="n">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="H439" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="440">
@@ -13536,10 +13536,10 @@
         <v>16.0</v>
       </c>
       <c r="G440" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H440" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="441">
@@ -13614,10 +13614,10 @@
         <v>132.0</v>
       </c>
       <c r="G443" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H443" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="444">
@@ -13692,10 +13692,10 @@
         <v>18.0</v>
       </c>
       <c r="G446" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H446" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="447">
@@ -13715,13 +13715,13 @@
         <v>680</v>
       </c>
       <c r="F447" t="n">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
       <c r="G447" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H447" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H447" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="448">
@@ -13744,10 +13744,10 @@
         <v>182.0</v>
       </c>
       <c r="G448" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H448" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H448" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="449">
@@ -13770,10 +13770,10 @@
         <v>32.0</v>
       </c>
       <c r="G449" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H449" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="450">
@@ -13796,10 +13796,10 @@
         <v>174.0</v>
       </c>
       <c r="G450" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H450" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H450" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="451">
@@ -13822,10 +13822,10 @@
         <v>129.0</v>
       </c>
       <c r="G451" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="H451" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H451" t="n">
-        <v>44.0</v>
       </c>
     </row>
     <row r="452">
@@ -13845,7 +13845,7 @@
         <v>678</v>
       </c>
       <c r="F452" t="n">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -13926,10 +13926,10 @@
         <v>218.0</v>
       </c>
       <c r="G455" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H455" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="456">
@@ -13978,10 +13978,10 @@
         <v>96.0</v>
       </c>
       <c r="G457" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H457" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="458">
@@ -14030,10 +14030,10 @@
         <v>64.0</v>
       </c>
       <c r="G459" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H459" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="460">
@@ -14108,10 +14108,10 @@
         <v>531.0</v>
       </c>
       <c r="G462" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H462" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="463">
@@ -14160,10 +14160,10 @@
         <v>235.0</v>
       </c>
       <c r="G464" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H464" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H464" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="465">
@@ -14316,10 +14316,10 @@
         <v>44.0</v>
       </c>
       <c r="G470" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H470" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="471">
@@ -14342,10 +14342,10 @@
         <v>33.0</v>
       </c>
       <c r="G471" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H471" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="472">
@@ -14368,10 +14368,10 @@
         <v>380.0</v>
       </c>
       <c r="G472" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="H472" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H472" t="n">
-        <v>39.0</v>
       </c>
     </row>
     <row r="473">
@@ -14498,10 +14498,10 @@
         <v>76.0</v>
       </c>
       <c r="G477" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H477" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="478">
@@ -14521,13 +14521,13 @@
         <v>678</v>
       </c>
       <c r="F478" t="n">
-        <v>585.0</v>
+        <v>586.0</v>
       </c>
       <c r="G478" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H478" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H478" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="479">
@@ -14550,10 +14550,10 @@
         <v>22.0</v>
       </c>
       <c r="G479" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H479" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="480">
@@ -14602,10 +14602,10 @@
         <v>42.0</v>
       </c>
       <c r="G481" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H481" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="482">
@@ -14628,10 +14628,10 @@
         <v>43.0</v>
       </c>
       <c r="G482" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H482" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="483">
@@ -14680,10 +14680,10 @@
         <v>190.0</v>
       </c>
       <c r="G484" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H484" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="485">
@@ -14732,10 +14732,10 @@
         <v>1.0</v>
       </c>
       <c r="G486" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H486" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="487">
@@ -14758,10 +14758,10 @@
         <v>96.0</v>
       </c>
       <c r="G487" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H487" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="488">
@@ -14810,10 +14810,10 @@
         <v>69.0</v>
       </c>
       <c r="G489" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H489" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="490">
@@ -14836,10 +14836,10 @@
         <v>185.0</v>
       </c>
       <c r="G490" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H490" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H490" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="491">
@@ -14862,10 +14862,10 @@
         <v>0.0</v>
       </c>
       <c r="G491" t="n">
-        <v>0.0</v>
+        <v>43.0</v>
       </c>
       <c r="H491" t="n">
-        <v>43.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="492">
@@ -14914,10 +14914,10 @@
         <v>2371.0</v>
       </c>
       <c r="G493" t="n">
+        <v>305.0</v>
+      </c>
+      <c r="H493" t="n">
         <v>45.0</v>
-      </c>
-      <c r="H493" t="n">
-        <v>305.0</v>
       </c>
     </row>
     <row r="494">
@@ -14940,10 +14940,10 @@
         <v>172.0</v>
       </c>
       <c r="G494" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="H494" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H494" t="n">
-        <v>26.0</v>
       </c>
     </row>
     <row r="495">
@@ -14966,10 +14966,10 @@
         <v>202.0</v>
       </c>
       <c r="G495" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H495" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="496">
@@ -14992,10 +14992,10 @@
         <v>30.0</v>
       </c>
       <c r="G496" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H496" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="497">
@@ -15018,10 +15018,10 @@
         <v>195.0</v>
       </c>
       <c r="G497" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H497" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="498">
@@ -15070,10 +15070,10 @@
         <v>112.0</v>
       </c>
       <c r="G499" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H499" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="500">
@@ -15122,10 +15122,10 @@
         <v>215.0</v>
       </c>
       <c r="G501" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H501" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="502">
@@ -15148,10 +15148,10 @@
         <v>80.0</v>
       </c>
       <c r="G502" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H502" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="503">
@@ -15174,10 +15174,10 @@
         <v>66.0</v>
       </c>
       <c r="G503" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H503" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H503" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="504">
@@ -15200,10 +15200,10 @@
         <v>24.0</v>
       </c>
       <c r="G504" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H504" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="505">
@@ -15226,10 +15226,10 @@
         <v>409.0</v>
       </c>
       <c r="G505" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H505" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H505" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="506">
@@ -15252,10 +15252,10 @@
         <v>20.0</v>
       </c>
       <c r="G506" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H506" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="507">
@@ -15304,10 +15304,10 @@
         <v>63.0</v>
       </c>
       <c r="G508" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H508" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="509">
@@ -15330,10 +15330,10 @@
         <v>1.0</v>
       </c>
       <c r="G509" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H509" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="510">
@@ -15382,10 +15382,10 @@
         <v>78.0</v>
       </c>
       <c r="G511" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H511" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="512">
@@ -15434,10 +15434,10 @@
         <v>29.0</v>
       </c>
       <c r="G513" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H513" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="514">
@@ -15512,10 +15512,10 @@
         <v>16.0</v>
       </c>
       <c r="G516" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H516" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="517">
@@ -15535,13 +15535,13 @@
         <v>678</v>
       </c>
       <c r="F517" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G517" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H517" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="518">
@@ -15564,10 +15564,10 @@
         <v>26.0</v>
       </c>
       <c r="G518" t="n">
-        <v>0.0</v>
+        <v>52.0</v>
       </c>
       <c r="H518" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="519">
@@ -15642,10 +15642,10 @@
         <v>54.0</v>
       </c>
       <c r="G521" t="n">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
       <c r="H521" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="522">
@@ -15668,10 +15668,10 @@
         <v>261.0</v>
       </c>
       <c r="G522" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H522" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="523">
@@ -15746,10 +15746,10 @@
         <v>23.0</v>
       </c>
       <c r="G525" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
       <c r="H525" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="526">
@@ -15798,10 +15798,10 @@
         <v>86.0</v>
       </c>
       <c r="G527" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H527" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="528">
@@ -15824,10 +15824,10 @@
         <v>7.0</v>
       </c>
       <c r="G528" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H528" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="529">
@@ -15873,13 +15873,13 @@
         <v>678</v>
       </c>
       <c r="F530" t="n">
-        <v>412.0</v>
+        <v>413.0</v>
       </c>
       <c r="G530" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H530" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H530" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="531">
@@ -15902,10 +15902,10 @@
         <v>205.0</v>
       </c>
       <c r="G531" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H531" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="532">
@@ -15928,10 +15928,10 @@
         <v>102.0</v>
       </c>
       <c r="G532" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H532" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H532" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="533">
@@ -15954,10 +15954,10 @@
         <v>131.0</v>
       </c>
       <c r="G533" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H533" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H533" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="534">
@@ -16006,10 +16006,10 @@
         <v>19.0</v>
       </c>
       <c r="G535" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H535" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H535" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="536">
@@ -16032,10 +16032,10 @@
         <v>7.0</v>
       </c>
       <c r="G536" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H536" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="537">
@@ -16058,10 +16058,10 @@
         <v>223.0</v>
       </c>
       <c r="G537" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="H537" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H537" t="n">
-        <v>29.0</v>
       </c>
     </row>
     <row r="538">
@@ -16214,10 +16214,10 @@
         <v>30.0</v>
       </c>
       <c r="G543" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H543" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="544">
@@ -16266,10 +16266,10 @@
         <v>92.0</v>
       </c>
       <c r="G545" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H545" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H545" t="n">
-        <v>10.0</v>
       </c>
     </row>
     <row r="546">
@@ -16292,10 +16292,10 @@
         <v>0.0</v>
       </c>
       <c r="G546" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H546" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="547">
@@ -16315,13 +16315,13 @@
         <v>678</v>
       </c>
       <c r="F547" t="n">
-        <v>265.0</v>
+        <v>272.0</v>
       </c>
       <c r="G547" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H547" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H547" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="548">
@@ -16396,10 +16396,10 @@
         <v>42.0</v>
       </c>
       <c r="G550" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H550" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H550" t="n">
-        <v>10.0</v>
       </c>
     </row>
     <row r="551">
@@ -16448,10 +16448,10 @@
         <v>26.0</v>
       </c>
       <c r="G552" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H552" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="553">
@@ -16549,13 +16549,13 @@
         <v>679</v>
       </c>
       <c r="F556" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G556" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H556" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H556" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="557">
@@ -16630,10 +16630,10 @@
         <v>91.0</v>
       </c>
       <c r="G559" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H559" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H559" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="560">
@@ -16838,10 +16838,10 @@
         <v>49.0</v>
       </c>
       <c r="G567" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H567" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="568">
@@ -16890,10 +16890,10 @@
         <v>77.0</v>
       </c>
       <c r="G569" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H569" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="570">
@@ -16965,13 +16965,13 @@
         <v>679</v>
       </c>
       <c r="F572" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G572" t="n">
         <v>0.0</v>
       </c>
       <c r="H572" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="573">
@@ -17046,10 +17046,10 @@
         <v>178.0</v>
       </c>
       <c r="G575" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H575" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="576">
@@ -17098,10 +17098,10 @@
         <v>347.0</v>
       </c>
       <c r="G577" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H577" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H577" t="n">
-        <v>12.0</v>
       </c>
     </row>
     <row r="578">
@@ -17121,13 +17121,13 @@
         <v>678</v>
       </c>
       <c r="F578" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G578" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H578" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H578" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="579">
@@ -17150,10 +17150,10 @@
         <v>19.0</v>
       </c>
       <c r="G579" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H579" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="580">
@@ -17173,7 +17173,7 @@
         <v>679</v>
       </c>
       <c r="F580" t="n">
-        <v>384.0</v>
+        <v>389.0</v>
       </c>
       <c r="G580" t="n">
         <v>0.0</v>
@@ -17228,10 +17228,10 @@
         <v>32.0</v>
       </c>
       <c r="G582" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H582" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="583">
@@ -17254,10 +17254,10 @@
         <v>211.0</v>
       </c>
       <c r="G583" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H583" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H583" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="584">
@@ -17306,10 +17306,10 @@
         <v>220.0</v>
       </c>
       <c r="G585" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H585" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="586">
@@ -17332,10 +17332,10 @@
         <v>70.0</v>
       </c>
       <c r="G586" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H586" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H586" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="587">
@@ -17358,10 +17358,10 @@
         <v>16.0</v>
       </c>
       <c r="G587" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H587" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="588">
@@ -17384,10 +17384,10 @@
         <v>93.0</v>
       </c>
       <c r="G588" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H588" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="589">
@@ -17410,10 +17410,10 @@
         <v>90.0</v>
       </c>
       <c r="G589" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H589" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="590">
@@ -17488,10 +17488,10 @@
         <v>23.0</v>
       </c>
       <c r="G592" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H592" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="593">
@@ -17514,10 +17514,10 @@
         <v>6.0</v>
       </c>
       <c r="G593" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H593" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H593" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="594">
@@ -17540,10 +17540,10 @@
         <v>24.0</v>
       </c>
       <c r="G594" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H594" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="595">
@@ -17592,10 +17592,10 @@
         <v>217.0</v>
       </c>
       <c r="G596" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="H596" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H596" t="n">
-        <v>32.0</v>
       </c>
     </row>
     <row r="597">
@@ -17670,10 +17670,10 @@
         <v>67.0</v>
       </c>
       <c r="G599" t="n">
-        <v>0.0</v>
+        <v>1851.0</v>
       </c>
       <c r="H599" t="n">
-        <v>1851.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="600">
@@ -17693,7 +17693,7 @@
         <v>678</v>
       </c>
       <c r="F600" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -17722,10 +17722,10 @@
         <v>18.0</v>
       </c>
       <c r="G601" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="H601" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="602">
@@ -17774,10 +17774,10 @@
         <v>69.0</v>
       </c>
       <c r="G603" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H603" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="604">
@@ -17878,10 +17878,10 @@
         <v>75.0</v>
       </c>
       <c r="G607" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H607" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="608">
@@ -17930,10 +17930,10 @@
         <v>95.0</v>
       </c>
       <c r="G609" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H609" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H609" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="610">
@@ -17956,10 +17956,10 @@
         <v>143.0</v>
       </c>
       <c r="G610" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="H610" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H610" t="n">
-        <v>79.0</v>
       </c>
     </row>
     <row r="611">
@@ -17982,10 +17982,10 @@
         <v>35.0</v>
       </c>
       <c r="G611" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H611" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="612">
@@ -18008,10 +18008,10 @@
         <v>27.0</v>
       </c>
       <c r="G612" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H612" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H612" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="613">
@@ -18112,10 +18112,10 @@
         <v>56.0</v>
       </c>
       <c r="G616" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="H616" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="617">
@@ -18138,10 +18138,10 @@
         <v>176.0</v>
       </c>
       <c r="G617" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H617" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="618">
@@ -18164,10 +18164,10 @@
         <v>6.0</v>
       </c>
       <c r="G618" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H618" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="619">
@@ -18294,10 +18294,10 @@
         <v>132.0</v>
       </c>
       <c r="G623" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H623" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="624">
@@ -18320,10 +18320,10 @@
         <v>19.0</v>
       </c>
       <c r="G624" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="H624" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H624" t="n">
-        <v>14.0</v>
       </c>
     </row>
     <row r="625">
@@ -18343,7 +18343,7 @@
         <v>679</v>
       </c>
       <c r="F625" t="n">
-        <v>100.0</v>
+        <v>105.0</v>
       </c>
       <c r="G625" t="n">
         <v>0.0</v>
@@ -18372,10 +18372,10 @@
         <v>24.0</v>
       </c>
       <c r="G626" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H626" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="627">
@@ -18398,10 +18398,10 @@
         <v>94.0</v>
       </c>
       <c r="G627" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="H627" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H627" t="n">
-        <v>44.0</v>
       </c>
     </row>
     <row r="628">
@@ -18502,10 +18502,10 @@
         <v>0.0</v>
       </c>
       <c r="G631" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H631" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="632">
@@ -18554,10 +18554,10 @@
         <v>109.0</v>
       </c>
       <c r="G633" t="n">
-        <v>0.0</v>
+        <v>32.0</v>
       </c>
       <c r="H633" t="n">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="634">
@@ -18580,10 +18580,10 @@
         <v>0.0</v>
       </c>
       <c r="G634" t="n">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="H634" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="635">
@@ -18632,10 +18632,10 @@
         <v>0.0</v>
       </c>
       <c r="G636" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="H636" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="637">
@@ -18658,10 +18658,10 @@
         <v>217.0</v>
       </c>
       <c r="G637" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H637" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H637" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="638">
@@ -18710,10 +18710,10 @@
         <v>86.0</v>
       </c>
       <c r="G639" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H639" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H639" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="640">
@@ -18736,10 +18736,10 @@
         <v>0.0</v>
       </c>
       <c r="G640" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H640" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="641">
@@ -18762,10 +18762,10 @@
         <v>116.0</v>
       </c>
       <c r="G641" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H641" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H641" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="642">
@@ -18840,10 +18840,10 @@
         <v>109.0</v>
       </c>
       <c r="G644" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H644" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H644" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="645">
@@ -18863,7 +18863,7 @@
         <v>678</v>
       </c>
       <c r="F645" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G645" t="n">
         <v>0.0</v>
@@ -18993,7 +18993,7 @@
         <v>679</v>
       </c>
       <c r="F650" t="n">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="G650" t="n">
         <v>0.0</v>
@@ -19152,10 +19152,10 @@
         <v>12.0</v>
       </c>
       <c r="G656" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H656" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H656" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="657">
@@ -19178,10 +19178,10 @@
         <v>55.0</v>
       </c>
       <c r="G657" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H657" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H657" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="658">
@@ -19279,7 +19279,7 @@
         <v>679</v>
       </c>
       <c r="F661" t="n">
-        <v>99.0</v>
+        <v>101.0</v>
       </c>
       <c r="G661" t="n">
         <v>0.0</v>
@@ -19360,7 +19360,7 @@
         <v>61.0</v>
       </c>
       <c r="G664" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H664" t="n">
         <v>0.0</v>
@@ -19438,10 +19438,10 @@
         <v>15.0</v>
       </c>
       <c r="G667" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H667" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H667" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="668">
@@ -19542,10 +19542,10 @@
         <v>158.0</v>
       </c>
       <c r="G671" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H671" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H671" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="672">
@@ -19594,10 +19594,10 @@
         <v>305.0</v>
       </c>
       <c r="G673" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H673" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H673" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="674">
@@ -19646,10 +19646,10 @@
         <v>382.0</v>
       </c>
       <c r="G675" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H675" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H675" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="676">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4749,7 +4749,7 @@
         <v>135.0</v>
       </c>
       <c r="G95" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -5191,7 +5191,7 @@
         <v>0.0</v>
       </c>
       <c r="G112" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -14028,7 +14028,7 @@
         <v>740</v>
       </c>
       <c r="F452" t="n">
-        <v>442.0</v>
+        <v>443.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -20424,7 +20424,7 @@
         <v>739</v>
       </c>
       <c r="F698" t="n">
-        <v>398.0</v>
+        <v>400.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20528,7 +20528,7 @@
         <v>740</v>
       </c>
       <c r="F702" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G702" t="n">
         <v>0.0</v>
@@ -20632,7 +20632,7 @@
         <v>740</v>
       </c>
       <c r="F706" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20710,7 +20710,7 @@
         <v>740</v>
       </c>
       <c r="F709" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G709" t="n">
         <v>0.0</v>
@@ -20814,7 +20814,7 @@
         <v>740</v>
       </c>
       <c r="F713" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>355.0</v>
+        <v>356.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3342,7 +3342,7 @@
         <v>739</v>
       </c>
       <c r="F41" t="n">
-        <v>321.0</v>
+        <v>324.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -4070,7 +4070,7 @@
         <v>739</v>
       </c>
       <c r="F69" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="G69" t="n">
         <v>18.0</v>
@@ -4928,7 +4928,7 @@
         <v>740</v>
       </c>
       <c r="F102" t="n">
-        <v>421.0</v>
+        <v>423.0</v>
       </c>
       <c r="G102" t="n">
         <v>0.0</v>
@@ -5162,7 +5162,7 @@
         <v>740</v>
       </c>
       <c r="F111" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -5500,7 +5500,7 @@
         <v>739</v>
       </c>
       <c r="F124" t="n">
-        <v>449.0</v>
+        <v>451.0</v>
       </c>
       <c r="G124" t="n">
         <v>12.0</v>
@@ -5552,7 +5552,7 @@
         <v>739</v>
       </c>
       <c r="F126" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G126" t="n">
         <v>0.0</v>
@@ -6462,7 +6462,7 @@
         <v>739</v>
       </c>
       <c r="F161" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G161" t="n">
         <v>1.0</v>
@@ -6696,7 +6696,7 @@
         <v>740</v>
       </c>
       <c r="F170" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>
@@ -6800,7 +6800,7 @@
         <v>739</v>
       </c>
       <c r="F174" t="n">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="G174" t="n">
         <v>1.0</v>
@@ -7190,7 +7190,7 @@
         <v>739</v>
       </c>
       <c r="F189" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G189" t="n">
         <v>1.0</v>
@@ -8334,7 +8334,7 @@
         <v>739</v>
       </c>
       <c r="F233" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="G233" t="n">
         <v>0.0</v>
@@ -8542,7 +8542,7 @@
         <v>739</v>
       </c>
       <c r="F241" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G241" t="n">
         <v>0.0</v>
@@ -8776,7 +8776,7 @@
         <v>739</v>
       </c>
       <c r="F250" t="n">
-        <v>148.0</v>
+        <v>150.0</v>
       </c>
       <c r="G250" t="n">
         <v>1.0</v>
@@ -9036,7 +9036,7 @@
         <v>739</v>
       </c>
       <c r="F260" t="n">
-        <v>937.0</v>
+        <v>938.0</v>
       </c>
       <c r="G260" t="n">
         <v>23.0</v>
@@ -9114,7 +9114,7 @@
         <v>739</v>
       </c>
       <c r="F263" t="n">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="G263" t="n">
         <v>0.0</v>
@@ -9764,7 +9764,7 @@
         <v>739</v>
       </c>
       <c r="F288" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G288" t="n">
         <v>4.0</v>
@@ -9894,7 +9894,7 @@
         <v>739</v>
       </c>
       <c r="F293" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G293" t="n">
         <v>0.0</v>
@@ -10336,7 +10336,7 @@
         <v>739</v>
       </c>
       <c r="F310" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G310" t="n">
         <v>0.0</v>
@@ -10544,7 +10544,7 @@
         <v>739</v>
       </c>
       <c r="F318" t="n">
-        <v>491.0</v>
+        <v>493.0</v>
       </c>
       <c r="G318" t="n">
         <v>0.0</v>
@@ -11194,7 +11194,7 @@
         <v>739</v>
       </c>
       <c r="F343" t="n">
-        <v>405.0</v>
+        <v>406.0</v>
       </c>
       <c r="G343" t="n">
         <v>1.0</v>
@@ -11792,7 +11792,7 @@
         <v>739</v>
       </c>
       <c r="F366" t="n">
-        <v>528.0</v>
+        <v>530.0</v>
       </c>
       <c r="G366" t="n">
         <v>0.0</v>
@@ -12078,7 +12078,7 @@
         <v>740</v>
       </c>
       <c r="F377" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12494,7 +12494,7 @@
         <v>739</v>
       </c>
       <c r="F393" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="G393" t="n">
         <v>1.0</v>
@@ -13092,7 +13092,7 @@
         <v>739</v>
       </c>
       <c r="F416" t="n">
-        <v>298.0</v>
+        <v>301.0</v>
       </c>
       <c r="G416" t="n">
         <v>28.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>563.0</v>
+        <v>565.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -14418,7 +14418,7 @@
         <v>739</v>
       </c>
       <c r="F467" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G467" t="n">
         <v>13.0</v>
@@ -14522,7 +14522,7 @@
         <v>741</v>
       </c>
       <c r="F471" t="n">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
       <c r="G471" t="n">
         <v>0.0</v>
@@ -15458,7 +15458,7 @@
         <v>740</v>
       </c>
       <c r="F507" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -16368,7 +16368,7 @@
         <v>740</v>
       </c>
       <c r="F542" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G542" t="n">
         <v>0.0</v>
@@ -16524,7 +16524,7 @@
         <v>739</v>
       </c>
       <c r="F548" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G548" t="n">
         <v>0.0</v>
@@ -17668,7 +17668,7 @@
         <v>739</v>
       </c>
       <c r="F592" t="n">
-        <v>309.0</v>
+        <v>310.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -18162,7 +18162,7 @@
         <v>740</v>
       </c>
       <c r="F611" t="n">
-        <v>389.0</v>
+        <v>390.0</v>
       </c>
       <c r="G611" t="n">
         <v>0.0</v>
@@ -18240,7 +18240,7 @@
         <v>739</v>
       </c>
       <c r="F614" t="n">
-        <v>211.0</v>
+        <v>214.0</v>
       </c>
       <c r="G614" t="n">
         <v>7.0</v>
@@ -19618,7 +19618,7 @@
         <v>739</v>
       </c>
       <c r="F667" t="n">
-        <v>109.0</v>
+        <v>111.0</v>
       </c>
       <c r="G667" t="n">
         <v>32.0</v>
@@ -19722,7 +19722,7 @@
         <v>739</v>
       </c>
       <c r="F671" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19748,7 +19748,7 @@
         <v>739</v>
       </c>
       <c r="F672" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19774,7 +19774,7 @@
         <v>739</v>
       </c>
       <c r="F673" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19826,7 +19826,7 @@
         <v>739</v>
       </c>
       <c r="F675" t="n">
-        <v>116.0</v>
+        <v>120.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19852,7 +19852,7 @@
         <v>740</v>
       </c>
       <c r="F676" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -19904,7 +19904,7 @@
         <v>739</v>
       </c>
       <c r="F678" t="n">
-        <v>109.0</v>
+        <v>115.0</v>
       </c>
       <c r="G678" t="n">
         <v>0.0</v>
@@ -20112,7 +20112,7 @@
         <v>740</v>
       </c>
       <c r="F686" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G686" t="n">
         <v>0.0</v>
@@ -20190,7 +20190,7 @@
         <v>740</v>
       </c>
       <c r="F689" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="F694" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20346,7 +20346,7 @@
         <v>740</v>
       </c>
       <c r="F695" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20554,7 +20554,7 @@
         <v>740</v>
       </c>
       <c r="F703" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -20661,7 +20661,7 @@
         <v>61.0</v>
       </c>
       <c r="G707" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H707" t="n">
         <v>0.0</v>
@@ -20866,7 +20866,7 @@
         <v>740</v>
       </c>
       <c r="F715" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="G715" t="n">
         <v>0.0</v>
@@ -21074,7 +21074,7 @@
         <v>739</v>
       </c>
       <c r="F723" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -21126,7 +21126,7 @@
         <v>739</v>
       </c>
       <c r="F725" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21152,7 +21152,7 @@
         <v>740</v>
       </c>
       <c r="F726" t="n">
-        <v>35.0</v>
+        <v>45.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -21178,7 +21178,7 @@
         <v>739</v>
       </c>
       <c r="F727" t="n">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
       <c r="G727" t="n">
         <v>0.0</v>
@@ -21204,7 +21204,7 @@
         <v>740</v>
       </c>
       <c r="F728" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G728" t="n">
         <v>0.0</v>
@@ -21230,7 +21230,7 @@
         <v>740</v>
       </c>
       <c r="F729" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="G729" t="n">
         <v>0.0</v>
@@ -21256,7 +21256,7 @@
         <v>740</v>
       </c>
       <c r="F730" t="n">
-        <v>42.0</v>
+        <v>53.0</v>
       </c>
       <c r="G730" t="n">
         <v>0.0</v>
@@ -21412,7 +21412,7 @@
         <v>739</v>
       </c>
       <c r="F736" t="n">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="G736" t="n">
         <v>0.0</v>
@@ -21438,7 +21438,7 @@
         <v>740</v>
       </c>
       <c r="F737" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G737" t="n">
         <v>0.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>382.0</v>
+        <v>384.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2562,7 +2562,7 @@
         <v>739</v>
       </c>
       <c r="F11" t="n">
-        <v>299.0</v>
+        <v>300.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -3966,7 +3966,7 @@
         <v>739</v>
       </c>
       <c r="F65" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -4252,7 +4252,7 @@
         <v>740</v>
       </c>
       <c r="F76" t="n">
-        <v>351.0</v>
+        <v>353.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -4304,7 +4304,7 @@
         <v>740</v>
       </c>
       <c r="F78" t="n">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -6930,7 +6930,7 @@
         <v>739</v>
       </c>
       <c r="F179" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7190,7 +7190,7 @@
         <v>739</v>
       </c>
       <c r="F189" t="n">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
       <c r="G189" t="n">
         <v>1.0</v>
@@ -7268,7 +7268,7 @@
         <v>740</v>
       </c>
       <c r="F192" t="n">
-        <v>668.0</v>
+        <v>671.0</v>
       </c>
       <c r="G192" t="n">
         <v>1.0</v>
@@ -7554,7 +7554,7 @@
         <v>740</v>
       </c>
       <c r="F203" t="n">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -8542,7 +8542,7 @@
         <v>739</v>
       </c>
       <c r="F241" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G241" t="n">
         <v>0.0</v>
@@ -9400,7 +9400,7 @@
         <v>739</v>
       </c>
       <c r="F274" t="n">
-        <v>611.0</v>
+        <v>612.0</v>
       </c>
       <c r="G274" t="n">
         <v>25.0</v>
@@ -9764,7 +9764,7 @@
         <v>739</v>
       </c>
       <c r="F288" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G288" t="n">
         <v>4.0</v>
@@ -10388,7 +10388,7 @@
         <v>739</v>
       </c>
       <c r="F312" t="n">
-        <v>1002.0</v>
+        <v>1007.0</v>
       </c>
       <c r="G312" t="n">
         <v>20.0</v>
@@ -10570,7 +10570,7 @@
         <v>739</v>
       </c>
       <c r="F319" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G319" t="n">
         <v>6.0</v>
@@ -10856,7 +10856,7 @@
         <v>739</v>
       </c>
       <c r="F330" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G330" t="n">
         <v>1.0</v>
@@ -11847,7 +11847,7 @@
         <v>101.0</v>
       </c>
       <c r="G368" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H368" t="n">
         <v>7.0</v>
@@ -12104,7 +12104,7 @@
         <v>740</v>
       </c>
       <c r="F378" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G378" t="n">
         <v>0.0</v>
@@ -12416,7 +12416,7 @@
         <v>740</v>
       </c>
       <c r="F390" t="n">
-        <v>123.0</v>
+        <v>125.0</v>
       </c>
       <c r="G390" t="n">
         <v>0.0</v>
@@ -13976,7 +13976,7 @@
         <v>739</v>
       </c>
       <c r="F450" t="n">
-        <v>135.0</v>
+        <v>139.0</v>
       </c>
       <c r="G450" t="n">
         <v>4.0</v>
@@ -14421,7 +14421,7 @@
         <v>134.0</v>
       </c>
       <c r="G467" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="H467" t="n">
         <v>0.0</v>
@@ -16498,7 +16498,7 @@
         <v>740</v>
       </c>
       <c r="F547" t="n">
-        <v>316.0</v>
+        <v>318.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -16576,7 +16576,7 @@
         <v>740</v>
       </c>
       <c r="F550" t="n">
-        <v>261.0</v>
+        <v>264.0</v>
       </c>
       <c r="G550" t="n">
         <v>1.0</v>
@@ -16628,7 +16628,7 @@
         <v>739</v>
       </c>
       <c r="F552" t="n">
-        <v>127.0</v>
+        <v>131.0</v>
       </c>
       <c r="G552" t="n">
         <v>1.0</v>
@@ -17486,7 +17486,7 @@
         <v>740</v>
       </c>
       <c r="F585" t="n">
-        <v>277.0</v>
+        <v>280.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>580.0</v>
+        <v>581.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2432,7 +2432,7 @@
         <v>739</v>
       </c>
       <c r="F6" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G6" t="n">
         <v>10.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>459.0</v>
+        <v>461.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2822,7 +2822,7 @@
         <v>739</v>
       </c>
       <c r="F21" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2900,7 +2900,7 @@
         <v>740</v>
       </c>
       <c r="F24" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3680,7 +3680,7 @@
         <v>739</v>
       </c>
       <c r="F54" t="n">
-        <v>122.0</v>
+        <v>124.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4044,7 +4044,7 @@
         <v>740</v>
       </c>
       <c r="F68" t="n">
-        <v>184.0</v>
+        <v>187.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -5032,7 +5032,7 @@
         <v>739</v>
       </c>
       <c r="F106" t="n">
-        <v>501.0</v>
+        <v>505.0</v>
       </c>
       <c r="G106" t="n">
         <v>2.0</v>
@@ -5214,7 +5214,7 @@
         <v>739</v>
       </c>
       <c r="F113" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -5682,13 +5682,13 @@
         <v>739</v>
       </c>
       <c r="F131" t="n">
-        <v>284.0</v>
+        <v>286.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
       </c>
       <c r="H131" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -5838,7 +5838,7 @@
         <v>739</v>
       </c>
       <c r="F137" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -5968,7 +5968,7 @@
         <v>739</v>
       </c>
       <c r="F142" t="n">
-        <v>654.0</v>
+        <v>657.0</v>
       </c>
       <c r="G142" t="n">
         <v>2.0</v>
@@ -6436,7 +6436,7 @@
         <v>739</v>
       </c>
       <c r="F160" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G160" t="n">
         <v>2.0</v>
@@ -6618,7 +6618,7 @@
         <v>740</v>
       </c>
       <c r="F167" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6800,7 +6800,7 @@
         <v>739</v>
       </c>
       <c r="F174" t="n">
-        <v>313.0</v>
+        <v>314.0</v>
       </c>
       <c r="G174" t="n">
         <v>1.0</v>
@@ -7008,7 +7008,7 @@
         <v>740</v>
       </c>
       <c r="F182" t="n">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
       <c r="G182" t="n">
         <v>0.0</v>
@@ -8340,7 +8340,7 @@
         <v>0.0</v>
       </c>
       <c r="H233" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="234">
@@ -10544,7 +10544,7 @@
         <v>739</v>
       </c>
       <c r="F318" t="n">
-        <v>493.0</v>
+        <v>495.0</v>
       </c>
       <c r="G318" t="n">
         <v>0.0</v>
@@ -11194,7 +11194,7 @@
         <v>739</v>
       </c>
       <c r="F343" t="n">
-        <v>406.0</v>
+        <v>407.0</v>
       </c>
       <c r="G343" t="n">
         <v>1.0</v>
@@ -12468,13 +12468,13 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>115.0</v>
+        <v>122.0</v>
       </c>
       <c r="G392" t="n">
         <v>0.0</v>
       </c>
       <c r="H392" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="393">
@@ -12494,7 +12494,7 @@
         <v>739</v>
       </c>
       <c r="F393" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="G393" t="n">
         <v>1.0</v>
@@ -12604,7 +12604,7 @@
         <v>0.0</v>
       </c>
       <c r="H397" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="398">
@@ -12780,7 +12780,7 @@
         <v>739</v>
       </c>
       <c r="F404" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G404" t="n">
         <v>1.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>565.0</v>
+        <v>566.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -14028,7 +14028,7 @@
         <v>740</v>
       </c>
       <c r="F452" t="n">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -14548,7 +14548,7 @@
         <v>739</v>
       </c>
       <c r="F472" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G472" t="n">
         <v>0.0</v>
@@ -15406,7 +15406,7 @@
         <v>739</v>
       </c>
       <c r="F505" t="n">
-        <v>586.0</v>
+        <v>590.0</v>
       </c>
       <c r="G505" t="n">
         <v>0.0</v>
@@ -16368,7 +16368,7 @@
         <v>740</v>
       </c>
       <c r="F542" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="G542" t="n">
         <v>0.0</v>
@@ -17590,7 +17590,7 @@
         <v>739</v>
       </c>
       <c r="F589" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -17668,7 +17668,7 @@
         <v>739</v>
       </c>
       <c r="F592" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -18760,7 +18760,7 @@
         <v>739</v>
       </c>
       <c r="F634" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>
@@ -19722,7 +19722,7 @@
         <v>739</v>
       </c>
       <c r="F671" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19904,7 +19904,7 @@
         <v>739</v>
       </c>
       <c r="F678" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G678" t="n">
         <v>0.0</v>
@@ -19930,7 +19930,7 @@
         <v>739</v>
       </c>
       <c r="F679" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20034,7 +20034,7 @@
         <v>740</v>
       </c>
       <c r="F683" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20424,7 +20424,7 @@
         <v>739</v>
       </c>
       <c r="F698" t="n">
-        <v>400.0</v>
+        <v>406.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20476,7 +20476,7 @@
         <v>740</v>
       </c>
       <c r="F700" t="n">
-        <v>129.0</v>
+        <v>132.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20554,7 +20554,7 @@
         <v>740</v>
       </c>
       <c r="F703" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -20632,7 +20632,7 @@
         <v>740</v>
       </c>
       <c r="F706" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -20970,7 +20970,7 @@
         <v>740</v>
       </c>
       <c r="F719" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -21100,10 +21100,10 @@
         <v>739</v>
       </c>
       <c r="F724" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G724" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="H724" t="n">
         <v>1.0</v>
@@ -21256,7 +21256,7 @@
         <v>740</v>
       </c>
       <c r="F730" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G730" t="n">
         <v>0.0</v>
@@ -21386,7 +21386,7 @@
         <v>740</v>
       </c>
       <c r="F735" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G735" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>581.0</v>
+        <v>583.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -3186,7 +3186,7 @@
         <v>739</v>
       </c>
       <c r="F35" t="n">
-        <v>203.0</v>
+        <v>206.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4044,7 +4044,7 @@
         <v>740</v>
       </c>
       <c r="F68" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -4073,7 +4073,7 @@
         <v>151.0</v>
       </c>
       <c r="G69" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="H69" t="n">
         <v>3.0</v>
@@ -4174,7 +4174,7 @@
         <v>739</v>
       </c>
       <c r="F73" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4460,7 +4460,7 @@
         <v>740</v>
       </c>
       <c r="F84" t="n">
-        <v>398.0</v>
+        <v>400.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -5032,7 +5032,7 @@
         <v>739</v>
       </c>
       <c r="F106" t="n">
-        <v>505.0</v>
+        <v>506.0</v>
       </c>
       <c r="G106" t="n">
         <v>2.0</v>
@@ -5682,7 +5682,7 @@
         <v>739</v>
       </c>
       <c r="F131" t="n">
-        <v>286.0</v>
+        <v>288.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
@@ -7476,7 +7476,7 @@
         <v>739</v>
       </c>
       <c r="F200" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G200" t="n">
         <v>0.0</v>
@@ -9764,7 +9764,7 @@
         <v>739</v>
       </c>
       <c r="F288" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="G288" t="n">
         <v>4.0</v>
@@ -9871,7 +9871,7 @@
         <v>538.0</v>
       </c>
       <c r="G292" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="H292" t="n">
         <v>6.0</v>
@@ -9894,13 +9894,13 @@
         <v>739</v>
       </c>
       <c r="F293" t="n">
-        <v>36.0</v>
+        <v>44.0</v>
       </c>
       <c r="G293" t="n">
         <v>0.0</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="294">
@@ -10726,7 +10726,7 @@
         <v>740</v>
       </c>
       <c r="F325" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="G325" t="n">
         <v>0.0</v>
@@ -11275,7 +11275,7 @@
         <v>201.0</v>
       </c>
       <c r="G346" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H346" t="n">
         <v>2.0</v>
@@ -12728,7 +12728,7 @@
         <v>739</v>
       </c>
       <c r="F402" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G402" t="n">
         <v>2.0</v>
@@ -13823,7 +13823,7 @@
         <v>220.0</v>
       </c>
       <c r="G444" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H444" t="n">
         <v>1.0</v>
@@ -14288,7 +14288,7 @@
         <v>740</v>
       </c>
       <c r="F462" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="G462" t="n">
         <v>0.0</v>
@@ -14522,7 +14522,7 @@
         <v>741</v>
       </c>
       <c r="F471" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G471" t="n">
         <v>0.0</v>
@@ -15822,7 +15822,7 @@
         <v>739</v>
       </c>
       <c r="F521" t="n">
-        <v>2379.0</v>
+        <v>2381.0</v>
       </c>
       <c r="G521" t="n">
         <v>305.0</v>
@@ -16628,7 +16628,7 @@
         <v>739</v>
       </c>
       <c r="F552" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G552" t="n">
         <v>1.0</v>
@@ -16862,7 +16862,7 @@
         <v>739</v>
       </c>
       <c r="F561" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
       <c r="G561" t="n">
         <v>0.0</v>
@@ -19098,7 +19098,7 @@
         <v>740</v>
       </c>
       <c r="F647" t="n">
-        <v>164.0</v>
+        <v>168.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19774,7 +19774,7 @@
         <v>739</v>
       </c>
       <c r="F673" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20424,7 +20424,7 @@
         <v>739</v>
       </c>
       <c r="F698" t="n">
-        <v>406.0</v>
+        <v>417.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20476,7 +20476,7 @@
         <v>740</v>
       </c>
       <c r="F700" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20840,7 +20840,7 @@
         <v>739</v>
       </c>
       <c r="F714" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G714" t="n">
         <v>0.0</v>
@@ -20866,7 +20866,7 @@
         <v>740</v>
       </c>
       <c r="F715" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="G715" t="n">
         <v>0.0</v>
@@ -21386,7 +21386,7 @@
         <v>740</v>
       </c>
       <c r="F735" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G735" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2796,7 +2796,7 @@
         <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>145.0</v>
+        <v>148.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -2874,7 +2874,7 @@
         <v>740</v>
       </c>
       <c r="F23" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -2900,7 +2900,7 @@
         <v>740</v>
       </c>
       <c r="F24" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -4252,7 +4252,7 @@
         <v>740</v>
       </c>
       <c r="F76" t="n">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
         <v>740</v>
       </c>
       <c r="F84" t="n">
-        <v>400.0</v>
+        <v>401.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -5191,7 +5191,7 @@
         <v>0.0</v>
       </c>
       <c r="G112" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -5552,7 +5552,7 @@
         <v>739</v>
       </c>
       <c r="F126" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G126" t="n">
         <v>0.0</v>
@@ -5630,7 +5630,7 @@
         <v>739</v>
       </c>
       <c r="F129" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G129" t="n">
         <v>11.0</v>
@@ -6956,7 +6956,7 @@
         <v>740</v>
       </c>
       <c r="F180" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -7268,7 +7268,7 @@
         <v>740</v>
       </c>
       <c r="F192" t="n">
-        <v>671.0</v>
+        <v>673.0</v>
       </c>
       <c r="G192" t="n">
         <v>1.0</v>
@@ -8100,7 +8100,7 @@
         <v>739</v>
       </c>
       <c r="F224" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G224" t="n">
         <v>0.0</v>
@@ -8308,7 +8308,7 @@
         <v>739</v>
       </c>
       <c r="F232" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -8412,7 +8412,7 @@
         <v>739</v>
       </c>
       <c r="F236" t="n">
-        <v>395.0</v>
+        <v>396.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -9169,7 +9169,7 @@
         <v>0.0</v>
       </c>
       <c r="G265" t="n">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="H265" t="n">
         <v>0.0</v>
@@ -9192,7 +9192,7 @@
         <v>739</v>
       </c>
       <c r="F266" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G266" t="n">
         <v>0.0</v>
@@ -9634,7 +9634,7 @@
         <v>739</v>
       </c>
       <c r="F283" t="n">
-        <v>498.0</v>
+        <v>500.0</v>
       </c>
       <c r="G283" t="n">
         <v>0.0</v>
@@ -10726,7 +10726,7 @@
         <v>740</v>
       </c>
       <c r="F325" t="n">
-        <v>236.0</v>
+        <v>238.0</v>
       </c>
       <c r="G325" t="n">
         <v>0.0</v>
@@ -11740,7 +11740,7 @@
         <v>740</v>
       </c>
       <c r="F364" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G364" t="n">
         <v>0.0</v>
@@ -12416,7 +12416,7 @@
         <v>740</v>
       </c>
       <c r="F390" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G390" t="n">
         <v>0.0</v>
@@ -13404,7 +13404,7 @@
         <v>740</v>
       </c>
       <c r="F428" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -13742,7 +13742,7 @@
         <v>739</v>
       </c>
       <c r="F441" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G441" t="n">
         <v>7.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>566.0</v>
+        <v>567.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -14028,7 +14028,7 @@
         <v>740</v>
       </c>
       <c r="F452" t="n">
-        <v>444.0</v>
+        <v>445.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -14054,7 +14054,7 @@
         <v>739</v>
       </c>
       <c r="F453" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="G453" t="n">
         <v>11.0</v>
@@ -15773,7 +15773,7 @@
         <v>0.0</v>
       </c>
       <c r="G519" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="H519" t="n">
         <v>0.0</v>
@@ -18058,7 +18058,7 @@
         <v>739</v>
       </c>
       <c r="F607" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="G607" t="n">
         <v>0.0</v>
@@ -18734,7 +18734,7 @@
         <v>740</v>
       </c>
       <c r="F633" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G633" t="n">
         <v>1851.0</v>
@@ -18994,7 +18994,7 @@
         <v>739</v>
       </c>
       <c r="F643" t="n">
-        <v>95.0</v>
+        <v>97.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -19647,7 +19647,7 @@
         <v>0.0</v>
       </c>
       <c r="G668" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="H668" t="n">
         <v>0.0</v>
@@ -19670,7 +19670,7 @@
         <v>739</v>
       </c>
       <c r="F669" t="n">
-        <v>177.0</v>
+        <v>180.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -19699,7 +19699,7 @@
         <v>0.0</v>
       </c>
       <c r="G670" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="H670" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -14028,7 +14028,7 @@
         <v>740</v>
       </c>
       <c r="F452" t="n">
-        <v>445.0</v>
+        <v>447.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -20294,7 +20294,7 @@
         <v>739</v>
       </c>
       <c r="F693" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G693" t="n">
         <v>0.0</v>
@@ -20372,7 +20372,7 @@
         <v>740</v>
       </c>
       <c r="F696" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G696" t="n">
         <v>0.0</v>
@@ -20892,7 +20892,7 @@
         <v>740</v>
       </c>
       <c r="F716" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G716" t="n">
         <v>0.0</v>
@@ -21048,7 +21048,7 @@
         <v>740</v>
       </c>
       <c r="F722" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2796,7 +2796,7 @@
         <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>148.0</v>
+        <v>152.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -5812,7 +5812,7 @@
         <v>739</v>
       </c>
       <c r="F136" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -6260,7 +6260,7 @@
         <v>0.0</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="154">
@@ -6670,7 +6670,7 @@
         <v>740</v>
       </c>
       <c r="F169" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -7606,7 +7606,7 @@
         <v>740</v>
       </c>
       <c r="F205" t="n">
-        <v>1004.0</v>
+        <v>1006.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -9010,7 +9010,7 @@
         <v>739</v>
       </c>
       <c r="F259" t="n">
-        <v>938.0</v>
+        <v>942.0</v>
       </c>
       <c r="G259" t="n">
         <v>23.0</v>
@@ -9270,7 +9270,7 @@
         <v>739</v>
       </c>
       <c r="F269" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="G269" t="n">
         <v>7.0</v>
@@ -9842,7 +9842,7 @@
         <v>739</v>
       </c>
       <c r="F291" t="n">
-        <v>538.0</v>
+        <v>540.0</v>
       </c>
       <c r="G291" t="n">
         <v>40.0</v>
@@ -9868,7 +9868,7 @@
         <v>739</v>
       </c>
       <c r="F292" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -9946,7 +9946,7 @@
         <v>739</v>
       </c>
       <c r="F295" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
       <c r="G295" t="n">
         <v>11.0</v>
@@ -11844,7 +11844,7 @@
         <v>740</v>
       </c>
       <c r="F368" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -12364,7 +12364,7 @@
         <v>739</v>
       </c>
       <c r="F388" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G388" t="n">
         <v>15.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>568.0</v>
+        <v>569.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14054,7 +14054,7 @@
         <v>739</v>
       </c>
       <c r="F453" t="n">
-        <v>760.0</v>
+        <v>762.0</v>
       </c>
       <c r="G453" t="n">
         <v>0.0</v>
@@ -14418,7 +14418,7 @@
         <v>739</v>
       </c>
       <c r="F467" t="n">
-        <v>56.0</v>
+        <v>59.0</v>
       </c>
       <c r="G467" t="n">
         <v>0.0</v>
@@ -14522,7 +14522,7 @@
         <v>739</v>
       </c>
       <c r="F471" t="n">
-        <v>184.0</v>
+        <v>187.0</v>
       </c>
       <c r="G471" t="n">
         <v>0.0</v>
@@ -15900,7 +15900,7 @@
         <v>739</v>
       </c>
       <c r="F524" t="n">
-        <v>195.0</v>
+        <v>199.0</v>
       </c>
       <c r="G524" t="n">
         <v>9.0</v>
@@ -16108,7 +16108,7 @@
         <v>739</v>
       </c>
       <c r="F532" t="n">
-        <v>409.0</v>
+        <v>412.0</v>
       </c>
       <c r="G532" t="n">
         <v>3.0</v>
@@ -16680,7 +16680,7 @@
         <v>739</v>
       </c>
       <c r="F554" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G554" t="n">
         <v>8.0</v>
@@ -16784,7 +16784,7 @@
         <v>741</v>
       </c>
       <c r="F558" t="n">
-        <v>205.0</v>
+        <v>209.0</v>
       </c>
       <c r="G558" t="n">
         <v>8.0</v>
@@ -18812,7 +18812,7 @@
         <v>739</v>
       </c>
       <c r="F636" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G636" t="n">
         <v>8.0</v>
@@ -20999,7 +20999,7 @@
         <v>160.0</v>
       </c>
       <c r="G720" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H720" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>586.0</v>
+        <v>588.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2435,7 +2435,7 @@
         <v>32.0</v>
       </c>
       <c r="G6" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="H6" t="n">
         <v>0.0</v>
@@ -2591,7 +2591,7 @@
         <v>0.0</v>
       </c>
       <c r="G12" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -2926,7 +2926,7 @@
         <v>739</v>
       </c>
       <c r="F25" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -3108,7 +3108,7 @@
         <v>740</v>
       </c>
       <c r="F32" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3186,7 +3186,7 @@
         <v>739</v>
       </c>
       <c r="F35" t="n">
-        <v>206.0</v>
+        <v>208.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>502.0</v>
+        <v>505.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3475,7 +3475,7 @@
         <v>287.0</v>
       </c>
       <c r="G46" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H46" t="n">
         <v>3.0</v>
@@ -4408,7 +4408,7 @@
         <v>739</v>
       </c>
       <c r="F82" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>401.0</v>
+        <v>404.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4668,7 +4668,7 @@
         <v>741</v>
       </c>
       <c r="F92" t="n">
-        <v>468.0</v>
+        <v>469.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>506.0</v>
+        <v>509.0</v>
       </c>
       <c r="G105" t="n">
         <v>2.0</v>
@@ -5370,10 +5370,10 @@
         <v>739</v>
       </c>
       <c r="F119" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>451.0</v>
+        <v>452.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5786,7 +5786,7 @@
         <v>739</v>
       </c>
       <c r="F135" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G135" t="n">
         <v>13.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>657.0</v>
+        <v>659.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6280,7 +6280,7 @@
         <v>740</v>
       </c>
       <c r="F154" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G154" t="n">
         <v>0.0</v>
@@ -6332,7 +6332,7 @@
         <v>740</v>
       </c>
       <c r="F156" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -6514,7 +6514,7 @@
         <v>740</v>
       </c>
       <c r="F163" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G163" t="n">
         <v>0.0</v>
@@ -6722,7 +6722,7 @@
         <v>740</v>
       </c>
       <c r="F171" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6774,7 +6774,7 @@
         <v>739</v>
       </c>
       <c r="F173" t="n">
-        <v>314.0</v>
+        <v>315.0</v>
       </c>
       <c r="G173" t="n">
         <v>1.0</v>
@@ -6881,7 +6881,7 @@
         <v>19.0</v>
       </c>
       <c r="G177" t="n">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -6930,7 +6930,7 @@
         <v>740</v>
       </c>
       <c r="F179" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>511.0</v>
+        <v>513.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7502,7 +7502,7 @@
         <v>739</v>
       </c>
       <c r="F201" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G201" t="n">
         <v>0.0</v>
@@ -7606,7 +7606,7 @@
         <v>740</v>
       </c>
       <c r="F205" t="n">
-        <v>1006.0</v>
+        <v>1008.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -7788,7 +7788,7 @@
         <v>740</v>
       </c>
       <c r="F212" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -8178,7 +8178,7 @@
         <v>739</v>
       </c>
       <c r="F227" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
       <c r="G227" t="n">
         <v>3.0</v>
@@ -9010,7 +9010,7 @@
         <v>739</v>
       </c>
       <c r="F259" t="n">
-        <v>942.0</v>
+        <v>943.0</v>
       </c>
       <c r="G259" t="n">
         <v>23.0</v>
@@ -9244,7 +9244,7 @@
         <v>739</v>
       </c>
       <c r="F268" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="G268" t="n">
         <v>0.0</v>
@@ -9530,7 +9530,7 @@
         <v>739</v>
       </c>
       <c r="F279" t="n">
-        <v>165.0</v>
+        <v>168.0</v>
       </c>
       <c r="G279" t="n">
         <v>7.0</v>
@@ -10310,7 +10310,7 @@
         <v>739</v>
       </c>
       <c r="F309" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G309" t="n">
         <v>0.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1007.0</v>
+        <v>1011.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>497.0</v>
+        <v>500.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>238.0</v>
+        <v>240.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10726,7 +10726,7 @@
         <v>739</v>
       </c>
       <c r="F325" t="n">
-        <v>533.0</v>
+        <v>538.0</v>
       </c>
       <c r="G325" t="n">
         <v>8.0</v>
@@ -10908,7 +10908,7 @@
         <v>739</v>
       </c>
       <c r="F332" t="n">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="G332" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>530.0</v>
+        <v>531.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -11844,7 +11844,7 @@
         <v>740</v>
       </c>
       <c r="F368" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -12052,7 +12052,7 @@
         <v>740</v>
       </c>
       <c r="F376" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -12416,7 +12416,7 @@
         <v>739</v>
       </c>
       <c r="F390" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G390" t="n">
         <v>2.0</v>
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>247.0</v>
+        <v>249.0</v>
       </c>
       <c r="G392" t="n">
         <v>1.0</v>
@@ -14496,7 +14496,7 @@
         <v>741</v>
       </c>
       <c r="F470" t="n">
-        <v>529.0</v>
+        <v>532.0</v>
       </c>
       <c r="G470" t="n">
         <v>0.0</v>
@@ -14941,7 +14941,7 @@
         <v>235.0</v>
       </c>
       <c r="G487" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H487" t="n">
         <v>1.0</v>
@@ -15380,7 +15380,7 @@
         <v>739</v>
       </c>
       <c r="F504" t="n">
-        <v>592.0</v>
+        <v>595.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
@@ -15900,7 +15900,7 @@
         <v>739</v>
       </c>
       <c r="F524" t="n">
-        <v>199.0</v>
+        <v>201.0</v>
       </c>
       <c r="G524" t="n">
         <v>9.0</v>
@@ -16004,7 +16004,7 @@
         <v>741</v>
       </c>
       <c r="F528" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="G528" t="n">
         <v>3.0</v>
@@ -16264,7 +16264,7 @@
         <v>739</v>
       </c>
       <c r="F538" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G538" t="n">
         <v>5.0</v>
@@ -17564,7 +17564,7 @@
         <v>739</v>
       </c>
       <c r="F588" t="n">
-        <v>92.0</v>
+        <v>94.0</v>
       </c>
       <c r="G588" t="n">
         <v>0.0</v>
@@ -17642,7 +17642,7 @@
         <v>739</v>
       </c>
       <c r="F591" t="n">
-        <v>311.0</v>
+        <v>314.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -18136,7 +18136,7 @@
         <v>740</v>
       </c>
       <c r="F610" t="n">
-        <v>390.0</v>
+        <v>392.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
@@ -18968,7 +18968,7 @@
         <v>739</v>
       </c>
       <c r="F642" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -19670,7 +19670,7 @@
         <v>739</v>
       </c>
       <c r="F669" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -19826,7 +19826,7 @@
         <v>739</v>
       </c>
       <c r="F675" t="n">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19852,7 +19852,7 @@
         <v>739</v>
       </c>
       <c r="F676" t="n">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -19956,7 +19956,7 @@
         <v>740</v>
       </c>
       <c r="F680" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -20112,7 +20112,7 @@
         <v>740</v>
       </c>
       <c r="F686" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G686" t="n">
         <v>0.0</v>
@@ -20138,7 +20138,7 @@
         <v>739</v>
       </c>
       <c r="F687" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="G687" t="n">
         <v>0.0</v>
@@ -20216,7 +20216,7 @@
         <v>741</v>
       </c>
       <c r="F690" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20242,7 +20242,7 @@
         <v>740</v>
       </c>
       <c r="F691" t="n">
-        <v>72.0</v>
+        <v>89.0</v>
       </c>
       <c r="G691" t="n">
         <v>0.0</v>
@@ -20268,7 +20268,7 @@
         <v>740</v>
       </c>
       <c r="F692" t="n">
-        <v>51.0</v>
+        <v>60.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="F694" t="n">
-        <v>110.0</v>
+        <v>116.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>134.0</v>
+        <v>137.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20424,7 +20424,7 @@
         <v>740</v>
       </c>
       <c r="F698" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20580,7 +20580,7 @@
         <v>740</v>
       </c>
       <c r="F704" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G704" t="n">
         <v>0.0</v>
@@ -20632,7 +20632,7 @@
         <v>739</v>
       </c>
       <c r="F706" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20658,7 +20658,7 @@
         <v>740</v>
       </c>
       <c r="F707" t="n">
-        <v>48.0</v>
+        <v>55.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20736,7 +20736,7 @@
         <v>739</v>
       </c>
       <c r="F710" t="n">
-        <v>109.0</v>
+        <v>112.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -20918,7 +20918,7 @@
         <v>740</v>
       </c>
       <c r="F717" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G717" t="n">
         <v>0.0</v>
@@ -20970,7 +20970,7 @@
         <v>739</v>
       </c>
       <c r="F719" t="n">
-        <v>100.0</v>
+        <v>104.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -20996,7 +20996,7 @@
         <v>741</v>
       </c>
       <c r="F720" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="G720" t="n">
         <v>12.0</v>
@@ -21074,7 +21074,7 @@
         <v>741</v>
       </c>
       <c r="F723" t="n">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -21282,7 +21282,7 @@
         <v>740</v>
       </c>
       <c r="F731" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G731" t="n">
         <v>0.0</v>
@@ -21308,7 +21308,7 @@
         <v>739</v>
       </c>
       <c r="F732" t="n">
-        <v>309.0</v>
+        <v>311.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21438,10 +21438,10 @@
         <v>741</v>
       </c>
       <c r="F737" t="n">
-        <v>57.0</v>
+        <v>65.0</v>
       </c>
       <c r="G737" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H737" t="n">
         <v>0.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>388.0</v>
+        <v>391.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>588.0</v>
+        <v>589.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2432,7 +2432,7 @@
         <v>739</v>
       </c>
       <c r="F6" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G6" t="n">
         <v>13.0</v>
@@ -2458,7 +2458,7 @@
         <v>739</v>
       </c>
       <c r="F7" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G7" t="n">
         <v>22.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>396.0</v>
+        <v>397.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2822,7 +2822,7 @@
         <v>739</v>
       </c>
       <c r="F21" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>363.0</v>
+        <v>367.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2900,7 +2900,7 @@
         <v>740</v>
       </c>
       <c r="F24" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>505.0</v>
+        <v>507.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3680,7 +3680,7 @@
         <v>739</v>
       </c>
       <c r="F54" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4018,7 +4018,7 @@
         <v>740</v>
       </c>
       <c r="F67" t="n">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -5136,7 +5136,7 @@
         <v>740</v>
       </c>
       <c r="F110" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>452.0</v>
+        <v>453.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -6228,7 +6228,7 @@
         <v>739</v>
       </c>
       <c r="F152" t="n">
-        <v>212.0</v>
+        <v>214.0</v>
       </c>
       <c r="G152" t="n">
         <v>2.0</v>
@@ -7398,7 +7398,7 @@
         <v>739</v>
       </c>
       <c r="F197" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="G197" t="n">
         <v>1.0</v>
@@ -7424,7 +7424,7 @@
         <v>739</v>
       </c>
       <c r="F198" t="n">
-        <v>322.0</v>
+        <v>324.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -8074,7 +8074,7 @@
         <v>739</v>
       </c>
       <c r="F223" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G223" t="n">
         <v>0.0</v>
@@ -8308,7 +8308,7 @@
         <v>739</v>
       </c>
       <c r="F232" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -8438,7 +8438,7 @@
         <v>740</v>
       </c>
       <c r="F237" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -9738,7 +9738,7 @@
         <v>739</v>
       </c>
       <c r="F287" t="n">
-        <v>259.0</v>
+        <v>262.0</v>
       </c>
       <c r="G287" t="n">
         <v>4.0</v>
@@ -10934,7 +10934,7 @@
         <v>739</v>
       </c>
       <c r="F333" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G333" t="n">
         <v>0.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>531.0</v>
+        <v>532.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G392" t="n">
         <v>1.0</v>
@@ -12702,7 +12702,7 @@
         <v>739</v>
       </c>
       <c r="F401" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="G401" t="n">
         <v>2.0</v>
@@ -12780,7 +12780,7 @@
         <v>739</v>
       </c>
       <c r="F404" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G404" t="n">
         <v>3.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>569.0</v>
+        <v>571.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14002,7 +14002,7 @@
         <v>740</v>
       </c>
       <c r="F451" t="n">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14262,7 +14262,7 @@
         <v>740</v>
       </c>
       <c r="F461" t="n">
-        <v>379.0</v>
+        <v>380.0</v>
       </c>
       <c r="G461" t="n">
         <v>0.0</v>
@@ -14938,7 +14938,7 @@
         <v>739</v>
       </c>
       <c r="F487" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="G487" t="n">
         <v>2.0</v>
@@ -15747,7 +15747,7 @@
         <v>0.0</v>
       </c>
       <c r="G518" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="H518" t="n">
         <v>0.0</v>
@@ -15796,10 +15796,10 @@
         <v>739</v>
       </c>
       <c r="F520" t="n">
-        <v>2381.0</v>
+        <v>2384.0</v>
       </c>
       <c r="G520" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="H520" t="n">
         <v>45.0</v>
@@ -16342,7 +16342,7 @@
         <v>740</v>
       </c>
       <c r="F541" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="G541" t="n">
         <v>0.0</v>
@@ -16810,7 +16810,7 @@
         <v>739</v>
       </c>
       <c r="F559" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G559" t="n">
         <v>0.0</v>
@@ -18734,7 +18734,7 @@
         <v>739</v>
       </c>
       <c r="F633" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -19384,7 +19384,7 @@
         <v>740</v>
       </c>
       <c r="F658" t="n">
-        <v>106.0</v>
+        <v>109.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -20164,7 +20164,7 @@
         <v>739</v>
       </c>
       <c r="F688" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G688" t="n">
         <v>2.0</v>
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="F694" t="n">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20346,7 +20346,7 @@
         <v>741</v>
       </c>
       <c r="F695" t="n">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21360,7 +21360,7 @@
         <v>740</v>
       </c>
       <c r="F734" t="n">
-        <v>149.0</v>
+        <v>151.0</v>
       </c>
       <c r="G734" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>589.0</v>
+        <v>590.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>397.0</v>
+        <v>398.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -3108,7 +3108,7 @@
         <v>740</v>
       </c>
       <c r="F32" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -5373,7 +5373,7 @@
         <v>26.0</v>
       </c>
       <c r="G119" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5656,7 +5656,7 @@
         <v>739</v>
       </c>
       <c r="F130" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -6566,7 +6566,7 @@
         <v>739</v>
       </c>
       <c r="F165" t="n">
-        <v>342.0</v>
+        <v>343.0</v>
       </c>
       <c r="G165" t="n">
         <v>0.0</v>
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>500.0</v>
+        <v>503.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -14002,7 +14002,7 @@
         <v>740</v>
       </c>
       <c r="F451" t="n">
-        <v>448.0</v>
+        <v>449.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14496,7 +14496,7 @@
         <v>741</v>
       </c>
       <c r="F470" t="n">
-        <v>532.0</v>
+        <v>534.0</v>
       </c>
       <c r="G470" t="n">
         <v>0.0</v>
@@ -17564,7 +17564,7 @@
         <v>739</v>
       </c>
       <c r="F588" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G588" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>137.0</v>
+        <v>141.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2432,7 +2432,7 @@
         <v>739</v>
       </c>
       <c r="F6" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G6" t="n">
         <v>13.0</v>
@@ -7658,7 +7658,7 @@
         <v>741</v>
       </c>
       <c r="F207" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G207" t="n">
         <v>0.0</v>
@@ -14002,7 +14002,7 @@
         <v>740</v>
       </c>
       <c r="F451" t="n">
-        <v>449.0</v>
+        <v>452.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -20216,7 +20216,7 @@
         <v>741</v>
       </c>
       <c r="F690" t="n">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>462.0</v>
+        <v>464.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2666,7 +2666,7 @@
         <v>739</v>
       </c>
       <c r="F15" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -3186,7 +3186,7 @@
         <v>739</v>
       </c>
       <c r="F35" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>507.0</v>
+        <v>509.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3342,7 +3342,7 @@
         <v>739</v>
       </c>
       <c r="F41" t="n">
-        <v>325.0</v>
+        <v>329.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -3472,7 +3472,7 @@
         <v>739</v>
       </c>
       <c r="F46" t="n">
-        <v>287.0</v>
+        <v>294.0</v>
       </c>
       <c r="G46" t="n">
         <v>12.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>404.0</v>
+        <v>407.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4902,7 +4902,7 @@
         <v>740</v>
       </c>
       <c r="F101" t="n">
-        <v>427.0</v>
+        <v>432.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -5110,7 +5110,7 @@
         <v>740</v>
       </c>
       <c r="F109" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>454.0</v>
+        <v>455.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5864,7 +5864,7 @@
         <v>741</v>
       </c>
       <c r="F138" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -6046,7 +6046,7 @@
         <v>739</v>
       </c>
       <c r="F145" t="n">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
       <c r="G145" t="n">
         <v>6.0</v>
@@ -6462,7 +6462,7 @@
         <v>740</v>
       </c>
       <c r="F161" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6566,7 +6566,7 @@
         <v>739</v>
       </c>
       <c r="F165" t="n">
-        <v>343.0</v>
+        <v>344.0</v>
       </c>
       <c r="G165" t="n">
         <v>0.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>513.0</v>
+        <v>514.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7528,7 +7528,7 @@
         <v>740</v>
       </c>
       <c r="F202" t="n">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="G202" t="n">
         <v>0.0</v>
@@ -7866,7 +7866,7 @@
         <v>739</v>
       </c>
       <c r="F215" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G215" t="n">
         <v>2.0</v>
@@ -8074,7 +8074,7 @@
         <v>739</v>
       </c>
       <c r="F223" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G223" t="n">
         <v>0.0</v>
@@ -8178,7 +8178,7 @@
         <v>739</v>
       </c>
       <c r="F227" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G227" t="n">
         <v>3.0</v>
@@ -8308,13 +8308,13 @@
         <v>739</v>
       </c>
       <c r="F232" t="n">
-        <v>237.0</v>
+        <v>242.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
       </c>
       <c r="H232" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="233">
@@ -8334,7 +8334,7 @@
         <v>739</v>
       </c>
       <c r="F233" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G233" t="n">
         <v>0.0</v>
@@ -9842,10 +9842,10 @@
         <v>739</v>
       </c>
       <c r="F291" t="n">
-        <v>540.0</v>
+        <v>542.0</v>
       </c>
       <c r="G291" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
       <c r="H291" t="n">
         <v>6.0</v>
@@ -10310,7 +10310,7 @@
         <v>739</v>
       </c>
       <c r="F309" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G309" t="n">
         <v>0.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1011.0</v>
+        <v>1012.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10492,13 +10492,13 @@
         <v>739</v>
       </c>
       <c r="F316" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G316" t="n">
         <v>0.0</v>
       </c>
       <c r="H316" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="317">
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>503.0</v>
+        <v>504.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11246,10 +11246,10 @@
         <v>739</v>
       </c>
       <c r="F345" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G345" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="H345" t="n">
         <v>2.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12442,7 +12442,7 @@
         <v>739</v>
       </c>
       <c r="F391" t="n">
-        <v>122.0</v>
+        <v>125.0</v>
       </c>
       <c r="G391" t="n">
         <v>0.0</v>
@@ -12754,7 +12754,7 @@
         <v>739</v>
       </c>
       <c r="F403" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G403" t="n">
         <v>1.0</v>
@@ -13066,7 +13066,7 @@
         <v>739</v>
       </c>
       <c r="F415" t="n">
-        <v>301.0</v>
+        <v>302.0</v>
       </c>
       <c r="G415" t="n">
         <v>28.0</v>
@@ -13170,7 +13170,7 @@
         <v>739</v>
       </c>
       <c r="F419" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G419" t="n">
         <v>1.0</v>
@@ -14236,7 +14236,7 @@
         <v>741</v>
       </c>
       <c r="F460" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G460" t="n">
         <v>2.0</v>
@@ -14574,7 +14574,7 @@
         <v>739</v>
       </c>
       <c r="F473" t="n">
-        <v>174.0</v>
+        <v>185.0</v>
       </c>
       <c r="G473" t="n">
         <v>3.0</v>
@@ -15900,7 +15900,7 @@
         <v>739</v>
       </c>
       <c r="F524" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G524" t="n">
         <v>9.0</v>
@@ -16108,7 +16108,7 @@
         <v>739</v>
       </c>
       <c r="F532" t="n">
-        <v>412.0</v>
+        <v>413.0</v>
       </c>
       <c r="G532" t="n">
         <v>3.0</v>
@@ -16420,7 +16420,7 @@
         <v>739</v>
       </c>
       <c r="F544" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G544" t="n">
         <v>11.0</v>
@@ -16758,7 +16758,7 @@
         <v>739</v>
       </c>
       <c r="F557" t="n">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="G557" t="n">
         <v>2.0</v>
@@ -18058,7 +18058,7 @@
         <v>739</v>
       </c>
       <c r="F607" t="n">
-        <v>347.0</v>
+        <v>348.0</v>
       </c>
       <c r="G607" t="n">
         <v>12.0</v>
@@ -18084,7 +18084,7 @@
         <v>739</v>
       </c>
       <c r="F608" t="n">
-        <v>253.0</v>
+        <v>255.0</v>
       </c>
       <c r="G608" t="n">
         <v>3.0</v>
@@ -18136,7 +18136,7 @@
         <v>740</v>
       </c>
       <c r="F610" t="n">
-        <v>392.0</v>
+        <v>394.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
@@ -19592,7 +19592,7 @@
         <v>739</v>
       </c>
       <c r="F666" t="n">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
       <c r="G666" t="n">
         <v>32.0</v>
@@ -19696,7 +19696,7 @@
         <v>739</v>
       </c>
       <c r="F670" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19800,7 +19800,7 @@
         <v>740</v>
       </c>
       <c r="F674" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19826,7 +19826,7 @@
         <v>739</v>
       </c>
       <c r="F675" t="n">
-        <v>118.0</v>
+        <v>125.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19852,7 +19852,7 @@
         <v>739</v>
       </c>
       <c r="F676" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -19904,7 +19904,7 @@
         <v>740</v>
       </c>
       <c r="F678" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G678" t="n">
         <v>0.0</v>
@@ -20008,7 +20008,7 @@
         <v>740</v>
       </c>
       <c r="F682" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20034,7 +20034,7 @@
         <v>740</v>
       </c>
       <c r="F683" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20060,7 +20060,7 @@
         <v>740</v>
       </c>
       <c r="F684" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20086,7 +20086,7 @@
         <v>740</v>
       </c>
       <c r="F685" t="n">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -20112,7 +20112,7 @@
         <v>740</v>
       </c>
       <c r="F686" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G686" t="n">
         <v>0.0</v>
@@ -21412,7 +21412,7 @@
         <v>739</v>
       </c>
       <c r="F736" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G736" t="n">
         <v>0.0</v>
@@ -21490,7 +21490,7 @@
         <v>739</v>
       </c>
       <c r="F739" t="n">
-        <v>191.0</v>
+        <v>192.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2796,7 +2796,7 @@
         <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -2926,7 +2926,7 @@
         <v>739</v>
       </c>
       <c r="F25" t="n">
-        <v>178.0</v>
+        <v>180.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -3475,7 +3475,7 @@
         <v>294.0</v>
       </c>
       <c r="G46" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H46" t="n">
         <v>3.0</v>
@@ -3654,7 +3654,7 @@
         <v>739</v>
       </c>
       <c r="F53" t="n">
-        <v>196.0</v>
+        <v>200.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -4616,7 +4616,7 @@
         <v>739</v>
       </c>
       <c r="F90" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G90" t="n">
         <v>16.0</v>
@@ -4668,7 +4668,7 @@
         <v>741</v>
       </c>
       <c r="F92" t="n">
-        <v>469.0</v>
+        <v>470.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -5009,7 +5009,7 @@
         <v>509.0</v>
       </c>
       <c r="G105" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H105" t="n">
         <v>4.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -5604,7 +5604,7 @@
         <v>739</v>
       </c>
       <c r="F128" t="n">
-        <v>224.0</v>
+        <v>226.0</v>
       </c>
       <c r="G128" t="n">
         <v>11.0</v>
@@ -6254,13 +6254,13 @@
         <v>740</v>
       </c>
       <c r="F153" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G153" t="n">
         <v>0.0</v>
       </c>
       <c r="H153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="154">
@@ -6670,7 +6670,7 @@
         <v>740</v>
       </c>
       <c r="F169" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -7424,7 +7424,7 @@
         <v>739</v>
       </c>
       <c r="F198" t="n">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -8334,7 +8334,7 @@
         <v>739</v>
       </c>
       <c r="F233" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="G233" t="n">
         <v>0.0</v>
@@ -9270,7 +9270,7 @@
         <v>739</v>
       </c>
       <c r="F269" t="n">
-        <v>235.0</v>
+        <v>238.0</v>
       </c>
       <c r="G269" t="n">
         <v>7.0</v>
@@ -9426,7 +9426,7 @@
         <v>739</v>
       </c>
       <c r="F275" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -9738,7 +9738,7 @@
         <v>739</v>
       </c>
       <c r="F287" t="n">
-        <v>262.0</v>
+        <v>267.0</v>
       </c>
       <c r="G287" t="n">
         <v>4.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1012.0</v>
+        <v>1015.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11246,13 +11246,13 @@
         <v>739</v>
       </c>
       <c r="F345" t="n">
-        <v>202.0</v>
+        <v>205.0</v>
       </c>
       <c r="G345" t="n">
         <v>13.0</v>
       </c>
       <c r="H345" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="346">
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11821,7 +11821,7 @@
         <v>101.0</v>
       </c>
       <c r="G367" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H367" t="n">
         <v>7.0</v>
@@ -12442,7 +12442,7 @@
         <v>739</v>
       </c>
       <c r="F391" t="n">
-        <v>125.0</v>
+        <v>127.0</v>
       </c>
       <c r="G391" t="n">
         <v>0.0</v>
@@ -12962,7 +12962,7 @@
         <v>739</v>
       </c>
       <c r="F411" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G411" t="n">
         <v>0.0</v>
@@ -14912,7 +14912,7 @@
         <v>739</v>
       </c>
       <c r="F486" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G486" t="n">
         <v>0.0</v>
@@ -14941,7 +14941,7 @@
         <v>236.0</v>
       </c>
       <c r="G487" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H487" t="n">
         <v>1.0</v>
@@ -17018,7 +17018,7 @@
         <v>739</v>
       </c>
       <c r="F567" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G567" t="n">
         <v>0.0</v>
@@ -18266,7 +18266,7 @@
         <v>739</v>
       </c>
       <c r="F615" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G615" t="n">
         <v>18.0</v>
@@ -18968,7 +18968,7 @@
         <v>739</v>
       </c>
       <c r="F642" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -21389,7 +21389,7 @@
         <v>0.0</v>
       </c>
       <c r="G735" t="n">
-        <v>39.0</v>
+        <v>47.0</v>
       </c>
       <c r="H735" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>590.0</v>
+        <v>591.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>464.0</v>
+        <v>466.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>398.0</v>
+        <v>399.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>190.0</v>
+        <v>196.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -4018,7 +4018,7 @@
         <v>740</v>
       </c>
       <c r="F67" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4122,7 +4122,7 @@
         <v>739</v>
       </c>
       <c r="F71" t="n">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>407.0</v>
+        <v>408.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4720,7 +4720,7 @@
         <v>739</v>
       </c>
       <c r="F94" t="n">
-        <v>135.0</v>
+        <v>138.0</v>
       </c>
       <c r="G94" t="n">
         <v>17.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>509.0</v>
+        <v>511.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5136,7 +5136,7 @@
         <v>740</v>
       </c>
       <c r="F110" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -5526,7 +5526,7 @@
         <v>739</v>
       </c>
       <c r="F125" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6306,7 +6306,7 @@
         <v>740</v>
       </c>
       <c r="F155" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -6774,7 +6774,7 @@
         <v>739</v>
       </c>
       <c r="F173" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="G173" t="n">
         <v>1.0</v>
@@ -6956,7 +6956,7 @@
         <v>739</v>
       </c>
       <c r="F180" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="G180" t="n">
         <v>4.0</v>
@@ -7788,7 +7788,7 @@
         <v>740</v>
       </c>
       <c r="F212" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -9868,7 +9868,7 @@
         <v>739</v>
       </c>
       <c r="F292" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -10053,7 +10053,7 @@
         <v>209.0</v>
       </c>
       <c r="G299" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H299" t="n">
         <v>4.0</v>
@@ -10310,7 +10310,7 @@
         <v>739</v>
       </c>
       <c r="F309" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G309" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>532.0</v>
+        <v>533.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -11818,7 +11818,7 @@
         <v>739</v>
       </c>
       <c r="F367" t="n">
-        <v>101.0</v>
+        <v>105.0</v>
       </c>
       <c r="G367" t="n">
         <v>8.0</v>
@@ -13066,7 +13066,7 @@
         <v>739</v>
       </c>
       <c r="F415" t="n">
-        <v>302.0</v>
+        <v>304.0</v>
       </c>
       <c r="G415" t="n">
         <v>28.0</v>
@@ -13612,7 +13612,7 @@
         <v>740</v>
       </c>
       <c r="F436" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G436" t="n">
         <v>1.0</v>
@@ -14941,7 +14941,7 @@
         <v>236.0</v>
       </c>
       <c r="G487" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H487" t="n">
         <v>1.0</v>
@@ -15380,7 +15380,7 @@
         <v>739</v>
       </c>
       <c r="F504" t="n">
-        <v>595.0</v>
+        <v>598.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
@@ -15770,7 +15770,7 @@
         <v>741</v>
       </c>
       <c r="F519" t="n">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="G519" t="n">
         <v>0.0</v>
@@ -16654,7 +16654,7 @@
         <v>739</v>
       </c>
       <c r="F553" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G553" t="n">
         <v>0.0</v>
@@ -17564,7 +17564,7 @@
         <v>739</v>
       </c>
       <c r="F588" t="n">
-        <v>95.0</v>
+        <v>99.0</v>
       </c>
       <c r="G588" t="n">
         <v>0.0</v>
@@ -19384,7 +19384,7 @@
         <v>740</v>
       </c>
       <c r="F658" t="n">
-        <v>109.0</v>
+        <v>111.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -19852,7 +19852,7 @@
         <v>739</v>
       </c>
       <c r="F676" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -20216,10 +20216,10 @@
         <v>741</v>
       </c>
       <c r="F690" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G690" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H690" t="n">
         <v>0.0</v>
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="F694" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20606,7 +20606,7 @@
         <v>740</v>
       </c>
       <c r="F705" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G705" t="n">
         <v>0.0</v>
@@ -20658,7 +20658,7 @@
         <v>740</v>
       </c>
       <c r="F707" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20999,7 +20999,7 @@
         <v>161.0</v>
       </c>
       <c r="G720" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="H720" t="n">
         <v>1.0</v>
@@ -21022,7 +21022,7 @@
         <v>741</v>
       </c>
       <c r="F721" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G721" t="n">
         <v>0.0</v>
@@ -21048,7 +21048,7 @@
         <v>740</v>
       </c>
       <c r="F722" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21126,7 +21126,7 @@
         <v>740</v>
       </c>
       <c r="F725" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21204,7 +21204,7 @@
         <v>740</v>
       </c>
       <c r="F728" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G728" t="n">
         <v>0.0</v>
@@ -21282,7 +21282,7 @@
         <v>740</v>
       </c>
       <c r="F731" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G731" t="n">
         <v>0.0</v>
@@ -21308,7 +21308,7 @@
         <v>739</v>
       </c>
       <c r="F732" t="n">
-        <v>311.0</v>
+        <v>314.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21389,7 +21389,7 @@
         <v>0.0</v>
       </c>
       <c r="G735" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="H735" t="n">
         <v>0.0</v>
@@ -21441,7 +21441,7 @@
         <v>65.0</v>
       </c>
       <c r="G737" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H737" t="n">
         <v>0.0</v>
@@ -21490,7 +21490,7 @@
         <v>739</v>
       </c>
       <c r="F739" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2432,7 +2432,7 @@
         <v>739</v>
       </c>
       <c r="F6" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G6" t="n">
         <v>13.0</v>
@@ -2822,7 +2822,7 @@
         <v>739</v>
       </c>
       <c r="F21" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>123.0</v>
+        <v>125.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3449,7 +3449,7 @@
         <v>59.0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4616,7 +4616,7 @@
         <v>739</v>
       </c>
       <c r="F90" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G90" t="n">
         <v>16.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -5373,7 +5373,7 @@
         <v>26.0</v>
       </c>
       <c r="G119" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -5604,7 +5604,7 @@
         <v>739</v>
       </c>
       <c r="F128" t="n">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
       <c r="G128" t="n">
         <v>11.0</v>
@@ -5656,7 +5656,7 @@
         <v>739</v>
       </c>
       <c r="F130" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -6670,7 +6670,7 @@
         <v>740</v>
       </c>
       <c r="F169" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6881,7 +6881,7 @@
         <v>19.0</v>
       </c>
       <c r="G177" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -7606,7 +7606,7 @@
         <v>740</v>
       </c>
       <c r="F205" t="n">
-        <v>1008.0</v>
+        <v>1009.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -9296,7 +9296,7 @@
         <v>739</v>
       </c>
       <c r="F270" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G270" t="n">
         <v>2.0</v>
@@ -9894,7 +9894,7 @@
         <v>739</v>
       </c>
       <c r="F293" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G293" t="n">
         <v>6.0</v>
@@ -9946,7 +9946,7 @@
         <v>739</v>
       </c>
       <c r="F295" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="G295" t="n">
         <v>11.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11249,7 +11249,7 @@
         <v>205.0</v>
       </c>
       <c r="G345" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="H345" t="n">
         <v>4.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12078,7 +12078,7 @@
         <v>740</v>
       </c>
       <c r="F377" t="n">
-        <v>175.0</v>
+        <v>180.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12260,7 +12260,7 @@
         <v>739</v>
       </c>
       <c r="F384" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G384" t="n">
         <v>0.0</v>
@@ -12832,7 +12832,7 @@
         <v>741</v>
       </c>
       <c r="F406" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
       <c r="G406" t="n">
         <v>0.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>571.0</v>
+        <v>573.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -13950,7 +13950,7 @@
         <v>739</v>
       </c>
       <c r="F449" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G449" t="n">
         <v>4.0</v>
@@ -14002,7 +14002,7 @@
         <v>740</v>
       </c>
       <c r="F451" t="n">
-        <v>452.0</v>
+        <v>453.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -16758,7 +16758,7 @@
         <v>739</v>
       </c>
       <c r="F557" t="n">
-        <v>414.0</v>
+        <v>417.0</v>
       </c>
       <c r="G557" t="n">
         <v>2.0</v>
@@ -17252,7 +17252,7 @@
         <v>739</v>
       </c>
       <c r="F576" t="n">
-        <v>272.0</v>
+        <v>274.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
@@ -20999,7 +20999,7 @@
         <v>161.0</v>
       </c>
       <c r="G720" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="H720" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2432,7 +2432,7 @@
         <v>739</v>
       </c>
       <c r="F6" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G6" t="n">
         <v>13.0</v>
@@ -2796,7 +2796,7 @@
         <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -2822,7 +2822,7 @@
         <v>739</v>
       </c>
       <c r="F21" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2874,7 +2874,7 @@
         <v>740</v>
       </c>
       <c r="F23" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>408.0</v>
+        <v>410.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4697,7 +4697,7 @@
         <v>110.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -5604,7 +5604,7 @@
         <v>739</v>
       </c>
       <c r="F128" t="n">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="G128" t="n">
         <v>11.0</v>
@@ -6881,7 +6881,7 @@
         <v>19.0</v>
       </c>
       <c r="G177" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -7528,7 +7528,7 @@
         <v>740</v>
       </c>
       <c r="F202" t="n">
-        <v>271.0</v>
+        <v>272.0</v>
       </c>
       <c r="G202" t="n">
         <v>0.0</v>
@@ -8074,7 +8074,7 @@
         <v>739</v>
       </c>
       <c r="F223" t="n">
-        <v>134.0</v>
+        <v>137.0</v>
       </c>
       <c r="G223" t="n">
         <v>0.0</v>
@@ -8516,7 +8516,7 @@
         <v>739</v>
       </c>
       <c r="F240" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G240" t="n">
         <v>0.0</v>
@@ -9585,7 +9585,7 @@
         <v>0.0</v>
       </c>
       <c r="G281" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="H281" t="n">
         <v>0.0</v>
@@ -10726,7 +10726,7 @@
         <v>739</v>
       </c>
       <c r="F325" t="n">
-        <v>538.0</v>
+        <v>552.0</v>
       </c>
       <c r="G325" t="n">
         <v>8.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>117.0</v>
+        <v>119.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12260,7 +12260,7 @@
         <v>739</v>
       </c>
       <c r="F384" t="n">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
       <c r="G384" t="n">
         <v>0.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>573.0</v>
+        <v>574.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14941,7 +14941,7 @@
         <v>236.0</v>
       </c>
       <c r="G487" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H487" t="n">
         <v>1.0</v>
@@ -15747,7 +15747,7 @@
         <v>0.0</v>
       </c>
       <c r="G518" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="H518" t="n">
         <v>0.0</v>
@@ -17229,7 +17229,7 @@
         <v>0.0</v>
       </c>
       <c r="G575" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="H575" t="n">
         <v>0.0</v>
@@ -17720,7 +17720,7 @@
         <v>739</v>
       </c>
       <c r="F594" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
@@ -18318,7 +18318,7 @@
         <v>739</v>
       </c>
       <c r="F617" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G617" t="n">
         <v>0.0</v>
@@ -19124,7 +19124,7 @@
         <v>739</v>
       </c>
       <c r="F648" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -20346,7 +20346,7 @@
         <v>741</v>
       </c>
       <c r="F695" t="n">
-        <v>418.0</v>
+        <v>419.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>591.0</v>
+        <v>596.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>399.0</v>
+        <v>402.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>509.0</v>
+        <v>510.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3478,7 +3478,7 @@
         <v>13.0</v>
       </c>
       <c r="H46" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="47">
@@ -4018,7 +4018,7 @@
         <v>740</v>
       </c>
       <c r="F67" t="n">
-        <v>191.0</v>
+        <v>194.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4148,7 +4148,7 @@
         <v>739</v>
       </c>
       <c r="F72" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4902,7 +4902,7 @@
         <v>740</v>
       </c>
       <c r="F101" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>511.0</v>
+        <v>513.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>455.0</v>
+        <v>457.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>660.0</v>
+        <v>662.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6722,7 +6722,7 @@
         <v>740</v>
       </c>
       <c r="F171" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6774,7 +6774,7 @@
         <v>739</v>
       </c>
       <c r="F173" t="n">
-        <v>316.0</v>
+        <v>319.0</v>
       </c>
       <c r="G173" t="n">
         <v>1.0</v>
@@ -6956,7 +6956,7 @@
         <v>739</v>
       </c>
       <c r="F180" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="G180" t="n">
         <v>4.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>514.0</v>
+        <v>516.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7788,7 +7788,7 @@
         <v>740</v>
       </c>
       <c r="F212" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -8756,7 +8756,7 @@
         <v>1.0</v>
       </c>
       <c r="H249" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="250">
@@ -9166,7 +9166,7 @@
         <v>739</v>
       </c>
       <c r="F265" t="n">
-        <v>234.0</v>
+        <v>236.0</v>
       </c>
       <c r="G265" t="n">
         <v>0.0</v>
@@ -10206,7 +10206,7 @@
         <v>739</v>
       </c>
       <c r="F305" t="n">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
       <c r="G305" t="n">
         <v>0.0</v>
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>504.0</v>
+        <v>506.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>409.0</v>
+        <v>410.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -11636,7 +11636,7 @@
         <v>739</v>
       </c>
       <c r="F360" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G360" t="n">
         <v>0.0</v>
@@ -11824,7 +11824,7 @@
         <v>8.0</v>
       </c>
       <c r="H367" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="368">
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G392" t="n">
         <v>1.0</v>
@@ -13072,7 +13072,7 @@
         <v>28.0</v>
       </c>
       <c r="H415" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="416">
@@ -14392,13 +14392,13 @@
         <v>739</v>
       </c>
       <c r="F466" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G466" t="n">
         <v>14.0</v>
       </c>
       <c r="H466" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="467">
@@ -15770,7 +15770,7 @@
         <v>741</v>
       </c>
       <c r="F519" t="n">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
       <c r="G519" t="n">
         <v>0.0</v>
@@ -16342,7 +16342,7 @@
         <v>740</v>
       </c>
       <c r="F541" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="G541" t="n">
         <v>0.0</v>
@@ -17252,7 +17252,7 @@
         <v>739</v>
       </c>
       <c r="F576" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
@@ -17642,7 +17642,7 @@
         <v>739</v>
       </c>
       <c r="F591" t="n">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -18610,7 +18610,7 @@
         <v>32.0</v>
       </c>
       <c r="H628" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="629">
@@ -18734,7 +18734,7 @@
         <v>739</v>
       </c>
       <c r="F633" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -19384,7 +19384,7 @@
         <v>740</v>
       </c>
       <c r="F658" t="n">
-        <v>111.0</v>
+        <v>114.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -19696,7 +19696,7 @@
         <v>739</v>
       </c>
       <c r="F670" t="n">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19748,7 +19748,7 @@
         <v>739</v>
       </c>
       <c r="F672" t="n">
-        <v>120.0</v>
+        <v>123.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19774,7 +19774,7 @@
         <v>740</v>
       </c>
       <c r="F673" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19826,7 +19826,7 @@
         <v>739</v>
       </c>
       <c r="F675" t="n">
-        <v>125.0</v>
+        <v>130.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19852,7 +19852,7 @@
         <v>739</v>
       </c>
       <c r="F676" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -19904,7 +19904,7 @@
         <v>740</v>
       </c>
       <c r="F678" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G678" t="n">
         <v>0.0</v>
@@ -20008,7 +20008,7 @@
         <v>740</v>
       </c>
       <c r="F682" t="n">
-        <v>106.0</v>
+        <v>109.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20034,7 +20034,7 @@
         <v>740</v>
       </c>
       <c r="F683" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20060,7 +20060,7 @@
         <v>740</v>
       </c>
       <c r="F684" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20112,7 +20112,7 @@
         <v>740</v>
       </c>
       <c r="F686" t="n">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
       <c r="G686" t="n">
         <v>0.0</v>
@@ -20242,7 +20242,7 @@
         <v>740</v>
       </c>
       <c r="F691" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G691" t="n">
         <v>0.0</v>
@@ -20268,7 +20268,7 @@
         <v>740</v>
       </c>
       <c r="F692" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20632,7 +20632,7 @@
         <v>739</v>
       </c>
       <c r="F706" t="n">
-        <v>91.0</v>
+        <v>93.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20658,7 +20658,7 @@
         <v>740</v>
       </c>
       <c r="F707" t="n">
-        <v>56.0</v>
+        <v>62.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20736,7 +20736,7 @@
         <v>739</v>
       </c>
       <c r="F710" t="n">
-        <v>112.0</v>
+        <v>115.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -20996,7 +20996,7 @@
         <v>741</v>
       </c>
       <c r="F720" t="n">
-        <v>161.0</v>
+        <v>164.0</v>
       </c>
       <c r="G720" t="n">
         <v>15.0</v>
@@ -21022,7 +21022,7 @@
         <v>741</v>
       </c>
       <c r="F721" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G721" t="n">
         <v>0.0</v>
@@ -21048,7 +21048,7 @@
         <v>740</v>
       </c>
       <c r="F722" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21152,7 +21152,7 @@
         <v>740</v>
       </c>
       <c r="F726" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -21308,7 +21308,7 @@
         <v>739</v>
       </c>
       <c r="F732" t="n">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21334,7 +21334,7 @@
         <v>739</v>
       </c>
       <c r="F733" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="G733" t="n">
         <v>16.0</v>
@@ -21438,7 +21438,7 @@
         <v>741</v>
       </c>
       <c r="F737" t="n">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
       <c r="G737" t="n">
         <v>7.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>391.0</v>
+        <v>392.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>
@@ -21490,7 +21490,7 @@
         <v>739</v>
       </c>
       <c r="F739" t="n">
-        <v>193.0</v>
+        <v>195.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -21568,7 +21568,7 @@
         <v>739</v>
       </c>
       <c r="F742" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G742" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>596.0</v>
+        <v>597.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>466.0</v>
+        <v>467.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2822,7 +2822,7 @@
         <v>739</v>
       </c>
       <c r="F21" t="n">
-        <v>81.0</v>
+        <v>83.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3348,7 +3348,7 @@
         <v>0.0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="42">
@@ -3368,7 +3368,7 @@
         <v>739</v>
       </c>
       <c r="F42" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G42" t="n">
         <v>15.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4902,7 +4902,7 @@
         <v>740</v>
       </c>
       <c r="F101" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>513.0</v>
+        <v>515.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>88.0</v>
+        <v>93.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -5136,7 +5136,7 @@
         <v>740</v>
       </c>
       <c r="F110" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -5214,7 +5214,7 @@
         <v>739</v>
       </c>
       <c r="F113" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G113" t="n">
         <v>2.0</v>
@@ -6228,7 +6228,7 @@
         <v>739</v>
       </c>
       <c r="F152" t="n">
-        <v>214.0</v>
+        <v>216.0</v>
       </c>
       <c r="G152" t="n">
         <v>2.0</v>
@@ -6930,7 +6930,7 @@
         <v>740</v>
       </c>
       <c r="F179" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7606,7 +7606,7 @@
         <v>740</v>
       </c>
       <c r="F205" t="n">
-        <v>1009.0</v>
+        <v>1011.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -8438,7 +8438,7 @@
         <v>740</v>
       </c>
       <c r="F237" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -9842,7 +9842,7 @@
         <v>739</v>
       </c>
       <c r="F291" t="n">
-        <v>542.0</v>
+        <v>543.0</v>
       </c>
       <c r="G291" t="n">
         <v>42.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1015.0</v>
+        <v>1027.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>533.0</v>
+        <v>534.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -11844,7 +11844,7 @@
         <v>740</v>
       </c>
       <c r="F368" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -12052,7 +12052,7 @@
         <v>740</v>
       </c>
       <c r="F376" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G392" t="n">
         <v>1.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>574.0</v>
+        <v>575.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14262,7 +14262,7 @@
         <v>740</v>
       </c>
       <c r="F461" t="n">
-        <v>380.0</v>
+        <v>381.0</v>
       </c>
       <c r="G461" t="n">
         <v>0.0</v>
@@ -14860,7 +14860,7 @@
         <v>740</v>
       </c>
       <c r="F484" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="G484" t="n">
         <v>0.0</v>
@@ -14938,13 +14938,13 @@
         <v>739</v>
       </c>
       <c r="F487" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
       <c r="G487" t="n">
         <v>7.0</v>
       </c>
       <c r="H487" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="488">
@@ -16784,7 +16784,7 @@
         <v>741</v>
       </c>
       <c r="F558" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
       <c r="G558" t="n">
         <v>8.0</v>
@@ -16966,7 +16966,7 @@
         <v>740</v>
       </c>
       <c r="F565" t="n">
-        <v>349.0</v>
+        <v>350.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -18136,7 +18136,7 @@
         <v>740</v>
       </c>
       <c r="F610" t="n">
-        <v>394.0</v>
+        <v>397.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
@@ -19384,7 +19384,7 @@
         <v>740</v>
       </c>
       <c r="F658" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -20242,7 +20242,7 @@
         <v>740</v>
       </c>
       <c r="F691" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G691" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -21048,7 +21048,7 @@
         <v>740</v>
       </c>
       <c r="F722" t="n">
-        <v>48.0</v>
+        <v>51.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21074,7 +21074,7 @@
         <v>741</v>
       </c>
       <c r="F723" t="n">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -21100,7 +21100,7 @@
         <v>740</v>
       </c>
       <c r="F724" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
@@ -21126,7 +21126,7 @@
         <v>740</v>
       </c>
       <c r="F725" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21152,7 +21152,7 @@
         <v>740</v>
       </c>
       <c r="F726" t="n">
-        <v>55.0</v>
+        <v>63.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>392.0</v>
+        <v>394.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2435,7 +2435,7 @@
         <v>37.0</v>
       </c>
       <c r="G6" t="n">
-        <v>13.0</v>
+        <v>19.0</v>
       </c>
       <c r="H6" t="n">
         <v>0.0</v>
@@ -3498,7 +3498,7 @@
         <v>739</v>
       </c>
       <c r="F47" t="n">
-        <v>182.0</v>
+        <v>184.0</v>
       </c>
       <c r="G47" t="n">
         <v>12.0</v>
@@ -4226,7 +4226,7 @@
         <v>740</v>
       </c>
       <c r="F75" t="n">
-        <v>354.0</v>
+        <v>359.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -4694,7 +4694,7 @@
         <v>739</v>
       </c>
       <c r="F93" t="n">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -5370,10 +5370,10 @@
         <v>739</v>
       </c>
       <c r="F119" t="n">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
       <c r="G119" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -6881,7 +6881,7 @@
         <v>19.0</v>
       </c>
       <c r="G177" t="n">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -7242,7 +7242,7 @@
         <v>740</v>
       </c>
       <c r="F191" t="n">
-        <v>673.0</v>
+        <v>683.0</v>
       </c>
       <c r="G191" t="n">
         <v>1.0</v>
@@ -9374,7 +9374,7 @@
         <v>739</v>
       </c>
       <c r="F273" t="n">
-        <v>612.0</v>
+        <v>613.0</v>
       </c>
       <c r="G273" t="n">
         <v>25.0</v>
@@ -12390,7 +12390,7 @@
         <v>740</v>
       </c>
       <c r="F389" t="n">
-        <v>126.0</v>
+        <v>130.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
@@ -12962,7 +12962,7 @@
         <v>739</v>
       </c>
       <c r="F411" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G411" t="n">
         <v>0.0</v>
@@ -13716,7 +13716,7 @@
         <v>739</v>
       </c>
       <c r="F440" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G440" t="n">
         <v>7.0</v>
@@ -15747,7 +15747,7 @@
         <v>0.0</v>
       </c>
       <c r="G518" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="H518" t="n">
         <v>0.0</v>
@@ -16472,7 +16472,7 @@
         <v>740</v>
       </c>
       <c r="F546" t="n">
-        <v>318.0</v>
+        <v>320.0</v>
       </c>
       <c r="G546" t="n">
         <v>1.0</v>
@@ -16550,7 +16550,7 @@
         <v>740</v>
       </c>
       <c r="F549" t="n">
-        <v>264.0</v>
+        <v>269.0</v>
       </c>
       <c r="G549" t="n">
         <v>1.0</v>
@@ -17229,7 +17229,7 @@
         <v>0.0</v>
       </c>
       <c r="G575" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="H575" t="n">
         <v>0.0</v>
@@ -17460,7 +17460,7 @@
         <v>740</v>
       </c>
       <c r="F584" t="n">
-        <v>280.0</v>
+        <v>285.0</v>
       </c>
       <c r="G584" t="n">
         <v>0.0</v>
@@ -19124,7 +19124,7 @@
         <v>739</v>
       </c>
       <c r="F648" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>
@@ -19332,7 +19332,7 @@
         <v>739</v>
       </c>
       <c r="F656" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G656" t="n">
         <v>5.0</v>
@@ -21389,7 +21389,7 @@
         <v>0.0</v>
       </c>
       <c r="G735" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="H735" t="n">
         <v>0.0</v>
@@ -21441,7 +21441,7 @@
         <v>69.0</v>
       </c>
       <c r="G737" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H737" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>597.0</v>
+        <v>600.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>467.0</v>
+        <v>469.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>367.0</v>
+        <v>368.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3342,7 +3342,7 @@
         <v>739</v>
       </c>
       <c r="F41" t="n">
-        <v>329.0</v>
+        <v>338.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -3472,7 +3472,7 @@
         <v>739</v>
       </c>
       <c r="F46" t="n">
-        <v>294.0</v>
+        <v>297.0</v>
       </c>
       <c r="G46" t="n">
         <v>13.0</v>
@@ -4148,7 +4148,7 @@
         <v>739</v>
       </c>
       <c r="F72" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4356,7 +4356,7 @@
         <v>739</v>
       </c>
       <c r="F80" t="n">
-        <v>185.0</v>
+        <v>187.0</v>
       </c>
       <c r="G80" t="n">
         <v>81.0</v>
@@ -4902,7 +4902,7 @@
         <v>740</v>
       </c>
       <c r="F101" t="n">
-        <v>434.0</v>
+        <v>437.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>515.0</v>
+        <v>518.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>457.0</v>
+        <v>458.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>662.0</v>
+        <v>668.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6046,7 +6046,7 @@
         <v>739</v>
       </c>
       <c r="F145" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G145" t="n">
         <v>6.0</v>
@@ -6150,7 +6150,7 @@
         <v>740</v>
       </c>
       <c r="F149" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G149" t="n">
         <v>0.0</v>
@@ -6722,7 +6722,7 @@
         <v>740</v>
       </c>
       <c r="F171" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6956,7 +6956,7 @@
         <v>739</v>
       </c>
       <c r="F180" t="n">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
       <c r="G180" t="n">
         <v>4.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>516.0</v>
+        <v>517.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7788,7 +7788,7 @@
         <v>740</v>
       </c>
       <c r="F212" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -8750,7 +8750,7 @@
         <v>739</v>
       </c>
       <c r="F249" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="G249" t="n">
         <v>1.0</v>
@@ -8776,7 +8776,7 @@
         <v>739</v>
       </c>
       <c r="F250" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G250" t="n">
         <v>0.0</v>
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
       <c r="G392" t="n">
         <v>1.0</v>
@@ -12832,7 +12832,7 @@
         <v>741</v>
       </c>
       <c r="F406" t="n">
-        <v>433.0</v>
+        <v>436.0</v>
       </c>
       <c r="G406" t="n">
         <v>0.0</v>
@@ -13066,7 +13066,7 @@
         <v>739</v>
       </c>
       <c r="F415" t="n">
-        <v>304.0</v>
+        <v>311.0</v>
       </c>
       <c r="G415" t="n">
         <v>28.0</v>
@@ -14002,7 +14002,7 @@
         <v>740</v>
       </c>
       <c r="F451" t="n">
-        <v>453.0</v>
+        <v>456.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14938,7 +14938,7 @@
         <v>739</v>
       </c>
       <c r="F487" t="n">
-        <v>237.0</v>
+        <v>242.0</v>
       </c>
       <c r="G487" t="n">
         <v>7.0</v>
@@ -15380,7 +15380,7 @@
         <v>739</v>
       </c>
       <c r="F504" t="n">
-        <v>598.0</v>
+        <v>612.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
@@ -16342,7 +16342,7 @@
         <v>740</v>
       </c>
       <c r="F541" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G541" t="n">
         <v>0.0</v>
@@ -17252,7 +17252,7 @@
         <v>739</v>
       </c>
       <c r="F576" t="n">
-        <v>275.0</v>
+        <v>277.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
@@ -17642,7 +17642,7 @@
         <v>739</v>
       </c>
       <c r="F591" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -18604,7 +18604,7 @@
         <v>739</v>
       </c>
       <c r="F628" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G628" t="n">
         <v>32.0</v>
@@ -18734,7 +18734,7 @@
         <v>739</v>
       </c>
       <c r="F633" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -19592,7 +19592,7 @@
         <v>739</v>
       </c>
       <c r="F666" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G666" t="n">
         <v>32.0</v>
@@ -19696,7 +19696,7 @@
         <v>739</v>
       </c>
       <c r="F670" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19748,7 +19748,7 @@
         <v>739</v>
       </c>
       <c r="F672" t="n">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19800,7 +19800,7 @@
         <v>740</v>
       </c>
       <c r="F674" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19826,7 +19826,7 @@
         <v>739</v>
       </c>
       <c r="F675" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19852,7 +19852,7 @@
         <v>739</v>
       </c>
       <c r="F676" t="n">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -20008,7 +20008,7 @@
         <v>740</v>
       </c>
       <c r="F682" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20034,7 +20034,7 @@
         <v>740</v>
       </c>
       <c r="F683" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20112,7 +20112,7 @@
         <v>740</v>
       </c>
       <c r="F686" t="n">
-        <v>91.0</v>
+        <v>95.0</v>
       </c>
       <c r="G686" t="n">
         <v>0.0</v>
@@ -20216,7 +20216,7 @@
         <v>741</v>
       </c>
       <c r="F690" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="G690" t="n">
         <v>1.0</v>
@@ -20242,7 +20242,7 @@
         <v>740</v>
       </c>
       <c r="F691" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G691" t="n">
         <v>0.0</v>
@@ -20268,7 +20268,7 @@
         <v>740</v>
       </c>
       <c r="F692" t="n">
-        <v>61.0</v>
+        <v>65.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="F694" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20658,7 +20658,7 @@
         <v>740</v>
       </c>
       <c r="F707" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -20996,7 +20996,7 @@
         <v>741</v>
       </c>
       <c r="F720" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="G720" t="n">
         <v>15.0</v>
@@ -21152,7 +21152,7 @@
         <v>740</v>
       </c>
       <c r="F726" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -21308,7 +21308,7 @@
         <v>739</v>
       </c>
       <c r="F732" t="n">
-        <v>316.0</v>
+        <v>319.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>394.0</v>
+        <v>413.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -11249,7 +11249,7 @@
         <v>205.0</v>
       </c>
       <c r="G345" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="H345" t="n">
         <v>4.0</v>
@@ -14941,7 +14941,7 @@
         <v>242.0</v>
       </c>
       <c r="G487" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H487" t="n">
         <v>4.0</v>
@@ -20216,10 +20216,10 @@
         <v>741</v>
       </c>
       <c r="F690" t="n">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
       <c r="G690" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H690" t="n">
         <v>0.0</v>
@@ -20996,7 +20996,7 @@
         <v>741</v>
       </c>
       <c r="F720" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="G720" t="n">
         <v>15.0</v>
@@ -21441,7 +21441,7 @@
         <v>69.0</v>
       </c>
       <c r="G737" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="H737" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2822,7 +2822,7 @@
         <v>739</v>
       </c>
       <c r="F21" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>196.0</v>
+        <v>198.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3368,7 +3368,7 @@
         <v>739</v>
       </c>
       <c r="F42" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G42" t="n">
         <v>15.0</v>
@@ -3446,7 +3446,7 @@
         <v>739</v>
       </c>
       <c r="F45" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="G45" t="n">
         <v>2.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>411.0</v>
+        <v>417.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -5526,7 +5526,7 @@
         <v>739</v>
       </c>
       <c r="F125" t="n">
-        <v>253.0</v>
+        <v>254.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
@@ -5656,7 +5656,7 @@
         <v>739</v>
       </c>
       <c r="F130" t="n">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -6436,7 +6436,7 @@
         <v>739</v>
       </c>
       <c r="F160" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G160" t="n">
         <v>1.0</v>
@@ -6670,7 +6670,7 @@
         <v>740</v>
       </c>
       <c r="F169" t="n">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -7060,7 +7060,7 @@
         <v>740</v>
       </c>
       <c r="F184" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G184" t="n">
         <v>0.0</v>
@@ -7398,7 +7398,7 @@
         <v>739</v>
       </c>
       <c r="F197" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G197" t="n">
         <v>1.0</v>
@@ -7606,7 +7606,7 @@
         <v>740</v>
       </c>
       <c r="F205" t="n">
-        <v>1011.0</v>
+        <v>1014.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -8126,7 +8126,7 @@
         <v>739</v>
       </c>
       <c r="F225" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="G225" t="n">
         <v>7.0</v>
@@ -8308,13 +8308,13 @@
         <v>739</v>
       </c>
       <c r="F232" t="n">
-        <v>242.0</v>
+        <v>245.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
       </c>
       <c r="H232" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="233">
@@ -8438,7 +8438,7 @@
         <v>740</v>
       </c>
       <c r="F237" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -9010,7 +9010,7 @@
         <v>739</v>
       </c>
       <c r="F259" t="n">
-        <v>943.0</v>
+        <v>946.0</v>
       </c>
       <c r="G259" t="n">
         <v>23.0</v>
@@ -9270,7 +9270,7 @@
         <v>739</v>
       </c>
       <c r="F269" t="n">
-        <v>238.0</v>
+        <v>240.0</v>
       </c>
       <c r="G269" t="n">
         <v>7.0</v>
@@ -9426,7 +9426,7 @@
         <v>739</v>
       </c>
       <c r="F275" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G275" t="n">
         <v>0.0</v>
@@ -9556,7 +9556,7 @@
         <v>741</v>
       </c>
       <c r="F280" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G280" t="n">
         <v>0.0</v>
@@ -9585,7 +9585,7 @@
         <v>0.0</v>
       </c>
       <c r="G281" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="H281" t="n">
         <v>0.0</v>
@@ -9738,7 +9738,7 @@
         <v>739</v>
       </c>
       <c r="F287" t="n">
-        <v>267.0</v>
+        <v>273.0</v>
       </c>
       <c r="G287" t="n">
         <v>4.0</v>
@@ -9868,7 +9868,7 @@
         <v>739</v>
       </c>
       <c r="F292" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -10050,7 +10050,7 @@
         <v>741</v>
       </c>
       <c r="F299" t="n">
-        <v>209.0</v>
+        <v>211.0</v>
       </c>
       <c r="G299" t="n">
         <v>3.0</v>
@@ -10310,7 +10310,7 @@
         <v>739</v>
       </c>
       <c r="F309" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G309" t="n">
         <v>0.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1027.0</v>
+        <v>1030.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>247.0</v>
+        <v>250.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11194,7 +11194,7 @@
         <v>739</v>
       </c>
       <c r="F343" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="G343" t="n">
         <v>6.0</v>
@@ -11246,10 +11246,10 @@
         <v>739</v>
       </c>
       <c r="F345" t="n">
-        <v>205.0</v>
+        <v>211.0</v>
       </c>
       <c r="G345" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="H345" t="n">
         <v>4.0</v>
@@ -11636,7 +11636,7 @@
         <v>739</v>
       </c>
       <c r="F360" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G360" t="n">
         <v>0.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>119.0</v>
+        <v>124.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>534.0</v>
+        <v>535.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -12052,7 +12052,7 @@
         <v>740</v>
       </c>
       <c r="F376" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -12702,7 +12702,7 @@
         <v>739</v>
       </c>
       <c r="F401" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
       <c r="G401" t="n">
         <v>2.0</v>
@@ -12754,7 +12754,7 @@
         <v>739</v>
       </c>
       <c r="F403" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="G403" t="n">
         <v>1.0</v>
@@ -12809,7 +12809,7 @@
         <v>0.0</v>
       </c>
       <c r="G405" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H405" t="n">
         <v>0.0</v>
@@ -13794,7 +13794,7 @@
         <v>739</v>
       </c>
       <c r="F443" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G443" t="n">
         <v>10.0</v>
@@ -13820,7 +13820,7 @@
         <v>739</v>
       </c>
       <c r="F444" t="n">
-        <v>80.0</v>
+        <v>83.0</v>
       </c>
       <c r="G444" t="n">
         <v>0.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>575.0</v>
+        <v>577.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14262,7 +14262,7 @@
         <v>740</v>
       </c>
       <c r="F461" t="n">
-        <v>381.0</v>
+        <v>382.0</v>
       </c>
       <c r="G461" t="n">
         <v>0.0</v>
@@ -14496,7 +14496,7 @@
         <v>741</v>
       </c>
       <c r="F470" t="n">
-        <v>534.0</v>
+        <v>537.0</v>
       </c>
       <c r="G470" t="n">
         <v>0.0</v>
@@ -14522,7 +14522,7 @@
         <v>739</v>
       </c>
       <c r="F471" t="n">
-        <v>187.0</v>
+        <v>190.0</v>
       </c>
       <c r="G471" t="n">
         <v>0.0</v>
@@ -15224,7 +15224,7 @@
         <v>740</v>
       </c>
       <c r="F498" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G498" t="n">
         <v>0.0</v>
@@ -15432,7 +15432,7 @@
         <v>740</v>
       </c>
       <c r="F506" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G506" t="n">
         <v>0.0</v>
@@ -15747,7 +15747,7 @@
         <v>0.0</v>
       </c>
       <c r="G518" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="H518" t="n">
         <v>0.0</v>
@@ -15796,7 +15796,7 @@
         <v>739</v>
       </c>
       <c r="F520" t="n">
-        <v>2384.0</v>
+        <v>2395.0</v>
       </c>
       <c r="G520" t="n">
         <v>306.0</v>
@@ -16108,7 +16108,7 @@
         <v>739</v>
       </c>
       <c r="F532" t="n">
-        <v>413.0</v>
+        <v>420.0</v>
       </c>
       <c r="G532" t="n">
         <v>3.0</v>
@@ -16498,7 +16498,7 @@
         <v>739</v>
       </c>
       <c r="F547" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16758,7 +16758,7 @@
         <v>739</v>
       </c>
       <c r="F557" t="n">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="G557" t="n">
         <v>2.0</v>
@@ -16940,7 +16940,7 @@
         <v>739</v>
       </c>
       <c r="F564" t="n">
-        <v>223.0</v>
+        <v>224.0</v>
       </c>
       <c r="G564" t="n">
         <v>29.0</v>
@@ -16966,7 +16966,7 @@
         <v>740</v>
       </c>
       <c r="F565" t="n">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -17174,7 +17174,7 @@
         <v>740</v>
       </c>
       <c r="F573" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G573" t="n">
         <v>0.0</v>
@@ -17564,7 +17564,7 @@
         <v>739</v>
       </c>
       <c r="F588" t="n">
-        <v>99.0</v>
+        <v>104.0</v>
       </c>
       <c r="G588" t="n">
         <v>0.0</v>
@@ -17902,7 +17902,7 @@
         <v>741</v>
       </c>
       <c r="F601" t="n">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -18214,7 +18214,7 @@
         <v>739</v>
       </c>
       <c r="F613" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="G613" t="n">
         <v>7.0</v>
@@ -19098,7 +19098,7 @@
         <v>740</v>
       </c>
       <c r="F647" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19621,7 +19621,7 @@
         <v>0.0</v>
       </c>
       <c r="G667" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="H667" t="n">
         <v>0.0</v>
@@ -20216,10 +20216,10 @@
         <v>741</v>
       </c>
       <c r="F690" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G690" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="H690" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -20999,7 +20999,7 @@
         <v>166.0</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="H720" t="n">
         <v>1.0</v>
@@ -21025,7 +21025,7 @@
         <v>50.0</v>
       </c>
       <c r="G721" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H721" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>600.0</v>
+        <v>602.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>469.0</v>
+        <v>473.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>402.0</v>
+        <v>405.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2796,7 +2796,7 @@
         <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>368.0</v>
+        <v>372.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3186,7 +3186,7 @@
         <v>739</v>
       </c>
       <c r="F35" t="n">
-        <v>209.0</v>
+        <v>212.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>510.0</v>
+        <v>514.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3342,7 +3342,7 @@
         <v>739</v>
       </c>
       <c r="F41" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -3680,7 +3680,7 @@
         <v>739</v>
       </c>
       <c r="F54" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -3810,7 +3810,7 @@
         <v>739</v>
       </c>
       <c r="F59" t="n">
-        <v>284.0</v>
+        <v>285.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -4018,7 +4018,7 @@
         <v>740</v>
       </c>
       <c r="F67" t="n">
-        <v>194.0</v>
+        <v>196.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4148,7 +4148,7 @@
         <v>739</v>
       </c>
       <c r="F72" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4694,7 +4694,7 @@
         <v>739</v>
       </c>
       <c r="F93" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>518.0</v>
+        <v>520.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -5136,7 +5136,7 @@
         <v>740</v>
       </c>
       <c r="F110" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -5370,7 +5370,7 @@
         <v>739</v>
       </c>
       <c r="F119" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="G119" t="n">
         <v>12.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>458.0</v>
+        <v>459.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5656,7 +5656,7 @@
         <v>739</v>
       </c>
       <c r="F130" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -6774,7 +6774,7 @@
         <v>739</v>
       </c>
       <c r="F173" t="n">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="G173" t="n">
         <v>1.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>517.0</v>
+        <v>518.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7008,7 +7008,7 @@
         <v>739</v>
       </c>
       <c r="F182" t="n">
-        <v>109.0</v>
+        <v>111.0</v>
       </c>
       <c r="G182" t="n">
         <v>0.0</v>
@@ -8282,7 +8282,7 @@
         <v>739</v>
       </c>
       <c r="F231" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G231" t="n">
         <v>0.0</v>
@@ -8311,7 +8311,7 @@
         <v>245.0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H232" t="n">
         <v>3.0</v>
@@ -8334,7 +8334,7 @@
         <v>739</v>
       </c>
       <c r="F233" t="n">
-        <v>140.0</v>
+        <v>143.0</v>
       </c>
       <c r="G233" t="n">
         <v>0.0</v>
@@ -8750,7 +8750,7 @@
         <v>739</v>
       </c>
       <c r="F249" t="n">
-        <v>151.0</v>
+        <v>154.0</v>
       </c>
       <c r="G249" t="n">
         <v>1.0</v>
@@ -9166,7 +9166,7 @@
         <v>739</v>
       </c>
       <c r="F265" t="n">
-        <v>236.0</v>
+        <v>238.0</v>
       </c>
       <c r="G265" t="n">
         <v>0.0</v>
@@ -9608,7 +9608,7 @@
         <v>739</v>
       </c>
       <c r="F282" t="n">
-        <v>500.0</v>
+        <v>501.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -9842,7 +9842,7 @@
         <v>739</v>
       </c>
       <c r="F291" t="n">
-        <v>543.0</v>
+        <v>552.0</v>
       </c>
       <c r="G291" t="n">
         <v>42.0</v>
@@ -10310,7 +10310,7 @@
         <v>739</v>
       </c>
       <c r="F309" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G309" t="n">
         <v>0.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1030.0</v>
+        <v>1034.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>506.0</v>
+        <v>509.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>411.0</v>
+        <v>412.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -11246,7 +11246,7 @@
         <v>739</v>
       </c>
       <c r="F345" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="G345" t="n">
         <v>17.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -11821,7 +11821,7 @@
         <v>105.0</v>
       </c>
       <c r="G367" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H367" t="n">
         <v>9.0</v>
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="G392" t="n">
         <v>1.0</v>
@@ -12754,7 +12754,7 @@
         <v>739</v>
       </c>
       <c r="F403" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G403" t="n">
         <v>1.0</v>
@@ -13066,7 +13066,7 @@
         <v>739</v>
       </c>
       <c r="F415" t="n">
-        <v>311.0</v>
+        <v>315.0</v>
       </c>
       <c r="G415" t="n">
         <v>28.0</v>
@@ -14054,7 +14054,7 @@
         <v>739</v>
       </c>
       <c r="F453" t="n">
-        <v>762.0</v>
+        <v>763.0</v>
       </c>
       <c r="G453" t="n">
         <v>0.0</v>
@@ -14938,7 +14938,7 @@
         <v>739</v>
       </c>
       <c r="F487" t="n">
-        <v>242.0</v>
+        <v>244.0</v>
       </c>
       <c r="G487" t="n">
         <v>8.0</v>
@@ -15380,7 +15380,7 @@
         <v>739</v>
       </c>
       <c r="F504" t="n">
-        <v>612.0</v>
+        <v>614.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
@@ -15770,7 +15770,7 @@
         <v>741</v>
       </c>
       <c r="F519" t="n">
-        <v>332.0</v>
+        <v>334.0</v>
       </c>
       <c r="G519" t="n">
         <v>0.0</v>
@@ -16238,7 +16238,7 @@
         <v>739</v>
       </c>
       <c r="F537" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
       <c r="G537" t="n">
         <v>0.0</v>
@@ -17642,7 +17642,7 @@
         <v>739</v>
       </c>
       <c r="F591" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -18968,7 +18968,7 @@
         <v>739</v>
       </c>
       <c r="F642" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -19384,7 +19384,7 @@
         <v>740</v>
       </c>
       <c r="F658" t="n">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -19595,7 +19595,7 @@
         <v>114.0</v>
       </c>
       <c r="G666" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="H666" t="n">
         <v>0.0</v>
@@ -19644,7 +19644,7 @@
         <v>741</v>
       </c>
       <c r="F668" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -20008,7 +20008,7 @@
         <v>740</v>
       </c>
       <c r="F682" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20034,7 +20034,7 @@
         <v>740</v>
       </c>
       <c r="F683" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20216,7 +20216,7 @@
         <v>741</v>
       </c>
       <c r="F690" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G690" t="n">
         <v>11.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>146.0</v>
+        <v>151.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20476,7 +20476,7 @@
         <v>740</v>
       </c>
       <c r="F700" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20632,7 +20632,7 @@
         <v>739</v>
       </c>
       <c r="F706" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20736,7 +20736,7 @@
         <v>739</v>
       </c>
       <c r="F710" t="n">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -20970,7 +20970,7 @@
         <v>739</v>
       </c>
       <c r="F719" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -21048,7 +21048,7 @@
         <v>740</v>
       </c>
       <c r="F722" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21152,7 +21152,7 @@
         <v>740</v>
       </c>
       <c r="F726" t="n">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -21438,7 +21438,7 @@
         <v>741</v>
       </c>
       <c r="F737" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G737" t="n">
         <v>11.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>413.0</v>
+        <v>415.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>
@@ -21490,7 +21490,7 @@
         <v>739</v>
       </c>
       <c r="F739" t="n">
-        <v>195.0</v>
+        <v>198.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2900,7 +2900,7 @@
         <v>740</v>
       </c>
       <c r="F24" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4226,7 +4226,7 @@
         <v>740</v>
       </c>
       <c r="F75" t="n">
-        <v>359.0</v>
+        <v>361.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -6670,7 +6670,7 @@
         <v>740</v>
       </c>
       <c r="F169" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6930,7 +6930,7 @@
         <v>740</v>
       </c>
       <c r="F179" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7242,7 +7242,7 @@
         <v>740</v>
       </c>
       <c r="F191" t="n">
-        <v>683.0</v>
+        <v>687.0</v>
       </c>
       <c r="G191" t="n">
         <v>1.0</v>
@@ -7424,7 +7424,7 @@
         <v>739</v>
       </c>
       <c r="F198" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -9868,7 +9868,7 @@
         <v>739</v>
       </c>
       <c r="F292" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10830,7 +10830,7 @@
         <v>739</v>
       </c>
       <c r="F329" t="n">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
       <c r="G329" t="n">
         <v>1.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11740,7 +11740,7 @@
         <v>739</v>
       </c>
       <c r="F364" t="n">
-        <v>159.0</v>
+        <v>168.0</v>
       </c>
       <c r="G364" t="n">
         <v>4.0</v>
@@ -12390,7 +12390,7 @@
         <v>740</v>
       </c>
       <c r="F389" t="n">
-        <v>130.0</v>
+        <v>133.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
@@ -12858,7 +12858,7 @@
         <v>740</v>
       </c>
       <c r="F407" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -13950,7 +13950,7 @@
         <v>739</v>
       </c>
       <c r="F449" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G449" t="n">
         <v>4.0</v>
@@ -14028,7 +14028,7 @@
         <v>739</v>
       </c>
       <c r="F452" t="n">
-        <v>190.0</v>
+        <v>192.0</v>
       </c>
       <c r="G452" t="n">
         <v>11.0</v>
@@ -15796,7 +15796,7 @@
         <v>739</v>
       </c>
       <c r="F520" t="n">
-        <v>2395.0</v>
+        <v>2406.0</v>
       </c>
       <c r="G520" t="n">
         <v>306.0</v>
@@ -16550,7 +16550,7 @@
         <v>740</v>
       </c>
       <c r="F549" t="n">
-        <v>269.0</v>
+        <v>274.0</v>
       </c>
       <c r="G549" t="n">
         <v>1.0</v>
@@ -16810,7 +16810,7 @@
         <v>739</v>
       </c>
       <c r="F559" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G559" t="n">
         <v>0.0</v>
@@ -17460,7 +17460,7 @@
         <v>740</v>
       </c>
       <c r="F584" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G584" t="n">
         <v>0.0</v>
@@ -18318,7 +18318,7 @@
         <v>739</v>
       </c>
       <c r="F617" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G617" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3706,7 +3706,7 @@
         <v>739</v>
       </c>
       <c r="F55" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G55" t="n">
         <v>8.0</v>
@@ -6150,7 +6150,7 @@
         <v>740</v>
       </c>
       <c r="F149" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G149" t="n">
         <v>0.0</v>
@@ -9143,7 +9143,7 @@
         <v>0.0</v>
       </c>
       <c r="G264" t="n">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
       <c r="H264" t="n">
         <v>0.0</v>
@@ -9166,7 +9166,7 @@
         <v>739</v>
       </c>
       <c r="F265" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="G265" t="n">
         <v>0.0</v>
@@ -11636,7 +11636,7 @@
         <v>739</v>
       </c>
       <c r="F360" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G360" t="n">
         <v>0.0</v>
@@ -14002,7 +14002,7 @@
         <v>740</v>
       </c>
       <c r="F451" t="n">
-        <v>456.0</v>
+        <v>459.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -17229,7 +17229,7 @@
         <v>0.0</v>
       </c>
       <c r="G575" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="H575" t="n">
         <v>0.0</v>
@@ -17252,7 +17252,7 @@
         <v>739</v>
       </c>
       <c r="F576" t="n">
-        <v>277.0</v>
+        <v>279.0</v>
       </c>
       <c r="G576" t="n">
         <v>0.0</v>
@@ -19644,7 +19644,7 @@
         <v>741</v>
       </c>
       <c r="F668" t="n">
-        <v>181.0</v>
+        <v>183.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -20219,7 +20219,7 @@
         <v>38.0</v>
       </c>
       <c r="G690" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H690" t="n">
         <v>0.0</v>
@@ -20349,7 +20349,7 @@
         <v>419.0</v>
       </c>
       <c r="G695" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H695" t="n">
         <v>0.0</v>
@@ -20814,7 +20814,7 @@
         <v>741</v>
       </c>
       <c r="F713" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -20996,10 +20996,10 @@
         <v>741</v>
       </c>
       <c r="F720" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G720" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="H720" t="n">
         <v>1.0</v>
@@ -21178,7 +21178,7 @@
         <v>740</v>
       </c>
       <c r="F727" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G727" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2406,7 +2406,7 @@
         <v>740</v>
       </c>
       <c r="F5" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -2435,7 +2435,7 @@
         <v>37.0</v>
       </c>
       <c r="G6" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="H6" t="n">
         <v>0.0</v>
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>198.0</v>
+        <v>202.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3550,7 +3550,7 @@
         <v>739</v>
       </c>
       <c r="F49" t="n">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>149.0</v>
+        <v>152.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>418.0</v>
+        <v>422.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4824,7 +4824,7 @@
         <v>739</v>
       </c>
       <c r="F98" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G98" t="n">
         <v>17.0</v>
@@ -5110,7 +5110,7 @@
         <v>740</v>
       </c>
       <c r="F109" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -7346,7 +7346,7 @@
         <v>740</v>
       </c>
       <c r="F195" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G195" t="n">
         <v>0.0</v>
@@ -7424,7 +7424,7 @@
         <v>739</v>
       </c>
       <c r="F198" t="n">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -9608,7 +9608,7 @@
         <v>739</v>
       </c>
       <c r="F282" t="n">
-        <v>501.0</v>
+        <v>502.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -9738,7 +9738,7 @@
         <v>739</v>
       </c>
       <c r="F287" t="n">
-        <v>273.0</v>
+        <v>275.0</v>
       </c>
       <c r="G287" t="n">
         <v>4.0</v>
@@ -10310,7 +10310,7 @@
         <v>739</v>
       </c>
       <c r="F309" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
       <c r="G309" t="n">
         <v>0.0</v>
@@ -11246,13 +11246,13 @@
         <v>739</v>
       </c>
       <c r="F345" t="n">
-        <v>212.0</v>
+        <v>214.0</v>
       </c>
       <c r="G345" t="n">
         <v>17.0</v>
       </c>
       <c r="H345" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="346">
@@ -11532,7 +11532,7 @@
         <v>740</v>
       </c>
       <c r="F356" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G356" t="n">
         <v>0.0</v>
@@ -11587,7 +11587,7 @@
         <v>25.0</v>
       </c>
       <c r="G358" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="H358" t="n">
         <v>0.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>536.0</v>
+        <v>537.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -11844,7 +11844,7 @@
         <v>740</v>
       </c>
       <c r="F368" t="n">
-        <v>102.0</v>
+        <v>104.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -12809,7 +12809,7 @@
         <v>0.0</v>
       </c>
       <c r="G405" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H405" t="n">
         <v>0.0</v>
@@ -12858,7 +12858,7 @@
         <v>740</v>
       </c>
       <c r="F407" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>577.0</v>
+        <v>579.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14002,7 +14002,7 @@
         <v>740</v>
       </c>
       <c r="F451" t="n">
-        <v>459.0</v>
+        <v>460.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14886,7 +14886,7 @@
         <v>739</v>
       </c>
       <c r="F485" t="n">
-        <v>531.0</v>
+        <v>532.0</v>
       </c>
       <c r="G485" t="n">
         <v>5.0</v>
@@ -15510,7 +15510,7 @@
         <v>740</v>
       </c>
       <c r="F509" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G509" t="n">
         <v>0.0</v>
@@ -15796,7 +15796,7 @@
         <v>739</v>
       </c>
       <c r="F520" t="n">
-        <v>2406.0</v>
+        <v>2408.0</v>
       </c>
       <c r="G520" t="n">
         <v>306.0</v>
@@ -15848,7 +15848,7 @@
         <v>740</v>
       </c>
       <c r="F522" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G522" t="n">
         <v>6.0</v>
@@ -18318,7 +18318,7 @@
         <v>739</v>
       </c>
       <c r="F617" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G617" t="n">
         <v>0.0</v>
@@ -19621,7 +19621,7 @@
         <v>0.0</v>
       </c>
       <c r="G667" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="H667" t="n">
         <v>0.0</v>
@@ -20346,7 +20346,7 @@
         <v>741</v>
       </c>
       <c r="F695" t="n">
-        <v>419.0</v>
+        <v>420.0</v>
       </c>
       <c r="G695" t="n">
         <v>1.0</v>
@@ -20840,7 +20840,7 @@
         <v>740</v>
       </c>
       <c r="F714" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G714" t="n">
         <v>0.0</v>
@@ -20996,7 +20996,7 @@
         <v>741</v>
       </c>
       <c r="F720" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G720" t="n">
         <v>19.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2432,7 +2432,7 @@
         <v>739</v>
       </c>
       <c r="F6" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G6" t="n">
         <v>20.0</v>
@@ -4278,7 +4278,7 @@
         <v>740</v>
       </c>
       <c r="F77" t="n">
-        <v>351.0</v>
+        <v>352.0</v>
       </c>
       <c r="G77" t="n">
         <v>1.0</v>
@@ -6592,7 +6592,7 @@
         <v>740</v>
       </c>
       <c r="F166" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -8308,7 +8308,7 @@
         <v>739</v>
       </c>
       <c r="F232" t="n">
-        <v>245.0</v>
+        <v>251.0</v>
       </c>
       <c r="G232" t="n">
         <v>1.0</v>
@@ -8438,7 +8438,7 @@
         <v>740</v>
       </c>
       <c r="F237" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -9270,7 +9270,7 @@
         <v>739</v>
       </c>
       <c r="F269" t="n">
-        <v>240.0</v>
+        <v>242.0</v>
       </c>
       <c r="G269" t="n">
         <v>7.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>537.0</v>
+        <v>538.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -12052,7 +12052,7 @@
         <v>740</v>
       </c>
       <c r="F376" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -14704,7 +14704,7 @@
         <v>739</v>
       </c>
       <c r="F478" t="n">
-        <v>218.0</v>
+        <v>220.0</v>
       </c>
       <c r="G478" t="n">
         <v>4.0</v>
@@ -15799,7 +15799,7 @@
         <v>2408.0</v>
       </c>
       <c r="G520" t="n">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
       <c r="H520" t="n">
         <v>45.0</v>
@@ -15900,7 +15900,7 @@
         <v>739</v>
       </c>
       <c r="F524" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G524" t="n">
         <v>9.0</v>
@@ -19124,7 +19124,7 @@
         <v>739</v>
       </c>
       <c r="F648" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G648" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -12832,7 +12832,7 @@
         <v>741</v>
       </c>
       <c r="F406" t="n">
-        <v>436.0</v>
+        <v>438.0</v>
       </c>
       <c r="G406" t="n">
         <v>0.0</v>
@@ -20528,7 +20528,7 @@
         <v>741</v>
       </c>
       <c r="F702" t="n">
-        <v>180.0</v>
+        <v>182.0</v>
       </c>
       <c r="G702" t="n">
         <v>0.0</v>
@@ -20710,7 +20710,7 @@
         <v>740</v>
       </c>
       <c r="F709" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G709" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>602.0</v>
+        <v>608.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2562,7 +2562,7 @@
         <v>739</v>
       </c>
       <c r="F11" t="n">
-        <v>300.0</v>
+        <v>301.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>473.0</v>
+        <v>475.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>405.0</v>
+        <v>409.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2796,7 +2796,7 @@
         <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>372.0</v>
+        <v>377.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2926,7 +2926,7 @@
         <v>739</v>
       </c>
       <c r="F25" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>514.0</v>
+        <v>524.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3342,7 +3342,7 @@
         <v>739</v>
       </c>
       <c r="F41" t="n">
-        <v>339.0</v>
+        <v>345.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -3680,7 +3680,7 @@
         <v>739</v>
       </c>
       <c r="F54" t="n">
-        <v>127.0</v>
+        <v>129.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4018,7 +4018,7 @@
         <v>740</v>
       </c>
       <c r="F67" t="n">
-        <v>196.0</v>
+        <v>199.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4044,7 +4044,7 @@
         <v>739</v>
       </c>
       <c r="F68" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="G68" t="n">
         <v>20.0</v>
@@ -4148,7 +4148,7 @@
         <v>739</v>
       </c>
       <c r="F72" t="n">
-        <v>134.0</v>
+        <v>136.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>422.0</v>
+        <v>423.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4902,7 +4902,7 @@
         <v>740</v>
       </c>
       <c r="F101" t="n">
-        <v>437.0</v>
+        <v>440.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>520.0</v>
+        <v>523.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5136,7 +5136,7 @@
         <v>740</v>
       </c>
       <c r="F110" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>459.0</v>
+        <v>462.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5604,7 +5604,7 @@
         <v>739</v>
       </c>
       <c r="F128" t="n">
-        <v>228.0</v>
+        <v>234.0</v>
       </c>
       <c r="G128" t="n">
         <v>11.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>668.0</v>
+        <v>672.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6046,7 +6046,7 @@
         <v>739</v>
       </c>
       <c r="F145" t="n">
-        <v>53.0</v>
+        <v>74.0</v>
       </c>
       <c r="G145" t="n">
         <v>6.0</v>
@@ -6228,7 +6228,7 @@
         <v>739</v>
       </c>
       <c r="F152" t="n">
-        <v>216.0</v>
+        <v>220.0</v>
       </c>
       <c r="G152" t="n">
         <v>2.0</v>
@@ -6722,7 +6722,7 @@
         <v>740</v>
       </c>
       <c r="F171" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6774,7 +6774,7 @@
         <v>739</v>
       </c>
       <c r="F173" t="n">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="G173" t="n">
         <v>1.0</v>
@@ -6930,7 +6930,7 @@
         <v>740</v>
       </c>
       <c r="F179" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -6956,7 +6956,7 @@
         <v>739</v>
       </c>
       <c r="F180" t="n">
-        <v>276.0</v>
+        <v>278.0</v>
       </c>
       <c r="G180" t="n">
         <v>4.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>518.0</v>
+        <v>527.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7346,7 +7346,7 @@
         <v>740</v>
       </c>
       <c r="F195" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G195" t="n">
         <v>0.0</v>
@@ -8022,7 +8022,7 @@
         <v>740</v>
       </c>
       <c r="F221" t="n">
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8074,7 +8074,7 @@
         <v>739</v>
       </c>
       <c r="F223" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
       <c r="G223" t="n">
         <v>0.0</v>
@@ -8750,7 +8750,7 @@
         <v>739</v>
       </c>
       <c r="F249" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="G249" t="n">
         <v>1.0</v>
@@ -8776,7 +8776,7 @@
         <v>739</v>
       </c>
       <c r="F250" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G250" t="n">
         <v>0.0</v>
@@ -9946,7 +9946,7 @@
         <v>739</v>
       </c>
       <c r="F295" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="G295" t="n">
         <v>11.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1034.0</v>
+        <v>1036.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>509.0</v>
+        <v>512.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10856,7 +10856,7 @@
         <v>740</v>
       </c>
       <c r="F330" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G330" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>412.0</v>
+        <v>414.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>125.0</v>
+        <v>129.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11818,7 +11818,7 @@
         <v>739</v>
       </c>
       <c r="F367" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G367" t="n">
         <v>10.0</v>
@@ -12442,7 +12442,7 @@
         <v>739</v>
       </c>
       <c r="F391" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G391" t="n">
         <v>0.0</v>
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>255.0</v>
+        <v>258.0</v>
       </c>
       <c r="G392" t="n">
         <v>1.0</v>
@@ -12754,7 +12754,7 @@
         <v>739</v>
       </c>
       <c r="F403" t="n">
-        <v>133.0</v>
+        <v>136.0</v>
       </c>
       <c r="G403" t="n">
         <v>1.0</v>
@@ -13066,13 +13066,13 @@
         <v>739</v>
       </c>
       <c r="F415" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="G415" t="n">
         <v>28.0</v>
       </c>
       <c r="H415" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="416">
@@ -13378,7 +13378,7 @@
         <v>740</v>
       </c>
       <c r="F427" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G427" t="n">
         <v>0.0</v>
@@ -13898,7 +13898,7 @@
         <v>739</v>
       </c>
       <c r="F447" t="n">
-        <v>579.0</v>
+        <v>581.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14444,7 +14444,7 @@
         <v>739</v>
       </c>
       <c r="F468" t="n">
-        <v>204.0</v>
+        <v>205.0</v>
       </c>
       <c r="G468" t="n">
         <v>0.0</v>
@@ -14522,7 +14522,7 @@
         <v>739</v>
       </c>
       <c r="F471" t="n">
-        <v>190.0</v>
+        <v>192.0</v>
       </c>
       <c r="G471" t="n">
         <v>0.0</v>
@@ -14938,7 +14938,7 @@
         <v>739</v>
       </c>
       <c r="F487" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G487" t="n">
         <v>8.0</v>
@@ -15380,7 +15380,7 @@
         <v>739</v>
       </c>
       <c r="F504" t="n">
-        <v>614.0</v>
+        <v>623.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
@@ -16238,7 +16238,7 @@
         <v>739</v>
       </c>
       <c r="F537" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
       <c r="G537" t="n">
         <v>0.0</v>
@@ -16342,7 +16342,7 @@
         <v>740</v>
       </c>
       <c r="F541" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="G541" t="n">
         <v>0.0</v>
@@ -17642,7 +17642,7 @@
         <v>739</v>
       </c>
       <c r="F591" t="n">
-        <v>318.0</v>
+        <v>319.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -17720,7 +17720,7 @@
         <v>739</v>
       </c>
       <c r="F594" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
@@ -18136,7 +18136,7 @@
         <v>740</v>
       </c>
       <c r="F610" t="n">
-        <v>397.0</v>
+        <v>403.0</v>
       </c>
       <c r="G610" t="n">
         <v>0.0</v>
@@ -18734,7 +18734,7 @@
         <v>739</v>
       </c>
       <c r="F633" t="n">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -19384,7 +19384,7 @@
         <v>740</v>
       </c>
       <c r="F658" t="n">
-        <v>117.0</v>
+        <v>123.0</v>
       </c>
       <c r="G658" t="n">
         <v>0.0</v>
@@ -19702,7 +19702,7 @@
         <v>0.0</v>
       </c>
       <c r="H670" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="671">
@@ -19826,7 +19826,7 @@
         <v>739</v>
       </c>
       <c r="F675" t="n">
-        <v>132.0</v>
+        <v>136.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19878,7 +19878,7 @@
         <v>740</v>
       </c>
       <c r="F677" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G677" t="n">
         <v>0.0</v>
@@ -19956,7 +19956,7 @@
         <v>740</v>
       </c>
       <c r="F680" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -20034,7 +20034,7 @@
         <v>740</v>
       </c>
       <c r="F683" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20086,7 +20086,7 @@
         <v>740</v>
       </c>
       <c r="F685" t="n">
-        <v>72.0</v>
+        <v>78.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -20112,7 +20112,7 @@
         <v>740</v>
       </c>
       <c r="F686" t="n">
-        <v>95.0</v>
+        <v>98.0</v>
       </c>
       <c r="G686" t="n">
         <v>0.0</v>
@@ -20164,7 +20164,7 @@
         <v>739</v>
       </c>
       <c r="F688" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="G688" t="n">
         <v>2.0</v>
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="F694" t="n">
-        <v>120.0</v>
+        <v>125.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20398,7 +20398,7 @@
         <v>740</v>
       </c>
       <c r="F697" t="n">
-        <v>151.0</v>
+        <v>157.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20476,7 +20476,7 @@
         <v>740</v>
       </c>
       <c r="F700" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20632,7 +20632,7 @@
         <v>739</v>
       </c>
       <c r="F706" t="n">
-        <v>94.0</v>
+        <v>97.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20658,7 +20658,7 @@
         <v>740</v>
       </c>
       <c r="F707" t="n">
-        <v>63.0</v>
+        <v>67.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>81.0</v>
+        <v>83.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21048,7 +21048,7 @@
         <v>740</v>
       </c>
       <c r="F722" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21100,7 +21100,7 @@
         <v>740</v>
       </c>
       <c r="F724" t="n">
-        <v>22.0</v>
+        <v>26.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
@@ -21152,7 +21152,7 @@
         <v>740</v>
       </c>
       <c r="F726" t="n">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -21308,7 +21308,7 @@
         <v>739</v>
       </c>
       <c r="F732" t="n">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21360,7 +21360,7 @@
         <v>740</v>
       </c>
       <c r="F734" t="n">
-        <v>151.0</v>
+        <v>153.0</v>
       </c>
       <c r="G734" t="n">
         <v>0.0</v>
@@ -21412,13 +21412,13 @@
         <v>739</v>
       </c>
       <c r="F736" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G736" t="n">
         <v>0.0</v>
       </c>
       <c r="H736" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="737">
@@ -21438,7 +21438,7 @@
         <v>741</v>
       </c>
       <c r="F737" t="n">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="G737" t="n">
         <v>11.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>415.0</v>
+        <v>416.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>
@@ -21490,7 +21490,7 @@
         <v>739</v>
       </c>
       <c r="F739" t="n">
-        <v>198.0</v>
+        <v>200.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>608.0</v>
+        <v>609.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2435,7 +2435,7 @@
         <v>38.0</v>
       </c>
       <c r="G6" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="H6" t="n">
         <v>0.0</v>
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>377.0</v>
+        <v>378.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>524.0</v>
+        <v>530.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3498,7 +3498,7 @@
         <v>739</v>
       </c>
       <c r="F47" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
       <c r="G47" t="n">
         <v>12.0</v>
@@ -3550,7 +3550,7 @@
         <v>739</v>
       </c>
       <c r="F49" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -3576,7 +3576,7 @@
         <v>739</v>
       </c>
       <c r="F50" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G50" t="n">
         <v>8.0</v>
@@ -3680,7 +3680,7 @@
         <v>739</v>
       </c>
       <c r="F54" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4226,7 +4226,7 @@
         <v>740</v>
       </c>
       <c r="F75" t="n">
-        <v>361.0</v>
+        <v>364.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -4668,7 +4668,7 @@
         <v>741</v>
       </c>
       <c r="F92" t="n">
-        <v>470.0</v>
+        <v>471.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -4720,7 +4720,7 @@
         <v>739</v>
       </c>
       <c r="F94" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G94" t="n">
         <v>17.0</v>
@@ -5136,7 +5136,7 @@
         <v>740</v>
       </c>
       <c r="F110" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>672.0</v>
+        <v>673.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6670,7 +6670,7 @@
         <v>740</v>
       </c>
       <c r="F169" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -7138,7 +7138,7 @@
         <v>739</v>
       </c>
       <c r="F187" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7242,7 +7242,7 @@
         <v>740</v>
       </c>
       <c r="F191" t="n">
-        <v>687.0</v>
+        <v>692.0</v>
       </c>
       <c r="G191" t="n">
         <v>1.0</v>
@@ -8178,7 +8178,7 @@
         <v>739</v>
       </c>
       <c r="F227" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G227" t="n">
         <v>3.0</v>
@@ -8256,7 +8256,7 @@
         <v>739</v>
       </c>
       <c r="F230" t="n">
-        <v>280.0</v>
+        <v>282.0</v>
       </c>
       <c r="G230" t="n">
         <v>20.0</v>
@@ -9010,7 +9010,7 @@
         <v>739</v>
       </c>
       <c r="F259" t="n">
-        <v>946.0</v>
+        <v>952.0</v>
       </c>
       <c r="G259" t="n">
         <v>23.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>414.0</v>
+        <v>415.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -11454,7 +11454,7 @@
         <v>739</v>
       </c>
       <c r="F353" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G353" t="n">
         <v>0.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>538.0</v>
+        <v>539.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -12390,7 +12390,7 @@
         <v>740</v>
       </c>
       <c r="F389" t="n">
-        <v>133.0</v>
+        <v>138.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
@@ -12598,7 +12598,7 @@
         <v>740</v>
       </c>
       <c r="F397" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G397" t="n">
         <v>0.0</v>
@@ -13170,7 +13170,7 @@
         <v>739</v>
       </c>
       <c r="F419" t="n">
-        <v>183.0</v>
+        <v>185.0</v>
       </c>
       <c r="G419" t="n">
         <v>1.0</v>
@@ -13950,7 +13950,7 @@
         <v>739</v>
       </c>
       <c r="F449" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G449" t="n">
         <v>4.0</v>
@@ -15380,7 +15380,7 @@
         <v>739</v>
       </c>
       <c r="F504" t="n">
-        <v>623.0</v>
+        <v>628.0</v>
       </c>
       <c r="G504" t="n">
         <v>0.0</v>
@@ -15822,7 +15822,7 @@
         <v>739</v>
       </c>
       <c r="F521" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G521" t="n">
         <v>26.0</v>
@@ -16108,7 +16108,7 @@
         <v>739</v>
       </c>
       <c r="F532" t="n">
-        <v>420.0</v>
+        <v>424.0</v>
       </c>
       <c r="G532" t="n">
         <v>3.0</v>
@@ -16472,7 +16472,7 @@
         <v>740</v>
       </c>
       <c r="F546" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="G546" t="n">
         <v>1.0</v>
@@ -16498,7 +16498,7 @@
         <v>739</v>
       </c>
       <c r="F547" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16550,7 +16550,7 @@
         <v>740</v>
       </c>
       <c r="F549" t="n">
-        <v>274.0</v>
+        <v>276.0</v>
       </c>
       <c r="G549" t="n">
         <v>1.0</v>
@@ -17460,7 +17460,7 @@
         <v>740</v>
       </c>
       <c r="F584" t="n">
-        <v>286.0</v>
+        <v>289.0</v>
       </c>
       <c r="G584" t="n">
         <v>0.0</v>
@@ -17642,7 +17642,7 @@
         <v>739</v>
       </c>
       <c r="F591" t="n">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -18214,7 +18214,7 @@
         <v>739</v>
       </c>
       <c r="F613" t="n">
-        <v>215.0</v>
+        <v>220.0</v>
       </c>
       <c r="G613" t="n">
         <v>7.0</v>
@@ -19774,7 +19774,7 @@
         <v>740</v>
       </c>
       <c r="F673" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19852,7 +19852,7 @@
         <v>739</v>
       </c>
       <c r="F676" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -19878,7 +19878,7 @@
         <v>740</v>
       </c>
       <c r="F677" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G677" t="n">
         <v>0.0</v>
@@ -19982,7 +19982,7 @@
         <v>740</v>
       </c>
       <c r="F681" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G681" t="n">
         <v>0.0</v>
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="F694" t="n">
-        <v>125.0</v>
+        <v>128.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20736,7 +20736,7 @@
         <v>739</v>
       </c>
       <c r="F710" t="n">
-        <v>117.0</v>
+        <v>119.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>740</v>
       </c>
       <c r="F711" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21360,7 +21360,7 @@
         <v>740</v>
       </c>
       <c r="F734" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="G734" t="n">
         <v>0.0</v>
@@ -21438,7 +21438,7 @@
         <v>741</v>
       </c>
       <c r="F737" t="n">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="G737" t="n">
         <v>11.0</v>
@@ -21464,7 +21464,7 @@
         <v>740</v>
       </c>
       <c r="F738" t="n">
-        <v>416.0</v>
+        <v>418.0</v>
       </c>
       <c r="G738" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2900,7 +2900,7 @@
         <v>740</v>
       </c>
       <c r="F24" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>423.0</v>
+        <v>425.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -7346,7 +7346,7 @@
         <v>740</v>
       </c>
       <c r="F195" t="n">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="G195" t="n">
         <v>0.0</v>
@@ -8308,10 +8308,10 @@
         <v>739</v>
       </c>
       <c r="F232" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G232" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H232" t="n">
         <v>3.0</v>
@@ -9608,7 +9608,7 @@
         <v>739</v>
       </c>
       <c r="F282" t="n">
-        <v>502.0</v>
+        <v>503.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11249,7 +11249,7 @@
         <v>214.0</v>
       </c>
       <c r="G345" t="n">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="H345" t="n">
         <v>3.0</v>
@@ -12052,7 +12052,7 @@
         <v>740</v>
       </c>
       <c r="F376" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -15250,7 +15250,7 @@
         <v>740</v>
       </c>
       <c r="F499" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -19670,7 +19670,7 @@
         <v>741</v>
       </c>
       <c r="F669" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -20372,7 +20372,7 @@
         <v>741</v>
       </c>
       <c r="F696" t="n">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
       <c r="G696" t="n">
         <v>1.0</v>
@@ -20736,7 +20736,7 @@
         <v>740</v>
       </c>
       <c r="F710" t="n">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>
@@ -20918,7 +20918,7 @@
         <v>741</v>
       </c>
       <c r="F717" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
       <c r="G717" t="n">
         <v>0.0</v>
@@ -21282,7 +21282,7 @@
         <v>740</v>
       </c>
       <c r="F731" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G731" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2380,7 +2380,7 @@
         <v>739</v>
       </c>
       <c r="F4" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -2406,7 +2406,7 @@
         <v>740</v>
       </c>
       <c r="F5" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -3966,7 +3966,7 @@
         <v>740</v>
       </c>
       <c r="F65" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -4278,7 +4278,7 @@
         <v>740</v>
       </c>
       <c r="F77" t="n">
-        <v>352.0</v>
+        <v>353.0</v>
       </c>
       <c r="G77" t="n">
         <v>1.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -6462,7 +6462,7 @@
         <v>740</v>
       </c>
       <c r="F161" t="n">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -7320,7 +7320,7 @@
         <v>740</v>
       </c>
       <c r="F194" t="n">
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
       <c r="G194" t="n">
         <v>0.0</v>
@@ -7424,7 +7424,7 @@
         <v>739</v>
       </c>
       <c r="F198" t="n">
-        <v>331.0</v>
+        <v>334.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -8074,7 +8074,7 @@
         <v>739</v>
       </c>
       <c r="F223" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G223" t="n">
         <v>0.0</v>
@@ -9738,7 +9738,7 @@
         <v>739</v>
       </c>
       <c r="F287" t="n">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
       <c r="G287" t="n">
         <v>4.0</v>
@@ -10310,7 +10310,7 @@
         <v>739</v>
       </c>
       <c r="F309" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
       <c r="G309" t="n">
         <v>0.0</v>
@@ -10368,7 +10368,7 @@
         <v>20.0</v>
       </c>
       <c r="H311" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="312">
@@ -10830,7 +10830,7 @@
         <v>739</v>
       </c>
       <c r="F329" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G329" t="n">
         <v>1.0</v>
@@ -11194,7 +11194,7 @@
         <v>739</v>
       </c>
       <c r="F343" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G343" t="n">
         <v>6.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>132.0</v>
+        <v>136.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11740,7 +11740,7 @@
         <v>739</v>
       </c>
       <c r="F364" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G364" t="n">
         <v>4.0</v>
@@ -12728,7 +12728,7 @@
         <v>739</v>
       </c>
       <c r="F402" t="n">
-        <v>198.0</v>
+        <v>202.0</v>
       </c>
       <c r="G402" t="n">
         <v>2.0</v>
@@ -13404,7 +13404,7 @@
         <v>740</v>
       </c>
       <c r="F428" t="n">
-        <v>218.0</v>
+        <v>220.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>581.0</v>
+        <v>582.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -14028,7 +14028,7 @@
         <v>740</v>
       </c>
       <c r="F452" t="n">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -14210,7 +14210,7 @@
         <v>739</v>
       </c>
       <c r="F459" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G459" t="n">
         <v>0.0</v>
@@ -15822,7 +15822,7 @@
         <v>739</v>
       </c>
       <c r="F521" t="n">
-        <v>2408.0</v>
+        <v>2414.0</v>
       </c>
       <c r="G521" t="n">
         <v>307.0</v>
@@ -18994,7 +18994,7 @@
         <v>739</v>
       </c>
       <c r="F643" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -20554,7 +20554,7 @@
         <v>741</v>
       </c>
       <c r="F703" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -8412,7 +8412,7 @@
         <v>739</v>
       </c>
       <c r="F236" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -9608,7 +9608,7 @@
         <v>739</v>
       </c>
       <c r="F282" t="n">
-        <v>503.0</v>
+        <v>506.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -12858,7 +12858,7 @@
         <v>741</v>
       </c>
       <c r="F407" t="n">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -20242,7 +20242,7 @@
         <v>741</v>
       </c>
       <c r="F691" t="n">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
       <c r="G691" t="n">
         <v>12.0</v>
@@ -21022,7 +21022,7 @@
         <v>741</v>
       </c>
       <c r="F721" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
       <c r="G721" t="n">
         <v>19.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>609.0</v>
+        <v>613.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>475.0</v>
+        <v>477.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>409.0</v>
+        <v>411.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>378.0</v>
+        <v>380.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3212,13 +3212,13 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>530.0</v>
+        <v>535.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="37">
@@ -3478,7 +3478,7 @@
         <v>13.0</v>
       </c>
       <c r="H46" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="47">
@@ -3680,7 +3680,7 @@
         <v>739</v>
       </c>
       <c r="F54" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4018,7 +4018,7 @@
         <v>740</v>
       </c>
       <c r="F67" t="n">
-        <v>199.0</v>
+        <v>201.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4148,7 +4148,7 @@
         <v>739</v>
       </c>
       <c r="F72" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>153.0</v>
+        <v>155.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>425.0</v>
+        <v>427.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>523.0</v>
+        <v>525.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>462.0</v>
+        <v>464.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>673.0</v>
+        <v>675.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6722,7 +6722,7 @@
         <v>740</v>
       </c>
       <c r="F171" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6774,7 +6774,7 @@
         <v>739</v>
       </c>
       <c r="F173" t="n">
-        <v>323.0</v>
+        <v>324.0</v>
       </c>
       <c r="G173" t="n">
         <v>1.0</v>
@@ -6956,7 +6956,7 @@
         <v>739</v>
       </c>
       <c r="F180" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
       <c r="G180" t="n">
         <v>4.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7788,7 +7788,7 @@
         <v>740</v>
       </c>
       <c r="F212" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -10206,7 +10206,7 @@
         <v>739</v>
       </c>
       <c r="F305" t="n">
-        <v>400.0</v>
+        <v>402.0</v>
       </c>
       <c r="G305" t="n">
         <v>0.0</v>
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>512.0</v>
+        <v>517.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>415.0</v>
+        <v>417.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -11766,7 +11766,7 @@
         <v>739</v>
       </c>
       <c r="F365" t="n">
-        <v>540.0</v>
+        <v>541.0</v>
       </c>
       <c r="G365" t="n">
         <v>0.0</v>
@@ -11824,7 +11824,7 @@
         <v>10.0</v>
       </c>
       <c r="H367" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="368">
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G392" t="n">
         <v>0.0</v>
@@ -12494,7 +12494,7 @@
         <v>739</v>
       </c>
       <c r="F393" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="G393" t="n">
         <v>1.0</v>
@@ -12780,7 +12780,7 @@
         <v>739</v>
       </c>
       <c r="F404" t="n">
-        <v>138.0</v>
+        <v>142.0</v>
       </c>
       <c r="G404" t="n">
         <v>1.0</v>
@@ -13092,7 +13092,7 @@
         <v>739</v>
       </c>
       <c r="F416" t="n">
-        <v>316.0</v>
+        <v>318.0</v>
       </c>
       <c r="G416" t="n">
         <v>28.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>582.0</v>
+        <v>585.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -14964,13 +14964,13 @@
         <v>739</v>
       </c>
       <c r="F488" t="n">
-        <v>245.0</v>
+        <v>248.0</v>
       </c>
       <c r="G488" t="n">
         <v>8.0</v>
       </c>
       <c r="H488" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="489">
@@ -17668,7 +17668,7 @@
         <v>739</v>
       </c>
       <c r="F592" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -18760,7 +18760,7 @@
         <v>739</v>
       </c>
       <c r="F634" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>
@@ -19410,7 +19410,7 @@
         <v>740</v>
       </c>
       <c r="F659" t="n">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -19722,7 +19722,7 @@
         <v>739</v>
       </c>
       <c r="F671" t="n">
-        <v>93.0</v>
+        <v>101.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19774,7 +19774,7 @@
         <v>739</v>
       </c>
       <c r="F673" t="n">
-        <v>126.0</v>
+        <v>128.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19800,7 +19800,7 @@
         <v>740</v>
       </c>
       <c r="F674" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19826,7 +19826,7 @@
         <v>740</v>
       </c>
       <c r="F675" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19930,7 +19930,7 @@
         <v>740</v>
       </c>
       <c r="F679" t="n">
-        <v>120.0</v>
+        <v>122.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20008,7 +20008,7 @@
         <v>740</v>
       </c>
       <c r="F682" t="n">
-        <v>73.0</v>
+        <v>76.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20060,7 +20060,7 @@
         <v>740</v>
       </c>
       <c r="F684" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20086,7 +20086,7 @@
         <v>740</v>
       </c>
       <c r="F685" t="n">
-        <v>58.0</v>
+        <v>64.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -20346,7 +20346,7 @@
         <v>740</v>
       </c>
       <c r="F695" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20424,7 +20424,7 @@
         <v>740</v>
       </c>
       <c r="F698" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20502,7 +20502,7 @@
         <v>740</v>
       </c>
       <c r="F701" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G701" t="n">
         <v>0.0</v>
@@ -20684,7 +20684,7 @@
         <v>740</v>
       </c>
       <c r="F708" t="n">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>739</v>
       </c>
       <c r="F711" t="n">
-        <v>119.0</v>
+        <v>122.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -20788,7 +20788,7 @@
         <v>740</v>
       </c>
       <c r="F712" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G712" t="n">
         <v>0.0</v>
@@ -20996,7 +20996,7 @@
         <v>739</v>
       </c>
       <c r="F720" t="n">
-        <v>105.0</v>
+        <v>107.0</v>
       </c>
       <c r="G720" t="n">
         <v>0.0</v>
@@ -21178,7 +21178,7 @@
         <v>740</v>
       </c>
       <c r="F727" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G727" t="n">
         <v>0.0</v>
@@ -21334,7 +21334,7 @@
         <v>739</v>
       </c>
       <c r="F733" t="n">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="G733" t="n">
         <v>0.0</v>
@@ -21386,7 +21386,7 @@
         <v>740</v>
       </c>
       <c r="F735" t="n">
-        <v>154.0</v>
+        <v>158.0</v>
       </c>
       <c r="G735" t="n">
         <v>0.0</v>
@@ -21464,7 +21464,7 @@
         <v>741</v>
       </c>
       <c r="F738" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G738" t="n">
         <v>11.0</v>
@@ -21516,7 +21516,7 @@
         <v>739</v>
       </c>
       <c r="F740" t="n">
-        <v>200.0</v>
+        <v>202.0</v>
       </c>
       <c r="G740" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3550,7 +3550,7 @@
         <v>739</v>
       </c>
       <c r="F49" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -4226,7 +4226,7 @@
         <v>740</v>
       </c>
       <c r="F75" t="n">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>427.0</v>
+        <v>428.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4720,7 +4720,7 @@
         <v>739</v>
       </c>
       <c r="F94" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G94" t="n">
         <v>17.0</v>
@@ -5370,7 +5370,7 @@
         <v>739</v>
       </c>
       <c r="F119" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G119" t="n">
         <v>12.0</v>
@@ -5656,7 +5656,7 @@
         <v>739</v>
       </c>
       <c r="F130" t="n">
-        <v>293.0</v>
+        <v>294.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -7138,7 +7138,7 @@
         <v>739</v>
       </c>
       <c r="F187" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7242,7 +7242,7 @@
         <v>740</v>
       </c>
       <c r="F191" t="n">
-        <v>692.0</v>
+        <v>696.0</v>
       </c>
       <c r="G191" t="n">
         <v>1.0</v>
@@ -8204,7 +8204,7 @@
         <v>739</v>
       </c>
       <c r="F228" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="G228" t="n">
         <v>11.0</v>
@@ -9868,7 +9868,7 @@
         <v>739</v>
       </c>
       <c r="F292" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -12468,7 +12468,7 @@
         <v>739</v>
       </c>
       <c r="F392" t="n">
-        <v>129.0</v>
+        <v>135.0</v>
       </c>
       <c r="G392" t="n">
         <v>0.0</v>
@@ -12884,7 +12884,7 @@
         <v>740</v>
       </c>
       <c r="F408" t="n">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="G408" t="n">
         <v>0.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>585.0</v>
+        <v>587.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -16498,7 +16498,7 @@
         <v>740</v>
       </c>
       <c r="F547" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -16576,7 +16576,7 @@
         <v>740</v>
       </c>
       <c r="F550" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
       <c r="G550" t="n">
         <v>1.0</v>
@@ -17486,7 +17486,7 @@
         <v>740</v>
       </c>
       <c r="F585" t="n">
-        <v>289.0</v>
+        <v>291.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -17590,7 +17590,7 @@
         <v>739</v>
       </c>
       <c r="F589" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>209.0</v>
+        <v>211.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3316,7 +3316,7 @@
         <v>740</v>
       </c>
       <c r="F40" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3550,7 +3550,7 @@
         <v>739</v>
       </c>
       <c r="F49" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -3810,7 +3810,7 @@
         <v>739</v>
       </c>
       <c r="F59" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -4044,7 +4044,7 @@
         <v>739</v>
       </c>
       <c r="F68" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G68" t="n">
         <v>20.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>428.0</v>
+        <v>430.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -5266,7 +5266,7 @@
         <v>739</v>
       </c>
       <c r="F115" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="G115" t="n">
         <v>7.0</v>
@@ -5344,7 +5344,7 @@
         <v>739</v>
       </c>
       <c r="F118" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G118" t="n">
         <v>0.0</v>
@@ -6072,7 +6072,7 @@
         <v>740</v>
       </c>
       <c r="F146" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -6748,7 +6748,7 @@
         <v>739</v>
       </c>
       <c r="F172" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="G172" t="n">
         <v>8.0</v>
@@ -6904,7 +6904,7 @@
         <v>739</v>
       </c>
       <c r="F178" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G178" t="n">
         <v>0.0</v>
@@ -7606,7 +7606,7 @@
         <v>740</v>
       </c>
       <c r="F205" t="n">
-        <v>1015.0</v>
+        <v>1018.0</v>
       </c>
       <c r="G205" t="n">
         <v>0.0</v>
@@ -8438,7 +8438,7 @@
         <v>740</v>
       </c>
       <c r="F237" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -9946,7 +9946,7 @@
         <v>739</v>
       </c>
       <c r="F295" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="G295" t="n">
         <v>11.0</v>
@@ -10050,7 +10050,7 @@
         <v>741</v>
       </c>
       <c r="F299" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="G299" t="n">
         <v>3.0</v>
@@ -10362,7 +10362,7 @@
         <v>739</v>
       </c>
       <c r="F311" t="n">
-        <v>1037.0</v>
+        <v>1039.0</v>
       </c>
       <c r="G311" t="n">
         <v>20.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11636,7 +11636,7 @@
         <v>739</v>
       </c>
       <c r="F360" t="n">
-        <v>125.0</v>
+        <v>127.0</v>
       </c>
       <c r="G360" t="n">
         <v>0.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12208,7 +12208,7 @@
         <v>740</v>
       </c>
       <c r="F382" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G382" t="n">
         <v>0.0</v>
@@ -12858,7 +12858,7 @@
         <v>741</v>
       </c>
       <c r="F407" t="n">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>587.0</v>
+        <v>588.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -14080,7 +14080,7 @@
         <v>739</v>
       </c>
       <c r="F454" t="n">
-        <v>763.0</v>
+        <v>771.0</v>
       </c>
       <c r="G454" t="n">
         <v>0.0</v>
@@ -14470,7 +14470,7 @@
         <v>739</v>
       </c>
       <c r="F469" t="n">
-        <v>205.0</v>
+        <v>206.0</v>
       </c>
       <c r="G469" t="n">
         <v>0.0</v>
@@ -14652,7 +14652,7 @@
         <v>739</v>
       </c>
       <c r="F476" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G476" t="n">
         <v>0.0</v>
@@ -17512,7 +17512,7 @@
         <v>740</v>
       </c>
       <c r="F586" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G586" t="n">
         <v>0.0</v>
@@ -17694,7 +17694,7 @@
         <v>739</v>
       </c>
       <c r="F593" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G593" t="n">
         <v>0.0</v>
@@ -17746,7 +17746,7 @@
         <v>739</v>
       </c>
       <c r="F595" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G595" t="n">
         <v>0.0</v>
@@ -17954,7 +17954,7 @@
         <v>739</v>
       </c>
       <c r="F603" t="n">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
       <c r="G603" t="n">
         <v>0.0</v>
@@ -17980,7 +17980,7 @@
         <v>739</v>
       </c>
       <c r="F604" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G604" t="n">
         <v>0.0</v>
@@ -18344,7 +18344,7 @@
         <v>739</v>
       </c>
       <c r="F618" t="n">
-        <v>73.0</v>
+        <v>76.0</v>
       </c>
       <c r="G618" t="n">
         <v>0.0</v>
@@ -18838,7 +18838,7 @@
         <v>739</v>
       </c>
       <c r="F637" t="n">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
       <c r="G637" t="n">
         <v>8.0</v>
@@ -19647,7 +19647,7 @@
         <v>0.0</v>
       </c>
       <c r="G668" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="H668" t="n">
         <v>0.0</v>
@@ -19670,7 +19670,7 @@
         <v>741</v>
       </c>
       <c r="F669" t="n">
-        <v>187.0</v>
+        <v>196.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -20372,7 +20372,7 @@
         <v>741</v>
       </c>
       <c r="F696" t="n">
-        <v>422.0</v>
+        <v>426.0</v>
       </c>
       <c r="G696" t="n">
         <v>1.0</v>
@@ -20554,7 +20554,7 @@
         <v>741</v>
       </c>
       <c r="F703" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -21022,7 +21022,7 @@
         <v>741</v>
       </c>
       <c r="F721" t="n">
-        <v>171.0</v>
+        <v>173.0</v>
       </c>
       <c r="G721" t="n">
         <v>19.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -5272,7 +5272,7 @@
         <v>7.0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="116">
@@ -9608,7 +9608,7 @@
         <v>739</v>
       </c>
       <c r="F282" t="n">
-        <v>506.0</v>
+        <v>507.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -9842,7 +9842,7 @@
         <v>739</v>
       </c>
       <c r="F291" t="n">
-        <v>552.0</v>
+        <v>553.0</v>
       </c>
       <c r="G291" t="n">
         <v>42.0</v>
@@ -12286,7 +12286,7 @@
         <v>739</v>
       </c>
       <c r="F385" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G385" t="n">
         <v>0.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>588.0</v>
+        <v>590.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -19670,7 +19670,7 @@
         <v>741</v>
       </c>
       <c r="F669" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -6904,7 +6904,7 @@
         <v>739</v>
       </c>
       <c r="F178" t="n">
-        <v>99.0</v>
+        <v>110.0</v>
       </c>
       <c r="G178" t="n">
         <v>0.0</v>
@@ -7086,7 +7086,7 @@
         <v>739</v>
       </c>
       <c r="F185" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G185" t="n">
         <v>17.0</v>
@@ -8724,7 +8724,7 @@
         <v>739</v>
       </c>
       <c r="F248" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G248" t="n">
         <v>14.0</v>
@@ -10726,7 +10726,7 @@
         <v>739</v>
       </c>
       <c r="F325" t="n">
-        <v>552.0</v>
+        <v>553.0</v>
       </c>
       <c r="G325" t="n">
         <v>8.0</v>
@@ -10830,7 +10830,7 @@
         <v>739</v>
       </c>
       <c r="F329" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G329" t="n">
         <v>1.0</v>
@@ -11740,7 +11740,7 @@
         <v>739</v>
       </c>
       <c r="F364" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G364" t="n">
         <v>4.0</v>
@@ -13274,7 +13274,7 @@
         <v>739</v>
       </c>
       <c r="F423" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G423" t="n">
         <v>5.0</v>
@@ -15250,7 +15250,7 @@
         <v>740</v>
       </c>
       <c r="F499" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G499" t="n">
         <v>0.0</v>
@@ -15458,7 +15458,7 @@
         <v>740</v>
       </c>
       <c r="F507" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15822,7 +15822,7 @@
         <v>739</v>
       </c>
       <c r="F521" t="n">
-        <v>2414.0</v>
+        <v>2423.0</v>
       </c>
       <c r="G521" t="n">
         <v>307.0</v>
@@ -17278,7 +17278,7 @@
         <v>739</v>
       </c>
       <c r="F577" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
       <c r="G577" t="n">
         <v>0.0</v>
@@ -20736,7 +20736,7 @@
         <v>740</v>
       </c>
       <c r="F710" t="n">
-        <v>78.0</v>
+        <v>88.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>
@@ -20866,7 +20866,7 @@
         <v>740</v>
       </c>
       <c r="F715" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G715" t="n">
         <v>0.0</v>
@@ -21022,7 +21022,7 @@
         <v>741</v>
       </c>
       <c r="F721" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G721" t="n">
         <v>19.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -5370,7 +5370,7 @@
         <v>739</v>
       </c>
       <c r="F119" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="G119" t="n">
         <v>12.0</v>
@@ -6150,7 +6150,7 @@
         <v>740</v>
       </c>
       <c r="F149" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G149" t="n">
         <v>0.0</v>
@@ -14028,7 +14028,7 @@
         <v>740</v>
       </c>
       <c r="F452" t="n">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="G452" t="n">
         <v>0.0</v>
@@ -17278,7 +17278,7 @@
         <v>739</v>
       </c>
       <c r="F577" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="G577" t="n">
         <v>0.0</v>
@@ -20242,7 +20242,7 @@
         <v>741</v>
       </c>
       <c r="F691" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G691" t="n">
         <v>12.0</v>
@@ -20580,7 +20580,7 @@
         <v>740</v>
       </c>
       <c r="F704" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G704" t="n">
         <v>0.0</v>
@@ -20918,7 +20918,7 @@
         <v>741</v>
       </c>
       <c r="F717" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="G717" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2796,7 +2796,7 @@
         <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>430.0</v>
+        <v>432.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -7138,7 +7138,7 @@
         <v>739</v>
       </c>
       <c r="F187" t="n">
-        <v>149.0</v>
+        <v>152.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -8074,7 +8074,7 @@
         <v>739</v>
       </c>
       <c r="F223" t="n">
-        <v>141.0</v>
+        <v>148.0</v>
       </c>
       <c r="G223" t="n">
         <v>0.0</v>
@@ -9010,7 +9010,7 @@
         <v>739</v>
       </c>
       <c r="F259" t="n">
-        <v>952.0</v>
+        <v>953.0</v>
       </c>
       <c r="G259" t="n">
         <v>23.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10934,7 +10934,7 @@
         <v>739</v>
       </c>
       <c r="F333" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G333" t="n">
         <v>0.0</v>
@@ -12052,7 +12052,7 @@
         <v>740</v>
       </c>
       <c r="F376" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G376" t="n">
         <v>0.0</v>
@@ -12780,7 +12780,7 @@
         <v>739</v>
       </c>
       <c r="F404" t="n">
-        <v>142.0</v>
+        <v>146.0</v>
       </c>
       <c r="G404" t="n">
         <v>1.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>590.0</v>
+        <v>591.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -14522,7 +14522,7 @@
         <v>741</v>
       </c>
       <c r="F471" t="n">
-        <v>538.0</v>
+        <v>539.0</v>
       </c>
       <c r="G471" t="n">
         <v>0.0</v>
@@ -15874,7 +15874,7 @@
         <v>740</v>
       </c>
       <c r="F523" t="n">
-        <v>203.0</v>
+        <v>204.0</v>
       </c>
       <c r="G523" t="n">
         <v>6.0</v>
@@ -16134,7 +16134,7 @@
         <v>739</v>
       </c>
       <c r="F533" t="n">
-        <v>424.0</v>
+        <v>426.0</v>
       </c>
       <c r="G533" t="n">
         <v>3.0</v>
@@ -16524,7 +16524,7 @@
         <v>739</v>
       </c>
       <c r="F548" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G548" t="n">
         <v>0.0</v>
@@ -18344,7 +18344,7 @@
         <v>739</v>
       </c>
       <c r="F618" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G618" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3550,7 +3550,7 @@
         <v>739</v>
       </c>
       <c r="F49" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -3654,7 +3654,7 @@
         <v>739</v>
       </c>
       <c r="F53" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4226,7 +4226,7 @@
         <v>740</v>
       </c>
       <c r="F75" t="n">
-        <v>365.0</v>
+        <v>367.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -6254,7 +6254,7 @@
         <v>740</v>
       </c>
       <c r="F153" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G153" t="n">
         <v>0.0</v>
@@ -6670,7 +6670,7 @@
         <v>740</v>
       </c>
       <c r="F169" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6930,7 +6930,7 @@
         <v>740</v>
       </c>
       <c r="F179" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7242,7 +7242,7 @@
         <v>740</v>
       </c>
       <c r="F191" t="n">
-        <v>696.0</v>
+        <v>699.0</v>
       </c>
       <c r="G191" t="n">
         <v>1.0</v>
@@ -7294,7 +7294,7 @@
         <v>739</v>
       </c>
       <c r="F193" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -8334,7 +8334,7 @@
         <v>739</v>
       </c>
       <c r="F233" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G233" t="n">
         <v>0.0</v>
@@ -8438,7 +8438,7 @@
         <v>740</v>
       </c>
       <c r="F237" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -8802,7 +8802,7 @@
         <v>739</v>
       </c>
       <c r="F251" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G251" t="n">
         <v>2.0</v>
@@ -9403,7 +9403,7 @@
         <v>33.0</v>
       </c>
       <c r="G274" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="H274" t="n">
         <v>0.0</v>
@@ -9738,7 +9738,7 @@
         <v>739</v>
       </c>
       <c r="F287" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
       <c r="G287" t="n">
         <v>4.0</v>
@@ -9842,7 +9842,7 @@
         <v>739</v>
       </c>
       <c r="F291" t="n">
-        <v>553.0</v>
+        <v>554.0</v>
       </c>
       <c r="G291" t="n">
         <v>42.0</v>
@@ -9868,7 +9868,7 @@
         <v>739</v>
       </c>
       <c r="F292" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -10544,7 +10544,7 @@
         <v>739</v>
       </c>
       <c r="F318" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G318" t="n">
         <v>6.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10726,7 +10726,7 @@
         <v>739</v>
       </c>
       <c r="F325" t="n">
-        <v>553.0</v>
+        <v>556.0</v>
       </c>
       <c r="G325" t="n">
         <v>8.0</v>
@@ -11064,7 +11064,7 @@
         <v>739</v>
       </c>
       <c r="F338" t="n">
-        <v>265.0</v>
+        <v>266.0</v>
       </c>
       <c r="G338" t="n">
         <v>10.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>138.0</v>
+        <v>142.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12416,7 +12416,7 @@
         <v>740</v>
       </c>
       <c r="F390" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="G390" t="n">
         <v>0.0</v>
@@ -13404,7 +13404,7 @@
         <v>740</v>
       </c>
       <c r="F428" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G428" t="n">
         <v>0.0</v>
@@ -14080,7 +14080,7 @@
         <v>739</v>
       </c>
       <c r="F454" t="n">
-        <v>771.0</v>
+        <v>772.0</v>
       </c>
       <c r="G454" t="n">
         <v>0.0</v>
@@ -15822,7 +15822,7 @@
         <v>739</v>
       </c>
       <c r="F521" t="n">
-        <v>2423.0</v>
+        <v>2431.0</v>
       </c>
       <c r="G521" t="n">
         <v>307.0</v>
@@ -15848,7 +15848,7 @@
         <v>739</v>
       </c>
       <c r="F522" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G522" t="n">
         <v>26.0</v>
@@ -16498,7 +16498,7 @@
         <v>740</v>
       </c>
       <c r="F547" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -16576,7 +16576,7 @@
         <v>740</v>
       </c>
       <c r="F550" t="n">
-        <v>277.0</v>
+        <v>279.0</v>
       </c>
       <c r="G550" t="n">
         <v>1.0</v>
@@ -17486,7 +17486,7 @@
         <v>740</v>
       </c>
       <c r="F585" t="n">
-        <v>291.0</v>
+        <v>293.0</v>
       </c>
       <c r="G585" t="n">
         <v>0.0</v>
@@ -18240,7 +18240,7 @@
         <v>739</v>
       </c>
       <c r="F614" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G614" t="n">
         <v>7.0</v>
@@ -18344,7 +18344,7 @@
         <v>739</v>
       </c>
       <c r="F618" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G618" t="n">
         <v>0.0</v>
@@ -18942,7 +18942,7 @@
         <v>739</v>
       </c>
       <c r="F641" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G641" t="n">
         <v>3.0</v>
@@ -19751,7 +19751,7 @@
         <v>0.0</v>
       </c>
       <c r="G672" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="H672" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3238,7 +3238,7 @@
         <v>739</v>
       </c>
       <c r="F37" t="n">
-        <v>211.0</v>
+        <v>217.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>739</v>
       </c>
       <c r="F45" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G45" t="n">
         <v>2.0</v>
@@ -3654,7 +3654,7 @@
         <v>739</v>
       </c>
       <c r="F53" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -3810,7 +3810,7 @@
         <v>739</v>
       </c>
       <c r="F59" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -4200,7 +4200,7 @@
         <v>739</v>
       </c>
       <c r="F74" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4434,7 +4434,7 @@
         <v>740</v>
       </c>
       <c r="F83" t="n">
-        <v>432.0</v>
+        <v>434.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -5058,7 +5058,7 @@
         <v>739</v>
       </c>
       <c r="F107" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -5188,7 +5188,7 @@
         <v>741</v>
       </c>
       <c r="F112" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G112" t="n">
         <v>0.0</v>
@@ -5656,7 +5656,7 @@
         <v>739</v>
       </c>
       <c r="F130" t="n">
-        <v>294.0</v>
+        <v>296.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -5786,7 +5786,7 @@
         <v>739</v>
       </c>
       <c r="F135" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G135" t="n">
         <v>13.0</v>
@@ -6644,7 +6644,7 @@
         <v>739</v>
       </c>
       <c r="F168" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G168" t="n">
         <v>0.0</v>
@@ -8308,10 +8308,10 @@
         <v>739</v>
       </c>
       <c r="F232" t="n">
-        <v>257.0</v>
+        <v>262.0</v>
       </c>
       <c r="G232" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="H232" t="n">
         <v>3.0</v>
@@ -8698,7 +8698,7 @@
         <v>740</v>
       </c>
       <c r="F247" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G247" t="n">
         <v>0.0</v>
@@ -9400,7 +9400,7 @@
         <v>739</v>
       </c>
       <c r="F274" t="n">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="G274" t="n">
         <v>53.0</v>
@@ -9608,7 +9608,7 @@
         <v>739</v>
       </c>
       <c r="F282" t="n">
-        <v>507.0</v>
+        <v>508.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -10700,7 +10700,7 @@
         <v>740</v>
       </c>
       <c r="F324" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10726,7 +10726,7 @@
         <v>739</v>
       </c>
       <c r="F325" t="n">
-        <v>556.0</v>
+        <v>558.0</v>
       </c>
       <c r="G325" t="n">
         <v>8.0</v>
@@ -10804,7 +10804,7 @@
         <v>739</v>
       </c>
       <c r="F328" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G328" t="n">
         <v>0.0</v>
@@ -11194,7 +11194,7 @@
         <v>739</v>
       </c>
       <c r="F343" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G343" t="n">
         <v>6.0</v>
@@ -11636,7 +11636,7 @@
         <v>739</v>
       </c>
       <c r="F360" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G360" t="n">
         <v>0.0</v>
@@ -11714,7 +11714,7 @@
         <v>740</v>
       </c>
       <c r="F363" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12858,7 +12858,7 @@
         <v>741</v>
       </c>
       <c r="F407" t="n">
-        <v>441.0</v>
+        <v>443.0</v>
       </c>
       <c r="G407" t="n">
         <v>0.0</v>
@@ -13846,7 +13846,7 @@
         <v>739</v>
       </c>
       <c r="F445" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G445" t="n">
         <v>0.0</v>
@@ -13924,7 +13924,7 @@
         <v>739</v>
       </c>
       <c r="F448" t="n">
-        <v>591.0</v>
+        <v>593.0</v>
       </c>
       <c r="G448" t="n">
         <v>0.0</v>
@@ -17512,7 +17512,7 @@
         <v>740</v>
       </c>
       <c r="F586" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G586" t="n">
         <v>0.0</v>
@@ -17590,7 +17590,7 @@
         <v>739</v>
       </c>
       <c r="F589" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -18344,7 +18344,7 @@
         <v>739</v>
       </c>
       <c r="F618" t="n">
-        <v>78.0</v>
+        <v>81.0</v>
       </c>
       <c r="G618" t="n">
         <v>0.0</v>
@@ -19176,7 +19176,7 @@
         <v>739</v>
       </c>
       <c r="F650" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G650" t="n">
         <v>19.0</v>
@@ -19670,7 +19670,7 @@
         <v>741</v>
       </c>
       <c r="F669" t="n">
-        <v>197.0</v>
+        <v>200.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -20372,7 +20372,7 @@
         <v>741</v>
       </c>
       <c r="F696" t="n">
-        <v>426.0</v>
+        <v>430.0</v>
       </c>
       <c r="G696" t="n">
         <v>1.0</v>
@@ -20554,7 +20554,7 @@
         <v>741</v>
       </c>
       <c r="F703" t="n">
-        <v>185.0</v>
+        <v>187.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -20918,7 +20918,7 @@
         <v>741</v>
       </c>
       <c r="F717" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="G717" t="n">
         <v>0.0</v>
@@ -21022,7 +21022,7 @@
         <v>741</v>
       </c>
       <c r="F721" t="n">
-        <v>174.0</v>
+        <v>186.0</v>
       </c>
       <c r="G721" t="n">
         <v>19.0</v>
@@ -21256,7 +21256,7 @@
         <v>740</v>
       </c>
       <c r="F730" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G730" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2328,7 +2328,7 @@
         <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>613.0</v>
+        <v>623.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2640,7 +2640,7 @@
         <v>739</v>
       </c>
       <c r="F14" t="n">
-        <v>477.0</v>
+        <v>483.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2692,7 +2692,7 @@
         <v>739</v>
       </c>
       <c r="F16" t="n">
-        <v>411.0</v>
+        <v>416.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2848,7 +2848,7 @@
         <v>740</v>
       </c>
       <c r="F22" t="n">
-        <v>380.0</v>
+        <v>385.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3186,7 +3186,7 @@
         <v>739</v>
       </c>
       <c r="F35" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -3212,7 +3212,7 @@
         <v>739</v>
       </c>
       <c r="F36" t="n">
-        <v>535.0</v>
+        <v>539.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3680,7 +3680,7 @@
         <v>739</v>
       </c>
       <c r="F54" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4018,7 +4018,7 @@
         <v>740</v>
       </c>
       <c r="F67" t="n">
-        <v>201.0</v>
+        <v>205.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4148,7 +4148,7 @@
         <v>739</v>
       </c>
       <c r="F72" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4902,7 +4902,7 @@
         <v>740</v>
       </c>
       <c r="F101" t="n">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -5006,7 +5006,7 @@
         <v>739</v>
       </c>
       <c r="F105" t="n">
-        <v>525.0</v>
+        <v>529.0</v>
       </c>
       <c r="G105" t="n">
         <v>3.0</v>
@@ -5474,7 +5474,7 @@
         <v>739</v>
       </c>
       <c r="F123" t="n">
-        <v>464.0</v>
+        <v>469.0</v>
       </c>
       <c r="G123" t="n">
         <v>12.0</v>
@@ -5526,7 +5526,7 @@
         <v>739</v>
       </c>
       <c r="F125" t="n">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
@@ -5942,7 +5942,7 @@
         <v>739</v>
       </c>
       <c r="F141" t="n">
-        <v>675.0</v>
+        <v>682.0</v>
       </c>
       <c r="G141" t="n">
         <v>2.0</v>
@@ -6228,7 +6228,7 @@
         <v>739</v>
       </c>
       <c r="F152" t="n">
-        <v>220.0</v>
+        <v>222.0</v>
       </c>
       <c r="G152" t="n">
         <v>2.0</v>
@@ -6722,7 +6722,7 @@
         <v>740</v>
       </c>
       <c r="F171" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6774,7 +6774,7 @@
         <v>739</v>
       </c>
       <c r="F173" t="n">
-        <v>324.0</v>
+        <v>327.0</v>
       </c>
       <c r="G173" t="n">
         <v>1.0</v>
@@ -6956,7 +6956,7 @@
         <v>739</v>
       </c>
       <c r="F180" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
       <c r="G180" t="n">
         <v>4.0</v>
@@ -6982,7 +6982,7 @@
         <v>740</v>
       </c>
       <c r="F181" t="n">
-        <v>528.0</v>
+        <v>533.0</v>
       </c>
       <c r="G181" t="n">
         <v>0.0</v>
@@ -7164,7 +7164,7 @@
         <v>739</v>
       </c>
       <c r="F188" t="n">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
       <c r="G188" t="n">
         <v>1.0</v>
@@ -7788,7 +7788,7 @@
         <v>740</v>
       </c>
       <c r="F212" t="n">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -9608,7 +9608,7 @@
         <v>739</v>
       </c>
       <c r="F282" t="n">
-        <v>508.0</v>
+        <v>510.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -10518,7 +10518,7 @@
         <v>739</v>
       </c>
       <c r="F317" t="n">
-        <v>517.0</v>
+        <v>528.0</v>
       </c>
       <c r="G317" t="n">
         <v>0.0</v>
@@ -11168,7 +11168,7 @@
         <v>739</v>
       </c>
       <c r="F342" t="n">
-        <v>417.0</v>
+        <v>419.0</v>
       </c>
       <c r="G342" t="n">
         <v>1.0</v>
@@ -12494,7 +12494,7 @@
         <v>739</v>
       </c>
       <c r="F393" t="n">
-        <v>259.0</v>
+        <v>261.0</v>
       </c>
       <c r="G393" t="n">
         <v>1.0</v>
@@ -12598,7 +12598,7 @@
         <v>739</v>
       </c>
       <c r="F397" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G397" t="n">
         <v>0.0</v>
@@ -13092,7 +13092,7 @@
         <v>739</v>
       </c>
       <c r="F416" t="n">
-        <v>318.0</v>
+        <v>320.0</v>
       </c>
       <c r="G416" t="n">
         <v>28.0</v>
@@ -15406,7 +15406,7 @@
         <v>739</v>
       </c>
       <c r="F505" t="n">
-        <v>628.0</v>
+        <v>636.0</v>
       </c>
       <c r="G505" t="n">
         <v>0.0</v>
@@ -15796,7 +15796,7 @@
         <v>741</v>
       </c>
       <c r="F520" t="n">
-        <v>334.0</v>
+        <v>335.0</v>
       </c>
       <c r="G520" t="n">
         <v>0.0</v>
@@ -16368,7 +16368,7 @@
         <v>740</v>
       </c>
       <c r="F542" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="G542" t="n">
         <v>0.0</v>
@@ -17278,7 +17278,7 @@
         <v>739</v>
       </c>
       <c r="F577" t="n">
-        <v>281.0</v>
+        <v>284.0</v>
       </c>
       <c r="G577" t="n">
         <v>0.0</v>
@@ -17668,7 +17668,7 @@
         <v>739</v>
       </c>
       <c r="F592" t="n">
-        <v>322.0</v>
+        <v>325.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -18760,7 +18760,7 @@
         <v>739</v>
       </c>
       <c r="F634" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>
@@ -19410,7 +19410,7 @@
         <v>740</v>
       </c>
       <c r="F659" t="n">
-        <v>126.0</v>
+        <v>130.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -19878,7 +19878,7 @@
         <v>739</v>
       </c>
       <c r="F677" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="G677" t="n">
         <v>0.0</v>
@@ -19930,7 +19930,7 @@
         <v>740</v>
       </c>
       <c r="F679" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20086,7 +20086,7 @@
         <v>740</v>
       </c>
       <c r="F685" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="G685" t="n">
         <v>0.0</v>
@@ -20242,7 +20242,7 @@
         <v>741</v>
       </c>
       <c r="F691" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G691" t="n">
         <v>12.0</v>
@@ -20346,7 +20346,7 @@
         <v>740</v>
       </c>
       <c r="F695" t="n">
-        <v>130.0</v>
+        <v>133.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20372,7 +20372,7 @@
         <v>741</v>
       </c>
       <c r="F696" t="n">
-        <v>430.0</v>
+        <v>431.0</v>
       </c>
       <c r="G696" t="n">
         <v>1.0</v>
@@ -20424,7 +20424,7 @@
         <v>740</v>
       </c>
       <c r="F698" t="n">
-        <v>159.0</v>
+        <v>167.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20502,7 +20502,7 @@
         <v>740</v>
       </c>
       <c r="F701" t="n">
-        <v>153.0</v>
+        <v>157.0</v>
       </c>
       <c r="G701" t="n">
         <v>0.0</v>
@@ -20684,7 +20684,7 @@
         <v>740</v>
       </c>
       <c r="F708" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -20762,7 +20762,7 @@
         <v>739</v>
       </c>
       <c r="F711" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21022,7 +21022,7 @@
         <v>741</v>
       </c>
       <c r="F721" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G721" t="n">
         <v>19.0</v>
@@ -21074,7 +21074,7 @@
         <v>740</v>
       </c>
       <c r="F723" t="n">
-        <v>53.0</v>
+        <v>56.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -21230,7 +21230,7 @@
         <v>740</v>
       </c>
       <c r="F729" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G729" t="n">
         <v>0.0</v>
@@ -21334,7 +21334,7 @@
         <v>739</v>
       </c>
       <c r="F733" t="n">
-        <v>323.0</v>
+        <v>328.0</v>
       </c>
       <c r="G733" t="n">
         <v>0.0</v>
@@ -21386,7 +21386,7 @@
         <v>740</v>
       </c>
       <c r="F735" t="n">
-        <v>158.0</v>
+        <v>160.0</v>
       </c>
       <c r="G735" t="n">
         <v>0.0</v>
@@ -21490,7 +21490,7 @@
         <v>740</v>
       </c>
       <c r="F739" t="n">
-        <v>418.0</v>
+        <v>422.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -21516,7 +21516,7 @@
         <v>739</v>
       </c>
       <c r="F740" t="n">
-        <v>202.0</v>
+        <v>204.0</v>
       </c>
       <c r="G740" t="n">
         <v>0.0</v>
